--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,57 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>00:45:00</t>
+  </si>
+  <si>
+    <t>19:45:00</t>
+  </si>
+  <si>
+    <t>Emelec</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Mushuc Runa</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Central Cordoba (SdE)</t>
+  </si>
+  <si>
+    <t>2026-07-22 00:03:14</t>
   </si>
 </sst>
 </file>
@@ -585,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +879,974 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2">
+        <v>1.85</v>
+      </c>
+      <c r="G2">
+        <v>1.99</v>
+      </c>
+      <c r="H2">
+        <v>4.6</v>
+      </c>
+      <c r="I2">
+        <v>5.3</v>
+      </c>
+      <c r="J2">
+        <v>3.45</v>
+      </c>
+      <c r="K2">
+        <v>3.85</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>3.05</v>
+      </c>
+      <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.77</v>
+      </c>
+      <c r="Q2">
+        <v>2.14</v>
+      </c>
+      <c r="R2">
+        <v>1.29</v>
+      </c>
+      <c r="S2">
+        <v>3.6</v>
+      </c>
+      <c r="T2">
+        <v>1.11</v>
+      </c>
+      <c r="U2">
+        <v>1.75</v>
+      </c>
+      <c r="V2">
+        <v>1.23</v>
+      </c>
+      <c r="W2">
+        <v>2</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>17</v>
+      </c>
+      <c r="Z2">
+        <v>42</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC2">
+        <v>9.6</v>
+      </c>
+      <c r="AD2">
+        <v>23</v>
+      </c>
+      <c r="AE2">
+        <v>85</v>
+      </c>
+      <c r="AF2">
+        <v>13</v>
+      </c>
+      <c r="AG2">
+        <v>12</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>26</v>
+      </c>
+      <c r="AK2">
+        <v>26</v>
+      </c>
+      <c r="AL2">
+        <v>50</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>20</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>3.45</v>
+      </c>
+      <c r="AQ2">
+        <v>10</v>
+      </c>
+      <c r="AR2">
+        <v>23</v>
+      </c>
+      <c r="AS2">
+        <v>3.45</v>
+      </c>
+      <c r="AT2">
+        <v>2.48</v>
+      </c>
+      <c r="AU2">
+        <v>2.54</v>
+      </c>
+      <c r="AV2">
+        <v>3</v>
+      </c>
+      <c r="AW2">
+        <v>3.3</v>
+      </c>
+      <c r="AX2">
+        <v>2.74</v>
+      </c>
+      <c r="AY2">
+        <v>2.68</v>
+      </c>
+      <c r="AZ2">
+        <v>3.05</v>
+      </c>
+      <c r="BA2">
+        <v>3.35</v>
+      </c>
+      <c r="BB2">
+        <v>17.5</v>
+      </c>
+      <c r="BC2">
+        <v>3.05</v>
+      </c>
+      <c r="BD2">
+        <v>3.25</v>
+      </c>
+      <c r="BE2">
+        <v>3.45</v>
+      </c>
+      <c r="BF2">
+        <v>10.5</v>
+      </c>
+      <c r="BG2">
+        <v>3.45</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.78</v>
+      </c>
+      <c r="BJ2">
+        <v>15.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.78</v>
+      </c>
+      <c r="BN2">
+        <v>6</v>
+      </c>
+      <c r="BO2">
+        <v>3</v>
+      </c>
+      <c r="BP2">
+        <v>20</v>
+      </c>
+      <c r="BQ2">
+        <v>1.63</v>
+      </c>
+      <c r="BR2">
+        <v>48</v>
+      </c>
+      <c r="BS2">
+        <v>1.72</v>
+      </c>
+      <c r="BT2">
+        <v>11.5</v>
+      </c>
+      <c r="BU2">
+        <v>1.54</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.73</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.74</v>
+      </c>
+      <c r="BZ2">
+        <v>46</v>
+      </c>
+      <c r="CA2">
+        <v>1.71</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3">
+        <v>2.4</v>
+      </c>
+      <c r="G3">
+        <v>3.1</v>
+      </c>
+      <c r="H3">
+        <v>2.84</v>
+      </c>
+      <c r="I3">
+        <v>990</v>
+      </c>
+      <c r="J3">
+        <v>1.96</v>
+      </c>
+      <c r="K3">
+        <v>950</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>1.1</v>
+      </c>
+      <c r="O3">
+        <v>1.52</v>
+      </c>
+      <c r="P3">
+        <v>1.45</v>
+      </c>
+      <c r="Q3">
+        <v>2.04</v>
+      </c>
+      <c r="R3">
+        <v>1.17</v>
+      </c>
+      <c r="S3">
+        <v>4.3</v>
+      </c>
+      <c r="T3">
+        <v>1.94</v>
+      </c>
+      <c r="U3">
+        <v>1.61</v>
+      </c>
+      <c r="V3">
+        <v>1.25</v>
+      </c>
+      <c r="W3">
+        <v>1.47</v>
+      </c>
+      <c r="X3">
+        <v>12</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>1.03</v>
+      </c>
+      <c r="AQ3">
+        <v>1.09</v>
+      </c>
+      <c r="AR3">
+        <v>1.09</v>
+      </c>
+      <c r="AS3">
+        <v>1.09</v>
+      </c>
+      <c r="AT3">
+        <v>1.09</v>
+      </c>
+      <c r="AU3">
+        <v>1.09</v>
+      </c>
+      <c r="AV3">
+        <v>1.09</v>
+      </c>
+      <c r="AW3">
+        <v>1.09</v>
+      </c>
+      <c r="AX3">
+        <v>1.09</v>
+      </c>
+      <c r="AY3">
+        <v>1.09</v>
+      </c>
+      <c r="AZ3">
+        <v>1.09</v>
+      </c>
+      <c r="BA3">
+        <v>1.09</v>
+      </c>
+      <c r="BB3">
+        <v>1.09</v>
+      </c>
+      <c r="BC3">
+        <v>1.09</v>
+      </c>
+      <c r="BD3">
+        <v>1.09</v>
+      </c>
+      <c r="BE3">
+        <v>1.09</v>
+      </c>
+      <c r="BF3">
+        <v>1.09</v>
+      </c>
+      <c r="BG3">
+        <v>1.09</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4">
+        <v>1.91</v>
+      </c>
+      <c r="G4">
+        <v>2.04</v>
+      </c>
+      <c r="H4">
+        <v>5.1</v>
+      </c>
+      <c r="I4">
+        <v>6.2</v>
+      </c>
+      <c r="J4">
+        <v>3.15</v>
+      </c>
+      <c r="K4">
+        <v>3.4</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.5</v>
+      </c>
+      <c r="O4">
+        <v>1.57</v>
+      </c>
+      <c r="P4">
+        <v>1.47</v>
+      </c>
+      <c r="Q4">
+        <v>2.72</v>
+      </c>
+      <c r="R4">
+        <v>1.16</v>
+      </c>
+      <c r="S4">
+        <v>5.6</v>
+      </c>
+      <c r="T4">
+        <v>2.24</v>
+      </c>
+      <c r="U4">
+        <v>1.62</v>
+      </c>
+      <c r="V4">
+        <v>1.19</v>
+      </c>
+      <c r="W4">
+        <v>1.96</v>
+      </c>
+      <c r="X4">
+        <v>9.4</v>
+      </c>
+      <c r="Y4">
+        <v>15</v>
+      </c>
+      <c r="Z4">
+        <v>46</v>
+      </c>
+      <c r="AA4">
+        <v>200</v>
+      </c>
+      <c r="AB4">
+        <v>7</v>
+      </c>
+      <c r="AC4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>27</v>
+      </c>
+      <c r="AE4">
+        <v>130</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>34</v>
+      </c>
+      <c r="AI4">
+        <v>160</v>
+      </c>
+      <c r="AJ4">
+        <v>28</v>
+      </c>
+      <c r="AK4">
+        <v>34</v>
+      </c>
+      <c r="AL4">
+        <v>80</v>
+      </c>
+      <c r="AM4">
+        <v>290</v>
+      </c>
+      <c r="AN4">
+        <v>30</v>
+      </c>
+      <c r="AO4">
+        <v>230</v>
+      </c>
+      <c r="AP4">
+        <v>7</v>
+      </c>
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>4.8</v>
+      </c>
+      <c r="AS4">
+        <v>5.2</v>
+      </c>
+      <c r="AT4">
+        <v>5.4</v>
+      </c>
+      <c r="AU4">
+        <v>6.6</v>
+      </c>
+      <c r="AV4">
+        <v>19.5</v>
+      </c>
+      <c r="AW4">
+        <v>5.2</v>
+      </c>
+      <c r="AX4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY4">
+        <v>9.6</v>
+      </c>
+      <c r="AZ4">
+        <v>4.6</v>
+      </c>
+      <c r="BA4">
+        <v>5.2</v>
+      </c>
+      <c r="BB4">
+        <v>20</v>
+      </c>
+      <c r="BC4">
+        <v>4.6</v>
+      </c>
+      <c r="BD4">
+        <v>5</v>
+      </c>
+      <c r="BE4">
+        <v>5.3</v>
+      </c>
+      <c r="BF4">
+        <v>20</v>
+      </c>
+      <c r="BG4">
+        <v>5.3</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.68</v>
+      </c>
+      <c r="BJ4">
+        <v>17.5</v>
+      </c>
+      <c r="BK4">
+        <v>1.54</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.68</v>
+      </c>
+      <c r="BN4">
+        <v>5.8</v>
+      </c>
+      <c r="BO4">
+        <v>3.05</v>
+      </c>
+      <c r="BP4">
+        <v>22</v>
+      </c>
+      <c r="BQ4">
+        <v>1.57</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.64</v>
+      </c>
+      <c r="BT4">
+        <v>11.5</v>
+      </c>
+      <c r="BU4">
+        <v>1.47</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.65</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.68</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.64</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5">
+        <v>1.82</v>
+      </c>
+      <c r="G5">
+        <v>1.88</v>
+      </c>
+      <c r="H5">
+        <v>6.2</v>
+      </c>
+      <c r="I5">
+        <v>7.4</v>
+      </c>
+      <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
+        <v>3.65</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.43</v>
+      </c>
+      <c r="Q5">
+        <v>2.58</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>2026-07-24</t>
   </si>
   <si>
@@ -277,6 +280,12 @@
     <t>00:45:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>19:45:00</t>
   </si>
   <si>
@@ -289,6 +298,12 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Volsungur</t>
+  </si>
+  <si>
+    <t>Njardvik</t>
+  </si>
+  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
@@ -301,10 +316,16 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
+    <t>HK Kopavogur</t>
+  </si>
+  <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 00:03:14</t>
+    <t>2026-07-22 02:10:19</t>
   </si>
 </sst>
 </file>
@@ -636,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -886,64 +907,64 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
         <v>5.3</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
         <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>1.23</v>
@@ -952,175 +973,175 @@
         <v>2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
+        <v>950</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
         <v>23</v>
-      </c>
-      <c r="AE2">
-        <v>85</v>
-      </c>
-      <c r="AF2">
-        <v>13</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
       </c>
       <c r="AI2">
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP2">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2">
+        <v>12.5</v>
+      </c>
+      <c r="AR2">
+        <v>8</v>
+      </c>
+      <c r="AS2">
+        <v>9.4</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>17</v>
+      </c>
+      <c r="AW2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX2">
+        <v>9.6</v>
+      </c>
+      <c r="AY2">
+        <v>9</v>
+      </c>
+      <c r="AZ2">
+        <v>7</v>
+      </c>
+      <c r="BA2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2">
+        <v>7</v>
+      </c>
+      <c r="BC2">
+        <v>7</v>
+      </c>
+      <c r="BD2">
+        <v>8.4</v>
+      </c>
+      <c r="BE2">
+        <v>9.6</v>
+      </c>
+      <c r="BF2">
+        <v>12</v>
+      </c>
+      <c r="BG2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH2">
+        <v>3.15</v>
+      </c>
+      <c r="BI2">
+        <v>2.54</v>
+      </c>
+      <c r="BJ2">
+        <v>11</v>
+      </c>
+      <c r="BK2">
+        <v>6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>12.5</v>
+      </c>
+      <c r="BN2">
+        <v>4.5</v>
+      </c>
+      <c r="BO2">
         <v>3.45</v>
       </c>
-      <c r="AQ2">
+      <c r="BP2">
+        <v>14.5</v>
+      </c>
+      <c r="BQ2">
+        <v>7</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>9.6</v>
+      </c>
+      <c r="BT2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU2">
+        <v>6</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
         <v>10</v>
       </c>
-      <c r="AR2">
-        <v>23</v>
-      </c>
-      <c r="AS2">
-        <v>3.45</v>
-      </c>
-      <c r="AT2">
-        <v>2.48</v>
-      </c>
-      <c r="AU2">
-        <v>2.54</v>
-      </c>
-      <c r="AV2">
-        <v>3</v>
-      </c>
-      <c r="AW2">
-        <v>3.3</v>
-      </c>
-      <c r="AX2">
-        <v>2.74</v>
-      </c>
-      <c r="AY2">
-        <v>2.68</v>
-      </c>
-      <c r="AZ2">
-        <v>3.05</v>
-      </c>
-      <c r="BA2">
-        <v>3.35</v>
-      </c>
-      <c r="BB2">
-        <v>17.5</v>
-      </c>
-      <c r="BC2">
-        <v>3.05</v>
-      </c>
-      <c r="BD2">
-        <v>3.25</v>
-      </c>
-      <c r="BE2">
-        <v>3.45</v>
-      </c>
-      <c r="BF2">
-        <v>10.5</v>
-      </c>
-      <c r="BG2">
-        <v>3.45</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>1.78</v>
-      </c>
-      <c r="BJ2">
-        <v>15.5</v>
-      </c>
-      <c r="BK2">
-        <v>1.6</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>1.78</v>
-      </c>
-      <c r="BN2">
-        <v>6</v>
-      </c>
-      <c r="BO2">
-        <v>3</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>1.63</v>
-      </c>
-      <c r="BR2">
-        <v>48</v>
-      </c>
-      <c r="BS2">
-        <v>1.72</v>
-      </c>
-      <c r="BT2">
-        <v>11.5</v>
-      </c>
-      <c r="BU2">
-        <v>1.54</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>1.73</v>
-      </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.74</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.71</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1128,34 +1149,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>990</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1164,142 +1185,142 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
         <v>1.52</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>1.09</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AT3">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="AX3">
-        <v>1.09</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>1.09</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="BB3">
-        <v>1.09</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>1.09</v>
+        <v>5.7</v>
       </c>
       <c r="BD3">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="BE3">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="BF3">
-        <v>1.09</v>
+        <v>28</v>
       </c>
       <c r="BG3">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1362,7 +1383,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1370,19 +1391,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
         <v>2.04</v>
@@ -1391,7 +1412,7 @@
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1400,16 +1421,16 @@
         <v>3.4</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P4">
         <v>1.47</v>
@@ -1418,19 +1439,19 @@
         <v>2.72</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>1.96</v>
@@ -1439,7 +1460,7 @@
         <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
         <v>46</v>
@@ -1448,13 +1469,13 @@
         <v>200</v>
       </c>
       <c r="AB4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4">
         <v>130</v>
@@ -1478,28 +1499,28 @@
         <v>34</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO4">
         <v>230</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AS4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT4">
         <v>5.4</v>
@@ -1511,7 +1532,7 @@
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1520,333 +1541,817 @@
         <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BA4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC4">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BE4">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.54</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.68</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="BP4">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
-        <v>1.57</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.64</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4">
-        <v>1.47</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.65</v>
+        <v>9.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.68</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.64</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1.04</v>
+      </c>
+      <c r="G5">
+        <v>1000</v>
+      </c>
+      <c r="H5">
+        <v>1.04</v>
+      </c>
+      <c r="I5">
+        <v>1000</v>
+      </c>
+      <c r="J5">
+        <v>1.01</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.24</v>
+      </c>
+      <c r="Q5">
+        <v>1.01</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>1.04</v>
+      </c>
+      <c r="G6">
+        <v>1000</v>
+      </c>
+      <c r="H6">
+        <v>1.04</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>1.01</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
         <v>82</v>
       </c>
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5">
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
         <v>1.82</v>
       </c>
-      <c r="G5">
-        <v>1.88</v>
-      </c>
-      <c r="H5">
-        <v>6.2</v>
-      </c>
-      <c r="I5">
-        <v>7.4</v>
-      </c>
-      <c r="J5">
+      <c r="G7">
+        <v>1.91</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
         <v>3.15</v>
       </c>
-      <c r="K5">
+      <c r="K7">
         <v>3.65</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>1.43</v>
       </c>
-      <c r="Q5">
-        <v>2.58</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>0</v>
-      </c>
-      <c r="BC5">
-        <v>0</v>
-      </c>
-      <c r="BD5">
-        <v>0</v>
-      </c>
-      <c r="BE5">
-        <v>0</v>
-      </c>
-      <c r="BF5">
-        <v>0</v>
-      </c>
-      <c r="BG5">
-        <v>0</v>
-      </c>
-      <c r="BH5">
-        <v>0</v>
-      </c>
-      <c r="BI5">
-        <v>0</v>
-      </c>
-      <c r="BJ5">
-        <v>0</v>
-      </c>
-      <c r="BK5">
-        <v>0</v>
-      </c>
-      <c r="BL5">
-        <v>0</v>
-      </c>
-      <c r="BM5">
-        <v>0</v>
-      </c>
-      <c r="BN5">
-        <v>0</v>
-      </c>
-      <c r="BO5">
-        <v>0</v>
-      </c>
-      <c r="BP5">
-        <v>0</v>
-      </c>
-      <c r="BQ5">
-        <v>0</v>
-      </c>
-      <c r="BR5">
-        <v>0</v>
-      </c>
-      <c r="BS5">
-        <v>0</v>
-      </c>
-      <c r="BT5">
-        <v>0</v>
-      </c>
-      <c r="BU5">
-        <v>0</v>
-      </c>
-      <c r="BV5">
-        <v>0</v>
-      </c>
-      <c r="BW5">
-        <v>0</v>
-      </c>
-      <c r="BX5">
-        <v>0</v>
-      </c>
-      <c r="BY5">
-        <v>0</v>
-      </c>
-      <c r="BZ5">
-        <v>0</v>
-      </c>
-      <c r="CA5">
-        <v>0</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>96</v>
+      <c r="Q7">
+        <v>2.88</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -325,7 +325,7 @@
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 02:10:19</t>
+    <t>2026-07-22 04:17:51</t>
   </si>
 </sst>
 </file>
@@ -919,43 +919,43 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
         <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
         <v>4</v>
@@ -964,7 +964,7 @@
         <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.23</v>
@@ -982,7 +982,7 @@
         <v>38</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -1018,7 +1018,7 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN2">
         <v>17.5</v>
@@ -1048,7 +1048,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1069,7 +1069,7 @@
         <v>7</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE2">
         <v>9.6</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
@@ -1108,13 +1108,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>8.199999999999999</v>
@@ -1126,19 +1126,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1164,37 +1164,37 @@
         <v>2.48</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
         <v>3.55</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="R3">
         <v>1.19</v>
@@ -1212,7 +1212,7 @@
         <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
         <v>9.4</v>
@@ -1227,7 +1227,7 @@
         <v>80</v>
       </c>
       <c r="AB3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
@@ -1278,7 +1278,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1290,7 +1290,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1302,85 +1302,85 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
         <v>34</v>
       </c>
       <c r="BC3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF3">
         <v>28</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>103</v>
@@ -1403,7 +1403,7 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
         <v>2.04</v>
@@ -1412,10 +1412,10 @@
         <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1427,7 +1427,7 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
         <v>1.58</v>
@@ -1451,10 +1451,10 @@
         <v>1.65</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X4">
         <v>9.4</v>
@@ -1574,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1586,22 +1586,22 @@
         <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BP4">
         <v>17</v>
       </c>
       <c r="BQ4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT4">
         <v>9</v>
-      </c>
-      <c r="BT4">
-        <v>8.800000000000001</v>
       </c>
       <c r="BU4">
         <v>4.9</v>
@@ -1610,19 +1610,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>103</v>
@@ -1660,7 +1660,7 @@
         <v>1.01</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>1.01</v>
       </c>
       <c r="K6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>102</v>
       </c>
       <c r="F7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G7">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H7">
         <v>6</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>1.43</v>
       </c>
       <c r="Q7">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -325,7 +325,7 @@
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 04:17:51</t>
+    <t>2026-07-22 06:25:20</t>
   </si>
 </sst>
 </file>
@@ -919,226 +919,226 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>990</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
         <v>2</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1161,226 +1161,226 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="G3">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>2.58</v>
+        <v>1.52</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>1.05</v>
       </c>
       <c r="T3">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.39</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>103</v>
@@ -1403,226 +1403,226 @@
         <v>99</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="G4">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L4">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>1.56</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>1.05</v>
       </c>
       <c r="T4">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>103</v>
@@ -2132,19 +2132,19 @@
         <v>1.81</v>
       </c>
       <c r="G7">
-        <v>1.9</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2159,10 +2159,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Argentinian Primera Division</t>
   </si>
   <si>
+    <t>South Korean K2 League</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>00:45:00</t>
   </si>
   <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
@@ -298,6 +304,12 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Gimhae City</t>
+  </si>
+  <si>
+    <t>Seoul E-Land FC</t>
+  </si>
+  <si>
     <t>Volsungur</t>
   </si>
   <si>
@@ -316,6 +328,12 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Cheongju FC</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
@@ -325,7 +343,7 @@
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 06:25:20</t>
+    <t>2026-07-22 08:32:45</t>
   </si>
 </sst>
 </file>
@@ -657,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -907,64 +925,64 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F2">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I2">
-        <v>990</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S2">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
         <v>1.24</v>
@@ -973,175 +991,175 @@
         <v>2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1149,241 +1167,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F3">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="G3">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>2.58</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>1.9</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
-        <v>1.52</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="U3">
+        <v>1.79</v>
+      </c>
+      <c r="V3">
         <v>1.39</v>
       </c>
-      <c r="V3">
-        <v>1.25</v>
-      </c>
       <c r="W3">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1391,241 +1409,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
-        <v>1.56</v>
+        <v>2.72</v>
       </c>
       <c r="R4">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>1.05</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1633,232 +1651,232 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1867,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1875,232 +1893,232 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
         <v>89</v>
       </c>
       <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6">
+        <v>1.55</v>
+      </c>
+      <c r="G6">
+        <v>1.67</v>
+      </c>
+      <c r="H6">
+        <v>5.7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4.2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.04</v>
+      </c>
+      <c r="N6">
+        <v>4.5</v>
+      </c>
+      <c r="O6">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>2.22</v>
+      </c>
+      <c r="Q6">
+        <v>1.66</v>
+      </c>
+      <c r="R6">
+        <v>1.45</v>
+      </c>
+      <c r="S6">
+        <v>2.6</v>
+      </c>
+      <c r="T6">
+        <v>1.76</v>
+      </c>
+      <c r="U6">
+        <v>2.08</v>
+      </c>
+      <c r="V6">
+        <v>1.17</v>
+      </c>
+      <c r="W6">
+        <v>2.48</v>
+      </c>
+      <c r="X6">
+        <v>24</v>
+      </c>
+      <c r="Y6">
+        <v>32</v>
+      </c>
+      <c r="Z6">
+        <v>70</v>
+      </c>
+      <c r="AA6">
+        <v>190</v>
+      </c>
+      <c r="AB6">
+        <v>10.5</v>
+      </c>
+      <c r="AC6">
+        <v>11</v>
+      </c>
+      <c r="AD6">
+        <v>25</v>
+      </c>
+      <c r="AE6">
         <v>95</v>
       </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6">
+      <c r="AF6">
+        <v>11</v>
+      </c>
+      <c r="AG6">
+        <v>10.5</v>
+      </c>
+      <c r="AH6">
+        <v>21</v>
+      </c>
+      <c r="AI6">
+        <v>85</v>
+      </c>
+      <c r="AJ6">
+        <v>16</v>
+      </c>
+      <c r="AK6">
+        <v>16.5</v>
+      </c>
+      <c r="AL6">
+        <v>42</v>
+      </c>
+      <c r="AM6">
+        <v>120</v>
+      </c>
+      <c r="AN6">
+        <v>7.8</v>
+      </c>
+      <c r="AO6">
+        <v>95</v>
+      </c>
+      <c r="AP6">
+        <v>15.5</v>
+      </c>
+      <c r="AQ6">
+        <v>20</v>
+      </c>
+      <c r="AR6">
+        <v>34</v>
+      </c>
+      <c r="AS6">
+        <v>8.6</v>
+      </c>
+      <c r="AT6">
+        <v>8.6</v>
+      </c>
+      <c r="AU6">
+        <v>9</v>
+      </c>
+      <c r="AV6">
+        <v>15.5</v>
+      </c>
+      <c r="AW6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX6">
+        <v>9</v>
+      </c>
+      <c r="AY6">
+        <v>8.6</v>
+      </c>
+      <c r="AZ6">
+        <v>17</v>
+      </c>
+      <c r="BA6">
+        <v>8</v>
+      </c>
+      <c r="BB6">
+        <v>13</v>
+      </c>
+      <c r="BC6">
+        <v>13.5</v>
+      </c>
+      <c r="BD6">
+        <v>20</v>
+      </c>
+      <c r="BE6">
+        <v>8.4</v>
+      </c>
+      <c r="BF6">
+        <v>6.4</v>
+      </c>
+      <c r="BG6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
         <v>1.04</v>
       </c>
-      <c r="G6">
-        <v>1000</v>
-      </c>
-      <c r="H6">
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
         <v>1.04</v>
       </c>
-      <c r="I6">
-        <v>1000</v>
-      </c>
-      <c r="J6">
-        <v>1.01</v>
-      </c>
-      <c r="K6">
-        <v>950</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>1.24</v>
-      </c>
-      <c r="Q6">
-        <v>1.01</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6">
-        <v>0</v>
-      </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>0</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>0</v>
-      </c>
-      <c r="BC6">
-        <v>0</v>
-      </c>
-      <c r="BD6">
-        <v>0</v>
-      </c>
-      <c r="BE6">
-        <v>0</v>
-      </c>
-      <c r="BF6">
-        <v>0</v>
-      </c>
-      <c r="BG6">
-        <v>0</v>
-      </c>
-      <c r="BH6">
-        <v>0</v>
-      </c>
-      <c r="BI6">
-        <v>0</v>
-      </c>
-      <c r="BJ6">
-        <v>0</v>
-      </c>
-      <c r="BK6">
-        <v>0</v>
-      </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2109,42 +2127,42 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F7">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H7">
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J7">
         <v>1.02</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2159,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
         <v>1.01</v>
@@ -2351,7 +2369,491 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8">
+        <v>1.04</v>
+      </c>
+      <c r="G8">
+        <v>600</v>
+      </c>
+      <c r="H8">
+        <v>1.04</v>
+      </c>
+      <c r="I8">
+        <v>870</v>
+      </c>
+      <c r="J8">
+        <v>1.02</v>
+      </c>
+      <c r="K8">
+        <v>950</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9">
+        <v>1.81</v>
+      </c>
+      <c r="G9">
+        <v>1.89</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>3.15</v>
+      </c>
+      <c r="K9">
+        <v>3.6</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1.43</v>
+      </c>
+      <c r="Q9">
+        <v>2.88</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <v>0</v>
+      </c>
+      <c r="BC9">
+        <v>0</v>
+      </c>
+      <c r="BD9">
+        <v>0</v>
+      </c>
+      <c r="BE9">
+        <v>0</v>
+      </c>
+      <c r="BF9">
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0</v>
+      </c>
+      <c r="BH9">
+        <v>0</v>
+      </c>
+      <c r="BI9">
+        <v>0</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BL9">
+        <v>0</v>
+      </c>
+      <c r="BM9">
+        <v>0</v>
+      </c>
+      <c r="BN9">
+        <v>0</v>
+      </c>
+      <c r="BO9">
+        <v>0</v>
+      </c>
+      <c r="BP9">
+        <v>0</v>
+      </c>
+      <c r="BQ9">
+        <v>0</v>
+      </c>
+      <c r="BR9">
+        <v>0</v>
+      </c>
+      <c r="BS9">
+        <v>0</v>
+      </c>
+      <c r="BT9">
+        <v>0</v>
+      </c>
+      <c r="BU9">
+        <v>0</v>
+      </c>
+      <c r="BV9">
+        <v>0</v>
+      </c>
+      <c r="BW9">
+        <v>0</v>
+      </c>
+      <c r="BX9">
+        <v>0</v>
+      </c>
+      <c r="BY9">
+        <v>0</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -343,7 +343,7 @@
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 08:32:45</t>
+    <t>2026-07-22 10:40:06</t>
   </si>
 </sst>
 </file>
@@ -937,10 +937,10 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G2">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H2">
         <v>4.7</v>
@@ -952,7 +952,7 @@
         <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -961,13 +961,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
         <v>2.14</v>
@@ -982,13 +982,13 @@
         <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.24</v>
       </c>
       <c r="W2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1000,7 +1000,7 @@
         <v>44</v>
       </c>
       <c r="AA2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>9</v>
@@ -1030,7 +1030,7 @@
         <v>27</v>
       </c>
       <c r="AK2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1039,22 +1039,22 @@
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP2">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
         <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1066,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1075,28 +1075,28 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="BD2">
         <v>30</v>
       </c>
       <c r="BE2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
@@ -1179,7 +1179,7 @@
         <v>102</v>
       </c>
       <c r="F3">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G3">
         <v>2.74</v>
@@ -1188,40 +1188,40 @@
         <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J3">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.12</v>
       </c>
       <c r="N3">
+        <v>2.58</v>
+      </c>
+      <c r="O3">
+        <v>1.56</v>
+      </c>
+      <c r="P3">
+        <v>1.5</v>
+      </c>
+      <c r="Q3">
         <v>2.64</v>
       </c>
-      <c r="O3">
-        <v>1.53</v>
-      </c>
-      <c r="P3">
-        <v>1.57</v>
-      </c>
-      <c r="Q3">
-        <v>2.6</v>
-      </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
         <v>1.79</v>
@@ -1230,10 +1230,10 @@
         <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Y3">
         <v>12</v>
@@ -1245,19 +1245,19 @@
         <v>75</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1272,7 +1272,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL3">
         <v>75</v>
@@ -1287,7 +1287,7 @@
         <v>75</v>
       </c>
       <c r="AP3">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
         <v>8.199999999999999</v>
@@ -1296,7 +1296,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1308,7 +1308,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1320,43 +1320,43 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH3">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BI3">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
@@ -1365,37 +1365,37 @@
         <v>4</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
         <v>7.6</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
         <v>34</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3">
         <v>9.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA3">
         <v>9</v>
@@ -1421,7 +1421,7 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G4">
         <v>2.06</v>
@@ -1436,7 +1436,7 @@
         <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1451,7 +1451,7 @@
         <v>1.58</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
         <v>2.72</v>
@@ -1493,7 +1493,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4">
         <v>130</v>
@@ -1535,10 +1535,10 @@
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT4">
         <v>5.5</v>
@@ -1550,7 +1550,7 @@
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1559,28 +1559,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
         <v>21</v>
       </c>
       <c r="BC4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH4">
         <v>2.72</v>
@@ -1675,7 +1675,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K5">
         <v>3.65</v>
@@ -1693,13 +1693,13 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
         <v>3.75</v>
@@ -1914,7 +1914,7 @@
         <v>5.7</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
         <v>4.2</v>
@@ -1941,10 +1941,10 @@
         <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="T6">
         <v>1.76</v>
@@ -1968,7 +1968,7 @@
         <v>70</v>
       </c>
       <c r="AA6">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB6">
         <v>10.5</v>
@@ -1980,7 +1980,7 @@
         <v>25</v>
       </c>
       <c r="AE6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF6">
         <v>11</v>
@@ -2004,7 +2004,7 @@
         <v>42</v>
       </c>
       <c r="AM6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6">
         <v>7.8</v>
@@ -2022,7 +2022,7 @@
         <v>34</v>
       </c>
       <c r="AS6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6">
         <v>8.6</v>
@@ -2034,10 +2034,10 @@
         <v>15.5</v>
       </c>
       <c r="AW6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6">
         <v>8.6</v>
@@ -2046,7 +2046,7 @@
         <v>17</v>
       </c>
       <c r="BA6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB6">
         <v>13</v>
@@ -2058,13 +2058,13 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF6">
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2147,22 +2147,22 @@
         <v>106</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>600</v>
+        <v>3.9</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="I7">
-        <v>870</v>
+        <v>2.16</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2389,22 +2389,22 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G8">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="I8">
-        <v>870</v>
+        <v>4.1</v>
       </c>
       <c r="J8">
-        <v>1.02</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2419,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2634,7 +2634,7 @@
         <v>1.81</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -2643,10 +2643,10 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>South Korean K2 League</t>
   </si>
   <si>
+    <t>Romanian Liga I</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -286,9 +289,15 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -310,9 +319,15 @@
     <t>Seoul E-Land FC</t>
   </si>
   <si>
+    <t>UTA Arad</t>
+  </si>
+  <si>
     <t>Volsungur</t>
   </si>
   <si>
+    <t>Arges Pitesti</t>
+  </si>
+  <si>
     <t>Njardvik</t>
   </si>
   <si>
@@ -334,16 +349,22 @@
     <t>Cheonan City</t>
   </si>
   <si>
+    <t>Otelul Galati</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
+    <t>ACS Petrolul 52</t>
+  </si>
+  <si>
     <t>HK Kopavogur</t>
   </si>
   <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 10:40:06</t>
+    <t>2026-07-22 12:47:32</t>
   </si>
 </sst>
 </file>
@@ -675,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -925,22 +946,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F2">
         <v>1.86</v>
       </c>
       <c r="G2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H2">
         <v>4.7</v>
@@ -967,7 +988,7 @@
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
         <v>2.14</v>
@@ -988,7 +1009,7 @@
         <v>1.24</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1087,7 +1108,7 @@
         <v>3.8</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>4.3</v>
@@ -1159,7 +1180,7 @@
         <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1167,19 +1188,19 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
         <v>2.74</v>
@@ -1188,28 +1209,28 @@
         <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
         <v>1.48</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
         <v>1.56</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
         <v>2.64</v>
@@ -1227,7 +1248,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W3">
         <v>1.57</v>
@@ -1251,7 +1272,7 @@
         <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>60</v>
@@ -1287,7 +1308,7 @@
         <v>75</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
         <v>8.199999999999999</v>
@@ -1335,28 +1356,28 @@
         <v>7.2</v>
       </c>
       <c r="BF3">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BG3">
         <v>6.8</v>
       </c>
       <c r="BH3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
         <v>5.5</v>
@@ -1374,7 +1395,7 @@
         <v>48</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1398,10 +1419,10 @@
         <v>55</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1409,28 +1430,28 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F4">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1445,7 +1466,7 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
         <v>1.58</v>
@@ -1472,7 +1493,7 @@
         <v>1.21</v>
       </c>
       <c r="W4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="X4">
         <v>9.4</v>
@@ -1505,7 +1526,7 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>160</v>
@@ -1517,7 +1538,7 @@
         <v>34</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>290</v>
@@ -1535,7 +1556,7 @@
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS4">
         <v>6.6</v>
@@ -1550,7 +1571,7 @@
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1574,7 +1595,7 @@
         <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1643,7 +1664,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1651,16 +1672,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F5">
         <v>3.2</v>
@@ -1693,7 +1714,7 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1885,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1893,16 +1914,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F6">
         <v>1.55</v>
@@ -1932,7 +1953,7 @@
         <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P6">
         <v>2.22</v>
@@ -1941,13 +1962,13 @@
         <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U6">
         <v>2.08</v>
@@ -1980,7 +2001,7 @@
         <v>25</v>
       </c>
       <c r="AE6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF6">
         <v>11</v>
@@ -2010,7 +2031,7 @@
         <v>7.8</v>
       </c>
       <c r="AO6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP6">
         <v>15.5</v>
@@ -2058,13 +2079,13 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF6">
         <v>6.4</v>
       </c>
       <c r="BG6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2127,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2135,273 +2156,273 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7">
+        <v>2.12</v>
+      </c>
+      <c r="G7">
+        <v>2.32</v>
+      </c>
+      <c r="H7">
+        <v>3.6</v>
+      </c>
+      <c r="I7">
+        <v>4.1</v>
+      </c>
+      <c r="J7">
+        <v>3.35</v>
+      </c>
+      <c r="K7">
+        <v>3.7</v>
+      </c>
+      <c r="L7">
+        <v>1.38</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
+        <v>3.35</v>
+      </c>
+      <c r="O7">
+        <v>1.35</v>
+      </c>
+      <c r="P7">
+        <v>1.81</v>
+      </c>
+      <c r="Q7">
+        <v>2.04</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
+        <v>3.65</v>
+      </c>
+      <c r="T7">
+        <v>1.81</v>
+      </c>
+      <c r="U7">
+        <v>2.04</v>
+      </c>
+      <c r="V7">
+        <v>1.33</v>
+      </c>
+      <c r="W7">
+        <v>1.76</v>
+      </c>
+      <c r="X7">
+        <v>15</v>
+      </c>
+      <c r="Y7">
+        <v>15.5</v>
+      </c>
+      <c r="Z7">
+        <v>32</v>
+      </c>
+      <c r="AA7">
         <v>85</v>
       </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7">
-        <v>3.9</v>
-      </c>
-      <c r="H7">
-        <v>1.91</v>
-      </c>
-      <c r="I7">
-        <v>2.16</v>
-      </c>
-      <c r="J7">
-        <v>4.1</v>
-      </c>
-      <c r="K7">
+      <c r="AB7">
+        <v>10.5</v>
+      </c>
+      <c r="AC7">
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <v>16.5</v>
+      </c>
+      <c r="AE7">
+        <v>60</v>
+      </c>
+      <c r="AF7">
+        <v>16</v>
+      </c>
+      <c r="AG7">
+        <v>13</v>
+      </c>
+      <c r="AH7">
+        <v>22</v>
+      </c>
+      <c r="AI7">
+        <v>70</v>
+      </c>
+      <c r="AJ7">
+        <v>34</v>
+      </c>
+      <c r="AK7">
+        <v>29</v>
+      </c>
+      <c r="AL7">
+        <v>48</v>
+      </c>
+      <c r="AM7">
+        <v>130</v>
+      </c>
+      <c r="AN7">
+        <v>21</v>
+      </c>
+      <c r="AO7">
+        <v>65</v>
+      </c>
+      <c r="AP7">
+        <v>10</v>
+      </c>
+      <c r="AQ7">
+        <v>10</v>
+      </c>
+      <c r="AR7">
+        <v>20</v>
+      </c>
+      <c r="AS7">
+        <v>5</v>
+      </c>
+      <c r="AT7">
+        <v>7</v>
+      </c>
+      <c r="AU7">
+        <v>6.2</v>
+      </c>
+      <c r="AV7">
+        <v>12</v>
+      </c>
+      <c r="AW7">
+        <v>38</v>
+      </c>
+      <c r="AX7">
+        <v>10.5</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>15.5</v>
+      </c>
+      <c r="BA7">
         <v>4.9</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>2.6</v>
-      </c>
-      <c r="Q7">
-        <v>1.33</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
       <c r="BB7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB7" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F8">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="H8">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="I8">
-        <v>4.1</v>
+        <v>2.16</v>
       </c>
       <c r="J8">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>4.9</v>
@@ -2419,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2611,249 +2632,733 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9">
+        <v>2.36</v>
+      </c>
+      <c r="G9">
+        <v>2.48</v>
+      </c>
+      <c r="H9">
+        <v>3.6</v>
+      </c>
+      <c r="I9">
+        <v>4.1</v>
+      </c>
+      <c r="J9">
+        <v>3.05</v>
+      </c>
+      <c r="K9">
+        <v>3.3</v>
+      </c>
+      <c r="L9">
+        <v>1.47</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.58</v>
+      </c>
+      <c r="O9">
+        <v>1.5</v>
+      </c>
+      <c r="P9">
+        <v>1.53</v>
+      </c>
+      <c r="Q9">
+        <v>2.5</v>
+      </c>
+      <c r="R9">
+        <v>1.2</v>
+      </c>
+      <c r="S9">
+        <v>5.1</v>
+      </c>
+      <c r="T9">
+        <v>2.06</v>
+      </c>
+      <c r="U9">
+        <v>1.76</v>
+      </c>
+      <c r="V9">
+        <v>1.33</v>
+      </c>
+      <c r="W9">
+        <v>1.67</v>
+      </c>
+      <c r="X9">
+        <v>11</v>
+      </c>
+      <c r="Y9">
+        <v>11</v>
+      </c>
+      <c r="Z9">
+        <v>36</v>
+      </c>
+      <c r="AA9">
+        <v>110</v>
+      </c>
+      <c r="AB9">
+        <v>7.8</v>
+      </c>
+      <c r="AC9">
+        <v>7.6</v>
+      </c>
+      <c r="AD9">
+        <v>17.5</v>
+      </c>
+      <c r="AE9">
+        <v>90</v>
+      </c>
+      <c r="AF9">
+        <v>14</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>32</v>
+      </c>
+      <c r="AI9">
+        <v>100</v>
+      </c>
+      <c r="AJ9">
+        <v>46</v>
+      </c>
+      <c r="AK9">
+        <v>46</v>
+      </c>
+      <c r="AL9">
+        <v>85</v>
+      </c>
+      <c r="AM9">
+        <v>220</v>
+      </c>
+      <c r="AN9">
+        <v>46</v>
+      </c>
+      <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>7.6</v>
+      </c>
+      <c r="AQ9">
+        <v>9</v>
+      </c>
+      <c r="AR9">
+        <v>19</v>
+      </c>
+      <c r="AS9">
+        <v>7.4</v>
+      </c>
+      <c r="AT9">
+        <v>6.4</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>14</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>11</v>
+      </c>
+      <c r="AY9">
+        <v>10</v>
+      </c>
+      <c r="AZ9">
+        <v>19.5</v>
+      </c>
+      <c r="BA9">
+        <v>7.4</v>
+      </c>
+      <c r="BB9">
+        <v>24</v>
+      </c>
+      <c r="BC9">
+        <v>6.4</v>
+      </c>
+      <c r="BD9">
+        <v>42</v>
+      </c>
+      <c r="BE9">
+        <v>7.6</v>
+      </c>
+      <c r="BF9">
+        <v>6.4</v>
+      </c>
+      <c r="BG9">
+        <v>7.4</v>
+      </c>
+      <c r="BH9">
+        <v>2.82</v>
+      </c>
+      <c r="BI9">
+        <v>2.24</v>
+      </c>
+      <c r="BJ9">
+        <v>12</v>
+      </c>
+      <c r="BK9">
+        <v>5.7</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>10.5</v>
+      </c>
+      <c r="BN9">
+        <v>5</v>
+      </c>
+      <c r="BO9">
+        <v>3.75</v>
+      </c>
+      <c r="BP9">
+        <v>20</v>
+      </c>
+      <c r="BQ9">
+        <v>7</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT9">
+        <v>7.4</v>
+      </c>
+      <c r="BU9">
+        <v>5.3</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>9.4</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>9</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10">
+        <v>1.81</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>2.36</v>
+      </c>
+      <c r="I10">
+        <v>4.1</v>
+      </c>
+      <c r="J10">
+        <v>3.95</v>
+      </c>
+      <c r="K10">
+        <v>4.9</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.28</v>
+      </c>
+      <c r="Q10">
+        <v>1.38</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
         <v>82</v>
       </c>
-      <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9">
-        <v>1.81</v>
-      </c>
-      <c r="G9">
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11">
+        <v>1.85</v>
+      </c>
+      <c r="G11">
         <v>1.92</v>
       </c>
-      <c r="H9">
+      <c r="H11">
         <v>6</v>
       </c>
-      <c r="I9">
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <v>3.1</v>
-      </c>
-      <c r="K9">
+      <c r="I11">
+        <v>6.8</v>
+      </c>
+      <c r="J11">
+        <v>3.05</v>
+      </c>
+      <c r="K11">
         <v>3.45</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>1.43</v>
-      </c>
-      <c r="Q9">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.42</v>
+      </c>
+      <c r="Q11">
         <v>2.88</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>0</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>0</v>
-      </c>
-      <c r="BC9">
-        <v>0</v>
-      </c>
-      <c r="BD9">
-        <v>0</v>
-      </c>
-      <c r="BE9">
-        <v>0</v>
-      </c>
-      <c r="BF9">
-        <v>0</v>
-      </c>
-      <c r="BG9">
-        <v>0</v>
-      </c>
-      <c r="BH9">
-        <v>0</v>
-      </c>
-      <c r="BI9">
-        <v>0</v>
-      </c>
-      <c r="BJ9">
-        <v>0</v>
-      </c>
-      <c r="BK9">
-        <v>0</v>
-      </c>
-      <c r="BL9">
-        <v>0</v>
-      </c>
-      <c r="BM9">
-        <v>0</v>
-      </c>
-      <c r="BN9">
-        <v>0</v>
-      </c>
-      <c r="BO9">
-        <v>0</v>
-      </c>
-      <c r="BP9">
-        <v>0</v>
-      </c>
-      <c r="BQ9">
-        <v>0</v>
-      </c>
-      <c r="BR9">
-        <v>0</v>
-      </c>
-      <c r="BS9">
-        <v>0</v>
-      </c>
-      <c r="BT9">
-        <v>0</v>
-      </c>
-      <c r="BU9">
-        <v>0</v>
-      </c>
-      <c r="BV9">
-        <v>0</v>
-      </c>
-      <c r="BW9">
-        <v>0</v>
-      </c>
-      <c r="BX9">
-        <v>0</v>
-      </c>
-      <c r="BY9">
-        <v>0</v>
-      </c>
-      <c r="BZ9">
-        <v>0</v>
-      </c>
-      <c r="CA9">
-        <v>0</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>109</v>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="164">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,30 @@
     <t>Romanian Liga I</t>
   </si>
   <si>
+    <t>Lithuanian A Lyga</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Danish 1st Division</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Swedish Allsvenskan</t>
+  </si>
+  <si>
+    <t>Swiss Challenge League</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -292,12 +316,27 @@
     <t>15:30:00</t>
   </si>
   <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
     <t>18:00:00</t>
   </si>
   <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
     <t>18:30:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -322,12 +361,63 @@
     <t>UTA Arad</t>
   </si>
   <si>
+    <t>Fk Siauliai</t>
+  </si>
+  <si>
+    <t>Jaro</t>
+  </si>
+  <si>
+    <t>Vejle</t>
+  </si>
+  <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Usti Nad Labem</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
+    <t>Vysocina Jihlava</t>
+  </si>
+  <si>
+    <t>H Slavia Kromeriz</t>
+  </si>
+  <si>
+    <t>AaB</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Vasteras SK</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>Neuchatel Xamax</t>
+  </si>
+  <si>
+    <t>Rapperswil-Jona</t>
+  </si>
+  <si>
     <t>Volsungur</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Etoile Carouge</t>
+  </si>
+  <si>
     <t>Arges Pitesti</t>
   </si>
   <si>
+    <t>Odra Opole</t>
+  </si>
+  <si>
     <t>Njardvik</t>
   </si>
   <si>
@@ -352,19 +442,70 @@
     <t>Otelul Galati</t>
   </si>
   <si>
+    <t>Hegelmann Litauen</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>Warta Poznan</t>
+  </si>
+  <si>
+    <t>SK Kladno</t>
+  </si>
+  <si>
+    <t>Arsenal Ceska Lipa</t>
+  </si>
+  <si>
+    <t>Zizkov</t>
+  </si>
+  <si>
+    <t>MAS Taborsko</t>
+  </si>
+  <si>
+    <t>Hillerod Fodbold</t>
+  </si>
+  <si>
+    <t>OB</t>
+  </si>
+  <si>
+    <t>Orgryte</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>Kriens</t>
+  </si>
+  <si>
+    <t>FC Wil</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
     <t>ACS Petrolul 52</t>
   </si>
   <si>
+    <t>Arka Gdynia</t>
+  </si>
+  <si>
     <t>HK Kopavogur</t>
   </si>
   <si>
     <t>Central Cordoba (SdE)</t>
   </si>
   <si>
-    <t>2026-07-22 12:47:32</t>
+    <t>2026-07-22 14:55:41</t>
   </si>
 </sst>
 </file>
@@ -696,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -946,28 +1087,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="F2">
         <v>1.86</v>
       </c>
       <c r="G2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="H2">
         <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
         <v>3.5</v>
@@ -985,7 +1126,7 @@
         <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
         <v>1.77</v>
@@ -1009,7 +1150,7 @@
         <v>1.24</v>
       </c>
       <c r="W2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1180,7 +1321,7 @@
         <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1188,16 +1329,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="F3">
         <v>2.56</v>
@@ -1215,7 +1356,7 @@
         <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.48</v>
@@ -1233,10 +1374,10 @@
         <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>5.5</v>
@@ -1248,7 +1389,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.57</v>
@@ -1329,7 +1470,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1341,19 +1482,19 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB3">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="BC3">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BD3">
         <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF3">
         <v>6.6</v>
@@ -1422,7 +1563,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1430,19 +1571,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="F4">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G4">
         <v>2.04</v>
@@ -1451,10 +1592,10 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1469,139 +1610,139 @@
         <v>2.5</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T4">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U4">
         <v>1.66</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
         <v>1.96</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AO4">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BB4">
         <v>21</v>
       </c>
       <c r="BC4">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>6.6</v>
+        <v>44</v>
       </c>
       <c r="BH4">
         <v>2.72</v>
@@ -1664,7 +1805,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1672,16 +1813,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="F5">
         <v>3.2</v>
@@ -1714,10 +1855,10 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1906,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1914,16 +2055,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="F6">
         <v>1.55</v>
@@ -1968,7 +2109,7 @@
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6">
         <v>2.08</v>
@@ -2148,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2156,16 +2297,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="F7">
         <v>2.12</v>
@@ -2180,7 +2321,7 @@
         <v>4.1</v>
       </c>
       <c r="J7">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
         <v>3.7</v>
@@ -2210,7 +2351,7 @@
         <v>3.65</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U7">
         <v>2.04</v>
@@ -2225,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7">
         <v>32</v>
@@ -2285,7 +2426,7 @@
         <v>20</v>
       </c>
       <c r="AS7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -2309,7 +2450,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB7">
         <v>21</v>
@@ -2321,19 +2462,19 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF7">
         <v>15</v>
       </c>
       <c r="BG7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
       </c>
       <c r="BI7">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
@@ -2345,7 +2486,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
         <v>5.1</v>
@@ -2354,7 +2495,7 @@
         <v>3.95</v>
       </c>
       <c r="BP7">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ7">
         <v>6.4</v>
@@ -2381,16 +2522,16 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7">
         <v>32</v>
       </c>
       <c r="CA7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2398,232 +2539,232 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="G8">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="H8">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="I8">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="J8">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
+        <v>1.98</v>
+      </c>
+      <c r="Q8">
+        <v>1.82</v>
+      </c>
+      <c r="R8">
+        <v>1.39</v>
+      </c>
+      <c r="S8">
+        <v>2.88</v>
+      </c>
+      <c r="T8">
+        <v>1.47</v>
+      </c>
+      <c r="U8">
+        <v>1.83</v>
+      </c>
+      <c r="V8">
+        <v>1.39</v>
+      </c>
+      <c r="W8">
+        <v>1.49</v>
+      </c>
+      <c r="X8">
+        <v>23</v>
+      </c>
+      <c r="Y8">
+        <v>18</v>
+      </c>
+      <c r="Z8">
+        <v>29</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>17.5</v>
+      </c>
+      <c r="AC8">
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <v>18.5</v>
+      </c>
+      <c r="AE8">
+        <v>46</v>
+      </c>
+      <c r="AF8">
+        <v>28</v>
+      </c>
+      <c r="AG8">
+        <v>18</v>
+      </c>
+      <c r="AH8">
+        <v>24</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>44</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>9.6</v>
+      </c>
+      <c r="AQ8">
+        <v>7.8</v>
+      </c>
+      <c r="AR8">
+        <v>12</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>7.4</v>
+      </c>
+      <c r="AU8">
+        <v>5.3</v>
+      </c>
+      <c r="AV8">
+        <v>8</v>
+      </c>
+      <c r="AW8">
+        <v>18.5</v>
+      </c>
+      <c r="AX8">
+        <v>11.5</v>
+      </c>
+      <c r="AY8">
+        <v>7.6</v>
+      </c>
+      <c r="AZ8">
+        <v>10</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>16.5</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>4.4</v>
+      </c>
+      <c r="BI8">
         <v>2.66</v>
       </c>
-      <c r="Q8">
-        <v>1.33</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0</v>
-      </c>
-      <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AH8">
-        <v>0</v>
-      </c>
-      <c r="AI8">
-        <v>0</v>
-      </c>
-      <c r="AJ8">
-        <v>0</v>
-      </c>
-      <c r="AK8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8">
-        <v>0</v>
-      </c>
-      <c r="BE8">
-        <v>0</v>
-      </c>
-      <c r="BF8">
-        <v>0</v>
-      </c>
-      <c r="BG8">
-        <v>0</v>
-      </c>
-      <c r="BH8">
-        <v>0</v>
-      </c>
-      <c r="BI8">
-        <v>0</v>
-      </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2632,733 +2773,4847 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="F9">
+        <v>3.1</v>
+      </c>
+      <c r="G9">
+        <v>3.4</v>
+      </c>
+      <c r="H9">
+        <v>2.2</v>
+      </c>
+      <c r="I9">
+        <v>2.34</v>
+      </c>
+      <c r="J9">
+        <v>3.85</v>
+      </c>
+      <c r="K9">
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <v>1.27</v>
+      </c>
+      <c r="M9">
+        <v>1.05</v>
+      </c>
+      <c r="N9">
+        <v>4.8</v>
+      </c>
+      <c r="O9">
+        <v>1.23</v>
+      </c>
+      <c r="P9">
+        <v>2.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.67</v>
+      </c>
+      <c r="R9">
+        <v>1.5</v>
+      </c>
+      <c r="S9">
+        <v>2.66</v>
+      </c>
+      <c r="T9">
+        <v>1.6</v>
+      </c>
+      <c r="U9">
         <v>2.36</v>
       </c>
-      <c r="G9">
-        <v>2.48</v>
-      </c>
-      <c r="H9">
-        <v>3.6</v>
-      </c>
-      <c r="I9">
+      <c r="V9">
+        <v>1.74</v>
+      </c>
+      <c r="W9">
+        <v>1.41</v>
+      </c>
+      <c r="X9">
+        <v>25</v>
+      </c>
+      <c r="Y9">
+        <v>15.5</v>
+      </c>
+      <c r="Z9">
+        <v>20</v>
+      </c>
+      <c r="AA9">
+        <v>36</v>
+      </c>
+      <c r="AB9">
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <v>11</v>
+      </c>
+      <c r="AD9">
+        <v>14</v>
+      </c>
+      <c r="AE9">
+        <v>27</v>
+      </c>
+      <c r="AF9">
+        <v>32</v>
+      </c>
+      <c r="AG9">
+        <v>17.5</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
+        <v>38</v>
+      </c>
+      <c r="AJ9">
+        <v>65</v>
+      </c>
+      <c r="AK9">
+        <v>36</v>
+      </c>
+      <c r="AL9">
+        <v>48</v>
+      </c>
+      <c r="AM9">
+        <v>80</v>
+      </c>
+      <c r="AN9">
+        <v>30</v>
+      </c>
+      <c r="AO9">
+        <v>16</v>
+      </c>
+      <c r="AP9">
+        <v>18</v>
+      </c>
+      <c r="AQ9">
+        <v>11</v>
+      </c>
+      <c r="AR9">
+        <v>14</v>
+      </c>
+      <c r="AS9">
+        <v>3.95</v>
+      </c>
+      <c r="AT9">
+        <v>13.5</v>
+      </c>
+      <c r="AU9">
+        <v>7.8</v>
+      </c>
+      <c r="AV9">
+        <v>9.6</v>
+      </c>
+      <c r="AW9">
+        <v>18.5</v>
+      </c>
+      <c r="AX9">
+        <v>21</v>
+      </c>
+      <c r="AY9">
+        <v>12</v>
+      </c>
+      <c r="AZ9">
+        <v>13</v>
+      </c>
+      <c r="BA9">
+        <v>3.95</v>
+      </c>
+      <c r="BB9">
         <v>4.1</v>
       </c>
-      <c r="J9">
-        <v>3.05</v>
-      </c>
-      <c r="K9">
-        <v>3.3</v>
-      </c>
-      <c r="L9">
-        <v>1.47</v>
-      </c>
-      <c r="M9">
-        <v>1.11</v>
-      </c>
-      <c r="N9">
-        <v>2.58</v>
-      </c>
-      <c r="O9">
-        <v>1.5</v>
-      </c>
-      <c r="P9">
-        <v>1.53</v>
-      </c>
-      <c r="Q9">
-        <v>2.5</v>
-      </c>
-      <c r="R9">
-        <v>1.2</v>
-      </c>
-      <c r="S9">
-        <v>5.1</v>
-      </c>
-      <c r="T9">
-        <v>2.06</v>
-      </c>
-      <c r="U9">
-        <v>1.76</v>
-      </c>
-      <c r="V9">
-        <v>1.33</v>
-      </c>
-      <c r="W9">
-        <v>1.67</v>
-      </c>
-      <c r="X9">
-        <v>11</v>
-      </c>
-      <c r="Y9">
-        <v>11</v>
-      </c>
-      <c r="Z9">
-        <v>36</v>
-      </c>
-      <c r="AA9">
-        <v>110</v>
-      </c>
-      <c r="AB9">
-        <v>7.8</v>
-      </c>
-      <c r="AC9">
+      <c r="BC9">
+        <v>3.95</v>
+      </c>
+      <c r="BD9">
+        <v>4</v>
+      </c>
+      <c r="BE9">
+        <v>4.2</v>
+      </c>
+      <c r="BF9">
+        <v>18</v>
+      </c>
+      <c r="BG9">
+        <v>9.6</v>
+      </c>
+      <c r="BH9">
+        <v>4.1</v>
+      </c>
+      <c r="BI9">
+        <v>3.1</v>
+      </c>
+      <c r="BJ9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK9">
+        <v>5.6</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>9.6</v>
+      </c>
+      <c r="BN9">
+        <v>7</v>
+      </c>
+      <c r="BO9">
+        <v>5.8</v>
+      </c>
+      <c r="BP9">
+        <v>25</v>
+      </c>
+      <c r="BQ9">
         <v>7.6</v>
       </c>
-      <c r="AD9">
-        <v>17.5</v>
-      </c>
-      <c r="AE9">
-        <v>90</v>
-      </c>
-      <c r="AF9">
-        <v>14</v>
-      </c>
-      <c r="AG9">
-        <v>13</v>
-      </c>
-      <c r="AH9">
+      <c r="BR9">
         <v>32</v>
       </c>
-      <c r="AI9">
-        <v>100</v>
-      </c>
-      <c r="AJ9">
-        <v>46</v>
-      </c>
-      <c r="AK9">
-        <v>46</v>
-      </c>
-      <c r="AL9">
-        <v>85</v>
-      </c>
-      <c r="AM9">
-        <v>220</v>
-      </c>
-      <c r="AN9">
-        <v>46</v>
-      </c>
-      <c r="AO9">
-        <v>110</v>
-      </c>
-      <c r="AP9">
+      <c r="BS9">
+        <v>8</v>
+      </c>
+      <c r="BT9">
+        <v>5.6</v>
+      </c>
+      <c r="BU9">
+        <v>4.7</v>
+      </c>
+      <c r="BV9">
+        <v>16</v>
+      </c>
+      <c r="BW9">
+        <v>6.4</v>
+      </c>
+      <c r="BX9">
+        <v>26</v>
+      </c>
+      <c r="BY9">
         <v>7.6</v>
       </c>
-      <c r="AQ9">
-        <v>9</v>
-      </c>
-      <c r="AR9">
-        <v>19</v>
-      </c>
-      <c r="AS9">
-        <v>7.4</v>
-      </c>
-      <c r="AT9">
-        <v>6.4</v>
-      </c>
-      <c r="AU9">
-        <v>6.2</v>
-      </c>
-      <c r="AV9">
-        <v>14</v>
-      </c>
-      <c r="AW9">
-        <v>7</v>
-      </c>
-      <c r="AX9">
-        <v>11</v>
-      </c>
-      <c r="AY9">
-        <v>10</v>
-      </c>
-      <c r="AZ9">
-        <v>19.5</v>
-      </c>
-      <c r="BA9">
-        <v>7.4</v>
-      </c>
-      <c r="BB9">
-        <v>24</v>
-      </c>
-      <c r="BC9">
-        <v>6.4</v>
-      </c>
-      <c r="BD9">
-        <v>42</v>
-      </c>
-      <c r="BE9">
-        <v>7.6</v>
-      </c>
-      <c r="BF9">
-        <v>6.4</v>
-      </c>
-      <c r="BG9">
-        <v>7.4</v>
-      </c>
-      <c r="BH9">
-        <v>2.82</v>
-      </c>
-      <c r="BI9">
-        <v>2.24</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>5.7</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>10.5</v>
-      </c>
-      <c r="BN9">
-        <v>5</v>
-      </c>
-      <c r="BO9">
-        <v>3.75</v>
-      </c>
-      <c r="BP9">
-        <v>20</v>
-      </c>
-      <c r="BQ9">
-        <v>7</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT9">
-        <v>7.4</v>
-      </c>
-      <c r="BU9">
-        <v>5.3</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>9.4</v>
-      </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>144</v>
       </c>
       <c r="F10">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="H10">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="I10">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="J10">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="F11">
         <v>1.85</v>
       </c>
       <c r="G11">
+        <v>2.02</v>
+      </c>
+      <c r="H11">
+        <v>3.9</v>
+      </c>
+      <c r="I11">
+        <v>4.7</v>
+      </c>
+      <c r="J11">
+        <v>3.8</v>
+      </c>
+      <c r="K11">
+        <v>4.5</v>
+      </c>
+      <c r="L11">
+        <v>1.31</v>
+      </c>
+      <c r="M11">
+        <v>1.04</v>
+      </c>
+      <c r="N11">
+        <v>4.5</v>
+      </c>
+      <c r="O11">
+        <v>1.22</v>
+      </c>
+      <c r="P11">
+        <v>2.2</v>
+      </c>
+      <c r="Q11">
+        <v>1.66</v>
+      </c>
+      <c r="R11">
+        <v>1.47</v>
+      </c>
+      <c r="S11">
+        <v>2.66</v>
+      </c>
+      <c r="T11">
+        <v>1.64</v>
+      </c>
+      <c r="U11">
+        <v>2.24</v>
+      </c>
+      <c r="V11">
+        <v>1.27</v>
+      </c>
+      <c r="W11">
+        <v>1.98</v>
+      </c>
+      <c r="X11">
+        <v>25</v>
+      </c>
+      <c r="Y11">
+        <v>23</v>
+      </c>
+      <c r="Z11">
+        <v>42</v>
+      </c>
+      <c r="AA11">
+        <v>95</v>
+      </c>
+      <c r="AB11">
+        <v>14</v>
+      </c>
+      <c r="AC11">
+        <v>11.5</v>
+      </c>
+      <c r="AD11">
+        <v>21</v>
+      </c>
+      <c r="AE11">
+        <v>60</v>
+      </c>
+      <c r="AF11">
+        <v>16.5</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>21</v>
+      </c>
+      <c r="AI11">
+        <v>60</v>
+      </c>
+      <c r="AJ11">
+        <v>26</v>
+      </c>
+      <c r="AK11">
+        <v>23</v>
+      </c>
+      <c r="AL11">
+        <v>36</v>
+      </c>
+      <c r="AM11">
+        <v>90</v>
+      </c>
+      <c r="AN11">
+        <v>10.5</v>
+      </c>
+      <c r="AO11">
+        <v>50</v>
+      </c>
+      <c r="AP11">
+        <v>14.5</v>
+      </c>
+      <c r="AQ11">
+        <v>13.5</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>8.4</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>12.5</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY11">
+        <v>7.8</v>
+      </c>
+      <c r="AZ11">
+        <v>12</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>15.5</v>
+      </c>
+      <c r="BC11">
+        <v>13.5</v>
+      </c>
+      <c r="BD11">
+        <v>21</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>7.6</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>4.2</v>
+      </c>
+      <c r="BI11">
+        <v>3.5</v>
+      </c>
+      <c r="BJ11">
+        <v>9.6</v>
+      </c>
+      <c r="BK11">
+        <v>5.8</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>9</v>
+      </c>
+      <c r="BN11">
+        <v>5</v>
+      </c>
+      <c r="BO11">
+        <v>4.2</v>
+      </c>
+      <c r="BP11">
+        <v>13</v>
+      </c>
+      <c r="BQ11">
+        <v>7.8</v>
+      </c>
+      <c r="BR11">
+        <v>25</v>
+      </c>
+      <c r="BS11">
+        <v>7</v>
+      </c>
+      <c r="BT11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU11">
+        <v>4.9</v>
+      </c>
+      <c r="BV11">
+        <v>34</v>
+      </c>
+      <c r="BW11">
+        <v>7.6</v>
+      </c>
+      <c r="BX11">
+        <v>40</v>
+      </c>
+      <c r="BY11">
+        <v>8</v>
+      </c>
+      <c r="BZ11">
+        <v>18.5</v>
+      </c>
+      <c r="CA11">
+        <v>6.4</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" t="s">
+        <v>146</v>
+      </c>
+      <c r="F12">
+        <v>1.61</v>
+      </c>
+      <c r="G12">
+        <v>1.77</v>
+      </c>
+      <c r="H12">
+        <v>5.1</v>
+      </c>
+      <c r="I12">
+        <v>7.4</v>
+      </c>
+      <c r="J12">
+        <v>3.4</v>
+      </c>
+      <c r="K12">
+        <v>4.6</v>
+      </c>
+      <c r="L12">
+        <v>1.3</v>
+      </c>
+      <c r="M12">
+        <v>1.06</v>
+      </c>
+      <c r="N12">
+        <v>1.1</v>
+      </c>
+      <c r="O12">
+        <v>1.27</v>
+      </c>
+      <c r="P12">
+        <v>2.02</v>
+      </c>
+      <c r="Q12">
+        <v>1.67</v>
+      </c>
+      <c r="R12">
+        <v>1.4</v>
+      </c>
+      <c r="S12">
+        <v>2.42</v>
+      </c>
+      <c r="T12">
+        <v>1.8</v>
+      </c>
+      <c r="U12">
+        <v>1.98</v>
+      </c>
+      <c r="V12">
+        <v>1.16</v>
+      </c>
+      <c r="W12">
+        <v>2.28</v>
+      </c>
+      <c r="X12">
+        <v>18</v>
+      </c>
+      <c r="Y12">
+        <v>22</v>
+      </c>
+      <c r="Z12">
+        <v>50</v>
+      </c>
+      <c r="AA12">
+        <v>180</v>
+      </c>
+      <c r="AB12">
+        <v>9.4</v>
+      </c>
+      <c r="AC12">
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <v>24</v>
+      </c>
+      <c r="AE12">
+        <v>90</v>
+      </c>
+      <c r="AF12">
+        <v>11</v>
+      </c>
+      <c r="AG12">
+        <v>10.5</v>
+      </c>
+      <c r="AH12">
+        <v>22</v>
+      </c>
+      <c r="AI12">
+        <v>85</v>
+      </c>
+      <c r="AJ12">
+        <v>17.5</v>
+      </c>
+      <c r="AK12">
+        <v>18.5</v>
+      </c>
+      <c r="AL12">
+        <v>36</v>
+      </c>
+      <c r="AM12">
+        <v>130</v>
+      </c>
+      <c r="AN12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO12">
+        <v>110</v>
+      </c>
+      <c r="AP12">
+        <v>5.9</v>
+      </c>
+      <c r="AQ12">
+        <v>6.2</v>
+      </c>
+      <c r="AR12">
+        <v>7.4</v>
+      </c>
+      <c r="AS12">
+        <v>8.4</v>
+      </c>
+      <c r="AT12">
+        <v>4.5</v>
+      </c>
+      <c r="AU12">
+        <v>4.7</v>
+      </c>
+      <c r="AV12">
+        <v>6.4</v>
+      </c>
+      <c r="AW12">
+        <v>8</v>
+      </c>
+      <c r="AX12">
+        <v>4.9</v>
+      </c>
+      <c r="AY12">
+        <v>4.8</v>
+      </c>
+      <c r="AZ12">
+        <v>6.2</v>
+      </c>
+      <c r="BA12">
+        <v>8</v>
+      </c>
+      <c r="BB12">
+        <v>5.9</v>
+      </c>
+      <c r="BC12">
+        <v>6</v>
+      </c>
+      <c r="BD12">
+        <v>7</v>
+      </c>
+      <c r="BE12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF12">
+        <v>4.6</v>
+      </c>
+      <c r="BG12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH12">
+        <v>3.8</v>
+      </c>
+      <c r="BI12">
+        <v>2.92</v>
+      </c>
+      <c r="BJ12">
+        <v>10.5</v>
+      </c>
+      <c r="BK12">
+        <v>5.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12">
+        <v>4.5</v>
+      </c>
+      <c r="BO12">
+        <v>3.15</v>
+      </c>
+      <c r="BP12">
+        <v>11.5</v>
+      </c>
+      <c r="BQ12">
+        <v>5.5</v>
+      </c>
+      <c r="BR12">
+        <v>26</v>
+      </c>
+      <c r="BS12">
+        <v>7.4</v>
+      </c>
+      <c r="BT12">
+        <v>9.6</v>
+      </c>
+      <c r="BU12">
+        <v>5</v>
+      </c>
+      <c r="BV12">
+        <v>50</v>
+      </c>
+      <c r="BW12">
+        <v>8.6</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ12">
+        <v>20</v>
+      </c>
+      <c r="CA12">
+        <v>6.8</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13">
+        <v>1.49</v>
+      </c>
+      <c r="G13">
+        <v>1.61</v>
+      </c>
+      <c r="H13">
+        <v>5.7</v>
+      </c>
+      <c r="I13">
+        <v>7.8</v>
+      </c>
+      <c r="J13">
+        <v>3.95</v>
+      </c>
+      <c r="K13">
+        <v>5.2</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.04</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="O13">
+        <v>1.23</v>
+      </c>
+      <c r="P13">
+        <v>1.95</v>
+      </c>
+      <c r="Q13">
+        <v>1.57</v>
+      </c>
+      <c r="R13">
+        <v>1.48</v>
+      </c>
+      <c r="S13">
+        <v>2.56</v>
+      </c>
+      <c r="T13">
+        <v>1.8</v>
+      </c>
+      <c r="U13">
+        <v>2</v>
+      </c>
+      <c r="V13">
+        <v>1.14</v>
+      </c>
+      <c r="W13">
+        <v>2.62</v>
+      </c>
+      <c r="X13">
+        <v>25</v>
+      </c>
+      <c r="Y13">
+        <v>27</v>
+      </c>
+      <c r="Z13">
+        <v>65</v>
+      </c>
+      <c r="AA13">
+        <v>240</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <v>27</v>
+      </c>
+      <c r="AE13">
+        <v>120</v>
+      </c>
+      <c r="AF13">
+        <v>10.5</v>
+      </c>
+      <c r="AG13">
+        <v>10.5</v>
+      </c>
+      <c r="AH13">
+        <v>23</v>
+      </c>
+      <c r="AI13">
+        <v>100</v>
+      </c>
+      <c r="AJ13">
+        <v>15</v>
+      </c>
+      <c r="AK13">
+        <v>16.5</v>
+      </c>
+      <c r="AL13">
+        <v>34</v>
+      </c>
+      <c r="AM13">
+        <v>130</v>
+      </c>
+      <c r="AN13">
+        <v>7.4</v>
+      </c>
+      <c r="AO13">
+        <v>130</v>
+      </c>
+      <c r="AP13">
+        <v>6.2</v>
+      </c>
+      <c r="AQ13">
+        <v>6.2</v>
+      </c>
+      <c r="AR13">
+        <v>7.2</v>
+      </c>
+      <c r="AS13">
+        <v>8</v>
+      </c>
+      <c r="AT13">
+        <v>4.5</v>
+      </c>
+      <c r="AU13">
+        <v>4.8</v>
+      </c>
+      <c r="AV13">
+        <v>6.2</v>
+      </c>
+      <c r="AW13">
+        <v>7.6</v>
+      </c>
+      <c r="AX13">
+        <v>4.6</v>
+      </c>
+      <c r="AY13">
+        <v>4.6</v>
+      </c>
+      <c r="AZ13">
+        <v>6</v>
+      </c>
+      <c r="BA13">
+        <v>7.6</v>
+      </c>
+      <c r="BB13">
+        <v>5.3</v>
+      </c>
+      <c r="BC13">
+        <v>5.5</v>
+      </c>
+      <c r="BD13">
+        <v>6.6</v>
+      </c>
+      <c r="BE13">
+        <v>7.8</v>
+      </c>
+      <c r="BF13">
+        <v>3.9</v>
+      </c>
+      <c r="BG13">
+        <v>7.8</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14">
+        <v>2.06</v>
+      </c>
+      <c r="G14">
+        <v>2.3</v>
+      </c>
+      <c r="H14">
+        <v>3.3</v>
+      </c>
+      <c r="I14">
+        <v>3.9</v>
+      </c>
+      <c r="J14">
+        <v>3.6</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>1.28</v>
+      </c>
+      <c r="M14">
+        <v>1.05</v>
+      </c>
+      <c r="N14">
+        <v>4.3</v>
+      </c>
+      <c r="O14">
+        <v>1.24</v>
+      </c>
+      <c r="P14">
+        <v>2.14</v>
+      </c>
+      <c r="Q14">
+        <v>1.71</v>
+      </c>
+      <c r="R14">
+        <v>1.45</v>
+      </c>
+      <c r="S14">
+        <v>2.78</v>
+      </c>
+      <c r="T14">
+        <v>1.63</v>
+      </c>
+      <c r="U14">
+        <v>2.28</v>
+      </c>
+      <c r="V14">
+        <v>1.35</v>
+      </c>
+      <c r="W14">
+        <v>1.78</v>
+      </c>
+      <c r="X14">
+        <v>23</v>
+      </c>
+      <c r="Y14">
+        <v>19.5</v>
+      </c>
+      <c r="Z14">
+        <v>34</v>
+      </c>
+      <c r="AA14">
+        <v>75</v>
+      </c>
+      <c r="AB14">
+        <v>14.5</v>
+      </c>
+      <c r="AC14">
+        <v>11</v>
+      </c>
+      <c r="AD14">
+        <v>18.5</v>
+      </c>
+      <c r="AE14">
+        <v>46</v>
+      </c>
+      <c r="AF14">
+        <v>18.5</v>
+      </c>
+      <c r="AG14">
+        <v>13.5</v>
+      </c>
+      <c r="AH14">
+        <v>19.5</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>34</v>
+      </c>
+      <c r="AK14">
+        <v>26</v>
+      </c>
+      <c r="AL14">
+        <v>38</v>
+      </c>
+      <c r="AM14">
+        <v>90</v>
+      </c>
+      <c r="AN14">
+        <v>16</v>
+      </c>
+      <c r="AO14">
+        <v>38</v>
+      </c>
+      <c r="AP14">
+        <v>13.5</v>
+      </c>
+      <c r="AQ14">
+        <v>11.5</v>
+      </c>
+      <c r="AR14">
+        <v>19.5</v>
+      </c>
+      <c r="AS14">
+        <v>4</v>
+      </c>
+      <c r="AT14">
+        <v>8.6</v>
+      </c>
+      <c r="AU14">
+        <v>6.6</v>
+      </c>
+      <c r="AV14">
+        <v>11</v>
+      </c>
+      <c r="AW14">
+        <v>3.85</v>
+      </c>
+      <c r="AX14">
+        <v>11</v>
+      </c>
+      <c r="AY14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ14">
+        <v>11.5</v>
+      </c>
+      <c r="BA14">
+        <v>3.9</v>
+      </c>
+      <c r="BB14">
+        <v>19.5</v>
+      </c>
+      <c r="BC14">
+        <v>15.5</v>
+      </c>
+      <c r="BD14">
+        <v>3.8</v>
+      </c>
+      <c r="BE14">
+        <v>4</v>
+      </c>
+      <c r="BF14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG14">
+        <v>3.8</v>
+      </c>
+      <c r="BH14">
+        <v>3.95</v>
+      </c>
+      <c r="BI14">
+        <v>3.05</v>
+      </c>
+      <c r="BJ14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK14">
+        <v>5.1</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>10</v>
+      </c>
+      <c r="BN14">
+        <v>5.4</v>
+      </c>
+      <c r="BO14">
+        <v>4</v>
+      </c>
+      <c r="BP14">
+        <v>15.5</v>
+      </c>
+      <c r="BQ14">
+        <v>6.6</v>
+      </c>
+      <c r="BR14">
+        <v>26</v>
+      </c>
+      <c r="BS14">
+        <v>8</v>
+      </c>
+      <c r="BT14">
+        <v>7.2</v>
+      </c>
+      <c r="BU14">
+        <v>5.2</v>
+      </c>
+      <c r="BV14">
+        <v>27</v>
+      </c>
+      <c r="BW14">
+        <v>8</v>
+      </c>
+      <c r="BX14">
+        <v>34</v>
+      </c>
+      <c r="BY14">
+        <v>8.6</v>
+      </c>
+      <c r="BZ14">
+        <v>21</v>
+      </c>
+      <c r="CA14">
+        <v>7.4</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15">
+        <v>2.54</v>
+      </c>
+      <c r="G15">
+        <v>2.8</v>
+      </c>
+      <c r="H15">
+        <v>2.66</v>
+      </c>
+      <c r="I15">
+        <v>3.1</v>
+      </c>
+      <c r="J15">
+        <v>3.3</v>
+      </c>
+      <c r="K15">
+        <v>3.9</v>
+      </c>
+      <c r="L15">
+        <v>1.32</v>
+      </c>
+      <c r="M15">
+        <v>1.06</v>
+      </c>
+      <c r="N15">
+        <v>3.8</v>
+      </c>
+      <c r="O15">
+        <v>1.28</v>
+      </c>
+      <c r="P15">
+        <v>1.96</v>
+      </c>
+      <c r="Q15">
+        <v>1.86</v>
+      </c>
+      <c r="R15">
+        <v>1.37</v>
+      </c>
+      <c r="S15">
+        <v>3.1</v>
+      </c>
+      <c r="T15">
+        <v>1.68</v>
+      </c>
+      <c r="U15">
+        <v>2.2</v>
+      </c>
+      <c r="V15">
+        <v>1.48</v>
+      </c>
+      <c r="W15">
+        <v>1.54</v>
+      </c>
+      <c r="X15">
+        <v>18</v>
+      </c>
+      <c r="Y15">
+        <v>13</v>
+      </c>
+      <c r="Z15">
+        <v>24</v>
+      </c>
+      <c r="AA15">
+        <v>55</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>15.5</v>
+      </c>
+      <c r="AE15">
+        <v>38</v>
+      </c>
+      <c r="AF15">
+        <v>19.5</v>
+      </c>
+      <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
+        <v>17</v>
+      </c>
+      <c r="AI15">
+        <v>50</v>
+      </c>
+      <c r="AJ15">
+        <v>42</v>
+      </c>
+      <c r="AK15">
+        <v>30</v>
+      </c>
+      <c r="AL15">
+        <v>40</v>
+      </c>
+      <c r="AM15">
+        <v>100</v>
+      </c>
+      <c r="AN15">
+        <v>24</v>
+      </c>
+      <c r="AO15">
+        <v>36</v>
+      </c>
+      <c r="AP15">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15">
+        <v>14</v>
+      </c>
+      <c r="AS15">
+        <v>6</v>
+      </c>
+      <c r="AT15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>9.4</v>
+      </c>
+      <c r="AW15">
+        <v>5.7</v>
+      </c>
+      <c r="AX15">
+        <v>15.5</v>
+      </c>
+      <c r="AY15">
+        <v>9</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
+        <v>5.9</v>
+      </c>
+      <c r="BB15">
+        <v>5.8</v>
+      </c>
+      <c r="BC15">
+        <v>5.5</v>
+      </c>
+      <c r="BD15">
+        <v>5.7</v>
+      </c>
+      <c r="BE15">
+        <v>6.2</v>
+      </c>
+      <c r="BF15">
+        <v>19</v>
+      </c>
+      <c r="BG15">
+        <v>5.6</v>
+      </c>
+      <c r="BH15">
+        <v>3.65</v>
+      </c>
+      <c r="BI15">
+        <v>2.84</v>
+      </c>
+      <c r="BJ15">
+        <v>9.4</v>
+      </c>
+      <c r="BK15">
+        <v>5</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>10</v>
+      </c>
+      <c r="BN15">
+        <v>6</v>
+      </c>
+      <c r="BO15">
+        <v>4.4</v>
+      </c>
+      <c r="BP15">
+        <v>21</v>
+      </c>
+      <c r="BQ15">
+        <v>7.2</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT15">
+        <v>6.2</v>
+      </c>
+      <c r="BU15">
+        <v>4.5</v>
+      </c>
+      <c r="BV15">
+        <v>22</v>
+      </c>
+      <c r="BW15">
+        <v>7.2</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ15">
+        <v>26</v>
+      </c>
+      <c r="CA15">
+        <v>7.6</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16">
+        <v>2.14</v>
+      </c>
+      <c r="G16">
+        <v>2.26</v>
+      </c>
+      <c r="H16">
+        <v>3.25</v>
+      </c>
+      <c r="I16">
+        <v>3.7</v>
+      </c>
+      <c r="J16">
+        <v>3.8</v>
+      </c>
+      <c r="K16">
+        <v>4.1</v>
+      </c>
+      <c r="L16">
+        <v>1.01</v>
+      </c>
+      <c r="M16">
+        <v>1.04</v>
+      </c>
+      <c r="N16">
+        <v>3.8</v>
+      </c>
+      <c r="O16">
+        <v>1.21</v>
+      </c>
+      <c r="P16">
+        <v>2.26</v>
+      </c>
+      <c r="Q16">
+        <v>1.67</v>
+      </c>
+      <c r="R16">
+        <v>1.48</v>
+      </c>
+      <c r="S16">
+        <v>2.62</v>
+      </c>
+      <c r="T16">
+        <v>1.5</v>
+      </c>
+      <c r="U16">
+        <v>2.14</v>
+      </c>
+      <c r="V16">
+        <v>1.37</v>
+      </c>
+      <c r="W16">
+        <v>1.79</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16">
+        <v>1.03</v>
+      </c>
+      <c r="AR16">
+        <v>1.03</v>
+      </c>
+      <c r="AS16">
+        <v>1.03</v>
+      </c>
+      <c r="AT16">
+        <v>1.03</v>
+      </c>
+      <c r="AU16">
+        <v>1.03</v>
+      </c>
+      <c r="AV16">
+        <v>1.03</v>
+      </c>
+      <c r="AW16">
+        <v>1.03</v>
+      </c>
+      <c r="AX16">
+        <v>1.03</v>
+      </c>
+      <c r="AY16">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16">
+        <v>1.03</v>
+      </c>
+      <c r="BA16">
+        <v>1.03</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>5.3</v>
+      </c>
+      <c r="BI16">
+        <v>2.86</v>
+      </c>
+      <c r="BJ16">
+        <v>12.5</v>
+      </c>
+      <c r="BK16">
+        <v>2.5</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>3.1</v>
+      </c>
+      <c r="BN16">
+        <v>7.4</v>
+      </c>
+      <c r="BO16">
+        <v>3.6</v>
+      </c>
+      <c r="BP16">
+        <v>21</v>
+      </c>
+      <c r="BQ16">
+        <v>2.72</v>
+      </c>
+      <c r="BR16">
+        <v>34</v>
+      </c>
+      <c r="BS16">
+        <v>2.86</v>
+      </c>
+      <c r="BT16">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU16">
+        <v>4.6</v>
+      </c>
+      <c r="BV16">
+        <v>34</v>
+      </c>
+      <c r="BW16">
+        <v>2.86</v>
+      </c>
+      <c r="BX16">
+        <v>44</v>
+      </c>
+      <c r="BY16">
+        <v>2.92</v>
+      </c>
+      <c r="BZ16">
+        <v>26</v>
+      </c>
+      <c r="CA16">
+        <v>2.78</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17">
+        <v>1.93</v>
+      </c>
+      <c r="G17">
+        <v>1.99</v>
+      </c>
+      <c r="H17">
+        <v>4.1</v>
+      </c>
+      <c r="I17">
+        <v>4.3</v>
+      </c>
+      <c r="J17">
+        <v>3.85</v>
+      </c>
+      <c r="K17">
+        <v>4.1</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.05</v>
+      </c>
+      <c r="N17">
+        <v>4.3</v>
+      </c>
+      <c r="O17">
+        <v>1.22</v>
+      </c>
+      <c r="P17">
+        <v>2.22</v>
+      </c>
+      <c r="Q17">
+        <v>1.64</v>
+      </c>
+      <c r="R17">
+        <v>1.49</v>
+      </c>
+      <c r="S17">
+        <v>2.72</v>
+      </c>
+      <c r="T17">
+        <v>1.64</v>
+      </c>
+      <c r="U17">
+        <v>2.3</v>
+      </c>
+      <c r="V17">
+        <v>1.3</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+      <c r="X17">
+        <v>24</v>
+      </c>
+      <c r="Y17">
+        <v>23</v>
+      </c>
+      <c r="Z17">
+        <v>40</v>
+      </c>
+      <c r="AA17">
+        <v>100</v>
+      </c>
+      <c r="AB17">
+        <v>13.5</v>
+      </c>
+      <c r="AC17">
+        <v>11.5</v>
+      </c>
+      <c r="AD17">
+        <v>21</v>
+      </c>
+      <c r="AE17">
+        <v>60</v>
+      </c>
+      <c r="AF17">
+        <v>16.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>21</v>
+      </c>
+      <c r="AI17">
+        <v>60</v>
+      </c>
+      <c r="AJ17">
+        <v>27</v>
+      </c>
+      <c r="AK17">
+        <v>20</v>
+      </c>
+      <c r="AL17">
+        <v>38</v>
+      </c>
+      <c r="AM17">
+        <v>90</v>
+      </c>
+      <c r="AN17">
+        <v>13</v>
+      </c>
+      <c r="AO17">
+        <v>50</v>
+      </c>
+      <c r="AP17">
+        <v>17</v>
+      </c>
+      <c r="AQ17">
+        <v>15.5</v>
+      </c>
+      <c r="AR17">
+        <v>3.9</v>
+      </c>
+      <c r="AS17">
+        <v>4.1</v>
+      </c>
+      <c r="AT17">
+        <v>9.6</v>
+      </c>
+      <c r="AU17">
+        <v>7.8</v>
+      </c>
+      <c r="AV17">
+        <v>14.5</v>
+      </c>
+      <c r="AW17">
+        <v>4</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>4</v>
+      </c>
+      <c r="BB17">
+        <v>18.5</v>
+      </c>
+      <c r="BC17">
+        <v>16</v>
+      </c>
+      <c r="BD17">
+        <v>3.85</v>
+      </c>
+      <c r="BE17">
+        <v>4.1</v>
+      </c>
+      <c r="BF17">
+        <v>7.8</v>
+      </c>
+      <c r="BG17">
+        <v>3.95</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.93</v>
+      </c>
+      <c r="BJ17">
+        <v>13</v>
+      </c>
+      <c r="BK17">
+        <v>1.68</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.93</v>
+      </c>
+      <c r="BN17">
+        <v>6.6</v>
+      </c>
+      <c r="BO17">
+        <v>3.25</v>
+      </c>
+      <c r="BP17">
+        <v>18.5</v>
+      </c>
+      <c r="BQ17">
+        <v>1.75</v>
+      </c>
+      <c r="BR17">
+        <v>34</v>
+      </c>
+      <c r="BS17">
+        <v>1.83</v>
+      </c>
+      <c r="BT17">
+        <v>11</v>
+      </c>
+      <c r="BU17">
+        <v>4.9</v>
+      </c>
+      <c r="BV17">
+        <v>46</v>
+      </c>
+      <c r="BW17">
+        <v>1.85</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.86</v>
+      </c>
+      <c r="BZ17">
+        <v>26</v>
+      </c>
+      <c r="CA17">
+        <v>1.8</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18">
+        <v>1.56</v>
+      </c>
+      <c r="G18">
+        <v>1.58</v>
+      </c>
+      <c r="H18">
+        <v>6.4</v>
+      </c>
+      <c r="I18">
+        <v>6.8</v>
+      </c>
+      <c r="J18">
+        <v>4.7</v>
+      </c>
+      <c r="K18">
+        <v>4.9</v>
+      </c>
+      <c r="L18">
+        <v>1.26</v>
+      </c>
+      <c r="M18">
+        <v>1.04</v>
+      </c>
+      <c r="N18">
+        <v>5.4</v>
+      </c>
+      <c r="O18">
+        <v>1.19</v>
+      </c>
+      <c r="P18">
+        <v>2.54</v>
+      </c>
+      <c r="Q18">
+        <v>1.57</v>
+      </c>
+      <c r="R18">
+        <v>1.62</v>
+      </c>
+      <c r="S18">
+        <v>2.4</v>
+      </c>
+      <c r="T18">
+        <v>1.7</v>
+      </c>
+      <c r="U18">
+        <v>2.26</v>
+      </c>
+      <c r="V18">
+        <v>1.17</v>
+      </c>
+      <c r="W18">
+        <v>2.72</v>
+      </c>
+      <c r="X18">
+        <v>26</v>
+      </c>
+      <c r="Y18">
+        <v>32</v>
+      </c>
+      <c r="Z18">
+        <v>70</v>
+      </c>
+      <c r="AA18">
+        <v>190</v>
+      </c>
+      <c r="AB18">
+        <v>12</v>
+      </c>
+      <c r="AC18">
+        <v>12</v>
+      </c>
+      <c r="AD18">
+        <v>27</v>
+      </c>
+      <c r="AE18">
+        <v>90</v>
+      </c>
+      <c r="AF18">
+        <v>12</v>
+      </c>
+      <c r="AG18">
+        <v>10.5</v>
+      </c>
+      <c r="AH18">
+        <v>19.5</v>
+      </c>
+      <c r="AI18">
+        <v>80</v>
+      </c>
+      <c r="AJ18">
+        <v>16</v>
+      </c>
+      <c r="AK18">
+        <v>16</v>
+      </c>
+      <c r="AL18">
+        <v>32</v>
+      </c>
+      <c r="AM18">
+        <v>90</v>
+      </c>
+      <c r="AN18">
+        <v>6.4</v>
+      </c>
+      <c r="AO18">
+        <v>80</v>
+      </c>
+      <c r="AP18">
+        <v>6.8</v>
+      </c>
+      <c r="AQ18">
+        <v>7.2</v>
+      </c>
+      <c r="AR18">
+        <v>8</v>
+      </c>
+      <c r="AS18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT18">
+        <v>10</v>
+      </c>
+      <c r="AU18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV18">
+        <v>21</v>
+      </c>
+      <c r="AW18">
+        <v>8.4</v>
+      </c>
+      <c r="AX18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>16</v>
+      </c>
+      <c r="BA18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB18">
+        <v>13</v>
+      </c>
+      <c r="BC18">
+        <v>12.5</v>
+      </c>
+      <c r="BD18">
+        <v>7</v>
+      </c>
+      <c r="BE18">
+        <v>8.4</v>
+      </c>
+      <c r="BF18">
+        <v>5.6</v>
+      </c>
+      <c r="BG18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH18">
+        <v>6</v>
+      </c>
+      <c r="BI18">
+        <v>3</v>
+      </c>
+      <c r="BJ18">
+        <v>13.5</v>
+      </c>
+      <c r="BK18">
+        <v>2.46</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>3</v>
+      </c>
+      <c r="BN18">
+        <v>6</v>
+      </c>
+      <c r="BO18">
+        <v>3</v>
+      </c>
+      <c r="BP18">
+        <v>13.5</v>
+      </c>
+      <c r="BQ18">
+        <v>2.46</v>
+      </c>
+      <c r="BR18">
+        <v>30</v>
+      </c>
+      <c r="BS18">
+        <v>2.72</v>
+      </c>
+      <c r="BT18">
+        <v>14.5</v>
+      </c>
+      <c r="BU18">
+        <v>2.48</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>2.88</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>2.88</v>
+      </c>
+      <c r="BZ18">
+        <v>19</v>
+      </c>
+      <c r="CA18">
+        <v>2.6</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>153</v>
+      </c>
+      <c r="F19">
+        <v>1.57</v>
+      </c>
+      <c r="G19">
+        <v>1.7</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19">
+        <v>4.6</v>
+      </c>
+      <c r="K19">
+        <v>5.4</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>6.6</v>
+      </c>
+      <c r="O19">
+        <v>1.13</v>
+      </c>
+      <c r="P19">
+        <v>2.92</v>
+      </c>
+      <c r="Q19">
+        <v>1.41</v>
+      </c>
+      <c r="R19">
+        <v>1.78</v>
+      </c>
+      <c r="S19">
+        <v>2</v>
+      </c>
+      <c r="T19">
+        <v>1.52</v>
+      </c>
+      <c r="U19">
+        <v>2.38</v>
+      </c>
+      <c r="V19">
+        <v>1.2</v>
+      </c>
+      <c r="W19">
+        <v>2.42</v>
+      </c>
+      <c r="X19">
+        <v>36</v>
+      </c>
+      <c r="Y19">
+        <v>34</v>
+      </c>
+      <c r="Z19">
+        <v>55</v>
+      </c>
+      <c r="AA19">
+        <v>130</v>
+      </c>
+      <c r="AB19">
+        <v>16</v>
+      </c>
+      <c r="AC19">
+        <v>13</v>
+      </c>
+      <c r="AD19">
+        <v>24</v>
+      </c>
+      <c r="AE19">
+        <v>60</v>
+      </c>
+      <c r="AF19">
+        <v>15</v>
+      </c>
+      <c r="AG19">
+        <v>11.5</v>
+      </c>
+      <c r="AH19">
+        <v>17.5</v>
+      </c>
+      <c r="AI19">
+        <v>50</v>
+      </c>
+      <c r="AJ19">
+        <v>18.5</v>
+      </c>
+      <c r="AK19">
+        <v>15.5</v>
+      </c>
+      <c r="AL19">
+        <v>25</v>
+      </c>
+      <c r="AM19">
+        <v>60</v>
+      </c>
+      <c r="AN19">
+        <v>5.7</v>
+      </c>
+      <c r="AO19">
+        <v>40</v>
+      </c>
+      <c r="AP19">
+        <v>26</v>
+      </c>
+      <c r="AQ19">
+        <v>24</v>
+      </c>
+      <c r="AR19">
+        <v>38</v>
+      </c>
+      <c r="AS19">
+        <v>80</v>
+      </c>
+      <c r="AT19">
+        <v>11.5</v>
+      </c>
+      <c r="AU19">
+        <v>9.4</v>
+      </c>
+      <c r="AV19">
+        <v>17</v>
+      </c>
+      <c r="AW19">
+        <v>40</v>
+      </c>
+      <c r="AX19">
+        <v>10.5</v>
+      </c>
+      <c r="AY19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19">
+        <v>12.5</v>
+      </c>
+      <c r="BA19">
+        <v>36</v>
+      </c>
+      <c r="BB19">
+        <v>13.5</v>
+      </c>
+      <c r="BC19">
+        <v>11.5</v>
+      </c>
+      <c r="BD19">
+        <v>19.5</v>
+      </c>
+      <c r="BE19">
+        <v>42</v>
+      </c>
+      <c r="BF19">
+        <v>4.7</v>
+      </c>
+      <c r="BG19">
+        <v>28</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>0</v>
+      </c>
+      <c r="CA19">
+        <v>0</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20">
+        <v>1.62</v>
+      </c>
+      <c r="G20">
+        <v>1.75</v>
+      </c>
+      <c r="H20">
+        <v>4.3</v>
+      </c>
+      <c r="I20">
+        <v>5.9</v>
+      </c>
+      <c r="J20">
+        <v>4.6</v>
+      </c>
+      <c r="K20">
+        <v>5.5</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.02</v>
+      </c>
+      <c r="N20">
+        <v>3.45</v>
+      </c>
+      <c r="O20">
+        <v>1.08</v>
+      </c>
+      <c r="P20">
+        <v>3.45</v>
+      </c>
+      <c r="Q20">
+        <v>1.33</v>
+      </c>
+      <c r="R20">
+        <v>1.99</v>
+      </c>
+      <c r="S20">
+        <v>1.8</v>
+      </c>
+      <c r="T20">
+        <v>1.43</v>
+      </c>
+      <c r="U20">
+        <v>1.01</v>
+      </c>
+      <c r="V20">
+        <v>1.2</v>
+      </c>
+      <c r="W20">
+        <v>2.32</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BI20">
+        <v>3.85</v>
+      </c>
+      <c r="BJ20">
+        <v>12.5</v>
+      </c>
+      <c r="BK20">
+        <v>5.4</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>21</v>
+      </c>
+      <c r="BN20">
+        <v>7.6</v>
+      </c>
+      <c r="BO20">
+        <v>3.55</v>
+      </c>
+      <c r="BP20">
+        <v>14.5</v>
+      </c>
+      <c r="BQ20">
+        <v>6.2</v>
+      </c>
+      <c r="BR20">
+        <v>23</v>
+      </c>
+      <c r="BS20">
+        <v>9.6</v>
+      </c>
+      <c r="BT20">
+        <v>13.5</v>
+      </c>
+      <c r="BU20">
+        <v>5.8</v>
+      </c>
+      <c r="BV20">
+        <v>44</v>
+      </c>
+      <c r="BW20">
+        <v>17.5</v>
+      </c>
+      <c r="BX20">
+        <v>40</v>
+      </c>
+      <c r="BY20">
+        <v>16.5</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21">
+        <v>2.78</v>
+      </c>
+      <c r="G21">
+        <v>3.5</v>
+      </c>
+      <c r="H21">
+        <v>2.22</v>
+      </c>
+      <c r="I21">
+        <v>2.88</v>
+      </c>
+      <c r="J21">
+        <v>3.25</v>
+      </c>
+      <c r="K21">
+        <v>5.3</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.03</v>
+      </c>
+      <c r="N21">
+        <v>1.01</v>
+      </c>
+      <c r="O21">
+        <v>1.17</v>
+      </c>
+      <c r="P21">
+        <v>2.14</v>
+      </c>
+      <c r="Q21">
+        <v>1.5</v>
+      </c>
+      <c r="R21">
+        <v>1.48</v>
+      </c>
+      <c r="S21">
+        <v>2.16</v>
+      </c>
+      <c r="T21">
+        <v>1.01</v>
+      </c>
+      <c r="U21">
+        <v>1.01</v>
+      </c>
+      <c r="V21">
+        <v>1.56</v>
+      </c>
+      <c r="W21">
+        <v>1.4</v>
+      </c>
+      <c r="X21">
+        <v>1000</v>
+      </c>
+      <c r="Y21">
+        <v>1000</v>
+      </c>
+      <c r="Z21">
+        <v>1000</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>1000</v>
+      </c>
+      <c r="AC21">
+        <v>1000</v>
+      </c>
+      <c r="AD21">
+        <v>1000</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>1000</v>
+      </c>
+      <c r="AG21">
+        <v>1000</v>
+      </c>
+      <c r="AH21">
+        <v>1000</v>
+      </c>
+      <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21">
+        <v>1.01</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.01</v>
+      </c>
+      <c r="AT21">
+        <v>1.01</v>
+      </c>
+      <c r="AU21">
+        <v>1.01</v>
+      </c>
+      <c r="AV21">
+        <v>1.01</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>1.01</v>
+      </c>
+      <c r="AY21">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21">
+        <v>1.01</v>
+      </c>
+      <c r="BA21">
+        <v>1.01</v>
+      </c>
+      <c r="BB21">
+        <v>1.01</v>
+      </c>
+      <c r="BC21">
+        <v>1.01</v>
+      </c>
+      <c r="BD21">
+        <v>1.01</v>
+      </c>
+      <c r="BE21">
+        <v>1.01</v>
+      </c>
+      <c r="BF21">
+        <v>1.01</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21">
+        <v>1000</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>1000</v>
+      </c>
+      <c r="BO21">
+        <v>1.01</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>1000</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22">
+        <v>3.9</v>
+      </c>
+      <c r="H22">
+        <v>1.91</v>
+      </c>
+      <c r="I22">
+        <v>2.16</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4.8</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>2.7</v>
+      </c>
+      <c r="Q22">
+        <v>1.39</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>130</v>
+      </c>
+      <c r="E23" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23">
+        <v>2.14</v>
+      </c>
+      <c r="G23">
+        <v>2.42</v>
+      </c>
+      <c r="H23">
+        <v>2.94</v>
+      </c>
+      <c r="I23">
+        <v>3.4</v>
+      </c>
+      <c r="J23">
+        <v>3.8</v>
+      </c>
+      <c r="K23">
+        <v>4.6</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.5</v>
+      </c>
+      <c r="Q23">
+        <v>1.52</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24">
+        <v>4.9</v>
+      </c>
+      <c r="G24">
+        <v>6.6</v>
+      </c>
+      <c r="H24">
+        <v>1.57</v>
+      </c>
+      <c r="I24">
+        <v>1.71</v>
+      </c>
+      <c r="J24">
+        <v>4.4</v>
+      </c>
+      <c r="K24">
+        <v>5.4</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>2.74</v>
+      </c>
+      <c r="Q24">
+        <v>1.47</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F25">
+        <v>2.36</v>
+      </c>
+      <c r="G25">
+        <v>2.48</v>
+      </c>
+      <c r="H25">
+        <v>3.55</v>
+      </c>
+      <c r="I25">
+        <v>4.1</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25">
+        <v>3.3</v>
+      </c>
+      <c r="L25">
+        <v>1.47</v>
+      </c>
+      <c r="M25">
+        <v>1.11</v>
+      </c>
+      <c r="N25">
+        <v>2.58</v>
+      </c>
+      <c r="O25">
+        <v>1.5</v>
+      </c>
+      <c r="P25">
+        <v>1.53</v>
+      </c>
+      <c r="Q25">
+        <v>2.5</v>
+      </c>
+      <c r="R25">
+        <v>1.2</v>
+      </c>
+      <c r="S25">
+        <v>5.1</v>
+      </c>
+      <c r="T25">
+        <v>2.06</v>
+      </c>
+      <c r="U25">
+        <v>1.76</v>
+      </c>
+      <c r="V25">
+        <v>1.33</v>
+      </c>
+      <c r="W25">
+        <v>1.67</v>
+      </c>
+      <c r="X25">
+        <v>11</v>
+      </c>
+      <c r="Y25">
+        <v>11</v>
+      </c>
+      <c r="Z25">
+        <v>36</v>
+      </c>
+      <c r="AA25">
+        <v>110</v>
+      </c>
+      <c r="AB25">
+        <v>7.8</v>
+      </c>
+      <c r="AC25">
+        <v>7.6</v>
+      </c>
+      <c r="AD25">
+        <v>17.5</v>
+      </c>
+      <c r="AE25">
+        <v>90</v>
+      </c>
+      <c r="AF25">
+        <v>14</v>
+      </c>
+      <c r="AG25">
+        <v>13</v>
+      </c>
+      <c r="AH25">
+        <v>32</v>
+      </c>
+      <c r="AI25">
+        <v>100</v>
+      </c>
+      <c r="AJ25">
+        <v>46</v>
+      </c>
+      <c r="AK25">
+        <v>46</v>
+      </c>
+      <c r="AL25">
+        <v>85</v>
+      </c>
+      <c r="AM25">
+        <v>220</v>
+      </c>
+      <c r="AN25">
+        <v>46</v>
+      </c>
+      <c r="AO25">
+        <v>110</v>
+      </c>
+      <c r="AP25">
+        <v>7.6</v>
+      </c>
+      <c r="AQ25">
+        <v>9</v>
+      </c>
+      <c r="AR25">
+        <v>19</v>
+      </c>
+      <c r="AS25">
+        <v>7.4</v>
+      </c>
+      <c r="AT25">
+        <v>6.4</v>
+      </c>
+      <c r="AU25">
+        <v>6.2</v>
+      </c>
+      <c r="AV25">
+        <v>14</v>
+      </c>
+      <c r="AW25">
+        <v>7</v>
+      </c>
+      <c r="AX25">
+        <v>11</v>
+      </c>
+      <c r="AY25">
+        <v>10</v>
+      </c>
+      <c r="AZ25">
+        <v>19.5</v>
+      </c>
+      <c r="BA25">
+        <v>7.4</v>
+      </c>
+      <c r="BB25">
+        <v>24</v>
+      </c>
+      <c r="BC25">
+        <v>6.4</v>
+      </c>
+      <c r="BD25">
+        <v>42</v>
+      </c>
+      <c r="BE25">
+        <v>7.6</v>
+      </c>
+      <c r="BF25">
+        <v>6.4</v>
+      </c>
+      <c r="BG25">
+        <v>7.4</v>
+      </c>
+      <c r="BH25">
+        <v>2.82</v>
+      </c>
+      <c r="BI25">
+        <v>2.24</v>
+      </c>
+      <c r="BJ25">
+        <v>12</v>
+      </c>
+      <c r="BK25">
+        <v>5.7</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>10.5</v>
+      </c>
+      <c r="BN25">
+        <v>5</v>
+      </c>
+      <c r="BO25">
+        <v>3.75</v>
+      </c>
+      <c r="BP25">
+        <v>20</v>
+      </c>
+      <c r="BQ25">
+        <v>7</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT25">
+        <v>7.4</v>
+      </c>
+      <c r="BU25">
+        <v>5.3</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>9.4</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>9</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26">
+        <v>3.2</v>
+      </c>
+      <c r="G26">
+        <v>3.55</v>
+      </c>
+      <c r="H26">
+        <v>2.28</v>
+      </c>
+      <c r="I26">
+        <v>2.44</v>
+      </c>
+      <c r="J26">
+        <v>3.3</v>
+      </c>
+      <c r="K26">
+        <v>3.65</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>1.9</v>
+      </c>
+      <c r="Q26">
+        <v>1.76</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>0</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
+      <c r="AV26">
+        <v>0</v>
+      </c>
+      <c r="AW26">
+        <v>0</v>
+      </c>
+      <c r="AX26">
+        <v>0</v>
+      </c>
+      <c r="AY26">
+        <v>0</v>
+      </c>
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+      <c r="BA26">
+        <v>0</v>
+      </c>
+      <c r="BB26">
+        <v>0</v>
+      </c>
+      <c r="BC26">
+        <v>0</v>
+      </c>
+      <c r="BD26">
+        <v>0</v>
+      </c>
+      <c r="BE26">
+        <v>0</v>
+      </c>
+      <c r="BF26">
+        <v>0</v>
+      </c>
+      <c r="BG26">
+        <v>0</v>
+      </c>
+      <c r="BH26">
+        <v>0</v>
+      </c>
+      <c r="BI26">
+        <v>0</v>
+      </c>
+      <c r="BJ26">
+        <v>0</v>
+      </c>
+      <c r="BK26">
+        <v>0</v>
+      </c>
+      <c r="BL26">
+        <v>0</v>
+      </c>
+      <c r="BM26">
+        <v>0</v>
+      </c>
+      <c r="BN26">
+        <v>0</v>
+      </c>
+      <c r="BO26">
+        <v>0</v>
+      </c>
+      <c r="BP26">
+        <v>0</v>
+      </c>
+      <c r="BQ26">
+        <v>0</v>
+      </c>
+      <c r="BR26">
+        <v>0</v>
+      </c>
+      <c r="BS26">
+        <v>0</v>
+      </c>
+      <c r="BT26">
+        <v>0</v>
+      </c>
+      <c r="BU26">
+        <v>0</v>
+      </c>
+      <c r="BV26">
+        <v>0</v>
+      </c>
+      <c r="BW26">
+        <v>0</v>
+      </c>
+      <c r="BX26">
+        <v>0</v>
+      </c>
+      <c r="BY26">
+        <v>0</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27">
+        <v>1.66</v>
+      </c>
+      <c r="G27">
+        <v>3.05</v>
+      </c>
+      <c r="H27">
+        <v>2.4</v>
+      </c>
+      <c r="I27">
+        <v>4.2</v>
+      </c>
+      <c r="J27">
+        <v>3.95</v>
+      </c>
+      <c r="K27">
+        <v>6.2</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>1.24</v>
+      </c>
+      <c r="Q27">
+        <v>1.01</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28">
+        <v>1.85</v>
+      </c>
+      <c r="G28">
         <v>1.92</v>
       </c>
-      <c r="H11">
+      <c r="H28">
         <v>6</v>
       </c>
-      <c r="I11">
+      <c r="I28">
         <v>6.8</v>
       </c>
-      <c r="J11">
+      <c r="J28">
         <v>3.05</v>
       </c>
-      <c r="K11">
-        <v>3.45</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
+      <c r="K28">
+        <v>3.4</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
         <v>1.42</v>
       </c>
-      <c r="Q11">
+      <c r="Q28">
         <v>2.88</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11">
-        <v>0</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>0</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11">
-        <v>0</v>
-      </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11">
-        <v>0</v>
-      </c>
-      <c r="BS11">
-        <v>0</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
-      <c r="BY11">
-        <v>0</v>
-      </c>
-      <c r="BZ11">
-        <v>0</v>
-      </c>
-      <c r="CA11">
-        <v>0</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>116</v>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
+      <c r="AW28">
+        <v>0</v>
+      </c>
+      <c r="AX28">
+        <v>0</v>
+      </c>
+      <c r="AY28">
+        <v>0</v>
+      </c>
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+      <c r="BA28">
+        <v>0</v>
+      </c>
+      <c r="BB28">
+        <v>0</v>
+      </c>
+      <c r="BC28">
+        <v>0</v>
+      </c>
+      <c r="BD28">
+        <v>0</v>
+      </c>
+      <c r="BE28">
+        <v>0</v>
+      </c>
+      <c r="BF28">
+        <v>0</v>
+      </c>
+      <c r="BG28">
+        <v>0</v>
+      </c>
+      <c r="BH28">
+        <v>0</v>
+      </c>
+      <c r="BI28">
+        <v>0</v>
+      </c>
+      <c r="BJ28">
+        <v>0</v>
+      </c>
+      <c r="BK28">
+        <v>0</v>
+      </c>
+      <c r="BL28">
+        <v>0</v>
+      </c>
+      <c r="BM28">
+        <v>0</v>
+      </c>
+      <c r="BN28">
+        <v>0</v>
+      </c>
+      <c r="BO28">
+        <v>0</v>
+      </c>
+      <c r="BP28">
+        <v>0</v>
+      </c>
+      <c r="BQ28">
+        <v>0</v>
+      </c>
+      <c r="BR28">
+        <v>0</v>
+      </c>
+      <c r="BS28">
+        <v>0</v>
+      </c>
+      <c r="BT28">
+        <v>0</v>
+      </c>
+      <c r="BU28">
+        <v>0</v>
+      </c>
+      <c r="BV28">
+        <v>0</v>
+      </c>
+      <c r="BW28">
+        <v>0</v>
+      </c>
+      <c r="BX28">
+        <v>0</v>
+      </c>
+      <c r="BY28">
+        <v>0</v>
+      </c>
+      <c r="BZ28">
+        <v>0</v>
+      </c>
+      <c r="CA28">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="201">
   <si>
     <t>League</t>
   </si>
@@ -457,21 +457,21 @@
     <t>Arges Pitesti</t>
   </si>
   <si>
+    <t>Kerry FC</t>
+  </si>
+  <si>
+    <t>St Patricks</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>St Patricks</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Kerry FC</t>
-  </si>
-  <si>
     <t>Odra Opole</t>
   </si>
   <si>
@@ -490,6 +490,9 @@
     <t>Vikingur Reykjavik</t>
   </si>
   <si>
+    <t>Hviti Riddarinn</t>
+  </si>
+  <si>
     <t>Alianza Atletico</t>
   </si>
   <si>
@@ -574,21 +577,21 @@
     <t>ACS Petrolul 52</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Arka Gdynia</t>
   </si>
   <si>
@@ -607,10 +610,13 @@
     <t>Keflavik</t>
   </si>
   <si>
+    <t>Kari</t>
+  </si>
+  <si>
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-07-22 17:04:10</t>
+    <t>2026-07-22 19:12:56</t>
   </si>
 </sst>
 </file>
@@ -942,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB40"/>
+  <dimension ref="A1:CB41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1201,7 +1207,7 @@
         <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F2">
         <v>1.86</v>
@@ -1216,13 +1222,13 @@
         <v>5.2</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1234,10 +1240,10 @@
         <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1426,7 +1432,7 @@
         <v>9.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1443,10 +1449,10 @@
         <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G3">
         <v>2.74</v>
@@ -1455,7 +1461,7 @@
         <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
         <v>2.94</v>
@@ -1464,7 +1470,7 @@
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.13</v>
@@ -1494,7 +1500,7 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
         <v>1.57</v>
@@ -1503,7 +1509,7 @@
         <v>10</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1563,7 +1569,7 @@
         <v>18.5</v>
       </c>
       <c r="AS3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
@@ -1575,7 +1581,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
@@ -1587,7 +1593,7 @@
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
         <v>34</v>
@@ -1596,16 +1602,16 @@
         <v>30</v>
       </c>
       <c r="BD3">
+        <v>7.4</v>
+      </c>
+      <c r="BE3">
+        <v>8</v>
+      </c>
+      <c r="BF3">
         <v>7</v>
       </c>
-      <c r="BE3">
+      <c r="BG3">
         <v>7.4</v>
-      </c>
-      <c r="BF3">
-        <v>6.6</v>
-      </c>
-      <c r="BG3">
-        <v>7</v>
       </c>
       <c r="BH3">
         <v>2.78</v>
@@ -1668,7 +1674,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1685,7 +1691,7 @@
         <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F4">
         <v>1.96</v>
@@ -1721,7 +1727,7 @@
         <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R4">
         <v>1.18</v>
@@ -1745,7 +1751,7 @@
         <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1835,7 +1841,7 @@
         <v>21</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD4">
         <v>34</v>
@@ -1910,7 +1916,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1927,7 +1933,7 @@
         <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F5">
         <v>3.2</v>
@@ -1936,13 +1942,13 @@
         <v>3.7</v>
       </c>
       <c r="H5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I5">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
         <v>3.65</v>
@@ -1960,10 +1966,10 @@
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.25</v>
@@ -1978,7 +1984,7 @@
         <v>1.52</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W5">
         <v>1.37</v>
@@ -2152,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2169,10 +2175,10 @@
         <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G6">
         <v>1.67</v>
@@ -2184,7 +2190,7 @@
         <v>6.8</v>
       </c>
       <c r="J6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
         <v>5</v>
@@ -2211,7 +2217,7 @@
         <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
         <v>1.76</v>
@@ -2229,10 +2235,10 @@
         <v>24</v>
       </c>
       <c r="Y6">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z6">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AA6">
         <v>180</v>
@@ -2247,7 +2253,7 @@
         <v>25</v>
       </c>
       <c r="AE6">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>11</v>
@@ -2259,7 +2265,7 @@
         <v>21</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ6">
         <v>16</v>
@@ -2268,7 +2274,7 @@
         <v>16.5</v>
       </c>
       <c r="AL6">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AM6">
         <v>110</v>
@@ -2277,7 +2283,7 @@
         <v>7.8</v>
       </c>
       <c r="AO6">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP6">
         <v>15.5</v>
@@ -2286,7 +2292,7 @@
         <v>20</v>
       </c>
       <c r="AR6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="AS6">
         <v>9</v>
@@ -2298,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="AV6">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="AW6">
         <v>8.4</v>
@@ -2322,7 +2328,7 @@
         <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BE6">
         <v>8.6</v>
@@ -2394,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2411,7 +2417,7 @@
         <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F7">
         <v>2.14</v>
@@ -2447,7 +2453,7 @@
         <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R7">
         <v>1.3</v>
@@ -2477,7 +2483,7 @@
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2504,7 +2510,7 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK7">
         <v>29</v>
@@ -2543,7 +2549,7 @@
         <v>12</v>
       </c>
       <c r="AW7">
-        <v>38</v>
+        <v>5.1</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2564,7 +2570,7 @@
         <v>19</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="BE7">
         <v>5.3</v>
@@ -2636,7 +2642,7 @@
         <v>7.8</v>
       </c>
       <c r="CB7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2653,10 +2659,10 @@
         <v>126</v>
       </c>
       <c r="E8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F8">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G8">
         <v>2.02</v>
@@ -2665,10 +2671,10 @@
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K8">
         <v>4.5</v>
@@ -2704,7 +2710,7 @@
         <v>2.26</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8">
         <v>1.98</v>
@@ -2719,7 +2725,7 @@
         <v>42</v>
       </c>
       <c r="AA8">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB8">
         <v>14</v>
@@ -2770,10 +2776,10 @@
         <v>13.5</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT8">
         <v>8.4</v>
@@ -2785,7 +2791,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX8">
         <v>9.800000000000001</v>
@@ -2797,7 +2803,7 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB8">
         <v>15.5</v>
@@ -2809,25 +2815,25 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF8">
         <v>7.6</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH8">
         <v>4.2</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
         <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2839,13 +2845,13 @@
         <v>5</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BP8">
         <v>13</v>
       </c>
       <c r="BQ8">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR8">
         <v>25</v>
@@ -2857,7 +2863,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
         <v>34</v>
@@ -2878,7 +2884,7 @@
         <v>6.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2895,49 +2901,49 @@
         <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F9">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="H9">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I9">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J9">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
         <v>1.48</v>
@@ -2946,28 +2952,28 @@
         <v>1.84</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X9">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB9">
         <v>17.5</v>
       </c>
       <c r="AC9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD9">
         <v>18.5</v>
@@ -2985,28 +2991,28 @@
         <v>24</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP9">
-        <v>9.6</v>
+        <v>2.42</v>
       </c>
       <c r="AQ9">
         <v>7.8</v>
@@ -3015,7 +3021,7 @@
         <v>12</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AT9">
         <v>7.4</v>
@@ -3039,31 +3045,31 @@
         <v>10</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH9">
         <v>4.4</v>
       </c>
       <c r="BI9">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
@@ -3120,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3137,7 +3143,7 @@
         <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F10">
         <v>3.15</v>
@@ -3170,7 +3176,7 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q10">
         <v>1.69</v>
@@ -3179,13 +3185,13 @@
         <v>1.5</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
         <v>1.74</v>
@@ -3206,10 +3212,10 @@
         <v>30</v>
       </c>
       <c r="AB10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD10">
         <v>14</v>
@@ -3218,31 +3224,31 @@
         <v>27</v>
       </c>
       <c r="AF10">
+        <v>30</v>
+      </c>
+      <c r="AG10">
+        <v>15</v>
+      </c>
+      <c r="AH10">
+        <v>16.5</v>
+      </c>
+      <c r="AI10">
         <v>32</v>
-      </c>
-      <c r="AG10">
-        <v>17.5</v>
-      </c>
-      <c r="AH10">
-        <v>19</v>
-      </c>
-      <c r="AI10">
-        <v>38</v>
       </c>
       <c r="AJ10">
         <v>65</v>
       </c>
       <c r="AK10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL10">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM10">
         <v>80</v>
       </c>
       <c r="AN10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO10">
         <v>16</v>
@@ -3257,7 +3263,7 @@
         <v>14</v>
       </c>
       <c r="AS10">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
         <v>13.5</v>
@@ -3281,61 +3287,61 @@
         <v>13</v>
       </c>
       <c r="BA10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB10">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD10">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF10">
         <v>18</v>
       </c>
       <c r="BG10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH10">
         <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10">
+        <v>9.4</v>
+      </c>
+      <c r="BK10">
+        <v>6.8</v>
+      </c>
+      <c r="BL10">
+        <v>90</v>
+      </c>
+      <c r="BM10">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BK10">
-        <v>5.6</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>9.6</v>
       </c>
       <c r="BN10">
         <v>7</v>
       </c>
       <c r="BO10">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP10">
         <v>25</v>
       </c>
       <c r="BQ10">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
         <v>32</v>
       </c>
       <c r="BS10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
         <v>5.6</v>
@@ -3344,16 +3350,16 @@
         <v>4.7</v>
       </c>
       <c r="BV10">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW10">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
         <v>26</v>
       </c>
       <c r="BY10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3362,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3379,7 +3385,7 @@
         <v>129</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F11">
         <v>1.66</v>
@@ -3418,7 +3424,7 @@
         <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
         <v>2.64</v>
@@ -3502,10 +3508,10 @@
         <v>4.4</v>
       </c>
       <c r="AT11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
         <v>15</v>
@@ -3604,7 +3610,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3621,7 +3627,7 @@
         <v>130</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F12">
         <v>1.61</v>
@@ -3630,22 +3636,22 @@
         <v>1.77</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
         <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
         <v>1.1</v>
@@ -3657,13 +3663,13 @@
         <v>2.02</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="R12">
         <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="T12">
         <v>1.81</v>
@@ -3672,7 +3678,7 @@
         <v>2</v>
       </c>
       <c r="V12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12">
         <v>2.28</v>
@@ -3846,7 +3852,7 @@
         <v>6.8</v>
       </c>
       <c r="CB12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3863,7 +3869,7 @@
         <v>131</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F13">
         <v>1.49</v>
@@ -3872,7 +3878,7 @@
         <v>1.61</v>
       </c>
       <c r="H13">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I13">
         <v>7.8</v>
@@ -3881,7 +3887,7 @@
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3896,7 +3902,7 @@
         <v>1.23</v>
       </c>
       <c r="P13">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q13">
         <v>1.57</v>
@@ -3905,7 +3911,7 @@
         <v>1.48</v>
       </c>
       <c r="S13">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="T13">
         <v>1.81</v>
@@ -3920,7 +3926,7 @@
         <v>2.62</v>
       </c>
       <c r="X13">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y13">
         <v>27</v>
@@ -3977,55 +3983,55 @@
         <v>6.2</v>
       </c>
       <c r="AQ13">
+        <v>6.6</v>
+      </c>
+      <c r="AR13">
+        <v>7.6</v>
+      </c>
+      <c r="AS13">
+        <v>8.4</v>
+      </c>
+      <c r="AT13">
+        <v>4.6</v>
+      </c>
+      <c r="AU13">
+        <v>4.9</v>
+      </c>
+      <c r="AV13">
+        <v>6.6</v>
+      </c>
+      <c r="AW13">
+        <v>8</v>
+      </c>
+      <c r="AX13">
+        <v>4.7</v>
+      </c>
+      <c r="AY13">
+        <v>4.7</v>
+      </c>
+      <c r="AZ13">
         <v>6.2</v>
       </c>
-      <c r="AR13">
-        <v>7.2</v>
-      </c>
-      <c r="AS13">
+      <c r="BA13">
         <v>8</v>
       </c>
-      <c r="AT13">
-        <v>4.5</v>
-      </c>
-      <c r="AU13">
-        <v>4.8</v>
-      </c>
-      <c r="AV13">
-        <v>6.2</v>
-      </c>
-      <c r="AW13">
-        <v>7.6</v>
-      </c>
-      <c r="AX13">
-        <v>4.6</v>
-      </c>
-      <c r="AY13">
-        <v>4.6</v>
-      </c>
-      <c r="AZ13">
-        <v>6</v>
-      </c>
-      <c r="BA13">
-        <v>7.6</v>
-      </c>
       <c r="BB13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC13">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BD13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BG13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4088,7 +4094,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4105,7 +4111,7 @@
         <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F14">
         <v>2.06</v>
@@ -4117,7 +4123,7 @@
         <v>3.3</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -4141,13 +4147,13 @@
         <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R14">
         <v>1.45</v>
       </c>
       <c r="S14">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T14">
         <v>1.63</v>
@@ -4159,7 +4165,7 @@
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X14">
         <v>23</v>
@@ -4216,13 +4222,13 @@
         <v>38</v>
       </c>
       <c r="AP14">
+        <v>16</v>
+      </c>
+      <c r="AQ14">
         <v>13.5</v>
       </c>
-      <c r="AQ14">
-        <v>11.5</v>
-      </c>
       <c r="AR14">
-        <v>19.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS14">
         <v>4</v>
@@ -4234,28 +4240,28 @@
         <v>6.6</v>
       </c>
       <c r="AV14">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW14">
         <v>3.85</v>
       </c>
       <c r="AX14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY14">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
         <v>3.9</v>
       </c>
       <c r="BB14">
-        <v>19.5</v>
+        <v>3.75</v>
       </c>
       <c r="BC14">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD14">
         <v>3.8</v>
@@ -4264,7 +4270,7 @@
         <v>4</v>
       </c>
       <c r="BF14">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BG14">
         <v>3.8</v>
@@ -4330,7 +4336,7 @@
         <v>7.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4347,22 +4353,22 @@
         <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F15">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="G15">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H15">
         <v>2.72</v>
       </c>
       <c r="I15">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
         <v>3.9</v>
@@ -4380,10 +4386,10 @@
         <v>1.29</v>
       </c>
       <c r="P15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R15">
         <v>1.37</v>
@@ -4398,7 +4404,7 @@
         <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
         <v>1.55</v>
@@ -4458,34 +4464,34 @@
         <v>36</v>
       </c>
       <c r="AP15">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS15">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT15">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15">
         <v>7</v>
       </c>
       <c r="AV15">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX15">
         <v>15.5</v>
       </c>
       <c r="AY15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
         <v>14</v>
@@ -4494,10 +4500,10 @@
         <v>5.9</v>
       </c>
       <c r="BB15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC15">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD15">
         <v>5.7</v>
@@ -4509,7 +4515,7 @@
         <v>19</v>
       </c>
       <c r="BG15">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BH15">
         <v>3.65</v>
@@ -4554,7 +4560,7 @@
         <v>4.5</v>
       </c>
       <c r="BV15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
         <v>7.4</v>
@@ -4566,13 +4572,13 @@
         <v>8.4</v>
       </c>
       <c r="BZ15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>7.8</v>
       </c>
       <c r="CB15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4589,7 +4595,7 @@
         <v>134</v>
       </c>
       <c r="E16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F16">
         <v>1.58</v>
@@ -4622,7 +4628,7 @@
         <v>1.19</v>
       </c>
       <c r="P16">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q16">
         <v>1.57</v>
@@ -4637,7 +4643,7 @@
         <v>1.69</v>
       </c>
       <c r="U16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V16">
         <v>1.18</v>
@@ -4646,13 +4652,13 @@
         <v>2.68</v>
       </c>
       <c r="X16">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y16">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="Z16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA16">
         <v>180</v>
@@ -4664,10 +4670,10 @@
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AE16">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF16">
         <v>12</v>
@@ -4676,10 +4682,10 @@
         <v>10.5</v>
       </c>
       <c r="AH16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI16">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
         <v>16</v>
@@ -4688,28 +4694,28 @@
         <v>16</v>
       </c>
       <c r="AL16">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM16">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN16">
         <v>6.4</v>
       </c>
       <c r="AO16">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP16">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR16">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AS16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT16">
         <v>10</v>
@@ -4721,7 +4727,7 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX16">
         <v>9.800000000000001</v>
@@ -4733,7 +4739,7 @@
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB16">
         <v>13</v>
@@ -4745,76 +4751,76 @@
         <v>22</v>
       </c>
       <c r="BE16">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF16">
         <v>5.7</v>
       </c>
       <c r="BG16">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH16">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BN16">
         <v>6</v>
       </c>
       <c r="BO16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="BP16">
         <v>13.5</v>
       </c>
       <c r="BQ16">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="BR16">
         <v>30</v>
       </c>
       <c r="BS16">
-        <v>2.72</v>
+        <v>1.88</v>
       </c>
       <c r="BT16">
         <v>14.5</v>
       </c>
       <c r="BU16">
-        <v>2.48</v>
+        <v>1.76</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="BZ16">
         <v>19</v>
       </c>
       <c r="CA16">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="CB16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4831,7 +4837,7 @@
         <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F17">
         <v>2.14</v>
@@ -4840,16 +4846,16 @@
         <v>2.26</v>
       </c>
       <c r="H17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J17">
         <v>3.75</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4858,10 +4864,10 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O17">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P17">
         <v>2.26</v>
@@ -4876,10 +4882,10 @@
         <v>2.7</v>
       </c>
       <c r="T17">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U17">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="V17">
         <v>1.39</v>
@@ -4888,118 +4894,118 @@
         <v>1.79</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y17">
+        <v>19</v>
+      </c>
+      <c r="Z17">
+        <v>30</v>
+      </c>
+      <c r="AA17">
+        <v>65</v>
+      </c>
+      <c r="AB17">
+        <v>15</v>
+      </c>
+      <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>17</v>
+      </c>
+      <c r="AE17">
+        <v>38</v>
+      </c>
+      <c r="AF17">
+        <v>18.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>18.5</v>
+      </c>
+      <c r="AI17">
+        <v>46</v>
+      </c>
+      <c r="AJ17">
+        <v>34</v>
+      </c>
+      <c r="AK17">
+        <v>25</v>
+      </c>
+      <c r="AL17">
+        <v>36</v>
+      </c>
+      <c r="AM17">
+        <v>80</v>
+      </c>
+      <c r="AN17">
+        <v>15</v>
+      </c>
+      <c r="AO17">
+        <v>30</v>
+      </c>
+      <c r="AP17">
+        <v>15.5</v>
+      </c>
+      <c r="AQ17">
+        <v>12.5</v>
+      </c>
+      <c r="AR17">
+        <v>21</v>
+      </c>
+      <c r="AS17">
+        <v>4.8</v>
+      </c>
+      <c r="AT17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU17">
+        <v>7.2</v>
+      </c>
+      <c r="AV17">
+        <v>11</v>
+      </c>
+      <c r="AW17">
+        <v>4.5</v>
+      </c>
+      <c r="AX17">
+        <v>12</v>
+      </c>
+      <c r="AY17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17">
+        <v>12</v>
+      </c>
+      <c r="BA17">
+        <v>4.7</v>
+      </c>
+      <c r="BB17">
+        <v>21</v>
+      </c>
+      <c r="BC17">
+        <v>16.5</v>
+      </c>
+      <c r="BD17">
+        <v>4.5</v>
+      </c>
+      <c r="BE17">
+        <v>4.9</v>
+      </c>
+      <c r="BF17">
+        <v>10</v>
+      </c>
+      <c r="BG17">
         <v>20</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>11</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17">
-        <v>1.03</v>
-      </c>
-      <c r="AR17">
-        <v>1.03</v>
-      </c>
-      <c r="AS17">
-        <v>1.03</v>
-      </c>
-      <c r="AT17">
-        <v>1.03</v>
-      </c>
-      <c r="AU17">
-        <v>1.03</v>
-      </c>
-      <c r="AV17">
-        <v>1.03</v>
-      </c>
-      <c r="AW17">
-        <v>1.03</v>
-      </c>
-      <c r="AX17">
-        <v>1.03</v>
-      </c>
-      <c r="AY17">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17">
-        <v>1.03</v>
-      </c>
-      <c r="BA17">
-        <v>1.03</v>
-      </c>
-      <c r="BB17">
-        <v>1.03</v>
-      </c>
-      <c r="BC17">
-        <v>1.03</v>
-      </c>
-      <c r="BD17">
-        <v>1.03</v>
-      </c>
-      <c r="BE17">
-        <v>1.03</v>
-      </c>
-      <c r="BF17">
-        <v>1.01</v>
-      </c>
-      <c r="BG17">
-        <v>1.01</v>
       </c>
       <c r="BH17">
         <v>5.3</v>
       </c>
       <c r="BI17">
-        <v>2.86</v>
+        <v>1.97</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>
@@ -5017,7 +5023,7 @@
         <v>7.4</v>
       </c>
       <c r="BO17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP17">
         <v>21</v>
@@ -5056,7 +5062,7 @@
         <v>2.78</v>
       </c>
       <c r="CB17" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5073,10 +5079,10 @@
         <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F18">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G18">
         <v>1.99</v>
@@ -5088,10 +5094,10 @@
         <v>4.4</v>
       </c>
       <c r="J18">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K18">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5100,16 +5106,16 @@
         <v>1.05</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18">
         <v>1.23</v>
       </c>
       <c r="P18">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q18">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R18">
         <v>1.5</v>
@@ -5154,7 +5160,7 @@
         <v>60</v>
       </c>
       <c r="AF18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG18">
         <v>13</v>
@@ -5205,7 +5211,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX18">
         <v>11</v>
@@ -5217,7 +5223,7 @@
         <v>14</v>
       </c>
       <c r="BA18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB18">
         <v>18.5</v>
@@ -5229,7 +5235,7 @@
         <v>4</v>
       </c>
       <c r="BE18">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF18">
         <v>7.8</v>
@@ -5259,7 +5265,7 @@
         <v>6.6</v>
       </c>
       <c r="BO18">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP18">
         <v>18.5</v>
@@ -5298,7 +5304,7 @@
         <v>1.8</v>
       </c>
       <c r="CB18" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5315,7 +5321,7 @@
         <v>137</v>
       </c>
       <c r="E19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F19">
         <v>1.66</v>
@@ -5327,7 +5333,7 @@
         <v>4.3</v>
       </c>
       <c r="I19">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J19">
         <v>4.7</v>
@@ -5357,16 +5363,16 @@
         <v>1.96</v>
       </c>
       <c r="S19">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="U19">
         <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
         <v>2.24</v>
@@ -5393,7 +5399,7 @@
         <v>1000</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF19">
         <v>1000</v>
@@ -5420,67 +5426,67 @@
         <v>1000</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO19">
         <v>1000</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BH19">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI19">
         <v>3.95</v>
@@ -5501,7 +5507,7 @@
         <v>7.6</v>
       </c>
       <c r="BO19">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP19">
         <v>15</v>
@@ -5540,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5557,7 +5563,7 @@
         <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F20">
         <v>1.57</v>
@@ -5572,7 +5578,7 @@
         <v>6</v>
       </c>
       <c r="J20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K20">
         <v>5.4</v>
@@ -5605,7 +5611,7 @@
         <v>1.52</v>
       </c>
       <c r="U20">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V20">
         <v>1.2</v>
@@ -5668,22 +5674,22 @@
         <v>38</v>
       </c>
       <c r="AP20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
         <v>11.5</v>
       </c>
       <c r="AU20">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AV20">
         <v>17</v>
@@ -5692,22 +5698,22 @@
         <v>40</v>
       </c>
       <c r="AX20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY20">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20">
+        <v>14</v>
+      </c>
+      <c r="BA20">
+        <v>7.6</v>
+      </c>
+      <c r="BB20">
+        <v>15</v>
+      </c>
+      <c r="BC20">
         <v>12.5</v>
-      </c>
-      <c r="BA20">
-        <v>1.01</v>
-      </c>
-      <c r="BB20">
-        <v>13.5</v>
-      </c>
-      <c r="BC20">
-        <v>11.5</v>
       </c>
       <c r="BD20">
         <v>19.5</v>
@@ -5719,7 +5725,7 @@
         <v>4.7</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5782,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5799,25 +5805,25 @@
         <v>139</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F21">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G21">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H21">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I21">
         <v>2.82</v>
       </c>
       <c r="J21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K21">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -5829,19 +5835,19 @@
         <v>1.1</v>
       </c>
       <c r="O21">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R21">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S21">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="T21">
         <v>1.11</v>
@@ -5910,52 +5916,52 @@
         <v>1000</v>
       </c>
       <c r="AP21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
         <v>1.01</v>
@@ -6024,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6041,31 +6047,31 @@
         <v>140</v>
       </c>
       <c r="E22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F22">
         <v>2.18</v>
       </c>
       <c r="G22">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H22">
         <v>3.05</v>
       </c>
       <c r="I22">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J22">
         <v>3.7</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22">
         <v>4.5</v>
@@ -6074,16 +6080,16 @@
         <v>1.21</v>
       </c>
       <c r="P22">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S22">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T22">
         <v>1.11</v>
@@ -6092,10 +6098,10 @@
         <v>1.11</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6152,52 +6158,52 @@
         <v>1000</v>
       </c>
       <c r="AP22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
         <v>1.01</v>
@@ -6209,7 +6215,7 @@
         <v>5.2</v>
       </c>
       <c r="BI22">
-        <v>2.84</v>
+        <v>2</v>
       </c>
       <c r="BJ22">
         <v>12</v>
@@ -6227,7 +6233,7 @@
         <v>7.4</v>
       </c>
       <c r="BO22">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP22">
         <v>21</v>
@@ -6266,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6283,7 +6289,7 @@
         <v>141</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F23">
         <v>3.05</v>
@@ -6295,142 +6301,142 @@
         <v>2.1</v>
       </c>
       <c r="I23">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="J23">
         <v>3.95</v>
       </c>
       <c r="K23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L23">
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="O23">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P23">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="Q23">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="R23">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="S23">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="T23">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="V23">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W23">
         <v>1.4</v>
       </c>
       <c r="X23">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Y23">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Z23">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AA23">
         <v>40</v>
       </c>
       <c r="AB23">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AC23">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AD23">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AE23">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AF23">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AG23">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AH23">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AI23">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK23">
         <v>46</v>
       </c>
       <c r="AL23">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO23">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AP23">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR23">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="AS23">
         <v>16.5</v>
       </c>
       <c r="AT23">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AU23">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AW23">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AX23">
         <v>16.5</v>
       </c>
       <c r="AY23">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AZ23">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BA23">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BB23">
-        <v>2.34</v>
+        <v>30</v>
       </c>
       <c r="BC23">
         <v>17.5</v>
@@ -6439,31 +6445,31 @@
         <v>18.5</v>
       </c>
       <c r="BE23">
-        <v>2.34</v>
+        <v>28</v>
       </c>
       <c r="BF23">
-        <v>2.34</v>
+        <v>14.5</v>
       </c>
       <c r="BG23">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH23">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BI23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ23">
         <v>12</v>
       </c>
       <c r="BK23">
-        <v>2.36</v>
+        <v>5.3</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BN23">
         <v>10</v>
@@ -6472,43 +6478,43 @@
         <v>4.6</v>
       </c>
       <c r="BP23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ23">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BR23">
         <v>38</v>
       </c>
       <c r="BS23">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BT23">
         <v>8</v>
       </c>
       <c r="BU23">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BV23">
         <v>20</v>
       </c>
       <c r="BW23">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BX23">
         <v>30</v>
       </c>
       <c r="BY23">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BZ23">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA23">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CB23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6525,7 +6531,7 @@
         <v>142</v>
       </c>
       <c r="E24" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F24">
         <v>1.65</v>
@@ -6540,10 +6546,10 @@
         <v>7</v>
       </c>
       <c r="J24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>1.4</v>
@@ -6558,7 +6564,7 @@
         <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q24">
         <v>2.02</v>
@@ -6624,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="AL24">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM24">
         <v>170</v>
@@ -6642,7 +6648,7 @@
         <v>15</v>
       </c>
       <c r="AR24">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="AS24">
         <v>9.4</v>
@@ -6657,7 +6663,7 @@
         <v>20</v>
       </c>
       <c r="AW24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX24">
         <v>8.199999999999999</v>
@@ -6681,7 +6687,7 @@
         <v>8</v>
       </c>
       <c r="BE24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF24">
         <v>10</v>
@@ -6711,7 +6717,7 @@
         <v>5.5</v>
       </c>
       <c r="BO24">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="BP24">
         <v>16</v>
@@ -6750,7 +6756,7 @@
         <v>1.78</v>
       </c>
       <c r="CB24" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6767,19 +6773,19 @@
         <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F25">
         <v>2.14</v>
       </c>
       <c r="G25">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H25">
         <v>2.96</v>
       </c>
       <c r="I25">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J25">
         <v>3.8</v>
@@ -6794,10 +6800,10 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P25">
         <v>2.5</v>
@@ -6818,10 +6824,10 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -6878,58 +6884,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AQ25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AR25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AS25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AT25">
         <v>11</v>
       </c>
       <c r="AU25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AV25">
         <v>10.5</v>
       </c>
       <c r="AW25">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AX25">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AY25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25">
         <v>11</v>
       </c>
       <c r="BA25">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="BB25">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="BC25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BD25">
         <v>19</v>
       </c>
       <c r="BE25">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -6992,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7009,7 +7015,7 @@
         <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F26">
         <v>4.9</v>
@@ -7024,7 +7030,7 @@
         <v>1.71</v>
       </c>
       <c r="J26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K26">
         <v>5.4</v>
@@ -7036,7 +7042,7 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>2.74</v>
+        <v>1.1</v>
       </c>
       <c r="O26">
         <v>1.13</v>
@@ -7045,13 +7051,13 @@
         <v>2.74</v>
       </c>
       <c r="Q26">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S26">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="T26">
         <v>1.11</v>
@@ -7063,7 +7069,7 @@
         <v>2.4</v>
       </c>
       <c r="W26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7078,7 +7084,7 @@
         <v>23</v>
       </c>
       <c r="AB26">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AC26">
         <v>17</v>
@@ -7090,10 +7096,10 @@
         <v>21</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG26">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AH26">
         <v>25</v>
@@ -7105,22 +7111,22 @@
         <v>1000</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM26">
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AP26">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="AQ26">
         <v>8.800000000000001</v>
@@ -7144,7 +7150,7 @@
         <v>9.6</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AY26">
         <v>14</v>
@@ -7156,28 +7162,28 @@
         <v>16</v>
       </c>
       <c r="BB26">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BD26">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BE26">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH26">
         <v>6.4</v>
       </c>
       <c r="BI26">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="BJ26">
         <v>12.5</v>
@@ -7213,7 +7219,7 @@
         <v>6.4</v>
       </c>
       <c r="BU26">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV26">
         <v>13.5</v>
@@ -7234,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7251,10 +7257,10 @@
         <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G27">
         <v>3.45</v>
@@ -7263,13 +7269,13 @@
         <v>2.54</v>
       </c>
       <c r="I27">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J27">
         <v>3.2</v>
       </c>
       <c r="K27">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L27">
         <v>1.38</v>
@@ -7278,22 +7284,22 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O27">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="P27">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q27">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R27">
         <v>1.24</v>
       </c>
       <c r="S27">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T27">
         <v>1.11</v>
@@ -7302,7 +7308,7 @@
         <v>1.11</v>
       </c>
       <c r="V27">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
         <v>1.41</v>
@@ -7356,64 +7362,64 @@
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO27">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP27">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AQ27">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="AR27">
         <v>11</v>
       </c>
       <c r="AS27">
+        <v>2.84</v>
+      </c>
+      <c r="AT27">
         <v>2.5</v>
       </c>
-      <c r="AT27">
-        <v>2.24</v>
-      </c>
       <c r="AU27">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AV27">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="AW27">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AX27">
         <v>14.5</v>
       </c>
       <c r="AY27">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AZ27">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="BA27">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BB27">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BC27">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="BD27">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="BE27">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="BF27">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="BG27">
-        <v>2.62</v>
+        <v>17.5</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7437,7 +7443,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO27">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP27">
         <v>34</v>
@@ -7455,7 +7461,7 @@
         <v>7.6</v>
       </c>
       <c r="BU27">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV27">
         <v>29</v>
@@ -7476,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7493,7 +7499,7 @@
         <v>146</v>
       </c>
       <c r="E28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F28">
         <v>2.36</v>
@@ -7505,19 +7511,19 @@
         <v>3.55</v>
       </c>
       <c r="I28">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L28">
         <v>1.47</v>
       </c>
       <c r="M28">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N28">
         <v>2.58</v>
@@ -7529,7 +7535,7 @@
         <v>1.53</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R28">
         <v>1.2</v>
@@ -7547,7 +7553,7 @@
         <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X28">
         <v>11</v>
@@ -7556,7 +7562,7 @@
         <v>11</v>
       </c>
       <c r="Z28">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AA28">
         <v>110</v>
@@ -7571,7 +7577,7 @@
         <v>17.5</v>
       </c>
       <c r="AE28">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AF28">
         <v>14</v>
@@ -7580,25 +7586,25 @@
         <v>13</v>
       </c>
       <c r="AH28">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI28">
         <v>100</v>
       </c>
       <c r="AJ28">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AK28">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL28">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AM28">
         <v>220</v>
       </c>
       <c r="AN28">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AO28">
         <v>110</v>
@@ -7610,7 +7616,7 @@
         <v>9</v>
       </c>
       <c r="AR28">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AS28">
         <v>7.4</v>
@@ -7640,13 +7646,13 @@
         <v>7.4</v>
       </c>
       <c r="BB28">
-        <v>24</v>
+        <v>6.4</v>
       </c>
       <c r="BC28">
         <v>6.4</v>
       </c>
       <c r="BD28">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="BE28">
         <v>7.6</v>
@@ -7697,7 +7703,7 @@
         <v>7.4</v>
       </c>
       <c r="BU28">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -7718,7 +7724,7 @@
         <v>9</v>
       </c>
       <c r="CB28" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7735,97 +7741,97 @@
         <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F29">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="G29">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="H29">
-        <v>1.95</v>
+        <v>4.5</v>
       </c>
       <c r="I29">
-        <v>2.52</v>
+        <v>6.2</v>
       </c>
       <c r="J29">
+        <v>3.7</v>
+      </c>
+      <c r="K29">
+        <v>4.3</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
         <v>3.45</v>
       </c>
-      <c r="K29">
-        <v>4.7</v>
-      </c>
-      <c r="L29">
-        <v>1.01</v>
-      </c>
-      <c r="M29">
-        <v>1.01</v>
-      </c>
-      <c r="N29">
-        <v>4.1</v>
-      </c>
       <c r="O29">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P29">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="Q29">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="R29">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S29">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U29">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V29">
-        <v>1.72</v>
+        <v>1.19</v>
       </c>
       <c r="W29">
-        <v>1.31</v>
+        <v>2.16</v>
       </c>
       <c r="X29">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y29">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB29">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC29">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD29">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE29">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG29">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ29">
         <v>1000</v>
@@ -7846,52 +7852,52 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR29">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS29">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT29">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU29">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV29">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW29">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX29">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY29">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF29">
         <v>1.01</v>
@@ -7900,67 +7906,67 @@
         <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI29">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BZ29">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="CB29" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -7977,7 +7983,7 @@
         <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F30">
         <v>1.58</v>
@@ -7986,7 +7992,7 @@
         <v>1.68</v>
       </c>
       <c r="H30">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I30">
         <v>6.6</v>
@@ -8010,22 +8016,22 @@
         <v>1.24</v>
       </c>
       <c r="P30">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q30">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S30">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="T30">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="U30">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V30">
         <v>1.17</v>
@@ -8202,7 +8208,7 @@
         <v>1.04</v>
       </c>
       <c r="CB30" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8219,7 +8225,7 @@
         <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F31">
         <v>2.7</v>
@@ -8246,22 +8252,22 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O31">
         <v>1.32</v>
       </c>
       <c r="P31">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S31">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8330,52 +8336,52 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31">
         <v>1.01</v>
@@ -8387,7 +8393,7 @@
         <v>4.1</v>
       </c>
       <c r="BI31">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31">
         <v>1000</v>
@@ -8444,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8461,22 +8467,22 @@
         <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F32">
         <v>2.58</v>
       </c>
       <c r="G32">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H32">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I32">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J32">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="K32">
         <v>4.6</v>
@@ -8488,22 +8494,22 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P32">
         <v>2.14</v>
       </c>
       <c r="Q32">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R32">
         <v>1.44</v>
       </c>
       <c r="S32">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T32">
         <v>1.11</v>
@@ -8512,10 +8518,10 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8572,52 +8578,52 @@
         <v>1000</v>
       </c>
       <c r="AP32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
         <v>1.01</v>
@@ -8686,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="CB32" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8703,232 +8709,232 @@
         <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F33">
-        <v>1.7</v>
+        <v>2.96</v>
       </c>
       <c r="G33">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="H33">
-        <v>4.7</v>
+        <v>1.97</v>
       </c>
       <c r="I33">
+        <v>2.38</v>
+      </c>
+      <c r="J33">
+        <v>3.5</v>
+      </c>
+      <c r="K33">
+        <v>4.1</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.04</v>
+      </c>
+      <c r="N33">
+        <v>4.1</v>
+      </c>
+      <c r="O33">
+        <v>1.22</v>
+      </c>
+      <c r="P33">
+        <v>1.96</v>
+      </c>
+      <c r="Q33">
+        <v>1.51</v>
+      </c>
+      <c r="R33">
+        <v>1.37</v>
+      </c>
+      <c r="S33">
+        <v>2.52</v>
+      </c>
+      <c r="T33">
+        <v>1.54</v>
+      </c>
+      <c r="U33">
+        <v>2.12</v>
+      </c>
+      <c r="V33">
+        <v>1.72</v>
+      </c>
+      <c r="W33">
+        <v>1.31</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>15.5</v>
+      </c>
+      <c r="Z33">
+        <v>21</v>
+      </c>
+      <c r="AA33">
+        <v>36</v>
+      </c>
+      <c r="AB33">
+        <v>21</v>
+      </c>
+      <c r="AC33">
+        <v>12</v>
+      </c>
+      <c r="AD33">
+        <v>15</v>
+      </c>
+      <c r="AE33">
+        <v>30</v>
+      </c>
+      <c r="AF33">
+        <v>34</v>
+      </c>
+      <c r="AG33">
+        <v>19.5</v>
+      </c>
+      <c r="AH33">
+        <v>22</v>
+      </c>
+      <c r="AI33">
+        <v>42</v>
+      </c>
+      <c r="AJ33">
+        <v>80</v>
+      </c>
+      <c r="AK33">
+        <v>50</v>
+      </c>
+      <c r="AL33">
+        <v>55</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>42</v>
+      </c>
+      <c r="AO33">
+        <v>18.5</v>
+      </c>
+      <c r="AP33">
+        <v>2.84</v>
+      </c>
+      <c r="AQ33">
+        <v>8</v>
+      </c>
+      <c r="AR33">
+        <v>10</v>
+      </c>
+      <c r="AS33">
+        <v>18</v>
+      </c>
+      <c r="AT33">
+        <v>10.5</v>
+      </c>
+      <c r="AU33">
         <v>6.2</v>
       </c>
-      <c r="J33">
-        <v>3.7</v>
-      </c>
-      <c r="K33">
-        <v>5</v>
-      </c>
-      <c r="L33">
-        <v>1.01</v>
-      </c>
-      <c r="M33">
-        <v>1.01</v>
-      </c>
-      <c r="N33">
-        <v>3.5</v>
-      </c>
-      <c r="O33">
-        <v>1.29</v>
-      </c>
-      <c r="P33">
-        <v>1.86</v>
-      </c>
-      <c r="Q33">
-        <v>1.89</v>
-      </c>
-      <c r="R33">
-        <v>1.31</v>
-      </c>
-      <c r="S33">
-        <v>3.2</v>
-      </c>
-      <c r="T33">
-        <v>1.11</v>
-      </c>
-      <c r="U33">
-        <v>1.11</v>
-      </c>
-      <c r="V33">
-        <v>1.19</v>
-      </c>
-      <c r="W33">
-        <v>2.1</v>
-      </c>
-      <c r="X33">
-        <v>1000</v>
-      </c>
-      <c r="Y33">
-        <v>1000</v>
-      </c>
-      <c r="Z33">
-        <v>1000</v>
-      </c>
-      <c r="AA33">
-        <v>1000</v>
-      </c>
-      <c r="AB33">
-        <v>1000</v>
-      </c>
-      <c r="AC33">
-        <v>1000</v>
-      </c>
-      <c r="AD33">
-        <v>1000</v>
-      </c>
-      <c r="AE33">
-        <v>1000</v>
-      </c>
-      <c r="AF33">
-        <v>1000</v>
-      </c>
-      <c r="AG33">
-        <v>1000</v>
-      </c>
-      <c r="AH33">
-        <v>1000</v>
-      </c>
-      <c r="AI33">
-        <v>1000</v>
-      </c>
-      <c r="AJ33">
-        <v>1000</v>
-      </c>
-      <c r="AK33">
-        <v>1000</v>
-      </c>
-      <c r="AL33">
-        <v>1000</v>
-      </c>
-      <c r="AM33">
-        <v>1000</v>
-      </c>
-      <c r="AN33">
-        <v>1000</v>
-      </c>
-      <c r="AO33">
-        <v>1000</v>
-      </c>
-      <c r="AP33">
-        <v>1.03</v>
-      </c>
-      <c r="AQ33">
-        <v>1.03</v>
-      </c>
-      <c r="AR33">
-        <v>1.03</v>
-      </c>
-      <c r="AS33">
-        <v>1.03</v>
-      </c>
-      <c r="AT33">
-        <v>1.03</v>
-      </c>
-      <c r="AU33">
-        <v>1.03</v>
-      </c>
       <c r="AV33">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AW33">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX33">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY33">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BA33">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BB33">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="BC33">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BD33">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="BE33">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="BF33">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG33">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH33">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI33">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33">
         <v>1000</v>
       </c>
       <c r="BK33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BL33">
         <v>1000</v>
       </c>
       <c r="BM33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BN33">
         <v>1000</v>
       </c>
       <c r="BO33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BP33">
         <v>1000</v>
       </c>
       <c r="BQ33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BR33">
         <v>1000</v>
       </c>
       <c r="BS33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BT33">
         <v>1000</v>
       </c>
       <c r="BU33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BV33">
         <v>1000</v>
       </c>
       <c r="BW33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BX33">
         <v>1000</v>
       </c>
       <c r="BY33">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA33">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8945,28 +8951,28 @@
         <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F34">
         <v>3.3</v>
       </c>
       <c r="G34">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H34">
         <v>2.3</v>
       </c>
       <c r="I34">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="J34">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K34">
         <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
         <v>1.01</v>
@@ -8984,22 +8990,22 @@
         <v>1.76</v>
       </c>
       <c r="R34">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S34">
-        <v>2.92</v>
+        <v>1.94</v>
       </c>
       <c r="T34">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="U34">
         <v>2</v>
       </c>
       <c r="V34">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X34">
         <v>15</v>
@@ -9014,7 +9020,7 @@
         <v>34</v>
       </c>
       <c r="AB34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC34">
         <v>8</v>
@@ -9029,7 +9035,7 @@
         <v>25</v>
       </c>
       <c r="AG34">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH34">
         <v>17</v>
@@ -9041,10 +9047,10 @@
         <v>65</v>
       </c>
       <c r="AK34">
+        <v>40</v>
+      </c>
+      <c r="AL34">
         <v>48</v>
-      </c>
-      <c r="AL34">
-        <v>55</v>
       </c>
       <c r="AM34">
         <v>100</v>
@@ -9053,19 +9059,19 @@
         <v>44</v>
       </c>
       <c r="AO34">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AP34">
         <v>12</v>
       </c>
       <c r="AQ34">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR34">
         <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="AT34">
         <v>11</v>
@@ -9074,10 +9080,10 @@
         <v>6.6</v>
       </c>
       <c r="AV34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW34">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX34">
         <v>20</v>
@@ -9089,19 +9095,19 @@
         <v>13.5</v>
       </c>
       <c r="BA34">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BB34">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BC34">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="BD34">
         <v>32</v>
       </c>
       <c r="BE34">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF34">
         <v>26</v>
@@ -9110,22 +9116,22 @@
         <v>13.5</v>
       </c>
       <c r="BH34">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI34">
-        <v>2.78</v>
+        <v>1.82</v>
       </c>
       <c r="BJ34">
         <v>13.5</v>
       </c>
       <c r="BK34">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="BN34">
         <v>9.6</v>
@@ -9137,31 +9143,31 @@
         <v>40</v>
       </c>
       <c r="BQ34">
-        <v>2.98</v>
+        <v>1.74</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="BT34">
         <v>7.4</v>
       </c>
       <c r="BU34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BV34">
         <v>23</v>
       </c>
       <c r="BW34">
-        <v>2.82</v>
+        <v>1.69</v>
       </c>
       <c r="BX34">
         <v>44</v>
       </c>
       <c r="BY34">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9170,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9187,22 +9193,22 @@
         <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G35">
         <v>990</v>
       </c>
       <c r="H35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I35">
         <v>990</v>
       </c>
       <c r="J35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9238,10 +9244,10 @@
         <v>1.11</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9298,52 +9304,52 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35">
         <v>1.01</v>
@@ -9412,7 +9418,7 @@
         <v>1.04</v>
       </c>
       <c r="CB35" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9429,61 +9435,61 @@
         <v>154</v>
       </c>
       <c r="E36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F36">
         <v>1.87</v>
       </c>
       <c r="G36">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="H36">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I36">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J36">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K36">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M36">
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="O36">
         <v>1.11</v>
       </c>
       <c r="P36">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q36">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R36">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S36">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T36">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U36">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V36">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9594,10 +9600,10 @@
         <v>1.01</v>
       </c>
       <c r="BH36">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI36">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ36">
         <v>1000</v>
@@ -9654,7 +9660,7 @@
         <v>1.04</v>
       </c>
       <c r="CB36" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9671,22 +9677,22 @@
         <v>155</v>
       </c>
       <c r="E37" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G37">
         <v>990</v>
       </c>
       <c r="H37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I37">
         <v>990</v>
       </c>
       <c r="J37">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K37">
         <v>950</v>
@@ -9722,10 +9728,10 @@
         <v>1.11</v>
       </c>
       <c r="V37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9896,7 +9902,7 @@
         <v>1.04</v>
       </c>
       <c r="CB37" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9913,7 +9919,7 @@
         <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F38">
         <v>1.85</v>
@@ -9922,178 +9928,178 @@
         <v>1.92</v>
       </c>
       <c r="H38">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I38">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J38">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K38">
         <v>3.4</v>
       </c>
       <c r="L38">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N38">
-        <v>1.42</v>
+        <v>2.36</v>
       </c>
       <c r="O38">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="P38">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S38">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V38">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W38">
         <v>2.08</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="Y38">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z38">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB38">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AC38">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD38">
+        <v>29</v>
+      </c>
+      <c r="AE38">
+        <v>190</v>
+      </c>
+      <c r="AF38">
+        <v>9.6</v>
+      </c>
+      <c r="AG38">
+        <v>12.5</v>
+      </c>
+      <c r="AH38">
+        <v>38</v>
+      </c>
+      <c r="AI38">
+        <v>240</v>
+      </c>
+      <c r="AJ38">
+        <v>23</v>
+      </c>
+      <c r="AK38">
         <v>32</v>
-      </c>
-      <c r="AE38">
-        <v>1000</v>
-      </c>
-      <c r="AF38">
-        <v>11</v>
-      </c>
-      <c r="AG38">
-        <v>14.5</v>
-      </c>
-      <c r="AH38">
-        <v>42</v>
-      </c>
-      <c r="AI38">
-        <v>1000</v>
-      </c>
-      <c r="AJ38">
-        <v>26</v>
-      </c>
-      <c r="AK38">
-        <v>36</v>
       </c>
       <c r="AL38">
         <v>95</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AP38">
-        <v>2.68</v>
+        <v>6.6</v>
       </c>
       <c r="AQ38">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR38">
-        <v>3.6</v>
+        <v>40</v>
       </c>
       <c r="AS38">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT38">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="AU38">
-        <v>2.72</v>
+        <v>6.8</v>
       </c>
       <c r="AV38">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW38">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="AX38">
-        <v>2.84</v>
+        <v>8</v>
       </c>
       <c r="AY38">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AZ38">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA38">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB38">
-        <v>3.3</v>
+        <v>18.5</v>
       </c>
       <c r="BC38">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="BD38">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="BE38">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF38">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="BG38">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH38">
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BJ38">
         <v>20</v>
       </c>
       <c r="BK38">
-        <v>8.199999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BN38">
         <v>5.6</v>
@@ -10105,40 +10111,40 @@
         <v>22</v>
       </c>
       <c r="BQ38">
-        <v>9.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="BR38">
         <v>1000</v>
       </c>
       <c r="BS38">
-        <v>21</v>
+        <v>1.57</v>
       </c>
       <c r="BT38">
         <v>13.5</v>
       </c>
       <c r="BU38">
-        <v>5.9</v>
+        <v>1.44</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BZ38">
         <v>1000</v>
       </c>
       <c r="CA38">
-        <v>21</v>
+        <v>1.57</v>
       </c>
       <c r="CB38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10155,7 +10161,7 @@
         <v>157</v>
       </c>
       <c r="E39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -10176,216 +10182,216 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P39">
+        <v>1.25</v>
+      </c>
+      <c r="Q39">
+        <v>1.06</v>
+      </c>
+      <c r="R39">
         <v>1.24</v>
       </c>
-      <c r="Q39">
-        <v>1.01</v>
-      </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB39" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
         <v>103</v>
@@ -10397,232 +10403,474 @@
         <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F40">
+        <v>1.01</v>
+      </c>
+      <c r="G40">
+        <v>1000</v>
+      </c>
+      <c r="H40">
+        <v>1.01</v>
+      </c>
+      <c r="I40">
+        <v>1000</v>
+      </c>
+      <c r="J40">
+        <v>1.02</v>
+      </c>
+      <c r="K40">
+        <v>1000</v>
+      </c>
+      <c r="L40">
+        <v>1.01</v>
+      </c>
+      <c r="M40">
+        <v>1.01</v>
+      </c>
+      <c r="N40">
+        <v>1.25</v>
+      </c>
+      <c r="O40">
+        <v>1.05</v>
+      </c>
+      <c r="P40">
+        <v>1.25</v>
+      </c>
+      <c r="Q40">
+        <v>1.05</v>
+      </c>
+      <c r="R40">
+        <v>1.24</v>
+      </c>
+      <c r="S40">
+        <v>1.05</v>
+      </c>
+      <c r="T40">
+        <v>1.01</v>
+      </c>
+      <c r="U40">
+        <v>1.01</v>
+      </c>
+      <c r="V40">
+        <v>1.01</v>
+      </c>
+      <c r="W40">
+        <v>1.01</v>
+      </c>
+      <c r="X40">
+        <v>1000</v>
+      </c>
+      <c r="Y40">
+        <v>1000</v>
+      </c>
+      <c r="Z40">
+        <v>1000</v>
+      </c>
+      <c r="AA40">
+        <v>1000</v>
+      </c>
+      <c r="AB40">
+        <v>1000</v>
+      </c>
+      <c r="AC40">
+        <v>1000</v>
+      </c>
+      <c r="AD40">
+        <v>1000</v>
+      </c>
+      <c r="AE40">
+        <v>1000</v>
+      </c>
+      <c r="AF40">
+        <v>1000</v>
+      </c>
+      <c r="AG40">
+        <v>1000</v>
+      </c>
+      <c r="AH40">
+        <v>1000</v>
+      </c>
+      <c r="AI40">
+        <v>1000</v>
+      </c>
+      <c r="AJ40">
+        <v>1000</v>
+      </c>
+      <c r="AK40">
+        <v>1000</v>
+      </c>
+      <c r="AL40">
+        <v>1000</v>
+      </c>
+      <c r="AM40">
+        <v>1000</v>
+      </c>
+      <c r="AN40">
+        <v>1000</v>
+      </c>
+      <c r="AO40">
+        <v>1000</v>
+      </c>
+      <c r="AP40">
+        <v>1.01</v>
+      </c>
+      <c r="AQ40">
+        <v>1.01</v>
+      </c>
+      <c r="AR40">
+        <v>1.01</v>
+      </c>
+      <c r="AS40">
+        <v>1.01</v>
+      </c>
+      <c r="AT40">
+        <v>1.01</v>
+      </c>
+      <c r="AU40">
+        <v>1.01</v>
+      </c>
+      <c r="AV40">
+        <v>1.01</v>
+      </c>
+      <c r="AW40">
+        <v>1.01</v>
+      </c>
+      <c r="AX40">
+        <v>1.01</v>
+      </c>
+      <c r="AY40">
+        <v>1.01</v>
+      </c>
+      <c r="AZ40">
+        <v>1.01</v>
+      </c>
+      <c r="BA40">
+        <v>1.01</v>
+      </c>
+      <c r="BB40">
+        <v>1.01</v>
+      </c>
+      <c r="BC40">
+        <v>1.01</v>
+      </c>
+      <c r="BD40">
+        <v>1.01</v>
+      </c>
+      <c r="BE40">
+        <v>1.01</v>
+      </c>
+      <c r="BF40">
+        <v>1.01</v>
+      </c>
+      <c r="BG40">
+        <v>1.01</v>
+      </c>
+      <c r="BH40">
+        <v>1000</v>
+      </c>
+      <c r="BI40">
+        <v>1.01</v>
+      </c>
+      <c r="BJ40">
+        <v>1000</v>
+      </c>
+      <c r="BK40">
+        <v>1.01</v>
+      </c>
+      <c r="BL40">
+        <v>1000</v>
+      </c>
+      <c r="BM40">
+        <v>1.01</v>
+      </c>
+      <c r="BN40">
+        <v>1000</v>
+      </c>
+      <c r="BO40">
+        <v>1.01</v>
+      </c>
+      <c r="BP40">
+        <v>1000</v>
+      </c>
+      <c r="BQ40">
+        <v>1.01</v>
+      </c>
+      <c r="BR40">
+        <v>1000</v>
+      </c>
+      <c r="BS40">
+        <v>1.01</v>
+      </c>
+      <c r="BT40">
+        <v>1000</v>
+      </c>
+      <c r="BU40">
+        <v>1.01</v>
+      </c>
+      <c r="BV40">
+        <v>1000</v>
+      </c>
+      <c r="BW40">
+        <v>1.01</v>
+      </c>
+      <c r="BX40">
+        <v>1000</v>
+      </c>
+      <c r="BY40">
+        <v>1.01</v>
+      </c>
+      <c r="BZ40">
+        <v>1000</v>
+      </c>
+      <c r="CA40">
+        <v>1.01</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:80">
+      <c r="A41" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41">
+        <v>1.75</v>
+      </c>
+      <c r="G41">
+        <v>1.91</v>
+      </c>
+      <c r="H41">
+        <v>4.8</v>
+      </c>
+      <c r="I41">
+        <v>5.8</v>
+      </c>
+      <c r="J41">
+        <v>3.6</v>
+      </c>
+      <c r="K41">
+        <v>4</v>
+      </c>
+      <c r="L41">
+        <v>1.01</v>
+      </c>
+      <c r="M41">
+        <v>1.07</v>
+      </c>
+      <c r="N41">
+        <v>2.9</v>
+      </c>
+      <c r="O41">
+        <v>1.34</v>
+      </c>
+      <c r="P41">
+        <v>1.73</v>
+      </c>
+      <c r="Q41">
+        <v>1.94</v>
+      </c>
+      <c r="R41">
+        <v>1.24</v>
+      </c>
+      <c r="S41">
+        <v>3.25</v>
+      </c>
+      <c r="T41">
+        <v>1.84</v>
+      </c>
+      <c r="U41">
+        <v>1.92</v>
+      </c>
+      <c r="V41">
+        <v>1.2</v>
+      </c>
+      <c r="W41">
+        <v>2.1</v>
+      </c>
+      <c r="X41">
+        <v>1000</v>
+      </c>
+      <c r="Y41">
+        <v>24</v>
+      </c>
+      <c r="Z41">
+        <v>55</v>
+      </c>
+      <c r="AA41">
+        <v>1000</v>
+      </c>
+      <c r="AB41">
+        <v>11</v>
+      </c>
+      <c r="AC41">
+        <v>12</v>
+      </c>
+      <c r="AD41">
+        <v>950</v>
+      </c>
+      <c r="AE41">
+        <v>100</v>
+      </c>
+      <c r="AF41">
+        <v>15</v>
+      </c>
+      <c r="AG41">
+        <v>14.5</v>
+      </c>
+      <c r="AH41">
+        <v>950</v>
+      </c>
+      <c r="AI41">
+        <v>100</v>
+      </c>
+      <c r="AJ41">
+        <v>28</v>
+      </c>
+      <c r="AK41">
+        <v>28</v>
+      </c>
+      <c r="AL41">
+        <v>55</v>
+      </c>
+      <c r="AM41">
+        <v>1000</v>
+      </c>
+      <c r="AN41">
+        <v>18</v>
+      </c>
+      <c r="AO41">
+        <v>1000</v>
+      </c>
+      <c r="AP41">
+        <v>2.52</v>
+      </c>
+      <c r="AQ41">
+        <v>11</v>
+      </c>
+      <c r="AR41">
+        <v>2.4</v>
+      </c>
+      <c r="AS41">
+        <v>2.52</v>
+      </c>
+      <c r="AT41">
+        <v>2.04</v>
+      </c>
+      <c r="AU41">
+        <v>2.08</v>
+      </c>
+      <c r="AV41">
+        <v>14.5</v>
+      </c>
+      <c r="AW41">
+        <v>2.46</v>
+      </c>
+      <c r="AX41">
+        <v>2.16</v>
+      </c>
+      <c r="AY41">
+        <v>2.14</v>
+      </c>
+      <c r="AZ41">
+        <v>2.32</v>
+      </c>
+      <c r="BA41">
+        <v>2.46</v>
+      </c>
+      <c r="BB41">
+        <v>2.32</v>
+      </c>
+      <c r="BC41">
+        <v>2.32</v>
+      </c>
+      <c r="BD41">
+        <v>2.4</v>
+      </c>
+      <c r="BE41">
+        <v>2.52</v>
+      </c>
+      <c r="BF41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG41">
+        <v>2.52</v>
+      </c>
+      <c r="BH41">
+        <v>1000</v>
+      </c>
+      <c r="BI41">
+        <v>1.04</v>
+      </c>
+      <c r="BJ41">
+        <v>1000</v>
+      </c>
+      <c r="BK41">
+        <v>1.04</v>
+      </c>
+      <c r="BL41">
+        <v>1000</v>
+      </c>
+      <c r="BM41">
+        <v>1.04</v>
+      </c>
+      <c r="BN41">
+        <v>1000</v>
+      </c>
+      <c r="BO41">
+        <v>1.04</v>
+      </c>
+      <c r="BP41">
+        <v>1000</v>
+      </c>
+      <c r="BQ41">
+        <v>1.04</v>
+      </c>
+      <c r="BR41">
+        <v>1000</v>
+      </c>
+      <c r="BS41">
+        <v>1.04</v>
+      </c>
+      <c r="BT41">
+        <v>1000</v>
+      </c>
+      <c r="BU41">
+        <v>1.04</v>
+      </c>
+      <c r="BV41">
+        <v>1000</v>
+      </c>
+      <c r="BW41">
+        <v>1.04</v>
+      </c>
+      <c r="BX41">
+        <v>1000</v>
+      </c>
+      <c r="BY41">
+        <v>1.04</v>
+      </c>
+      <c r="BZ41">
         <v>0</v>
       </c>
-      <c r="G40">
+      <c r="CA41">
         <v>0</v>
       </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>1.24</v>
-      </c>
-      <c r="Q40">
-        <v>1.01</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
-      <c r="AB40">
-        <v>0</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
-      </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
-      <c r="AF40">
-        <v>0</v>
-      </c>
-      <c r="AG40">
-        <v>0</v>
-      </c>
-      <c r="AH40">
-        <v>0</v>
-      </c>
-      <c r="AI40">
-        <v>0</v>
-      </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
-      <c r="AK40">
-        <v>0</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>0</v>
-      </c>
-      <c r="AO40">
-        <v>0</v>
-      </c>
-      <c r="AP40">
-        <v>0</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40">
-        <v>0</v>
-      </c>
-      <c r="AV40">
-        <v>0</v>
-      </c>
-      <c r="AW40">
-        <v>0</v>
-      </c>
-      <c r="AX40">
-        <v>0</v>
-      </c>
-      <c r="AY40">
-        <v>0</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>0</v>
-      </c>
-      <c r="BC40">
-        <v>0</v>
-      </c>
-      <c r="BD40">
-        <v>0</v>
-      </c>
-      <c r="BE40">
-        <v>0</v>
-      </c>
-      <c r="BF40">
-        <v>0</v>
-      </c>
-      <c r="BG40">
-        <v>0</v>
-      </c>
-      <c r="BH40">
-        <v>0</v>
-      </c>
-      <c r="BI40">
-        <v>0</v>
-      </c>
-      <c r="BJ40">
-        <v>0</v>
-      </c>
-      <c r="BK40">
-        <v>0</v>
-      </c>
-      <c r="BL40">
-        <v>0</v>
-      </c>
-      <c r="BM40">
-        <v>0</v>
-      </c>
-      <c r="BN40">
-        <v>0</v>
-      </c>
-      <c r="BO40">
-        <v>0</v>
-      </c>
-      <c r="BP40">
-        <v>0</v>
-      </c>
-      <c r="BQ40">
-        <v>0</v>
-      </c>
-      <c r="BR40">
-        <v>0</v>
-      </c>
-      <c r="BS40">
-        <v>0</v>
-      </c>
-      <c r="BT40">
-        <v>0</v>
-      </c>
-      <c r="BU40">
-        <v>0</v>
-      </c>
-      <c r="BV40">
-        <v>0</v>
-      </c>
-      <c r="BW40">
-        <v>0</v>
-      </c>
-      <c r="BX40">
-        <v>0</v>
-      </c>
-      <c r="BY40">
-        <v>0</v>
-      </c>
-      <c r="BZ40">
-        <v>0</v>
-      </c>
-      <c r="CA40">
-        <v>0</v>
-      </c>
-      <c r="CB40" t="s">
-        <v>198</v>
+      <c r="CB41" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -616,7 +616,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-07-22 19:12:56</t>
+    <t>2026-07-22 21:21:53</t>
   </si>
 </sst>
 </file>
@@ -1210,25 +1210,25 @@
         <v>160</v>
       </c>
       <c r="F2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G2">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="H2">
         <v>4.7</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.08</v>
@@ -1240,13 +1240,13 @@
         <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
         <v>4</v>
@@ -1261,7 +1261,7 @@
         <v>1.24</v>
       </c>
       <c r="W2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1294,10 +1294,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
         <v>27</v>
@@ -1309,7 +1309,7 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN2">
         <v>20</v>
@@ -1324,10 +1324,10 @@
         <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1339,7 +1339,7 @@
         <v>17</v>
       </c>
       <c r="AW2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1348,22 +1348,22 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF2">
         <v>12</v>
@@ -1375,19 +1375,19 @@
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>4.5</v>
@@ -1399,13 +1399,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
         <v>8.199999999999999</v>
@@ -1417,19 +1417,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>200</v>
@@ -1706,10 +1706,10 @@
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.52</v>
@@ -1718,16 +1718,16 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O4">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P4">
         <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
         <v>1.18</v>
@@ -1736,10 +1736,10 @@
         <v>5.8</v>
       </c>
       <c r="T4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
         <v>1.22</v>
@@ -1751,7 +1751,7 @@
         <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1787,7 +1787,7 @@
         <v>24</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1796,13 +1796,13 @@
         <v>290</v>
       </c>
       <c r="AN4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
         <v>11</v>
@@ -1814,10 +1814,10 @@
         <v>42</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
@@ -1832,7 +1832,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA4">
         <v>42</v>
@@ -1841,7 +1841,7 @@
         <v>21</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>34</v>
@@ -1936,7 +1936,7 @@
         <v>163</v>
       </c>
       <c r="F5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G5">
         <v>3.7</v>
@@ -1969,7 +1969,7 @@
         <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
         <v>1.25</v>
@@ -2178,10 +2178,10 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G6">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H6">
         <v>5.7</v>
@@ -2193,7 +2193,7 @@
         <v>4.3</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2202,10 +2202,10 @@
         <v>1.04</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
         <v>2.22</v>
@@ -2214,10 +2214,10 @@
         <v>1.66</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
         <v>1.76</v>
@@ -2229,7 +2229,7 @@
         <v>1.17</v>
       </c>
       <c r="W6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X6">
         <v>24</v>
@@ -2827,7 +2827,7 @@
         <v>4.2</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
         <v>9.6</v>
@@ -3179,7 +3179,7 @@
         <v>2.26</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
         <v>1.5</v>
@@ -3191,7 +3191,7 @@
         <v>1.58</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
         <v>1.74</v>
@@ -3317,7 +3317,7 @@
         <v>9.4</v>
       </c>
       <c r="BK10">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL10">
         <v>90</v>
@@ -3353,7 +3353,7 @@
         <v>16.5</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX10">
         <v>26</v>
@@ -3391,7 +3391,7 @@
         <v>1.66</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H11">
         <v>4.8</v>
@@ -3418,13 +3418,13 @@
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
         <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S11">
         <v>2.64</v>
@@ -3636,19 +3636,19 @@
         <v>1.77</v>
       </c>
       <c r="H12">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
         <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3660,7 +3660,7 @@
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q12">
         <v>1.78</v>
@@ -3669,7 +3669,7 @@
         <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="T12">
         <v>1.81</v>
@@ -3887,7 +3887,7 @@
         <v>3.95</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3902,16 +3902,16 @@
         <v>1.23</v>
       </c>
       <c r="P13">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q13">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R13">
         <v>1.48</v>
       </c>
       <c r="S13">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T13">
         <v>1.81</v>
@@ -4123,7 +4123,7 @@
         <v>3.3</v>
       </c>
       <c r="I14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J14">
         <v>3.6</v>
@@ -4147,7 +4147,7 @@
         <v>2.14</v>
       </c>
       <c r="Q14">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="R14">
         <v>1.45</v>
@@ -4270,7 +4270,7 @@
         <v>4</v>
       </c>
       <c r="BF14">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14">
         <v>3.8</v>
@@ -4374,7 +4374,7 @@
         <v>3.9</v>
       </c>
       <c r="L15">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M15">
         <v>1.06</v>
@@ -4395,10 +4395,10 @@
         <v>1.37</v>
       </c>
       <c r="S15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T15">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U15">
         <v>2.2</v>
@@ -4446,7 +4446,7 @@
         <v>50</v>
       </c>
       <c r="AJ15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK15">
         <v>30</v>
@@ -4473,7 +4473,7 @@
         <v>17</v>
       </c>
       <c r="AS15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT15">
         <v>10</v>
@@ -4485,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="AW15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX15">
         <v>15.5</v>
@@ -4503,7 +4503,7 @@
         <v>5.7</v>
       </c>
       <c r="BC15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD15">
         <v>5.7</v>
@@ -4515,7 +4515,7 @@
         <v>19</v>
       </c>
       <c r="BG15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH15">
         <v>3.65</v>
@@ -4643,7 +4643,7 @@
         <v>1.69</v>
       </c>
       <c r="U16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V16">
         <v>1.18</v>
@@ -4652,7 +4652,7 @@
         <v>2.68</v>
       </c>
       <c r="X16">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Y16">
         <v>950</v>
@@ -4661,7 +4661,7 @@
         <v>60</v>
       </c>
       <c r="AA16">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB16">
         <v>12</v>
@@ -4670,7 +4670,7 @@
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE16">
         <v>80</v>
@@ -4679,22 +4679,22 @@
         <v>12</v>
       </c>
       <c r="AG16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH16">
         <v>18.5</v>
       </c>
       <c r="AI16">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM16">
         <v>80</v>
@@ -4706,19 +4706,19 @@
         <v>70</v>
       </c>
       <c r="AP16">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AQ16">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="AR16">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="AS16">
+        <v>11</v>
+      </c>
+      <c r="AT16">
         <v>10.5</v>
-      </c>
-      <c r="AT16">
-        <v>10</v>
       </c>
       <c r="AU16">
         <v>9.800000000000001</v>
@@ -4727,10 +4727,10 @@
         <v>21</v>
       </c>
       <c r="AW16">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="AX16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY16">
         <v>9</v>
@@ -4739,85 +4739,85 @@
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC16">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE16">
-        <v>9.800000000000001</v>
+        <v>60</v>
       </c>
       <c r="BF16">
         <v>5.7</v>
       </c>
       <c r="BG16">
-        <v>9.6</v>
+        <v>46</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BJ16">
         <v>13.5</v>
       </c>
       <c r="BK16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BN16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BP16">
         <v>13.5</v>
       </c>
       <c r="BQ16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BR16">
         <v>30</v>
       </c>
       <c r="BS16">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BT16">
         <v>14.5</v>
       </c>
       <c r="BU16">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BZ16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA16">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CB16" t="s">
         <v>200</v>
@@ -4882,7 +4882,7 @@
         <v>2.7</v>
       </c>
       <c r="T17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
         <v>2.42</v>
@@ -4915,7 +4915,7 @@
         <v>17</v>
       </c>
       <c r="AE17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF17">
         <v>18.5</v>
@@ -4957,7 +4957,7 @@
         <v>21</v>
       </c>
       <c r="AS17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -4981,7 +4981,7 @@
         <v>12</v>
       </c>
       <c r="BA17">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4993,10 +4993,10 @@
         <v>4.5</v>
       </c>
       <c r="BE17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG17">
         <v>20</v>
@@ -5005,7 +5005,7 @@
         <v>5.3</v>
       </c>
       <c r="BI17">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>
@@ -5085,13 +5085,13 @@
         <v>1.93</v>
       </c>
       <c r="G18">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H18">
         <v>4.1</v>
       </c>
       <c r="I18">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18">
         <v>3.85</v>
@@ -5115,7 +5115,7 @@
         <v>2.24</v>
       </c>
       <c r="Q18">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R18">
         <v>1.5</v>
@@ -5133,7 +5133,7 @@
         <v>1.3</v>
       </c>
       <c r="W18">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X18">
         <v>24</v>
@@ -5605,13 +5605,13 @@
         <v>1.78</v>
       </c>
       <c r="S20">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="T20">
         <v>1.52</v>
       </c>
       <c r="U20">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V20">
         <v>1.2</v>
@@ -5850,10 +5850,10 @@
         <v>2.38</v>
       </c>
       <c r="T21">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="U21">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
         <v>1.55</v>
@@ -6092,10 +6092,10 @@
         <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U22">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
         <v>1.39</v>
@@ -6316,13 +6316,13 @@
         <v>1.03</v>
       </c>
       <c r="N23">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="O23">
         <v>1.15</v>
       </c>
       <c r="P23">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q23">
         <v>1.47</v>
@@ -6331,7 +6331,7 @@
         <v>1.71</v>
       </c>
       <c r="S23">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T23">
         <v>1.46</v>
@@ -6340,7 +6340,7 @@
         <v>2.72</v>
       </c>
       <c r="V23">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W23">
         <v>1.4</v>
@@ -6403,55 +6403,55 @@
         <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR23">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AS23">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT23">
+        <v>15.5</v>
+      </c>
+      <c r="AU23">
+        <v>8</v>
+      </c>
+      <c r="AV23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW23">
+        <v>14</v>
+      </c>
+      <c r="AX23">
+        <v>21</v>
+      </c>
+      <c r="AY23">
+        <v>11</v>
+      </c>
+      <c r="AZ23">
+        <v>10.5</v>
+      </c>
+      <c r="BA23">
         <v>18</v>
       </c>
-      <c r="AU23">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV23">
-        <v>10</v>
-      </c>
-      <c r="AW23">
-        <v>16.5</v>
-      </c>
-      <c r="AX23">
-        <v>16.5</v>
-      </c>
-      <c r="AY23">
+      <c r="BB23">
+        <v>36</v>
+      </c>
+      <c r="BC23">
+        <v>21</v>
+      </c>
+      <c r="BD23">
+        <v>6.6</v>
+      </c>
+      <c r="BE23">
+        <v>7</v>
+      </c>
+      <c r="BF23">
         <v>12.5</v>
       </c>
-      <c r="AZ23">
-        <v>12</v>
-      </c>
-      <c r="BA23">
-        <v>21</v>
-      </c>
-      <c r="BB23">
-        <v>30</v>
-      </c>
-      <c r="BC23">
-        <v>17.5</v>
-      </c>
-      <c r="BD23">
-        <v>18.5</v>
-      </c>
-      <c r="BE23">
-        <v>28</v>
-      </c>
-      <c r="BF23">
-        <v>14.5</v>
-      </c>
       <c r="BG23">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH23">
         <v>6.6</v>
@@ -6579,7 +6579,7 @@
         <v>1.97</v>
       </c>
       <c r="U24">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V24">
         <v>1.17</v>
@@ -6699,19 +6699,19 @@
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BJ24">
         <v>15</v>
       </c>
       <c r="BK24">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BN24">
         <v>5.5</v>
@@ -6723,13 +6723,13 @@
         <v>16</v>
       </c>
       <c r="BQ24">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BR24">
         <v>40</v>
       </c>
       <c r="BS24">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BT24">
         <v>13</v>
@@ -6741,19 +6741,19 @@
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BZ24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="CA24">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CB24" t="s">
         <v>200</v>
@@ -6779,7 +6779,7 @@
         <v>2.14</v>
       </c>
       <c r="G25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H25">
         <v>2.96</v>
@@ -6827,7 +6827,7 @@
         <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7060,10 +7060,10 @@
         <v>2.14</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="U26">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V26">
         <v>2.4</v>
@@ -7260,7 +7260,7 @@
         <v>185</v>
       </c>
       <c r="F27">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G27">
         <v>3.45</v>
@@ -7290,7 +7290,7 @@
         <v>1.31</v>
       </c>
       <c r="P27">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q27">
         <v>2.04</v>
@@ -7302,10 +7302,10 @@
         <v>3.35</v>
       </c>
       <c r="T27">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U27">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V27">
         <v>1.5</v>
@@ -7777,7 +7777,7 @@
         <v>1.89</v>
       </c>
       <c r="Q29">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R29">
         <v>1.33</v>
@@ -8028,10 +8028,10 @@
         <v>2.64</v>
       </c>
       <c r="T30">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="U30">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V30">
         <v>1.17</v>
@@ -8261,7 +8261,7 @@
         <v>1.83</v>
       </c>
       <c r="Q31">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R31">
         <v>1.3</v>
@@ -8479,7 +8479,7 @@
         <v>2.56</v>
       </c>
       <c r="I32">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J32">
         <v>3.5</v>
@@ -8494,16 +8494,16 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P32">
         <v>2.14</v>
       </c>
       <c r="Q32">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R32">
         <v>1.44</v>
@@ -8518,7 +8518,7 @@
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W32">
         <v>1.51</v>
@@ -8718,7 +8718,7 @@
         <v>4.2</v>
       </c>
       <c r="H33">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I33">
         <v>2.38</v>
@@ -8745,7 +8745,7 @@
         <v>1.96</v>
       </c>
       <c r="Q33">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="R33">
         <v>1.37</v>
@@ -8984,10 +8984,10 @@
         <v>1.3</v>
       </c>
       <c r="P34">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q34">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R34">
         <v>1.18</v>
@@ -9208,7 +9208,7 @@
         <v>990</v>
       </c>
       <c r="J35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9480,10 +9480,10 @@
         <v>1.86</v>
       </c>
       <c r="T36">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="U36">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V36">
         <v>1.32</v>
@@ -9692,7 +9692,7 @@
         <v>990</v>
       </c>
       <c r="J37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K37">
         <v>950</v>
@@ -10188,7 +10188,7 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O39">
         <v>1.06</v>
@@ -10200,7 +10200,7 @@
         <v>1.06</v>
       </c>
       <c r="R39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S39">
         <v>1.06</v>
@@ -10409,19 +10409,19 @@
         <v>1.01</v>
       </c>
       <c r="G40">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H40">
         <v>1.01</v>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K40">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10430,28 +10430,28 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O40">
         <v>1.05</v>
       </c>
       <c r="P40">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q40">
         <v>1.05</v>
       </c>
       <c r="R40">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S40">
         <v>1.05</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
         <v>1.01</v>
@@ -10571,61 +10571,61 @@
         <v>1000</v>
       </c>
       <c r="BI40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ40">
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB40" t="s">
         <v>200</v>
@@ -10690,10 +10690,10 @@
         <v>3.25</v>
       </c>
       <c r="T41">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U41">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V41">
         <v>1.2</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -616,7 +616,7 @@
     <t>CD Los Chankas</t>
   </si>
   <si>
-    <t>2026-07-22 21:21:53</t>
+    <t>2026-07-22 23:29:18</t>
   </si>
 </sst>
 </file>
@@ -1213,16 +1213,16 @@
         <v>1.87</v>
       </c>
       <c r="G2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -1234,13 +1234,13 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
         <v>2.14</v>
@@ -1249,7 +1249,7 @@
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
         <v>1.96</v>
@@ -1258,61 +1258,61 @@
         <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA2">
         <v>150</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AK2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM2">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO2">
         <v>120</v>
@@ -1321,25 +1321,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="AS2">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AW2">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>9.6</v>
@@ -1348,28 +1348,28 @@
         <v>9</v>
       </c>
       <c r="AZ2">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="BC2">
-        <v>3.85</v>
+        <v>7.4</v>
       </c>
       <c r="BD2">
         <v>36</v>
       </c>
       <c r="BE2">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>12</v>
       </c>
       <c r="BG2">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
@@ -1455,13 +1455,13 @@
         <v>2.58</v>
       </c>
       <c r="G3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="H3">
         <v>3.25</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
         <v>2.94</v>
@@ -1470,16 +1470,16 @@
         <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P3">
         <v>1.51</v>
@@ -1491,34 +1491,34 @@
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
@@ -1527,10 +1527,10 @@
         <v>16</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1542,10 +1542,10 @@
         <v>80</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL3">
         <v>75</v>
@@ -1554,64 +1554,64 @@
         <v>220</v>
       </c>
       <c r="AN3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP3">
         <v>7.6</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT3">
         <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
         <v>19</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
         <v>2.78</v>
@@ -1635,7 +1635,7 @@
         <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>25</v>
@@ -1694,10 +1694,10 @@
         <v>162</v>
       </c>
       <c r="F4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1706,7 +1706,7 @@
         <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1718,16 +1718,16 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P4">
         <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
         <v>1.18</v>
@@ -1736,7 +1736,7 @@
         <v>5.8</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
         <v>1.67</v>
@@ -1745,13 +1745,13 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X4">
         <v>8.4</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1778,7 +1778,7 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1805,7 +1805,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
         <v>21</v>
@@ -1820,10 +1820,10 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -1838,19 +1838,19 @@
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4">
         <v>44</v>
@@ -1871,7 +1871,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
@@ -1895,13 +1895,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1936,46 +1936,46 @@
         <v>163</v>
       </c>
       <c r="F5">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G5">
         <v>3.7</v>
       </c>
       <c r="H5">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="I5">
         <v>2.58</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
         <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>3.75</v>
+        <v>2.46</v>
       </c>
       <c r="T5">
         <v>1.54</v>
@@ -1993,31 +1993,31 @@
         <v>1000</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
         <v>1000</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
         <v>1000</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
         <v>1000</v>
       </c>
       <c r="AG5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
         <v>1000</v>
@@ -2041,115 +2041,115 @@
         <v>1000</v>
       </c>
       <c r="AO5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -2178,7 +2178,7 @@
         <v>164</v>
       </c>
       <c r="F6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G6">
         <v>1.66</v>
@@ -2187,10 +2187,10 @@
         <v>5.7</v>
       </c>
       <c r="I6">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
         <v>4.9</v>
@@ -2199,145 +2199,145 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>2.06</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="T6">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
         <v>2.5</v>
       </c>
       <c r="X6">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2420,37 +2420,37 @@
         <v>165</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G7">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I7">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>3.5</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="Q7">
         <v>2.06</v>
@@ -2459,22 +2459,22 @@
         <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
         <v>15</v>
@@ -2483,7 +2483,7 @@
         <v>32</v>
       </c>
       <c r="AA7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB7">
         <v>10.5</v>
@@ -2492,7 +2492,7 @@
         <v>9</v>
       </c>
       <c r="AD7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>60</v>
@@ -2510,7 +2510,7 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AK7">
         <v>29</v>
@@ -2522,37 +2522,37 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO7">
         <v>65</v>
       </c>
       <c r="AP7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2561,85 +2561,85 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB7">
+        <v>4.4</v>
+      </c>
+      <c r="BC7">
         <v>21</v>
       </c>
-      <c r="BC7">
-        <v>19</v>
-      </c>
       <c r="BD7">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BE7">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF7">
         <v>15</v>
       </c>
       <c r="BG7">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH7">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>200</v>
@@ -2662,7 +2662,7 @@
         <v>166</v>
       </c>
       <c r="F8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G8">
         <v>2.02</v>
@@ -2671,7 +2671,7 @@
         <v>3.9</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="J8">
         <v>3.75</v>
@@ -2680,7 +2680,7 @@
         <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.04</v>
@@ -2707,10 +2707,10 @@
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
         <v>1.98</v>
@@ -2725,7 +2725,7 @@
         <v>42</v>
       </c>
       <c r="AA8">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB8">
         <v>14</v>
@@ -2764,7 +2764,7 @@
         <v>90</v>
       </c>
       <c r="AN8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO8">
         <v>50</v>
@@ -2776,10 +2776,10 @@
         <v>13.5</v>
       </c>
       <c r="AR8">
+        <v>3.8</v>
+      </c>
+      <c r="AS8">
         <v>4</v>
-      </c>
-      <c r="AS8">
-        <v>4.3</v>
       </c>
       <c r="AT8">
         <v>8.4</v>
@@ -2791,7 +2791,7 @@
         <v>12.5</v>
       </c>
       <c r="AW8">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX8">
         <v>9.800000000000001</v>
@@ -2803,7 +2803,7 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BB8">
         <v>15.5</v>
@@ -2815,73 +2815,73 @@
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BF8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BH8">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>200</v>
@@ -2904,22 +2904,22 @@
         <v>167</v>
       </c>
       <c r="F9">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="G9">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I9">
         <v>3.5</v>
       </c>
       <c r="J9">
-        <v>2.94</v>
+        <v>1.02</v>
       </c>
       <c r="K9">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2928,196 +2928,196 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
         <v>1000</v>
       </c>
       <c r="Y9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>168</v>
       </c>
       <c r="F10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G10">
         <v>3.4</v>
@@ -3155,7 +3155,7 @@
         <v>2.22</v>
       </c>
       <c r="I10">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J10">
         <v>3.85</v>
@@ -3164,28 +3164,28 @@
         <v>3.95</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="M10">
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O10">
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
         <v>1.58</v>
@@ -3194,28 +3194,28 @@
         <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W10">
         <v>1.41</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z10">
+        <v>21</v>
+      </c>
+      <c r="AA10">
+        <v>36</v>
+      </c>
+      <c r="AB10">
         <v>20</v>
       </c>
-      <c r="AA10">
-        <v>30</v>
-      </c>
-      <c r="AB10">
-        <v>17</v>
-      </c>
       <c r="AC10">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD10">
         <v>14</v>
@@ -3224,25 +3224,25 @@
         <v>27</v>
       </c>
       <c r="AF10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AH10">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ10">
         <v>65</v>
       </c>
       <c r="AK10">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL10">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>80</v>
@@ -3263,16 +3263,16 @@
         <v>14</v>
       </c>
       <c r="AS10">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AT10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU10">
         <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10">
         <v>18.5</v>
@@ -3287,79 +3287,79 @@
         <v>13</v>
       </c>
       <c r="BA10">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="BB10">
-        <v>5.4</v>
+        <v>3.95</v>
       </c>
       <c r="BC10">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="BD10">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BE10">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BF10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3391,13 +3391,13 @@
         <v>1.66</v>
       </c>
       <c r="G11">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H11">
         <v>4.8</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J11">
         <v>4.4</v>
@@ -3418,22 +3418,22 @@
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T11">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V11">
         <v>1.21</v>
@@ -3451,7 +3451,7 @@
         <v>55</v>
       </c>
       <c r="AA11">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB11">
         <v>13</v>
@@ -3463,7 +3463,7 @@
         <v>25</v>
       </c>
       <c r="AE11">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF11">
         <v>14</v>
@@ -3475,49 +3475,49 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
         <v>22</v>
       </c>
       <c r="AK11">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN11">
         <v>9.800000000000001</v>
       </c>
       <c r="AO11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP11">
         <v>15</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AS11">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AT11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV11">
         <v>15</v>
       </c>
       <c r="AW11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX11">
         <v>8.6</v>
@@ -3529,7 +3529,7 @@
         <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB11">
         <v>12.5</v>
@@ -3541,13 +3541,13 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BF11">
         <v>6</v>
       </c>
       <c r="BG11">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3633,22 +3633,22 @@
         <v>1.61</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I12">
         <v>7.4</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
         <v>4.6</v>
       </c>
       <c r="L12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="M12">
         <v>1.05</v>
@@ -3660,7 +3660,7 @@
         <v>1.27</v>
       </c>
       <c r="P12">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q12">
         <v>1.78</v>
@@ -3669,19 +3669,19 @@
         <v>1.4</v>
       </c>
       <c r="S12">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T12">
         <v>1.81</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W12">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="X12">
         <v>18</v>
@@ -3705,7 +3705,7 @@
         <v>24</v>
       </c>
       <c r="AE12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF12">
         <v>11</v>
@@ -3774,7 +3774,7 @@
         <v>8</v>
       </c>
       <c r="BB12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BC12">
         <v>6</v>
@@ -3792,64 +3792,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH12">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="BJ12">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>1.56</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>8.800000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="BN12">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BO12">
-        <v>3.15</v>
+        <v>1.34</v>
       </c>
       <c r="BP12">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BQ12">
-        <v>5.5</v>
+        <v>1.57</v>
       </c>
       <c r="BR12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>7.4</v>
+        <v>1.74</v>
       </c>
       <c r="BT12">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BU12">
-        <v>5</v>
+        <v>1.54</v>
       </c>
       <c r="BV12">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>8.6</v>
+        <v>1.74</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>1.71</v>
       </c>
       <c r="BZ12">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="CA12">
-        <v>6.8</v>
+        <v>1.64</v>
       </c>
       <c r="CB12" t="s">
         <v>200</v>
@@ -3875,16 +3875,16 @@
         <v>1.49</v>
       </c>
       <c r="G13">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H13">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I13">
         <v>7.8</v>
       </c>
       <c r="J13">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
         <v>5.2</v>
@@ -3893,61 +3893,61 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
         <v>1.1</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P13">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="Q13">
-        <v>1.67</v>
+        <v>1.31</v>
       </c>
       <c r="R13">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T13">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="V13">
         <v>1.14</v>
       </c>
       <c r="W13">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AA13">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD13">
         <v>27</v>
       </c>
       <c r="AE13">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
         <v>10.5</v>
@@ -3956,10 +3956,10 @@
         <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI13">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
         <v>15</v>
@@ -3968,70 +3968,70 @@
         <v>16.5</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AM13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
         <v>7.4</v>
       </c>
       <c r="AO13">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AQ13">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="AR13">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="AS13">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="AT13">
-        <v>4.6</v>
+        <v>2.84</v>
       </c>
       <c r="AU13">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="AV13">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="AX13">
-        <v>4.7</v>
+        <v>2.86</v>
       </c>
       <c r="AY13">
-        <v>4.7</v>
+        <v>2.86</v>
       </c>
       <c r="AZ13">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="BA13">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BB13">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="BC13">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="BD13">
-        <v>6.8</v>
+        <v>3.65</v>
       </c>
       <c r="BE13">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BF13">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="BG13">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4114,226 +4114,226 @@
         <v>172</v>
       </c>
       <c r="F14">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G14">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H14">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
-        <v>4.3</v>
+        <v>2.46</v>
       </c>
       <c r="O14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P14">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="R14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S14">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T14">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>200</v>
@@ -4356,226 +4356,226 @@
         <v>173</v>
       </c>
       <c r="F15">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="I15">
+        <v>3.6</v>
+      </c>
+      <c r="J15">
         <v>3.1</v>
       </c>
-      <c r="J15">
-        <v>3.35</v>
-      </c>
       <c r="K15">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L15">
+        <v>1.11</v>
+      </c>
+      <c r="M15">
+        <v>1.05</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>1.27</v>
+      </c>
+      <c r="P15">
+        <v>1.69</v>
+      </c>
+      <c r="Q15">
+        <v>1.81</v>
+      </c>
+      <c r="R15">
+        <v>1.26</v>
+      </c>
+      <c r="S15">
+        <v>2.58</v>
+      </c>
+      <c r="T15">
         <v>1.32</v>
       </c>
-      <c r="M15">
-        <v>1.06</v>
-      </c>
-      <c r="N15">
-        <v>3.75</v>
-      </c>
-      <c r="O15">
-        <v>1.29</v>
-      </c>
-      <c r="P15">
-        <v>1.95</v>
-      </c>
-      <c r="Q15">
-        <v>1.87</v>
-      </c>
-      <c r="R15">
-        <v>1.37</v>
-      </c>
-      <c r="S15">
-        <v>3.15</v>
-      </c>
-      <c r="T15">
-        <v>1.69</v>
-      </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X15">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>200</v>
@@ -4598,10 +4598,10 @@
         <v>174</v>
       </c>
       <c r="F16">
+        <v>1.57</v>
+      </c>
+      <c r="G16">
         <v>1.58</v>
-      </c>
-      <c r="G16">
-        <v>1.59</v>
       </c>
       <c r="H16">
         <v>6.2</v>
@@ -4619,13 +4619,13 @@
         <v>1.26</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>5.4</v>
       </c>
       <c r="O16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P16">
         <v>2.52</v>
@@ -4634,7 +4634,7 @@
         <v>1.57</v>
       </c>
       <c r="R16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S16">
         <v>2.42</v>
@@ -4652,16 +4652,16 @@
         <v>2.68</v>
       </c>
       <c r="X16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y16">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="Z16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA16">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AB16">
         <v>12</v>
@@ -4673,16 +4673,16 @@
         <v>25</v>
       </c>
       <c r="AE16">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG16">
         <v>10</v>
       </c>
       <c r="AH16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI16">
         <v>65</v>
@@ -4697,7 +4697,7 @@
         <v>27</v>
       </c>
       <c r="AM16">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN16">
         <v>6.4</v>
@@ -4706,7 +4706,7 @@
         <v>70</v>
       </c>
       <c r="AP16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ16">
         <v>25</v>
@@ -4721,7 +4721,7 @@
         <v>10.5</v>
       </c>
       <c r="AU16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV16">
         <v>21</v>
@@ -4739,7 +4739,7 @@
         <v>15.5</v>
       </c>
       <c r="BA16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB16">
         <v>13.5</v>
@@ -4751,73 +4751,73 @@
         <v>23</v>
       </c>
       <c r="BE16">
-        <v>60</v>
+        <v>12.5</v>
       </c>
       <c r="BF16">
         <v>5.7</v>
       </c>
       <c r="BG16">
-        <v>46</v>
+        <v>10.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
       </c>
       <c r="BI16">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.99</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
         <v>1000</v>
       </c>
       <c r="BW16">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
         <v>1000</v>
       </c>
       <c r="BY16">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>200</v>
@@ -4846,7 +4846,7 @@
         <v>2.26</v>
       </c>
       <c r="H17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I17">
         <v>3.55</v>
@@ -4855,10 +4855,10 @@
         <v>3.75</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M17">
         <v>1.05</v>
@@ -4879,7 +4879,7 @@
         <v>1.5</v>
       </c>
       <c r="S17">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T17">
         <v>1.62</v>
@@ -4912,7 +4912,7 @@
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE17">
         <v>40</v>
@@ -4954,10 +4954,10 @@
         <v>12.5</v>
       </c>
       <c r="AR17">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AS17">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT17">
         <v>9.800000000000001</v>
@@ -4966,10 +4966,10 @@
         <v>7.2</v>
       </c>
       <c r="AV17">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX17">
         <v>12</v>
@@ -4981,7 +4981,7 @@
         <v>12</v>
       </c>
       <c r="BA17">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4990,52 +4990,52 @@
         <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG17">
         <v>20</v>
       </c>
       <c r="BH17">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.9</v>
+        <v>1.97</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="BN17">
         <v>7.4</v>
       </c>
       <c r="BO17">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BP17">
         <v>21</v>
       </c>
       <c r="BQ17">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="BR17">
         <v>34</v>
       </c>
       <c r="BS17">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="BT17">
         <v>9.199999999999999</v>
@@ -5047,19 +5047,19 @@
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="BX17">
         <v>44</v>
       </c>
       <c r="BY17">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="BZ17">
         <v>26</v>
       </c>
       <c r="CA17">
-        <v>2.78</v>
+        <v>1.83</v>
       </c>
       <c r="CB17" t="s">
         <v>200</v>
@@ -5082,7 +5082,7 @@
         <v>176</v>
       </c>
       <c r="F18">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="G18">
         <v>1.98</v>
@@ -5091,7 +5091,7 @@
         <v>4.1</v>
       </c>
       <c r="I18">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J18">
         <v>3.85</v>
@@ -5118,10 +5118,10 @@
         <v>1.69</v>
       </c>
       <c r="R18">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S18">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T18">
         <v>1.64</v>
@@ -5130,7 +5130,7 @@
         <v>2.3</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W18">
         <v>2.02</v>
@@ -5142,19 +5142,19 @@
         <v>23</v>
       </c>
       <c r="Z18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA18">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB18">
         <v>13.5</v>
       </c>
       <c r="AC18">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD18">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE18">
         <v>60</v>
@@ -5175,25 +5175,25 @@
         <v>26</v>
       </c>
       <c r="AK18">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL18">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM18">
         <v>90</v>
       </c>
       <c r="AN18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO18">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP18">
         <v>17</v>
       </c>
       <c r="AQ18">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR18">
         <v>4</v>
@@ -5205,7 +5205,7 @@
         <v>9.6</v>
       </c>
       <c r="AU18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV18">
         <v>14.5</v>
@@ -5229,7 +5229,7 @@
         <v>18.5</v>
       </c>
       <c r="BC18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD18">
         <v>4</v>
@@ -5238,7 +5238,7 @@
         <v>4.3</v>
       </c>
       <c r="BF18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG18">
         <v>4.1</v>
@@ -5247,61 +5247,61 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BJ18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BN18">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP18">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BR18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BT18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV18">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="BZ18">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB18" t="s">
         <v>200</v>
@@ -5327,13 +5327,13 @@
         <v>1.66</v>
       </c>
       <c r="G19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19">
         <v>4.7</v>
@@ -5348,196 +5348,196 @@
         <v>1.02</v>
       </c>
       <c r="N19">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="O19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q19">
         <v>1.35</v>
       </c>
       <c r="R19">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="S19">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="T19">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="V19">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE19">
         <v>55</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19">
-        <v>1.23</v>
+        <v>4.1</v>
       </c>
       <c r="AR19">
-        <v>1.23</v>
+        <v>4.3</v>
       </c>
       <c r="AS19">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="AT19">
-        <v>1.23</v>
+        <v>13.5</v>
       </c>
       <c r="AU19">
-        <v>1.23</v>
+        <v>11</v>
       </c>
       <c r="AV19">
-        <v>1.23</v>
+        <v>14.5</v>
       </c>
       <c r="AW19">
-        <v>1.21</v>
+        <v>4.3</v>
       </c>
       <c r="AX19">
-        <v>1.23</v>
+        <v>14</v>
       </c>
       <c r="AY19">
-        <v>1.23</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="BA19">
-        <v>1.23</v>
+        <v>4.2</v>
       </c>
       <c r="BB19">
-        <v>1.23</v>
+        <v>15</v>
       </c>
       <c r="BC19">
-        <v>1.23</v>
+        <v>13</v>
       </c>
       <c r="BD19">
-        <v>1.23</v>
+        <v>15.5</v>
       </c>
       <c r="BE19">
-        <v>1.23</v>
+        <v>4.3</v>
       </c>
       <c r="BF19">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="BG19">
-        <v>1.23</v>
+        <v>17.5</v>
       </c>
       <c r="BH19">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>2.7</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>0</v>
@@ -5569,16 +5569,16 @@
         <v>1.57</v>
       </c>
       <c r="G20">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H20">
         <v>5</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20">
         <v>5.4</v>
@@ -5590,142 +5590,142 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P20">
-        <v>2.92</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="R20">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="S20">
         <v>2.04</v>
       </c>
       <c r="T20">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="U20">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W20">
         <v>2.42</v>
       </c>
       <c r="X20">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5808,16 +5808,16 @@
         <v>179</v>
       </c>
       <c r="F21">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G21">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="H21">
         <v>2.24</v>
       </c>
       <c r="I21">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J21">
         <v>3.3</v>
@@ -5838,16 +5838,16 @@
         <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
         <v>1.47</v>
       </c>
       <c r="R21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="T21">
         <v>1.26</v>
@@ -5856,10 +5856,10 @@
         <v>2.06</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X21">
         <v>1000</v>
@@ -6050,16 +6050,16 @@
         <v>180</v>
       </c>
       <c r="F22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H22">
         <v>3.05</v>
       </c>
       <c r="I22">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <v>3.7</v>
@@ -6074,148 +6074,148 @@
         <v>1.05</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
         <v>2.22</v>
       </c>
       <c r="Q22">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R22">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S22">
         <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
         <v>1.71</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BH22">
         <v>5.2</v>
       </c>
       <c r="BI22">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="BJ22">
         <v>12</v>
@@ -6233,7 +6233,7 @@
         <v>7.4</v>
       </c>
       <c r="BO22">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP22">
         <v>21</v>
@@ -6298,7 +6298,7 @@
         <v>3.5</v>
       </c>
       <c r="H23">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I23">
         <v>2.3</v>
@@ -6310,10 +6310,10 @@
         <v>4.6</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N23">
         <v>6.2</v>
@@ -6322,16 +6322,16 @@
         <v>1.15</v>
       </c>
       <c r="P23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
         <v>1.47</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S23">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T23">
         <v>1.46</v>
@@ -6346,7 +6346,7 @@
         <v>1.4</v>
       </c>
       <c r="X23">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Y23">
         <v>18</v>
@@ -6355,7 +6355,7 @@
         <v>20</v>
       </c>
       <c r="AA23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB23">
         <v>23</v>
@@ -6370,7 +6370,7 @@
         <v>21</v>
       </c>
       <c r="AF23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG23">
         <v>15.5</v>
@@ -6385,7 +6385,7 @@
         <v>75</v>
       </c>
       <c r="AK23">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL23">
         <v>34</v>
@@ -6403,61 +6403,61 @@
         <v>6.8</v>
       </c>
       <c r="AQ23">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR23">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AS23">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AT23">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AU23">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV23">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW23">
         <v>14</v>
       </c>
       <c r="AX23">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AY23">
         <v>11</v>
       </c>
       <c r="AZ23">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA23">
         <v>18</v>
       </c>
       <c r="BB23">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BC23">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BD23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE23">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF23">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG23">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH23">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.3</v>
+        <v>2.04</v>
       </c>
       <c r="BJ23">
         <v>12</v>
@@ -6469,49 +6469,49 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="BN23">
         <v>10</v>
       </c>
       <c r="BO23">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP23">
         <v>30</v>
       </c>
       <c r="BQ23">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="BR23">
         <v>38</v>
       </c>
       <c r="BS23">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="BT23">
         <v>8</v>
       </c>
       <c r="BU23">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV23">
         <v>20</v>
       </c>
       <c r="BW23">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="BX23">
         <v>30</v>
       </c>
       <c r="BY23">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="BZ23">
         <v>19</v>
       </c>
       <c r="CA23">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="CB23" t="s">
         <v>200</v>
@@ -6534,7 +6534,7 @@
         <v>182</v>
       </c>
       <c r="F24">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G24">
         <v>1.77</v>
@@ -6552,31 +6552,31 @@
         <v>4.4</v>
       </c>
       <c r="L24">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="M24">
         <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O24">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P24">
         <v>1.82</v>
       </c>
       <c r="Q24">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R24">
         <v>1.31</v>
       </c>
       <c r="S24">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="T24">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U24">
         <v>1.85</v>
@@ -6585,13 +6585,13 @@
         <v>1.17</v>
       </c>
       <c r="W24">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y24">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Z24">
         <v>55</v>
@@ -6600,10 +6600,10 @@
         <v>210</v>
       </c>
       <c r="AB24">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD24">
         <v>25</v>
@@ -6612,7 +6612,7 @@
         <v>120</v>
       </c>
       <c r="AF24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6630,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="AL24">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM24">
         <v>170</v>
@@ -6642,118 +6642,118 @@
         <v>160</v>
       </c>
       <c r="AP24">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ24">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR24">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS24">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT24">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24">
         <v>20</v>
       </c>
       <c r="AW24">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AX24">
         <v>8.199999999999999</v>
       </c>
       <c r="AY24">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA24">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="BB24">
         <v>14.5</v>
       </c>
       <c r="BC24">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD24">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BE24">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BG24">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.87</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>200</v>
@@ -6782,16 +6782,16 @@
         <v>2.4</v>
       </c>
       <c r="H25">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I25">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K25">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6800,16 +6800,16 @@
         <v>1.03</v>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O25">
         <v>1.15</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q25">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R25">
         <v>1.61</v>
@@ -6824,7 +6824,7 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
         <v>1.71</v>
@@ -6842,37 +6842,37 @@
         <v>1000</v>
       </c>
       <c r="AB25">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
         <v>1000</v>
       </c>
       <c r="AD25">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
         <v>1000</v>
       </c>
       <c r="AH25">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
         <v>1000</v>
       </c>
       <c r="AL25">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
         <v>1000</v>
@@ -6884,58 +6884,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7030,7 +7030,7 @@
         <v>1.71</v>
       </c>
       <c r="J26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K26">
         <v>5.4</v>
@@ -7042,22 +7042,22 @@
         <v>1.02</v>
       </c>
       <c r="N26">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O26">
         <v>1.13</v>
       </c>
       <c r="P26">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="Q26">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R26">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S26">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="T26">
         <v>1.29</v>
@@ -7075,163 +7075,163 @@
         <v>1000</v>
       </c>
       <c r="Y26">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
         <v>1000</v>
       </c>
       <c r="AK26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
         <v>1000</v>
       </c>
       <c r="AN26">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>2.58</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7260,25 +7260,25 @@
         <v>185</v>
       </c>
       <c r="F27">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="G27">
         <v>3.45</v>
       </c>
       <c r="H27">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I27">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J27">
         <v>3.2</v>
       </c>
       <c r="K27">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L27">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="M27">
         <v>1.01</v>
@@ -7293,10 +7293,10 @@
         <v>1.64</v>
       </c>
       <c r="Q27">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S27">
         <v>3.35</v>
@@ -7308,172 +7308,172 @@
         <v>1.58</v>
       </c>
       <c r="V27">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X27">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z27">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA27">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB27">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC27">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE27">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG27">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI27">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL27">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM27">
         <v>1000</v>
       </c>
       <c r="AN27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO27">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP27">
-        <v>2.54</v>
+        <v>1.11</v>
       </c>
       <c r="AQ27">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="AR27">
-        <v>11</v>
+        <v>1.11</v>
       </c>
       <c r="AS27">
-        <v>2.84</v>
+        <v>1.11</v>
       </c>
       <c r="AT27">
-        <v>2.5</v>
+        <v>1.11</v>
       </c>
       <c r="AU27">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="AV27">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="AW27">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="AX27">
-        <v>14.5</v>
+        <v>1.11</v>
       </c>
       <c r="AY27">
-        <v>2.56</v>
+        <v>1.11</v>
       </c>
       <c r="AZ27">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="BA27">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="BB27">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="BC27">
-        <v>2.82</v>
+        <v>1.11</v>
       </c>
       <c r="BD27">
-        <v>2.86</v>
+        <v>1.11</v>
       </c>
       <c r="BE27">
-        <v>2.98</v>
+        <v>1.11</v>
       </c>
       <c r="BF27">
-        <v>2.82</v>
+        <v>1.11</v>
       </c>
       <c r="BG27">
-        <v>17.5</v>
+        <v>1.11</v>
       </c>
       <c r="BH27">
         <v>1000</v>
       </c>
       <c r="BI27">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK27">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BN27">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO27">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP27">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ27">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BR27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS27">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BT27">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU27">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV27">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW27">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX27">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7520,7 +7520,7 @@
         <v>3.25</v>
       </c>
       <c r="L28">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M28">
         <v>1.12</v>
@@ -7553,7 +7553,7 @@
         <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X28">
         <v>11</v>
@@ -7562,10 +7562,10 @@
         <v>11</v>
       </c>
       <c r="Z28">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AA28">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB28">
         <v>7.8</v>
@@ -7577,7 +7577,7 @@
         <v>17.5</v>
       </c>
       <c r="AE28">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF28">
         <v>14</v>
@@ -7586,40 +7586,40 @@
         <v>13</v>
       </c>
       <c r="AH28">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI28">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ28">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK28">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL28">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM28">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN28">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AO28">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP28">
         <v>7.6</v>
       </c>
       <c r="AQ28">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR28">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS28">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT28">
         <v>6.4</v>
@@ -7631,7 +7631,7 @@
         <v>14</v>
       </c>
       <c r="AW28">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX28">
         <v>11</v>
@@ -7643,85 +7643,85 @@
         <v>19.5</v>
       </c>
       <c r="BA28">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BB28">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC28">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD28">
+        <v>6.8</v>
+      </c>
+      <c r="BE28">
+        <v>7.2</v>
+      </c>
+      <c r="BF28">
+        <v>6.2</v>
+      </c>
+      <c r="BG28">
         <v>7</v>
       </c>
-      <c r="BE28">
-        <v>7.6</v>
-      </c>
-      <c r="BF28">
-        <v>6.4</v>
-      </c>
-      <c r="BG28">
-        <v>7.4</v>
-      </c>
       <c r="BH28">
-        <v>2.82</v>
+        <v>1000</v>
       </c>
       <c r="BI28">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL28">
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN28">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP28">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR28">
         <v>1000</v>
       </c>
       <c r="BS28">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT28">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV28">
         <v>1000</v>
       </c>
       <c r="BW28">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX28">
         <v>1000</v>
       </c>
       <c r="BY28">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ28">
         <v>1000</v>
       </c>
       <c r="CA28">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB28" t="s">
         <v>200</v>
@@ -7744,43 +7744,43 @@
         <v>187</v>
       </c>
       <c r="F29">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G29">
         <v>1.86</v>
       </c>
       <c r="H29">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I29">
         <v>6.2</v>
       </c>
       <c r="J29">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K29">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M29">
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O29">
         <v>1.29</v>
       </c>
       <c r="P29">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q29">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S29">
         <v>3.1</v>
@@ -7906,64 +7906,64 @@
         <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
       </c>
       <c r="BK29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BN29">
         <v>1000</v>
       </c>
       <c r="BO29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP29">
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT29">
         <v>1000</v>
       </c>
       <c r="BU29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV29">
         <v>1000</v>
       </c>
       <c r="BW29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BX29">
         <v>1000</v>
       </c>
       <c r="BY29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29">
         <v>1000</v>
       </c>
       <c r="CA29">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="s">
         <v>200</v>
@@ -7986,22 +7986,22 @@
         <v>188</v>
       </c>
       <c r="F30">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="G30">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="H30">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I30">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8016,16 +8016,16 @@
         <v>1.24</v>
       </c>
       <c r="P30">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q30">
         <v>1.64</v>
       </c>
       <c r="R30">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S30">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T30">
         <v>1.66</v>
@@ -8034,10 +8034,10 @@
         <v>1.87</v>
       </c>
       <c r="V30">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="W30">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8228,7 +8228,7 @@
         <v>189</v>
       </c>
       <c r="F31">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G31">
         <v>3.2</v>
@@ -8252,7 +8252,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O31">
         <v>1.32</v>
@@ -8261,13 +8261,13 @@
         <v>1.83</v>
       </c>
       <c r="Q31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T31">
         <v>1.11</v>
@@ -8470,22 +8470,22 @@
         <v>190</v>
       </c>
       <c r="F32">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="G32">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H32">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I32">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J32">
         <v>3.5</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8497,31 +8497,31 @@
         <v>4.1</v>
       </c>
       <c r="O32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P32">
         <v>2.14</v>
       </c>
       <c r="Q32">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R32">
         <v>1.44</v>
       </c>
       <c r="S32">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T32">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U32">
         <v>1.11</v>
       </c>
       <c r="V32">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8712,28 +8712,28 @@
         <v>191</v>
       </c>
       <c r="F33">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G33">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H33">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I33">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="J33">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K33">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="L33">
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N33">
         <v>4.1</v>
@@ -8742,25 +8742,25 @@
         <v>1.22</v>
       </c>
       <c r="P33">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q33">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R33">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S33">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T33">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V33">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="W33">
         <v>1.31</v>
@@ -8769,109 +8769,109 @@
         <v>1000</v>
       </c>
       <c r="Y33">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
         <v>1000</v>
       </c>
       <c r="AN33">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -8954,28 +8954,28 @@
         <v>192</v>
       </c>
       <c r="F34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G34">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H34">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I34">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K34">
         <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N34">
         <v>3.75</v>
@@ -8990,67 +8990,67 @@
         <v>1.89</v>
       </c>
       <c r="R34">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S34">
-        <v>1.94</v>
+        <v>3.25</v>
       </c>
       <c r="T34">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V34">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y34">
         <v>12</v>
       </c>
       <c r="Z34">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AA34">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB34">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD34">
         <v>13</v>
       </c>
       <c r="AE34">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AF34">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG34">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH34">
         <v>17</v>
       </c>
       <c r="AI34">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AJ34">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK34">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AL34">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM34">
         <v>100</v>
@@ -9062,55 +9062,55 @@
         <v>19.5</v>
       </c>
       <c r="AP34">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ34">
+        <v>8.4</v>
+      </c>
+      <c r="AR34">
+        <v>11.5</v>
+      </c>
+      <c r="AS34">
+        <v>4.7</v>
+      </c>
+      <c r="AT34">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR34">
-        <v>13.5</v>
-      </c>
-      <c r="AS34">
-        <v>7</v>
-      </c>
-      <c r="AT34">
-        <v>11</v>
-      </c>
       <c r="AU34">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV34">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AW34">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX34">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY34">
+        <v>10</v>
+      </c>
+      <c r="AZ34">
         <v>11.5</v>
       </c>
-      <c r="AZ34">
-        <v>13.5</v>
-      </c>
       <c r="BA34">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB34">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BC34">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD34">
         <v>32</v>
       </c>
       <c r="BE34">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BF34">
-        <v>26</v>
+        <v>4.8</v>
       </c>
       <c r="BG34">
         <v>13.5</v>
@@ -9119,55 +9119,55 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK34">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL34">
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="BN34">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO34">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP34">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ34">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BR34">
         <v>1000</v>
       </c>
       <c r="BS34">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BT34">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU34">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV34">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW34">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BX34">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY34">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34">
         <v>0</v>
@@ -9438,46 +9438,46 @@
         <v>194</v>
       </c>
       <c r="F36">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H36">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="I36">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J36">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K36">
-        <v>7.2</v>
+        <v>4.8</v>
       </c>
       <c r="L36">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
         <v>1.01</v>
       </c>
       <c r="N36">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O36">
         <v>1.11</v>
       </c>
       <c r="P36">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R36">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S36">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T36">
         <v>1.11</v>
@@ -9486,10 +9486,10 @@
         <v>1.11</v>
       </c>
       <c r="V36">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9940,7 +9940,7 @@
         <v>3.4</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M38">
         <v>1.14</v>
@@ -9949,22 +9949,22 @@
         <v>2.36</v>
       </c>
       <c r="O38">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P38">
         <v>1.46</v>
       </c>
       <c r="Q38">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="R38">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S38">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T38">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U38">
         <v>1.55</v>
@@ -9976,10 +9976,10 @@
         <v>2.08</v>
       </c>
       <c r="X38">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z38">
         <v>55</v>
@@ -9994,16 +9994,16 @@
         <v>8.4</v>
       </c>
       <c r="AD38">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE38">
         <v>190</v>
       </c>
       <c r="AF38">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AG38">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH38">
         <v>38</v>
@@ -10018,13 +10018,13 @@
         <v>32</v>
       </c>
       <c r="AL38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM38">
         <v>410</v>
       </c>
       <c r="AN38">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO38">
         <v>380</v>
@@ -10036,10 +10036,10 @@
         <v>11.5</v>
       </c>
       <c r="AR38">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="AS38">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AT38">
         <v>5</v>
@@ -10048,10 +10048,10 @@
         <v>6.8</v>
       </c>
       <c r="AV38">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AW38">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="AX38">
         <v>8</v>
@@ -10060,88 +10060,88 @@
         <v>10</v>
       </c>
       <c r="AZ38">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BA38">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BB38">
         <v>18.5</v>
       </c>
       <c r="BC38">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BD38">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BE38">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BF38">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG38">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BH38">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI38">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="BJ38">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BK38">
-        <v>1.49</v>
+        <v>6.4</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>1.61</v>
+        <v>11</v>
       </c>
       <c r="BN38">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BO38">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="BP38">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BQ38">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS38">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="BT38">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU38">
-        <v>1.44</v>
+        <v>5.3</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>1.61</v>
+        <v>10</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>1.61</v>
+        <v>10.5</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA38">
-        <v>1.57</v>
+        <v>9.4</v>
       </c>
       <c r="CB38" t="s">
         <v>200</v>
@@ -10430,19 +10430,19 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O40">
         <v>1.05</v>
       </c>
       <c r="P40">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q40">
         <v>1.05</v>
       </c>
       <c r="R40">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S40">
         <v>1.05</v>
@@ -10648,7 +10648,7 @@
         <v>199</v>
       </c>
       <c r="F41">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G41">
         <v>1.91</v>
@@ -10657,13 +10657,13 @@
         <v>4.8</v>
       </c>
       <c r="I41">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
         <v>3.6</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10672,28 +10672,28 @@
         <v>1.07</v>
       </c>
       <c r="N41">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="O41">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P41">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q41">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R41">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S41">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T41">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="U41">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V41">
         <v>1.2</v>
@@ -10702,112 +10702,112 @@
         <v>2.1</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y41">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z41">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB41">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AC41">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AD41">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AE41">
         <v>100</v>
       </c>
       <c r="AF41">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AG41">
+        <v>11</v>
+      </c>
+      <c r="AH41">
+        <v>22</v>
+      </c>
+      <c r="AI41">
+        <v>80</v>
+      </c>
+      <c r="AJ41">
+        <v>21</v>
+      </c>
+      <c r="AK41">
+        <v>21</v>
+      </c>
+      <c r="AL41">
+        <v>48</v>
+      </c>
+      <c r="AM41">
+        <v>150</v>
+      </c>
+      <c r="AN41">
+        <v>13.5</v>
+      </c>
+      <c r="AO41">
+        <v>120</v>
+      </c>
+      <c r="AP41">
+        <v>11.5</v>
+      </c>
+      <c r="AQ41">
         <v>14.5</v>
       </c>
-      <c r="AH41">
-        <v>950</v>
-      </c>
-      <c r="AI41">
-        <v>100</v>
-      </c>
-      <c r="AJ41">
-        <v>28</v>
-      </c>
-      <c r="AK41">
-        <v>28</v>
-      </c>
-      <c r="AL41">
-        <v>55</v>
-      </c>
-      <c r="AM41">
-        <v>1000</v>
-      </c>
-      <c r="AN41">
-        <v>18</v>
-      </c>
-      <c r="AO41">
-        <v>1000</v>
-      </c>
-      <c r="AP41">
-        <v>2.52</v>
-      </c>
-      <c r="AQ41">
-        <v>11</v>
-      </c>
       <c r="AR41">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS41">
-        <v>2.52</v>
+        <v>7.4</v>
       </c>
       <c r="AT41">
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="AU41">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="AV41">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AW41">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="AX41">
-        <v>2.16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY41">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ41">
-        <v>2.32</v>
+        <v>17.5</v>
       </c>
       <c r="BA41">
-        <v>2.46</v>
+        <v>7</v>
       </c>
       <c r="BB41">
-        <v>2.32</v>
+        <v>16.5</v>
       </c>
       <c r="BC41">
-        <v>2.32</v>
+        <v>16.5</v>
       </c>
       <c r="BD41">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE41">
-        <v>2.52</v>
+        <v>7.4</v>
       </c>
       <c r="BF41">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG41">
-        <v>2.52</v>
+        <v>7.2</v>
       </c>
       <c r="BH41">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -709,7 +709,7 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
-    <t>2026-07-23 03:47:31</t>
+    <t>2026-07-23 05:56:42</t>
   </si>
 </sst>
 </file>
@@ -1303,16 +1303,16 @@
         <v>181</v>
       </c>
       <c r="F2">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G2">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="H2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J2">
         <v>3.65</v>
@@ -1333,7 +1333,7 @@
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q2">
         <v>2.16</v>
@@ -1345,16 +1345,16 @@
         <v>4</v>
       </c>
       <c r="T2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U2">
         <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1548,7 +1548,7 @@
         <v>2.68</v>
       </c>
       <c r="G3">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
         <v>3.25</v>
@@ -1557,7 +1557,7 @@
         <v>3.45</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1569,13 +1569,13 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O3">
         <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q3">
         <v>2.74</v>
@@ -1596,7 +1596,7 @@
         <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X3">
         <v>8</v>
@@ -1796,55 +1796,55 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O4">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P4">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q4">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
         <v>2</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>40</v>
@@ -1856,13 +1856,13 @@
         <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
@@ -1877,25 +1877,25 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AK4">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AL4">
         <v>1000</v>
       </c>
       <c r="AM4">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4">
         <v>11</v>
@@ -1907,7 +1907,7 @@
         <v>42</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1922,10 +1922,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4">
         <v>42</v>
@@ -1952,19 +1952,19 @@
         <v>2.72</v>
       </c>
       <c r="BI4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
@@ -1973,40 +1973,40 @@
         <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
         <v>8.800000000000001</v>
       </c>
       <c r="BU4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
+        <v>10</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>11</v>
+      </c>
+      <c r="BZ4">
+        <v>46</v>
+      </c>
+      <c r="CA4">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>10</v>
-      </c>
-      <c r="BZ4">
-        <v>48</v>
-      </c>
-      <c r="CA4">
-        <v>9.4</v>
       </c>
       <c r="CB4" t="s">
         <v>231</v>
@@ -2340,7 +2340,7 @@
         <v>10.5</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD6">
         <v>27</v>
@@ -2358,7 +2358,7 @@
         <v>24</v>
       </c>
       <c r="AI6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ6">
         <v>18</v>
@@ -2385,10 +2385,10 @@
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AS6">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT6">
         <v>7.8</v>
@@ -2400,7 +2400,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX6">
         <v>8.199999999999999</v>
@@ -2412,7 +2412,7 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2421,16 +2421,16 @@
         <v>12</v>
       </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF6">
         <v>5.9</v>
       </c>
       <c r="BG6">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2758,7 +2758,7 @@
         <v>1.84</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H8">
         <v>3.9</v>
@@ -2806,7 +2806,7 @@
         <v>1.27</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2997,178 +2997,178 @@
         <v>188</v>
       </c>
       <c r="F9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G9">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="H9">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I9">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J9">
         <v>2.96</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P9">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R9">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA9">
         <v>55</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC9">
         <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE9">
         <v>38</v>
       </c>
       <c r="AF9">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI9">
+        <v>55</v>
+      </c>
+      <c r="AJ9">
         <v>50</v>
-      </c>
-      <c r="AJ9">
-        <v>48</v>
       </c>
       <c r="AK9">
         <v>36</v>
       </c>
       <c r="AL9">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP9">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="AQ9">
+        <v>3.35</v>
+      </c>
+      <c r="AR9">
+        <v>3.65</v>
+      </c>
+      <c r="AS9">
+        <v>4</v>
+      </c>
+      <c r="AT9">
+        <v>3.3</v>
+      </c>
+      <c r="AU9">
+        <v>3</v>
+      </c>
+      <c r="AV9">
+        <v>3.4</v>
+      </c>
+      <c r="AW9">
+        <v>3.9</v>
+      </c>
+      <c r="AX9">
+        <v>3.65</v>
+      </c>
+      <c r="AY9">
+        <v>3.35</v>
+      </c>
+      <c r="AZ9">
+        <v>3.6</v>
+      </c>
+      <c r="BA9">
+        <v>4</v>
+      </c>
+      <c r="BB9">
+        <v>4</v>
+      </c>
+      <c r="BC9">
+        <v>3.85</v>
+      </c>
+      <c r="BD9">
+        <v>4</v>
+      </c>
+      <c r="BE9">
         <v>4.2</v>
       </c>
-      <c r="AR9">
-        <v>4.8</v>
-      </c>
-      <c r="AS9">
-        <v>5.6</v>
-      </c>
-      <c r="AT9">
-        <v>4.1</v>
-      </c>
-      <c r="AU9">
+      <c r="BF9">
+        <v>3.7</v>
+      </c>
+      <c r="BG9">
         <v>3.8</v>
       </c>
-      <c r="AV9">
-        <v>4.2</v>
-      </c>
-      <c r="AW9">
-        <v>5.3</v>
-      </c>
-      <c r="AX9">
-        <v>4.7</v>
-      </c>
-      <c r="AY9">
-        <v>4.2</v>
-      </c>
-      <c r="AZ9">
-        <v>4.6</v>
-      </c>
-      <c r="BA9">
-        <v>5.5</v>
-      </c>
-      <c r="BB9">
-        <v>5.5</v>
-      </c>
-      <c r="BC9">
-        <v>5.3</v>
-      </c>
-      <c r="BD9">
-        <v>5.4</v>
-      </c>
-      <c r="BE9">
-        <v>5.9</v>
-      </c>
-      <c r="BF9">
-        <v>4.9</v>
-      </c>
-      <c r="BG9">
-        <v>5.1</v>
-      </c>
       <c r="BH9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI9">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="BJ9">
         <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3186,31 +3186,31 @@
         <v>21</v>
       </c>
       <c r="BQ9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT9">
         <v>6.2</v>
       </c>
       <c r="BU9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BV9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -3481,7 +3481,7 @@
         <v>190</v>
       </c>
       <c r="F11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G11">
         <v>3.5</v>
@@ -3493,10 +3493,10 @@
         <v>2.22</v>
       </c>
       <c r="J11">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K11">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.26</v>
@@ -3505,28 +3505,28 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T11">
         <v>1.62</v>
       </c>
       <c r="U11">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
         <v>1.82</v>
@@ -3535,7 +3535,7 @@
         <v>1.4</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y11">
         <v>13.5</v>
@@ -3547,7 +3547,7 @@
         <v>30</v>
       </c>
       <c r="AB11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC11">
         <v>9.199999999999999</v>
@@ -3559,13 +3559,13 @@
         <v>21</v>
       </c>
       <c r="AF11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI11">
         <v>30</v>
@@ -3577,7 +3577,7 @@
         <v>38</v>
       </c>
       <c r="AL11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM11">
         <v>70</v>
@@ -3589,7 +3589,7 @@
         <v>12</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
         <v>11.5</v>
@@ -3604,7 +3604,7 @@
         <v>15.5</v>
       </c>
       <c r="AU11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11">
         <v>10</v>
@@ -3616,7 +3616,7 @@
         <v>24</v>
       </c>
       <c r="AY11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ11">
         <v>14</v>
@@ -3637,7 +3637,7 @@
         <v>55</v>
       </c>
       <c r="BF11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG11">
         <v>10.5</v>
@@ -3658,19 +3658,19 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN11">
         <v>7.4</v>
       </c>
       <c r="BO11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP11">
         <v>26</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR11">
         <v>34</v>
@@ -3723,13 +3723,13 @@
         <v>191</v>
       </c>
       <c r="F12">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="G12">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I12">
         <v>990</v>
@@ -3759,7 +3759,7 @@
         <v>1.49</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
         <v>1.5</v>
@@ -3774,7 +3774,7 @@
         <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4330,7 +4330,7 @@
         <v>3.95</v>
       </c>
       <c r="AU14">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AV14">
         <v>4.2</v>
@@ -4339,16 +4339,16 @@
         <v>4.8</v>
       </c>
       <c r="AX14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AY14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AZ14">
         <v>4.1</v>
       </c>
       <c r="BA14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB14">
         <v>4.7</v>
@@ -4363,10 +4363,10 @@
         <v>5.1</v>
       </c>
       <c r="BF14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH14">
         <v>3.95</v>
@@ -4452,7 +4452,7 @@
         <v>2.46</v>
       </c>
       <c r="G15">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H15">
         <v>2.8</v>
@@ -4467,7 +4467,7 @@
         <v>3.85</v>
       </c>
       <c r="L15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M15">
         <v>1.06</v>
@@ -4482,7 +4482,7 @@
         <v>1.78</v>
       </c>
       <c r="Q15">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
         <v>1.36</v>
@@ -4500,7 +4500,7 @@
         <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X15">
         <v>18</v>
@@ -4706,7 +4706,7 @@
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.23</v>
@@ -4724,10 +4724,10 @@
         <v>2.26</v>
       </c>
       <c r="Q16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16">
         <v>2.64</v>
@@ -4933,58 +4933,58 @@
         <v>196</v>
       </c>
       <c r="F17">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G17">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="H17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I17">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M17">
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O17">
         <v>1.23</v>
       </c>
       <c r="P17">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R17">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S17">
         <v>2.72</v>
       </c>
       <c r="T17">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X17">
         <v>24</v>
@@ -4996,7 +4996,7 @@
         <v>40</v>
       </c>
       <c r="AA17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>13.5</v>
@@ -5038,7 +5038,7 @@
         <v>12</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP17">
         <v>17.5</v>
@@ -5062,7 +5062,7 @@
         <v>14.5</v>
       </c>
       <c r="AW17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX17">
         <v>11</v>
@@ -5074,7 +5074,7 @@
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB17">
         <v>18.5</v>
@@ -5083,13 +5083,13 @@
         <v>15.5</v>
       </c>
       <c r="BD17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE17">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF17">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG17">
         <v>4.4</v>
@@ -5098,61 +5098,61 @@
         <v>4.2</v>
       </c>
       <c r="BI17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ17">
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL17">
         <v>95</v>
       </c>
       <c r="BM17">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP17">
         <v>13.5</v>
       </c>
       <c r="BQ17">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS17">
         <v>7.2</v>
       </c>
       <c r="BT17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU17">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV17">
         <v>32</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ17">
         <v>18.5</v>
       </c>
       <c r="CA17">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="s">
         <v>231</v>
@@ -5178,7 +5178,7 @@
         <v>1.59</v>
       </c>
       <c r="G18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -5199,43 +5199,43 @@
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O18">
         <v>1.19</v>
       </c>
       <c r="P18">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q18">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S18">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T18">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V18">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W18">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X18">
         <v>25</v>
       </c>
       <c r="Y18">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA18">
         <v>160</v>
@@ -5247,13 +5247,13 @@
         <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE18">
         <v>75</v>
       </c>
       <c r="AF18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -5265,7 +5265,7 @@
         <v>65</v>
       </c>
       <c r="AJ18">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK18">
         <v>15.5</v>
@@ -5283,7 +5283,7 @@
         <v>60</v>
       </c>
       <c r="AP18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ18">
         <v>25</v>
@@ -5292,19 +5292,19 @@
         <v>46</v>
       </c>
       <c r="AS18">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AT18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU18">
         <v>10</v>
       </c>
       <c r="AV18">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW18">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AX18">
         <v>10</v>
@@ -5322,25 +5322,25 @@
         <v>13.5</v>
       </c>
       <c r="BC18">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD18">
         <v>23</v>
       </c>
       <c r="BE18">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BF18">
         <v>5.7</v>
       </c>
       <c r="BG18">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH18">
         <v>4.7</v>
       </c>
       <c r="BI18">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BJ18">
         <v>10</v>
@@ -5426,10 +5426,10 @@
         <v>2.26</v>
       </c>
       <c r="I19">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
         <v>4.3</v>
@@ -5441,16 +5441,16 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O19">
         <v>1.19</v>
       </c>
       <c r="P19">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q19">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
         <v>1.57</v>
@@ -5513,7 +5513,7 @@
         <v>30</v>
       </c>
       <c r="AL19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM19">
         <v>75</v>
@@ -5618,7 +5618,7 @@
         <v>6</v>
       </c>
       <c r="BU19">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BV19">
         <v>16.5</v>
@@ -5731,7 +5731,7 @@
         <v>14</v>
       </c>
       <c r="AD20">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20">
         <v>50</v>
@@ -5767,16 +5767,16 @@
         <v>27</v>
       </c>
       <c r="AP20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ20">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS20">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT20">
         <v>13.5</v>
@@ -5788,7 +5788,7 @@
         <v>14.5</v>
       </c>
       <c r="AW20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX20">
         <v>12</v>
@@ -5800,7 +5800,7 @@
         <v>11.5</v>
       </c>
       <c r="BA20">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB20">
         <v>15</v>
@@ -5812,10 +5812,10 @@
         <v>15.5</v>
       </c>
       <c r="BE20">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF20">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG20">
         <v>17.5</v>
@@ -5842,7 +5842,7 @@
         <v>5.5</v>
       </c>
       <c r="BO20">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP20">
         <v>11</v>
@@ -6152,10 +6152,10 @@
         <v>2.06</v>
       </c>
       <c r="I22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J22">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
         <v>4.6</v>
@@ -6173,7 +6173,7 @@
         <v>1.15</v>
       </c>
       <c r="P22">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q22">
         <v>1.45</v>
@@ -6191,7 +6191,7 @@
         <v>2.72</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W22">
         <v>1.4</v>
@@ -6385,10 +6385,10 @@
         <v>202</v>
       </c>
       <c r="F23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G23">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H23">
         <v>3.15</v>
@@ -6403,7 +6403,7 @@
         <v>3.9</v>
       </c>
       <c r="L23">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M23">
         <v>1.05</v>
@@ -6436,7 +6436,7 @@
         <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X23">
         <v>24</v>
@@ -6636,7 +6636,7 @@
         <v>2.98</v>
       </c>
       <c r="I24">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J24">
         <v>3.85</v>
@@ -6675,7 +6675,7 @@
         <v>1.11</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
         <v>1.71</v>
@@ -6872,13 +6872,13 @@
         <v>5.1</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H25">
         <v>1.58</v>
       </c>
       <c r="I25">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J25">
         <v>4.5</v>
@@ -6902,7 +6902,7 @@
         <v>2.74</v>
       </c>
       <c r="Q25">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="R25">
         <v>1.69</v>
@@ -6917,7 +6917,7 @@
         <v>2.38</v>
       </c>
       <c r="V25">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="W25">
         <v>1.2</v>
@@ -7353,19 +7353,19 @@
         <v>206</v>
       </c>
       <c r="F27">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H27">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I27">
         <v>2.8</v>
       </c>
       <c r="J27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K27">
         <v>3.6</v>
@@ -7380,13 +7380,13 @@
         <v>3.3</v>
       </c>
       <c r="O27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R27">
         <v>1.29</v>
@@ -7401,10 +7401,10 @@
         <v>2.02</v>
       </c>
       <c r="V27">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W27">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X27">
         <v>13</v>
@@ -7428,7 +7428,7 @@
         <v>13</v>
       </c>
       <c r="AE27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF27">
         <v>22</v>
@@ -7497,7 +7497,7 @@
         <v>36</v>
       </c>
       <c r="BB27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC27">
         <v>30</v>
@@ -7506,10 +7506,10 @@
         <v>40</v>
       </c>
       <c r="BE27">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF27">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG27">
         <v>21</v>
@@ -7598,10 +7598,10 @@
         <v>2.28</v>
       </c>
       <c r="G28">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H28">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I28">
         <v>4.1</v>
@@ -7619,13 +7619,13 @@
         <v>1.12</v>
       </c>
       <c r="N28">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>1.51</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q28">
         <v>2.52</v>
@@ -7646,7 +7646,7 @@
         <v>1.32</v>
       </c>
       <c r="W28">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X28">
         <v>11</v>
@@ -7688,7 +7688,7 @@
         <v>40</v>
       </c>
       <c r="AK28">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL28">
         <v>75</v>
@@ -7703,7 +7703,7 @@
         <v>110</v>
       </c>
       <c r="AP28">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ28">
         <v>8.800000000000001</v>
@@ -7840,16 +7840,16 @@
         <v>2.52</v>
       </c>
       <c r="G29">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H29">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J29">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
         <v>4.2</v>
@@ -7867,31 +7867,31 @@
         <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q29">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R29">
         <v>1.46</v>
       </c>
       <c r="S29">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T29">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U29">
         <v>2.36</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W29">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y29">
         <v>17</v>
@@ -7903,7 +7903,7 @@
         <v>46</v>
       </c>
       <c r="AB29">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC29">
         <v>11</v>
@@ -7918,7 +7918,7 @@
         <v>24</v>
       </c>
       <c r="AG29">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH29">
         <v>19</v>
@@ -7939,7 +7939,7 @@
         <v>80</v>
       </c>
       <c r="AN29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO29">
         <v>22</v>
@@ -7954,7 +7954,7 @@
         <v>17</v>
       </c>
       <c r="AS29">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AT29">
         <v>11.5</v>
@@ -7966,7 +7966,7 @@
         <v>10.5</v>
       </c>
       <c r="AW29">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX29">
         <v>16.5</v>
@@ -7978,19 +7978,19 @@
         <v>13</v>
       </c>
       <c r="BA29">
+        <v>4</v>
+      </c>
+      <c r="BB29">
+        <v>4.1</v>
+      </c>
+      <c r="BC29">
         <v>3.95</v>
       </c>
-      <c r="BB29">
+      <c r="BD29">
         <v>4</v>
       </c>
-      <c r="BC29">
-        <v>3.9</v>
-      </c>
-      <c r="BD29">
-        <v>3.95</v>
-      </c>
       <c r="BE29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF29">
         <v>15.5</v>
@@ -8079,175 +8079,175 @@
         <v>209</v>
       </c>
       <c r="F30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H30">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I30">
         <v>2.34</v>
       </c>
       <c r="J30">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N30">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q30">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="R30">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S30">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U30">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
         <v>1.75</v>
       </c>
       <c r="W30">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X30">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB30">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC30">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE30">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF30">
         <v>30</v>
       </c>
       <c r="AG30">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AH30">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI30">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ30">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK30">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM30">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO30">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AP30">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ30">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR30">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS30">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AT30">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU30">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV30">
         <v>8.6</v>
       </c>
       <c r="AW30">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX30">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY30">
         <v>12.5</v>
       </c>
       <c r="AZ30">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA30">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB30">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC30">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD30">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BE30">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF30">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG30">
         <v>11.5</v>
       </c>
       <c r="BH30">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BI30">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ30">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK30">
         <v>4.9</v>
@@ -8265,13 +8265,13 @@
         <v>5.4</v>
       </c>
       <c r="BP30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ30">
         <v>7.4</v>
       </c>
       <c r="BR30">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS30">
         <v>8</v>
@@ -8283,13 +8283,13 @@
         <v>4.1</v>
       </c>
       <c r="BV30">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW30">
         <v>6.2</v>
       </c>
       <c r="BX30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY30">
         <v>7.4</v>
@@ -8321,22 +8321,22 @@
         <v>210</v>
       </c>
       <c r="F31">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G31">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H31">
         <v>4.8</v>
       </c>
       <c r="I31">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J31">
         <v>3.75</v>
       </c>
       <c r="K31">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L31">
         <v>1.38</v>
@@ -8348,22 +8348,22 @@
         <v>3.75</v>
       </c>
       <c r="O31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P31">
         <v>1.94</v>
       </c>
       <c r="Q31">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R31">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T31">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U31">
         <v>2</v>
@@ -8372,10 +8372,10 @@
         <v>1.2</v>
       </c>
       <c r="W31">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X31">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y31">
         <v>22</v>
@@ -8405,7 +8405,7 @@
         <v>12.5</v>
       </c>
       <c r="AH31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI31">
         <v>90</v>
@@ -8423,10 +8423,10 @@
         <v>140</v>
       </c>
       <c r="AN31">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO31">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP31">
         <v>11</v>
@@ -8435,13 +8435,13 @@
         <v>13</v>
       </c>
       <c r="AR31">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AS31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT31">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU31">
         <v>6.6</v>
@@ -8450,7 +8450,7 @@
         <v>15</v>
       </c>
       <c r="AW31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AX31">
         <v>8</v>
@@ -8462,7 +8462,7 @@
         <v>14.5</v>
       </c>
       <c r="BA31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BB31">
         <v>13.5</v>
@@ -8471,10 +8471,10 @@
         <v>13.5</v>
       </c>
       <c r="BD31">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE31">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF31">
         <v>8.4</v>
@@ -8483,22 +8483,22 @@
         <v>4.1</v>
       </c>
       <c r="BH31">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI31">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ31">
         <v>10.5</v>
       </c>
       <c r="BK31">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN31">
         <v>4.6</v>
@@ -8510,37 +8510,37 @@
         <v>12.5</v>
       </c>
       <c r="BQ31">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR31">
         <v>28</v>
       </c>
       <c r="BS31">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT31">
         <v>9</v>
       </c>
       <c r="BU31">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV31">
         <v>46</v>
       </c>
       <c r="BW31">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX31">
         <v>55</v>
       </c>
       <c r="BY31">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ31">
         <v>23</v>
       </c>
       <c r="CA31">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB31" t="s">
         <v>231</v>
@@ -8563,13 +8563,13 @@
         <v>211</v>
       </c>
       <c r="F32">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G32">
         <v>3.15</v>
       </c>
       <c r="H32">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I32">
         <v>2.92</v>
@@ -8581,19 +8581,19 @@
         <v>3.8</v>
       </c>
       <c r="L32">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M32">
         <v>1.07</v>
       </c>
       <c r="N32">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O32">
         <v>1.33</v>
       </c>
       <c r="P32">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q32">
         <v>1.96</v>
@@ -8602,13 +8602,13 @@
         <v>1.32</v>
       </c>
       <c r="S32">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T32">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U32">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
         <v>1.52</v>
@@ -8805,37 +8805,37 @@
         <v>212</v>
       </c>
       <c r="F33">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G33">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="H33">
         <v>5.7</v>
       </c>
       <c r="I33">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L33">
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O33">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P33">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q33">
         <v>1.64</v>
@@ -8844,7 +8844,7 @@
         <v>1.33</v>
       </c>
       <c r="S33">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T33">
         <v>1.66</v>
@@ -8856,7 +8856,7 @@
         <v>1.15</v>
       </c>
       <c r="W33">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="X33">
         <v>21</v>
@@ -8868,7 +8868,7 @@
         <v>60</v>
       </c>
       <c r="AA33">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB33">
         <v>10.5</v>
@@ -8880,7 +8880,7 @@
         <v>27</v>
       </c>
       <c r="AE33">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF33">
         <v>12</v>
@@ -8889,40 +8889,40 @@
         <v>11.5</v>
       </c>
       <c r="AH33">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI33">
+        <v>80</v>
+      </c>
+      <c r="AJ33">
+        <v>18</v>
+      </c>
+      <c r="AK33">
+        <v>18.5</v>
+      </c>
+      <c r="AL33">
+        <v>36</v>
+      </c>
+      <c r="AM33">
+        <v>110</v>
+      </c>
+      <c r="AN33">
+        <v>8.6</v>
+      </c>
+      <c r="AO33">
         <v>90</v>
-      </c>
-      <c r="AJ33">
-        <v>18.5</v>
-      </c>
-      <c r="AK33">
-        <v>19.5</v>
-      </c>
-      <c r="AL33">
-        <v>40</v>
-      </c>
-      <c r="AM33">
-        <v>130</v>
-      </c>
-      <c r="AN33">
-        <v>10</v>
-      </c>
-      <c r="AO33">
-        <v>110</v>
       </c>
       <c r="AP33">
         <v>15</v>
       </c>
       <c r="AQ33">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR33">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS33">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT33">
         <v>7.8</v>
@@ -8934,7 +8934,7 @@
         <v>20</v>
       </c>
       <c r="AW33">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX33">
         <v>8.800000000000001</v>
@@ -8946,25 +8946,25 @@
         <v>17.5</v>
       </c>
       <c r="BA33">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB33">
         <v>13.5</v>
       </c>
       <c r="BC33">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD33">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE33">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF33">
         <v>6.8</v>
       </c>
       <c r="BG33">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9047,25 +9047,25 @@
         <v>213</v>
       </c>
       <c r="F34">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="G34">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H34">
         <v>2.3</v>
       </c>
       <c r="I34">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="J34">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L34">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="M34">
         <v>1.07</v>
@@ -9086,19 +9086,19 @@
         <v>1.37</v>
       </c>
       <c r="S34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T34">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U34">
         <v>2.2</v>
       </c>
       <c r="V34">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W34">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X34">
         <v>17</v>
@@ -9107,34 +9107,34 @@
         <v>12</v>
       </c>
       <c r="Z34">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AA34">
         <v>34</v>
       </c>
       <c r="AB34">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC34">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE34">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF34">
         <v>25</v>
       </c>
       <c r="AG34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH34">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI34">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ34">
         <v>60</v>
@@ -9143,7 +9143,7 @@
         <v>40</v>
       </c>
       <c r="AL34">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM34">
         <v>95</v>
@@ -9164,13 +9164,13 @@
         <v>13.5</v>
       </c>
       <c r="AS34">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT34">
         <v>11</v>
       </c>
       <c r="AU34">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV34">
         <v>10.5</v>
@@ -9182,16 +9182,16 @@
         <v>20</v>
       </c>
       <c r="AY34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34">
         <v>11.5</v>
       </c>
       <c r="BA34">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB34">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BC34">
         <v>29</v>
@@ -9200,10 +9200,10 @@
         <v>32</v>
       </c>
       <c r="BE34">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF34">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG34">
         <v>13.5</v>
@@ -9224,7 +9224,7 @@
         <v>1000</v>
       </c>
       <c r="BM34">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN34">
         <v>7</v>
@@ -9251,7 +9251,7 @@
         <v>4</v>
       </c>
       <c r="BV34">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW34">
         <v>6.4</v>
@@ -9295,13 +9295,13 @@
         <v>990</v>
       </c>
       <c r="H35">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="I35">
         <v>990</v>
       </c>
       <c r="J35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -9546,7 +9546,7 @@
         <v>4.1</v>
       </c>
       <c r="K36">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L36">
         <v>1.2</v>
@@ -9555,7 +9555,7 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="O36">
         <v>1.14</v>
@@ -9573,13 +9573,13 @@
         <v>2.06</v>
       </c>
       <c r="T36">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U36">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.75</v>
@@ -9687,7 +9687,7 @@
         <v>6.8</v>
       </c>
       <c r="BF36">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="BG36">
         <v>5.5</v>
@@ -9797,7 +9797,7 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O37">
         <v>1.07</v>
@@ -10015,22 +10015,22 @@
         <v>217</v>
       </c>
       <c r="F38">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G38">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="H38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I38">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K38">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L38">
         <v>1.54</v>
@@ -10039,37 +10039,37 @@
         <v>1.15</v>
       </c>
       <c r="N38">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P38">
         <v>1.46</v>
       </c>
       <c r="Q38">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S38">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T38">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U38">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V38">
         <v>1.2</v>
       </c>
       <c r="W38">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="X38">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Y38">
         <v>12.5</v>
@@ -10078,34 +10078,34 @@
         <v>44</v>
       </c>
       <c r="AA38">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="AC38">
         <v>8</v>
       </c>
       <c r="AD38">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE38">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF38">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG38">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH38">
         <v>36</v>
       </c>
       <c r="AI38">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ38">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK38">
         <v>32</v>
@@ -10117,73 +10117,73 @@
         <v>390</v>
       </c>
       <c r="AN38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO38">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AP38">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR38">
-        <v>5.6</v>
+        <v>22</v>
       </c>
       <c r="AS38">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="AT38">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU38">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV38">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW38">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="AX38">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AY38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ38">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="BA38">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="BB38">
         <v>18.5</v>
       </c>
       <c r="BC38">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="BD38">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="BE38">
-        <v>6.4</v>
+        <v>95</v>
       </c>
       <c r="BF38">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG38">
-        <v>6.2</v>
+        <v>48</v>
       </c>
       <c r="BH38">
         <v>2.6</v>
       </c>
       <c r="BI38">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ38">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BK38">
         <v>6.2</v>
@@ -10192,7 +10192,7 @@
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN38">
         <v>4.3</v>
@@ -10204,37 +10204,37 @@
         <v>16.5</v>
       </c>
       <c r="BQ38">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR38">
         <v>50</v>
       </c>
       <c r="BS38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT38">
         <v>9.800000000000001</v>
       </c>
       <c r="BU38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV38">
         <v>1000</v>
       </c>
       <c r="BW38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX38">
         <v>1000</v>
       </c>
       <c r="BY38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ38">
         <v>55</v>
       </c>
       <c r="CA38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB38" t="s">
         <v>231</v>
@@ -10257,13 +10257,13 @@
         <v>218</v>
       </c>
       <c r="F39">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="G39">
         <v>990</v>
       </c>
       <c r="H39">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="I39">
         <v>990</v>
@@ -10281,7 +10281,7 @@
         <v>1.01</v>
       </c>
       <c r="N39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O39">
         <v>1.06</v>
@@ -10750,7 +10750,7 @@
         <v>4.4</v>
       </c>
       <c r="I41">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J41">
         <v>3.6</v>
@@ -10801,7 +10801,7 @@
         <v>21</v>
       </c>
       <c r="Z41">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA41">
         <v>150</v>
@@ -10819,7 +10819,7 @@
         <v>85</v>
       </c>
       <c r="AF41">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG41">
         <v>12.5</v>
@@ -10849,58 +10849,58 @@
         <v>95</v>
       </c>
       <c r="AP41">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AQ41">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR41">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AS41">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AT41">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AU41">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AV41">
         <v>3.7</v>
       </c>
       <c r="AW41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX41">
         <v>3.3</v>
       </c>
       <c r="AY41">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ41">
         <v>3.7</v>
       </c>
       <c r="BA41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB41">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BC41">
         <v>3.7</v>
       </c>
       <c r="BD41">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE41">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF41">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11228,16 +11228,16 @@
         <v>2.18</v>
       </c>
       <c r="G43">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H43">
         <v>4.1</v>
       </c>
       <c r="I43">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J43">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K43">
         <v>3.15</v>
@@ -11470,7 +11470,7 @@
         <v>1.85</v>
       </c>
       <c r="G44">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H44">
         <v>5.1</v>
@@ -11500,7 +11500,7 @@
         <v>1.59</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R44">
         <v>1.2</v>
@@ -11518,7 +11518,7 @@
         <v>1.2</v>
       </c>
       <c r="W44">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X44">
         <v>9.4</v>
@@ -11742,13 +11742,13 @@
         <v>1.25</v>
       </c>
       <c r="Q45">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R45">
         <v>1.18</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T45">
         <v>1.11</v>
@@ -11954,16 +11954,16 @@
         <v>1.81</v>
       </c>
       <c r="G46">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H46">
         <v>4.3</v>
       </c>
       <c r="I46">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J46">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="K46">
         <v>3.95</v>
@@ -11999,10 +11999,10 @@
         <v>1.93</v>
       </c>
       <c r="V46">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W46">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="X46">
         <v>16</v>
@@ -12205,7 +12205,7 @@
         <v>3.45</v>
       </c>
       <c r="J47">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K47">
         <v>4</v>
@@ -12217,7 +12217,7 @@
         <v>1.05</v>
       </c>
       <c r="N47">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O47">
         <v>1.25</v>
@@ -12358,61 +12358,61 @@
         <v>3.9</v>
       </c>
       <c r="BI47">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ47">
         <v>9.199999999999999</v>
       </c>
       <c r="BK47">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL47">
         <v>1000</v>
       </c>
       <c r="BM47">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BN47">
         <v>5.5</v>
       </c>
       <c r="BO47">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP47">
         <v>16.5</v>
       </c>
       <c r="BQ47">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR47">
         <v>27</v>
       </c>
       <c r="BS47">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT47">
         <v>6.8</v>
       </c>
       <c r="BU47">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV47">
         <v>25</v>
       </c>
       <c r="BW47">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX47">
         <v>34</v>
       </c>
       <c r="BY47">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BZ47">
         <v>22</v>
       </c>
       <c r="CA47">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB47" t="s">
         <v>231</v>
@@ -12438,22 +12438,22 @@
         <v>2.42</v>
       </c>
       <c r="G48">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H48">
         <v>3.15</v>
       </c>
       <c r="I48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J48">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K48">
         <v>3.5</v>
       </c>
       <c r="L48">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M48">
         <v>1.09</v>
@@ -12486,7 +12486,7 @@
         <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X48">
         <v>13</v>
@@ -13164,13 +13164,13 @@
         <v>1.6</v>
       </c>
       <c r="G51">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H51">
         <v>6.6</v>
       </c>
       <c r="I51">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J51">
         <v>3.55</v>
@@ -13194,7 +13194,7 @@
         <v>1.65</v>
       </c>
       <c r="Q51">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R51">
         <v>1.24</v>
@@ -13206,7 +13206,7 @@
         <v>2.16</v>
       </c>
       <c r="U51">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V51">
         <v>1.14</v>
@@ -13227,7 +13227,7 @@
         <v>310</v>
       </c>
       <c r="AB51">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC51">
         <v>10</v>
@@ -13236,7 +13236,7 @@
         <v>34</v>
       </c>
       <c r="AE51">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AF51">
         <v>10</v>
@@ -13266,16 +13266,16 @@
         <v>14.5</v>
       </c>
       <c r="AO51">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AP51">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ51">
         <v>15.5</v>
       </c>
       <c r="AR51">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS51">
         <v>6.4</v>
@@ -13287,10 +13287,10 @@
         <v>7.6</v>
       </c>
       <c r="AV51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW51">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX51">
         <v>7.4</v>
@@ -13302,22 +13302,22 @@
         <v>20</v>
       </c>
       <c r="BA51">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB51">
         <v>14</v>
       </c>
       <c r="BC51">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD51">
         <v>38</v>
       </c>
       <c r="BE51">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF51">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG51">
         <v>6.4</v>
@@ -13380,7 +13380,7 @@
         <v>1000</v>
       </c>
       <c r="CA51">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB51" t="s">
         <v>231</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="265">
   <si>
     <t>League</t>
   </si>
@@ -340,6 +340,9 @@
     <t>Peruvian Primera Division</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Brazilian Campeonato Women</t>
   </si>
   <si>
@@ -352,9 +355,6 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
-    <t>Colombian Primera B</t>
-  </si>
-  <si>
     <t>Colombian Primera A</t>
   </si>
   <si>
@@ -415,6 +415,9 @@
     <t>20:15:00</t>
   </si>
   <si>
+    <t>21:05:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -577,6 +580,9 @@
     <t>Comerciantes FC</t>
   </si>
   <si>
+    <t>Quindio</t>
+  </si>
+  <si>
     <t>Cerro Porteno</t>
   </si>
   <si>
@@ -760,6 +766,9 @@
     <t>Alianza Universidad</t>
   </si>
   <si>
+    <t>Boca Juniors de Cali</t>
+  </si>
+  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
@@ -799,7 +808,7 @@
     <t>Escobar FC</t>
   </si>
   <si>
-    <t>2026-07-23 12:27:09</t>
+    <t>2026-07-23 14:38:54</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB62"/>
+  <dimension ref="A1:CB63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1387,43 +1396,43 @@
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F2">
+        <v>1.84</v>
+      </c>
+      <c r="G2">
         <v>1.86</v>
       </c>
-      <c r="G2">
-        <v>1.91</v>
-      </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
         <v>2.2</v>
@@ -1432,46 +1441,46 @@
         <v>1.29</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W2">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA2">
         <v>180</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>10.5</v>
@@ -1480,10 +1489,10 @@
         <v>28</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2">
         <v>29</v>
@@ -1495,10 +1504,10 @@
         <v>170</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO2">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
@@ -1510,34 +1519,34 @@
         <v>30</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC2">
         <v>17</v>
@@ -1546,13 +1555,13 @@
         <v>30</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
         <v>13</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
@@ -1573,13 +1582,13 @@
         <v>15.5</v>
       </c>
       <c r="BN2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ2">
         <v>7.4</v>
@@ -1591,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="BT2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
@@ -1606,7 +1615,7 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
@@ -1615,7 +1624,7 @@
         <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1629,25 +1638,25 @@
         <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F3">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="G3">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="H3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1659,58 +1668,58 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
         <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U3">
         <v>1.81</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3">
         <v>15.5</v>
@@ -1722,7 +1731,7 @@
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>44</v>
@@ -1734,73 +1743,73 @@
         <v>70</v>
       </c>
       <c r="AM3">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AN3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR3">
         <v>18</v>
       </c>
       <c r="AS3">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD3">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BE3">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BI3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1821,13 +1830,13 @@
         <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BS3">
         <v>10.5</v>
@@ -1839,10 +1848,10 @@
         <v>5.4</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1857,7 +1866,7 @@
         <v>11</v>
       </c>
       <c r="CB3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1871,16 +1880,16 @@
         <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F4">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1892,37 +1901,37 @@
         <v>3.25</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
         <v>1.6</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="O4">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T4">
         <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
         <v>1.23</v>
@@ -1931,37 +1940,37 @@
         <v>2</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA4">
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AI4">
         <v>1000</v>
@@ -1970,7 +1979,7 @@
         <v>27</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1979,43 +1988,43 @@
         <v>270</v>
       </c>
       <c r="AN4">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA4">
         <v>42</v>
@@ -2027,19 +2036,19 @@
         <v>24</v>
       </c>
       <c r="BD4">
+        <v>60</v>
+      </c>
+      <c r="BE4">
         <v>50</v>
       </c>
-      <c r="BE4">
-        <v>60</v>
-      </c>
       <c r="BF4">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BG4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BH4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
         <v>2.28</v>
@@ -2048,13 +2057,13 @@
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
@@ -2066,40 +2075,40 @@
         <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR4">
         <v>44</v>
       </c>
       <c r="BS4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
         <v>8.6</v>
       </c>
       <c r="BU4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>60</v>
       </c>
       <c r="BW4">
+        <v>10.5</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>11</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>9.800000000000001</v>
       </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>10</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>9.4</v>
-      </c>
       <c r="CB4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2113,37 +2122,37 @@
         <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G5">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
         <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M5">
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -2161,19 +2170,19 @@
         <v>4.4</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V5">
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y5">
         <v>18.5</v>
@@ -2182,61 +2191,61 @@
         <v>70</v>
       </c>
       <c r="AA5">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AB5">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF5">
         <v>9</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL5">
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN5">
         <v>13.5</v>
       </c>
       <c r="AO5">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP5">
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -2245,10 +2254,10 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AX5">
         <v>7.6</v>
@@ -2257,10 +2266,10 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BB5">
         <v>12</v>
@@ -2269,34 +2278,34 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.1</v>
@@ -2305,43 +2314,43 @@
         <v>3.1</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT5">
         <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2355,10 +2364,10 @@
         <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F6">
         <v>3.35</v>
@@ -2484,7 +2493,7 @@
         <v>9</v>
       </c>
       <c r="AU6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV6">
         <v>8.4</v>
@@ -2583,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2597,10 +2606,10 @@
         <v>119</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F7">
         <v>1.56</v>
@@ -2642,7 +2651,7 @@
         <v>1.49</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T7">
         <v>1.76</v>
@@ -2696,7 +2705,7 @@
         <v>17.5</v>
       </c>
       <c r="AK7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7">
         <v>36</v>
@@ -2735,7 +2744,7 @@
         <v>7</v>
       </c>
       <c r="AX7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7">
         <v>7.8</v>
@@ -2825,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2839,28 +2848,28 @@
         <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G8">
         <v>2.32</v>
       </c>
       <c r="H8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I8">
         <v>4</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8">
         <v>1.43</v>
@@ -2890,7 +2899,7 @@
         <v>1.83</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V8">
         <v>1.33</v>
@@ -2941,7 +2950,7 @@
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM8">
         <v>130</v>
@@ -2962,7 +2971,7 @@
         <v>5.2</v>
       </c>
       <c r="AS8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT8">
         <v>7.6</v>
@@ -2986,10 +2995,10 @@
         <v>15.5</v>
       </c>
       <c r="BA8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC8">
         <v>21</v>
@@ -2998,7 +3007,7 @@
         <v>5.5</v>
       </c>
       <c r="BE8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF8">
         <v>15</v>
@@ -3022,7 +3031,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
         <v>5.1</v>
@@ -3031,7 +3040,7 @@
         <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
         <v>6.4</v>
@@ -3058,16 +3067,16 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8">
         <v>32</v>
       </c>
       <c r="CA8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3081,10 +3090,10 @@
         <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F9">
         <v>1.84</v>
@@ -3093,7 +3102,7 @@
         <v>2.02</v>
       </c>
       <c r="H9">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I9">
         <v>4.6</v>
@@ -3105,7 +3114,7 @@
         <v>4.4</v>
       </c>
       <c r="L9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -3165,7 +3174,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG9">
         <v>13</v>
@@ -3189,7 +3198,7 @@
         <v>90</v>
       </c>
       <c r="AN9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO9">
         <v>50</v>
@@ -3201,10 +3210,10 @@
         <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT9">
         <v>8.4</v>
@@ -3216,7 +3225,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -3228,7 +3237,7 @@
         <v>12</v>
       </c>
       <c r="BA9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB9">
         <v>16</v>
@@ -3240,52 +3249,52 @@
         <v>21</v>
       </c>
       <c r="BE9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF9">
         <v>7.8</v>
       </c>
       <c r="BG9">
+        <v>4.2</v>
+      </c>
+      <c r="BH9">
         <v>4.1</v>
       </c>
-      <c r="BH9">
-        <v>4.2</v>
-      </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9">
         <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO9">
         <v>3.75</v>
       </c>
       <c r="BP9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR9">
         <v>25</v>
       </c>
       <c r="BS9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU9">
         <v>5.8</v>
@@ -3294,22 +3303,22 @@
         <v>34</v>
       </c>
       <c r="BW9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA9">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3323,13 +3332,13 @@
         <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F10">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G10">
         <v>2.9</v>
@@ -3359,10 +3368,10 @@
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q10">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R10">
         <v>1.34</v>
@@ -3494,7 +3503,7 @@
         <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
@@ -3512,7 +3521,7 @@
         <v>6</v>
       </c>
       <c r="BO10">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
         <v>22</v>
@@ -3530,7 +3539,7 @@
         <v>6.2</v>
       </c>
       <c r="BU10">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BV10">
         <v>23</v>
@@ -3551,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3565,10 +3574,10 @@
         <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F11">
         <v>3.35</v>
@@ -3610,13 +3619,13 @@
         <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T11">
         <v>1.62</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V11">
         <v>1.82</v>
@@ -3772,7 +3781,7 @@
         <v>5.5</v>
       </c>
       <c r="BU11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV11">
         <v>15.5</v>
@@ -3793,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3807,13 +3816,13 @@
         <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F12">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G12">
         <v>1.77</v>
@@ -3825,7 +3834,7 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.7</v>
@@ -3837,10 +3846,10 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P12">
         <v>2.32</v>
@@ -3849,7 +3858,7 @@
         <v>1.65</v>
       </c>
       <c r="R12">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S12">
         <v>2.66</v>
@@ -3933,10 +3942,10 @@
         <v>4.7</v>
       </c>
       <c r="AT12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12">
         <v>15</v>
@@ -3978,7 +3987,7 @@
         <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ12">
         <v>10</v>
@@ -4035,7 +4044,7 @@
         <v>6.2</v>
       </c>
       <c r="CB12" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -4049,16 +4058,16 @@
         <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F13">
         <v>2.68</v>
       </c>
       <c r="G13">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H13">
         <v>2.58</v>
@@ -4067,10 +4076,10 @@
         <v>2.78</v>
       </c>
       <c r="J13">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4082,13 +4091,13 @@
         <v>4.3</v>
       </c>
       <c r="O13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
         <v>2.16</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R13">
         <v>1.46</v>
@@ -4100,13 +4109,13 @@
         <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X13">
         <v>22</v>
@@ -4124,7 +4133,7 @@
         <v>16.5</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
         <v>15</v>
@@ -4163,16 +4172,16 @@
         <v>24</v>
       </c>
       <c r="AP13">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AS13">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AT13">
         <v>12</v>
@@ -4184,10 +4193,10 @@
         <v>11</v>
       </c>
       <c r="AW13">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX13">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AY13">
         <v>11</v>
@@ -4196,19 +4205,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB13">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC13">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD13">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE13">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF13">
         <v>15</v>
@@ -4277,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4291,13 +4300,13 @@
         <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
         <v>1.76</v>
@@ -4306,10 +4315,10 @@
         <v>5.1</v>
       </c>
       <c r="I14">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K14">
         <v>4.6</v>
@@ -4318,16 +4327,16 @@
         <v>1.3</v>
       </c>
       <c r="M14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="O14">
         <v>1.27</v>
       </c>
       <c r="P14">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
         <v>1.78</v>
@@ -4345,13 +4354,13 @@
         <v>2</v>
       </c>
       <c r="V14">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W14">
         <v>2.3</v>
       </c>
       <c r="X14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y14">
         <v>22</v>
@@ -4372,10 +4381,10 @@
         <v>24</v>
       </c>
       <c r="AE14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG14">
         <v>10.5</v>
@@ -4384,10 +4393,10 @@
         <v>22</v>
       </c>
       <c r="AI14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ14">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK14">
         <v>18.5</v>
@@ -4405,64 +4414,64 @@
         <v>110</v>
       </c>
       <c r="AP14">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AQ14">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR14">
+        <v>7.4</v>
+      </c>
+      <c r="AS14">
+        <v>8.4</v>
+      </c>
+      <c r="AT14">
+        <v>4.5</v>
+      </c>
+      <c r="AU14">
+        <v>4.7</v>
+      </c>
+      <c r="AV14">
+        <v>6.4</v>
+      </c>
+      <c r="AW14">
+        <v>8</v>
+      </c>
+      <c r="AX14">
+        <v>4.9</v>
+      </c>
+      <c r="AY14">
+        <v>4.8</v>
+      </c>
+      <c r="AZ14">
+        <v>6.2</v>
+      </c>
+      <c r="BA14">
+        <v>8</v>
+      </c>
+      <c r="BB14">
+        <v>5.9</v>
+      </c>
+      <c r="BC14">
         <v>6</v>
       </c>
-      <c r="AS14">
-        <v>6.6</v>
-      </c>
-      <c r="AT14">
-        <v>3.95</v>
-      </c>
-      <c r="AU14">
-        <v>6.2</v>
-      </c>
-      <c r="AV14">
-        <v>5.3</v>
-      </c>
-      <c r="AW14">
-        <v>6.2</v>
-      </c>
-      <c r="AX14">
-        <v>4.5</v>
-      </c>
-      <c r="AY14">
-        <v>4.1</v>
-      </c>
-      <c r="AZ14">
-        <v>5.2</v>
-      </c>
-      <c r="BA14">
-        <v>6.4</v>
-      </c>
-      <c r="BB14">
-        <v>5.2</v>
-      </c>
-      <c r="BC14">
-        <v>5</v>
-      </c>
       <c r="BD14">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BE14">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BG14">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH14">
         <v>3.8</v>
       </c>
       <c r="BI14">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
@@ -4519,7 +4528,7 @@
         <v>6.8</v>
       </c>
       <c r="CB14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4533,10 +4542,10 @@
         <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F15">
         <v>1.49</v>
@@ -4545,7 +4554,7 @@
         <v>1.61</v>
       </c>
       <c r="H15">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I15">
         <v>7.8</v>
@@ -4578,7 +4587,7 @@
         <v>1.47</v>
       </c>
       <c r="S15">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
         <v>1.81</v>
@@ -4635,7 +4644,7 @@
         <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM15">
         <v>130</v>
@@ -4647,58 +4656,58 @@
         <v>130</v>
       </c>
       <c r="AP15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS15">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AU15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ15">
         <v>6.2</v>
       </c>
       <c r="BA15">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB15">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC15">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD15">
         <v>7</v>
       </c>
       <c r="BE15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG15">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4722,7 +4731,7 @@
         <v>5.8</v>
       </c>
       <c r="BO15">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BP15">
         <v>13.5</v>
@@ -4761,7 +4770,7 @@
         <v>1.76</v>
       </c>
       <c r="CB15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4775,10 +4784,10 @@
         <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F16">
         <v>1.04</v>
@@ -4811,7 +4820,7 @@
         <v>1.25</v>
       </c>
       <c r="P16">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Q16">
         <v>1.25</v>
@@ -5003,7 +5012,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -5017,10 +5026,10 @@
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F17">
         <v>2.06</v>
@@ -5047,7 +5056,7 @@
         <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17">
         <v>1.24</v>
@@ -5170,7 +5179,7 @@
         <v>4.7</v>
       </c>
       <c r="BC17">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD17">
         <v>4.7</v>
@@ -5245,7 +5254,7 @@
         <v>7.4</v>
       </c>
       <c r="CB17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5259,25 +5268,25 @@
         <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F18">
         <v>2.5</v>
       </c>
       <c r="G18">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H18">
         <v>2.72</v>
       </c>
       <c r="I18">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
         <v>3.85</v>
@@ -5304,7 +5313,7 @@
         <v>1.37</v>
       </c>
       <c r="S18">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T18">
         <v>1.69</v>
@@ -5316,19 +5325,19 @@
         <v>1.47</v>
       </c>
       <c r="W18">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X18">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y18">
         <v>15</v>
       </c>
       <c r="Z18">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA18">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB18">
         <v>14.5</v>
@@ -5340,10 +5349,10 @@
         <v>16</v>
       </c>
       <c r="AE18">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF18">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG18">
         <v>15</v>
@@ -5352,13 +5361,13 @@
         <v>20</v>
       </c>
       <c r="AI18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL18">
         <v>48</v>
@@ -5370,61 +5379,61 @@
         <v>28</v>
       </c>
       <c r="AO18">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP18">
         <v>11</v>
       </c>
       <c r="AQ18">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR18">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AS18">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT18">
         <v>8.6</v>
       </c>
       <c r="AU18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV18">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AX18">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY18">
         <v>9</v>
       </c>
       <c r="AZ18">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA18">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB18">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BC18">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BD18">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BE18">
+        <v>4.5</v>
+      </c>
+      <c r="BF18">
+        <v>19</v>
+      </c>
+      <c r="BG18">
         <v>4</v>
-      </c>
-      <c r="BF18">
-        <v>16.5</v>
-      </c>
-      <c r="BG18">
-        <v>19</v>
       </c>
       <c r="BH18">
         <v>3.6</v>
@@ -5487,7 +5496,7 @@
         <v>8</v>
       </c>
       <c r="CB18" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5501,10 +5510,10 @@
         <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F19">
         <v>2.14</v>
@@ -5543,7 +5552,7 @@
         <v>1.68</v>
       </c>
       <c r="R19">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S19">
         <v>2.68</v>
@@ -5672,37 +5681,37 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BJ19">
         <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BN19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO19">
         <v>3.95</v>
       </c>
       <c r="BP19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ19">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BR19">
         <v>34</v>
       </c>
       <c r="BS19">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BT19">
         <v>9.199999999999999</v>
@@ -5714,22 +5723,22 @@
         <v>34</v>
       </c>
       <c r="BW19">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BX19">
         <v>44</v>
       </c>
       <c r="BY19">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BZ19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA19">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="CB19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5743,16 +5752,16 @@
         <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F20">
         <v>1.96</v>
       </c>
       <c r="G20">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -5794,13 +5803,13 @@
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
         <v>1.31</v>
       </c>
       <c r="W20">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5839,7 +5848,7 @@
         <v>48</v>
       </c>
       <c r="AJ20">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK20">
         <v>19</v>
@@ -5851,7 +5860,7 @@
         <v>75</v>
       </c>
       <c r="AN20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO20">
         <v>38</v>
@@ -5866,7 +5875,7 @@
         <v>27</v>
       </c>
       <c r="AS20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT20">
         <v>10.5</v>
@@ -5884,7 +5893,7 @@
         <v>12</v>
       </c>
       <c r="AY20">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
         <v>15</v>
@@ -5902,10 +5911,10 @@
         <v>26</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG20">
         <v>30</v>
@@ -5971,7 +5980,7 @@
         <v>6.4</v>
       </c>
       <c r="CB20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5985,31 +5994,31 @@
         <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F21">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G21">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K21">
         <v>4.8</v>
       </c>
       <c r="L21">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.04</v>
@@ -6021,10 +6030,10 @@
         <v>1.2</v>
       </c>
       <c r="P21">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R21">
         <v>1.66</v>
@@ -6033,7 +6042,7 @@
         <v>2.44</v>
       </c>
       <c r="T21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U21">
         <v>2.34</v>
@@ -6042,7 +6051,7 @@
         <v>1.19</v>
       </c>
       <c r="W21">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X21">
         <v>25</v>
@@ -6081,7 +6090,7 @@
         <v>65</v>
       </c>
       <c r="AJ21">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK21">
         <v>15.5</v>
@@ -6090,7 +6099,7 @@
         <v>27</v>
       </c>
       <c r="AM21">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
         <v>6.4</v>
@@ -6111,10 +6120,10 @@
         <v>44</v>
       </c>
       <c r="AT21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV21">
         <v>20</v>
@@ -6135,7 +6144,7 @@
         <v>50</v>
       </c>
       <c r="BB21">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC21">
         <v>13.5</v>
@@ -6213,7 +6222,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CB21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6227,19 +6236,19 @@
         <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F22">
         <v>1.5</v>
       </c>
       <c r="G22">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I22">
         <v>6.8</v>
@@ -6248,7 +6257,7 @@
         <v>5.1</v>
       </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L22">
         <v>1.2</v>
@@ -6269,22 +6278,22 @@
         <v>1.4</v>
       </c>
       <c r="R22">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S22">
         <v>1.98</v>
       </c>
       <c r="T22">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U22">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V22">
         <v>1.17</v>
       </c>
       <c r="W22">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="X22">
         <v>40</v>
@@ -6308,7 +6317,7 @@
         <v>26</v>
       </c>
       <c r="AE22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF22">
         <v>13.5</v>
@@ -6338,7 +6347,7 @@
         <v>4.9</v>
       </c>
       <c r="AO22">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP22">
         <v>27</v>
@@ -6350,7 +6359,7 @@
         <v>50</v>
       </c>
       <c r="AS22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT22">
         <v>13</v>
@@ -6371,7 +6380,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA22">
         <v>44</v>
@@ -6401,52 +6410,52 @@
         <v>4.2</v>
       </c>
       <c r="BJ22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK22">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO22">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP22">
         <v>9.6</v>
       </c>
       <c r="BQ22">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BR22">
         <v>18</v>
       </c>
       <c r="BS22">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT22">
         <v>10.5</v>
       </c>
       <c r="BU22">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV22">
         <v>38</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX22">
         <v>36</v>
       </c>
       <c r="BY22">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6455,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6469,28 +6478,28 @@
         <v>123</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F23">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="G23">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="H23">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
         <v>1.17</v>
@@ -6499,43 +6508,43 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="O23">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q23">
         <v>1.37</v>
       </c>
       <c r="R23">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S23">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="T23">
         <v>1.43</v>
       </c>
       <c r="U23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="X23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Y23">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z23">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -6544,13 +6553,13 @@
         <v>23</v>
       </c>
       <c r="AC23">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE23">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF23">
         <v>22</v>
@@ -6559,10 +6568,10 @@
         <v>14.5</v>
       </c>
       <c r="AH23">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI23">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ23">
         <v>28</v>
@@ -6577,22 +6586,22 @@
         <v>55</v>
       </c>
       <c r="AN23">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AO23">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AP23">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ23">
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS23">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT23">
         <v>13.5</v>
@@ -6604,7 +6613,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX23">
         <v>13</v>
@@ -6616,7 +6625,7 @@
         <v>11</v>
       </c>
       <c r="BA23">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB23">
         <v>16</v>
@@ -6628,64 +6637,64 @@
         <v>16</v>
       </c>
       <c r="BE23">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF23">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG23">
         <v>14.5</v>
       </c>
       <c r="BH23">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BI23">
         <v>4.3</v>
       </c>
       <c r="BJ23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK23">
         <v>4.6</v>
       </c>
       <c r="BL23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN23">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BO23">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP23">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ23">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BR23">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS23">
         <v>6.4</v>
       </c>
       <c r="BT23">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BU23">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BW23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY23">
         <v>7.2</v>
@@ -6697,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6711,22 +6720,22 @@
         <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F24">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="G24">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H24">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I24">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="J24">
         <v>3.85</v>
@@ -6744,28 +6753,28 @@
         <v>5.3</v>
       </c>
       <c r="O24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P24">
         <v>2.46</v>
       </c>
       <c r="Q24">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
         <v>1.57</v>
       </c>
       <c r="S24">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T24">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V24">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
         <v>1.47</v>
@@ -6918,7 +6927,7 @@
         <v>6</v>
       </c>
       <c r="BU24">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV24">
         <v>16.5</v>
@@ -6939,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6953,10 +6962,10 @@
         <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F25">
         <v>1.04</v>
@@ -6983,13 +6992,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
         <v>1.01</v>
       </c>
       <c r="P25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
         <v>1.01</v>
@@ -6998,7 +7007,7 @@
         <v>1.12</v>
       </c>
       <c r="S25">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -7181,7 +7190,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7195,16 +7204,16 @@
         <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F26">
         <v>2.36</v>
       </c>
       <c r="G26">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H26">
         <v>3.15</v>
@@ -7216,7 +7225,7 @@
         <v>3.6</v>
       </c>
       <c r="K26">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L26">
         <v>1.28</v>
@@ -7234,25 +7243,25 @@
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R26">
         <v>1.49</v>
       </c>
       <c r="S26">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T26">
         <v>1.62</v>
       </c>
       <c r="U26">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
         <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X26">
         <v>22</v>
@@ -7363,7 +7372,7 @@
         <v>17</v>
       </c>
       <c r="BH26">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI26">
         <v>3.25</v>
@@ -7372,16 +7381,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK26">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BN26">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO26">
         <v>4.9</v>
@@ -7390,16 +7399,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ26">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR26">
         <v>26</v>
       </c>
       <c r="BS26">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU26">
         <v>5.1</v>
@@ -7408,13 +7417,13 @@
         <v>22</v>
       </c>
       <c r="BW26">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX26">
         <v>30</v>
       </c>
       <c r="BY26">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7423,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7437,10 +7446,10 @@
         <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F27">
         <v>3.05</v>
@@ -7452,10 +7461,10 @@
         <v>2.1</v>
       </c>
       <c r="I27">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J27">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K27">
         <v>4.5</v>
@@ -7473,7 +7482,7 @@
         <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
         <v>1.46</v>
@@ -7491,7 +7500,7 @@
         <v>2.72</v>
       </c>
       <c r="V27">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W27">
         <v>1.42</v>
@@ -7515,7 +7524,7 @@
         <v>11.5</v>
       </c>
       <c r="AD27">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE27">
         <v>21</v>
@@ -7551,16 +7560,16 @@
         <v>9.6</v>
       </c>
       <c r="AP27">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ27">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR27">
         <v>13.5</v>
       </c>
       <c r="AS27">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT27">
         <v>18</v>
@@ -7569,40 +7578,40 @@
         <v>8</v>
       </c>
       <c r="AV27">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW27">
         <v>14</v>
       </c>
       <c r="AX27">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AY27">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ27">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA27">
         <v>18</v>
       </c>
       <c r="BB27">
-        <v>30</v>
+        <v>7.8</v>
       </c>
       <c r="BC27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD27">
         <v>18.5</v>
       </c>
       <c r="BE27">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BF27">
         <v>12.5</v>
       </c>
       <c r="BG27">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7626,7 +7635,7 @@
         <v>10</v>
       </c>
       <c r="BO27">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP27">
         <v>30</v>
@@ -7665,7 +7674,7 @@
         <v>1.86</v>
       </c>
       <c r="CB27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7679,10 +7688,10 @@
         <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E28" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F28">
         <v>1.04</v>
@@ -7712,19 +7721,19 @@
         <v>1.1</v>
       </c>
       <c r="O28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R28">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S28">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7907,7 +7916,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7921,10 +7930,10 @@
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E29" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F29">
         <v>4.1</v>
@@ -7936,7 +7945,7 @@
         <v>1.8</v>
       </c>
       <c r="I29">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="J29">
         <v>4.1</v>
@@ -7966,13 +7975,13 @@
         <v>1.64</v>
       </c>
       <c r="S29">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="T29">
         <v>1.53</v>
       </c>
       <c r="U29">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V29">
         <v>2.1</v>
@@ -8149,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8163,10 +8172,10 @@
         <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E30" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F30">
         <v>1.7</v>
@@ -8229,7 +8238,7 @@
         <v>18.5</v>
       </c>
       <c r="Z30">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA30">
         <v>180</v>
@@ -8241,7 +8250,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE30">
         <v>90</v>
@@ -8283,10 +8292,10 @@
         <v>15</v>
       </c>
       <c r="AR30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT30">
         <v>6.6</v>
@@ -8298,7 +8307,7 @@
         <v>19</v>
       </c>
       <c r="AW30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX30">
         <v>8.4</v>
@@ -8310,7 +8319,7 @@
         <v>18.5</v>
       </c>
       <c r="BA30">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB30">
         <v>15</v>
@@ -8319,16 +8328,16 @@
         <v>16.5</v>
       </c>
       <c r="BD30">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30">
         <v>9.6</v>
       </c>
       <c r="BG30">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH30">
         <v>3.4</v>
@@ -8391,7 +8400,7 @@
         <v>7.4</v>
       </c>
       <c r="CB30" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8405,16 +8414,16 @@
         <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F31">
         <v>2.2</v>
       </c>
       <c r="G31">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H31">
         <v>3.1</v>
@@ -8423,7 +8432,7 @@
         <v>3.3</v>
       </c>
       <c r="J31">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K31">
         <v>4.3</v>
@@ -8462,7 +8471,7 @@
         <v>1.43</v>
       </c>
       <c r="W31">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X31">
         <v>28</v>
@@ -8633,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8647,19 +8656,19 @@
         <v>126</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F32">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G32">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I32">
         <v>4.1</v>
@@ -8668,7 +8677,7 @@
         <v>3.1</v>
       </c>
       <c r="K32">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L32">
         <v>1.47</v>
@@ -8680,7 +8689,7 @@
         <v>2.6</v>
       </c>
       <c r="O32">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P32">
         <v>1.54</v>
@@ -8704,7 +8713,7 @@
         <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X32">
         <v>11</v>
@@ -8824,7 +8833,7 @@
         <v>12</v>
       </c>
       <c r="BK32">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL32">
         <v>1000</v>
@@ -8836,7 +8845,7 @@
         <v>5</v>
       </c>
       <c r="BO32">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP32">
         <v>20</v>
@@ -8875,7 +8884,7 @@
         <v>9</v>
       </c>
       <c r="CB32" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8889,13 +8898,13 @@
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F33">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="G33">
         <v>3.25</v>
@@ -8904,13 +8913,13 @@
         <v>2.52</v>
       </c>
       <c r="I33">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L33">
         <v>1.43</v>
@@ -8934,16 +8943,16 @@
         <v>1.29</v>
       </c>
       <c r="S33">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T33">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U33">
         <v>2.02</v>
       </c>
       <c r="V33">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.45</v>
@@ -8964,7 +8973,7 @@
         <v>12</v>
       </c>
       <c r="AC33">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD33">
         <v>13</v>
@@ -9048,10 +9057,10 @@
         <v>40</v>
       </c>
       <c r="BE33">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG33">
         <v>21</v>
@@ -9117,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9131,10 +9140,10 @@
         <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F34">
         <v>2.56</v>
@@ -9182,7 +9191,7 @@
         <v>1.6</v>
       </c>
       <c r="U34">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -9359,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9373,31 +9382,31 @@
         <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F35">
         <v>3.2</v>
       </c>
       <c r="G35">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H35">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I35">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J35">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K35">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L35">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M35">
         <v>1.06</v>
@@ -9409,28 +9418,28 @@
         <v>1.27</v>
       </c>
       <c r="P35">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q35">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="R35">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U35">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W35">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X35">
         <v>19.5</v>
@@ -9484,7 +9493,7 @@
         <v>38</v>
       </c>
       <c r="AO35">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AP35">
         <v>13</v>
@@ -9520,61 +9529,61 @@
         <v>12.5</v>
       </c>
       <c r="BA35">
+        <v>5.5</v>
+      </c>
+      <c r="BB35">
+        <v>5.9</v>
+      </c>
+      <c r="BC35">
         <v>5.7</v>
-      </c>
-      <c r="BB35">
-        <v>6</v>
-      </c>
-      <c r="BC35">
-        <v>5.9</v>
       </c>
       <c r="BD35">
         <v>32</v>
       </c>
       <c r="BE35">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF35">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG35">
         <v>11</v>
       </c>
       <c r="BH35">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI35">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ35">
+        <v>9.6</v>
+      </c>
+      <c r="BK35">
+        <v>5</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
         <v>9.4</v>
       </c>
-      <c r="BK35">
-        <v>4.9</v>
-      </c>
-      <c r="BL35">
-        <v>1000</v>
-      </c>
-      <c r="BM35">
-        <v>9.6</v>
-      </c>
       <c r="BN35">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO35">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP35">
         <v>27</v>
       </c>
       <c r="BQ35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR35">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS35">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT35">
         <v>5.4</v>
@@ -9583,13 +9592,13 @@
         <v>4.1</v>
       </c>
       <c r="BV35">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW35">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX35">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY35">
         <v>7.6</v>
@@ -9601,7 +9610,7 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9615,10 +9624,10 @@
         <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F36">
         <v>1.73</v>
@@ -9654,10 +9663,10 @@
         <v>1.94</v>
       </c>
       <c r="Q36">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="R36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S36">
         <v>3.35</v>
@@ -9666,7 +9675,7 @@
         <v>1.84</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V36">
         <v>1.2</v>
@@ -9690,7 +9699,7 @@
         <v>10.5</v>
       </c>
       <c r="AC36">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD36">
         <v>25</v>
@@ -9735,10 +9744,10 @@
         <v>13</v>
       </c>
       <c r="AR36">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AS36">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT36">
         <v>7.4</v>
@@ -9750,7 +9759,7 @@
         <v>15</v>
       </c>
       <c r="AW36">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AX36">
         <v>8</v>
@@ -9762,7 +9771,7 @@
         <v>14.5</v>
       </c>
       <c r="BA36">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB36">
         <v>13.5</v>
@@ -9771,22 +9780,22 @@
         <v>13.5</v>
       </c>
       <c r="BD36">
+        <v>3.95</v>
+      </c>
+      <c r="BE36">
         <v>4.2</v>
-      </c>
-      <c r="BE36">
-        <v>4.5</v>
       </c>
       <c r="BF36">
         <v>8.6</v>
       </c>
       <c r="BG36">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH36">
         <v>3.6</v>
       </c>
       <c r="BI36">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="BJ36">
         <v>10.5</v>
@@ -9843,7 +9852,7 @@
         <v>7.4</v>
       </c>
       <c r="CB36" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9857,10 +9866,10 @@
         <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F37">
         <v>2.76</v>
@@ -9881,7 +9890,7 @@
         <v>3.75</v>
       </c>
       <c r="L37">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M37">
         <v>1.07</v>
@@ -10028,7 +10037,7 @@
         <v>3.45</v>
       </c>
       <c r="BI37">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BJ37">
         <v>10</v>
@@ -10085,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -10099,13 +10108,13 @@
         <v>127</v>
       </c>
       <c r="D38" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F38">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="G38">
         <v>1.67</v>
@@ -10114,13 +10123,13 @@
         <v>5.7</v>
       </c>
       <c r="I38">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J38">
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10132,28 +10141,28 @@
         <v>4.5</v>
       </c>
       <c r="O38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P38">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q38">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R38">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S38">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="T38">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V38">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W38">
         <v>2.48</v>
@@ -10183,7 +10192,7 @@
         <v>80</v>
       </c>
       <c r="AF38">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG38">
         <v>10.5</v>
@@ -10201,7 +10210,7 @@
         <v>16.5</v>
       </c>
       <c r="AL38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AM38">
         <v>110</v>
@@ -10216,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="AQ38">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR38">
         <v>7.2</v>
@@ -10228,7 +10237,7 @@
         <v>7.8</v>
       </c>
       <c r="AU38">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV38">
         <v>20</v>
@@ -10237,7 +10246,7 @@
         <v>7.6</v>
       </c>
       <c r="AX38">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY38">
         <v>8.800000000000001</v>
@@ -10246,7 +10255,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB38">
         <v>13.5</v>
@@ -10327,7 +10336,7 @@
         <v>1.04</v>
       </c>
       <c r="CB38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10341,10 +10350,10 @@
         <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F39">
         <v>1.04</v>
@@ -10374,19 +10383,19 @@
         <v>1.19</v>
       </c>
       <c r="O39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P39">
         <v>1.19</v>
       </c>
       <c r="Q39">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S39">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10569,7 +10578,7 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10583,10 +10592,10 @@
         <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F40">
         <v>2.46</v>
@@ -10595,7 +10604,7 @@
         <v>2.76</v>
       </c>
       <c r="H40">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I40">
         <v>3.95</v>
@@ -10604,7 +10613,7 @@
         <v>2.58</v>
       </c>
       <c r="K40">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L40">
         <v>1.54</v>
@@ -10613,7 +10622,7 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="O40">
         <v>1.52</v>
@@ -10625,7 +10634,7 @@
         <v>2.56</v>
       </c>
       <c r="R40">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S40">
         <v>4.8</v>
@@ -10811,7 +10820,7 @@
         <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10825,22 +10834,22 @@
         <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F41">
         <v>3.45</v>
       </c>
       <c r="G41">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H41">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I41">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="J41">
         <v>3.2</v>
@@ -10849,7 +10858,7 @@
         <v>3.55</v>
       </c>
       <c r="L41">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M41">
         <v>1.07</v>
@@ -10879,7 +10888,7 @@
         <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
         <v>1.37</v>
@@ -10894,10 +10903,10 @@
         <v>16.5</v>
       </c>
       <c r="AA41">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AB41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC41">
         <v>7.8</v>
@@ -10909,7 +10918,7 @@
         <v>27</v>
       </c>
       <c r="AF41">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG41">
         <v>15</v>
@@ -10933,7 +10942,7 @@
         <v>95</v>
       </c>
       <c r="AN41">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO41">
         <v>21</v>
@@ -10942,13 +10951,13 @@
         <v>10</v>
       </c>
       <c r="AQ41">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR41">
         <v>11.5</v>
       </c>
       <c r="AS41">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT41">
         <v>10</v>
@@ -10957,7 +10966,7 @@
         <v>5.6</v>
       </c>
       <c r="AV41">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW41">
         <v>18.5</v>
@@ -10996,55 +11005,55 @@
         <v>3.6</v>
       </c>
       <c r="BI41">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="BJ41">
         <v>9.800000000000001</v>
       </c>
       <c r="BK41">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL41">
         <v>1000</v>
       </c>
       <c r="BM41">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN41">
         <v>7</v>
       </c>
       <c r="BO41">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP41">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BQ41">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR41">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BS41">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT41">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BU41">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV41">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW41">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX41">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BY41">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ41">
         <v>0</v>
@@ -11053,7 +11062,7 @@
         <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -11067,10 +11076,10 @@
         <v>129</v>
       </c>
       <c r="D42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F42">
         <v>2.08</v>
@@ -11079,7 +11088,7 @@
         <v>2.28</v>
       </c>
       <c r="H42">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I42">
         <v>3.35</v>
@@ -11088,7 +11097,7 @@
         <v>4.1</v>
       </c>
       <c r="K42">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L42">
         <v>1.2</v>
@@ -11124,7 +11133,7 @@
         <v>1.42</v>
       </c>
       <c r="W42">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X42">
         <v>38</v>
@@ -11163,7 +11172,7 @@
         <v>32</v>
       </c>
       <c r="AJ42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK42">
         <v>21</v>
@@ -11175,34 +11184,34 @@
         <v>48</v>
       </c>
       <c r="AN42">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO42">
         <v>20</v>
       </c>
       <c r="AP42">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ42">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AR42">
         <v>17.5</v>
       </c>
       <c r="AS42">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="AT42">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU42">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AV42">
         <v>12.5</v>
       </c>
       <c r="AW42">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX42">
         <v>6</v>
@@ -11217,7 +11226,7 @@
         <v>18.5</v>
       </c>
       <c r="BB42">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC42">
         <v>14</v>
@@ -11232,7 +11241,7 @@
         <v>6.6</v>
       </c>
       <c r="BG42">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="BH42">
         <v>5.2</v>
@@ -11256,7 +11265,7 @@
         <v>6</v>
       </c>
       <c r="BO42">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BP42">
         <v>14.5</v>
@@ -11274,7 +11283,7 @@
         <v>7.4</v>
       </c>
       <c r="BU42">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BV42">
         <v>22</v>
@@ -11295,7 +11304,7 @@
         <v>5.7</v>
       </c>
       <c r="CB42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11309,10 +11318,10 @@
         <v>129</v>
       </c>
       <c r="D43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F43">
         <v>1.03</v>
@@ -11321,13 +11330,13 @@
         <v>990</v>
       </c>
       <c r="H43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I43">
         <v>990</v>
       </c>
       <c r="J43">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K43">
         <v>950</v>
@@ -11537,7 +11546,7 @@
         <v>1.04</v>
       </c>
       <c r="CB43" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11551,10 +11560,10 @@
         <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F44">
         <v>1.09</v>
@@ -11779,7 +11788,7 @@
         <v>1.04</v>
       </c>
       <c r="CB44" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11793,13 +11802,13 @@
         <v>130</v>
       </c>
       <c r="D45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F45">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G45">
         <v>1.97</v>
@@ -11814,7 +11823,7 @@
         <v>3.25</v>
       </c>
       <c r="K45">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L45">
         <v>1.53</v>
@@ -11823,7 +11832,7 @@
         <v>1.15</v>
       </c>
       <c r="N45">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O45">
         <v>1.65</v>
@@ -11832,7 +11841,7 @@
         <v>1.46</v>
       </c>
       <c r="Q45">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="R45">
         <v>1.16</v>
@@ -11844,13 +11853,13 @@
         <v>2.5</v>
       </c>
       <c r="U45">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V45">
         <v>1.2</v>
       </c>
       <c r="W45">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X45">
         <v>7.8</v>
@@ -12021,7 +12030,7 @@
         <v>10.5</v>
       </c>
       <c r="CB45" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -12035,10 +12044,10 @@
         <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -12263,7 +12272,7 @@
         <v>1.04</v>
       </c>
       <c r="CB46" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12277,28 +12286,28 @@
         <v>131</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E47" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F47">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G47">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="H47">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I47">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J47">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K47">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L47">
         <v>1.17</v>
@@ -12307,34 +12316,34 @@
         <v>1.07</v>
       </c>
       <c r="N47">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O47">
         <v>1.33</v>
       </c>
       <c r="P47">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q47">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="R47">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S47">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T47">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U47">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V47">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W47">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X47">
         <v>17</v>
@@ -12358,10 +12367,10 @@
         <v>25</v>
       </c>
       <c r="AE47">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF47">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG47">
         <v>12.5</v>
@@ -12370,22 +12379,22 @@
         <v>25</v>
       </c>
       <c r="AI47">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ47">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK47">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL47">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM47">
         <v>140</v>
       </c>
       <c r="AN47">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO47">
         <v>95</v>
@@ -12394,13 +12403,13 @@
         <v>12</v>
       </c>
       <c r="AQ47">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR47">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AS47">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AT47">
         <v>7.2</v>
@@ -12412,37 +12421,37 @@
         <v>17</v>
       </c>
       <c r="AW47">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX47">
         <v>9.199999999999999</v>
       </c>
       <c r="AY47">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ47">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA47">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB47">
+        <v>15.5</v>
+      </c>
+      <c r="BC47">
         <v>16.5</v>
-      </c>
-      <c r="BC47">
-        <v>4.2</v>
       </c>
       <c r="BD47">
         <v>30</v>
       </c>
       <c r="BE47">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF47">
         <v>9.4</v>
       </c>
       <c r="BG47">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12505,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="CB47" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="48" spans="1:80">
@@ -12519,10 +12528,10 @@
         <v>131</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F48">
         <v>1.08</v>
@@ -12747,7 +12756,7 @@
         <v>1.04</v>
       </c>
       <c r="CB48" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:80">
@@ -12761,16 +12770,16 @@
         <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E49" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F49">
         <v>1.04</v>
       </c>
       <c r="G49">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H49">
         <v>1.04</v>
@@ -12782,7 +12791,7 @@
         <v>1.02</v>
       </c>
       <c r="K49">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -12791,28 +12800,28 @@
         <v>1.01</v>
       </c>
       <c r="N49">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="O49">
         <v>1.01</v>
       </c>
       <c r="P49">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="Q49">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R49">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S49">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49">
         <v>1.01</v>
@@ -12875,52 +12884,52 @@
         <v>1000</v>
       </c>
       <c r="AP49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE49">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF49">
         <v>1.01</v>
@@ -12932,69 +12941,69 @@
         <v>1000</v>
       </c>
       <c r="BI49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ49">
         <v>1000</v>
       </c>
       <c r="BK49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL49">
         <v>1000</v>
       </c>
       <c r="BM49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN49">
         <v>1000</v>
       </c>
       <c r="BO49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP49">
         <v>1000</v>
       </c>
       <c r="BQ49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR49">
         <v>1000</v>
       </c>
       <c r="BS49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT49">
         <v>1000</v>
       </c>
       <c r="BU49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV49">
         <v>1000</v>
       </c>
       <c r="BW49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX49">
         <v>1000</v>
       </c>
       <c r="BY49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ49">
         <v>1000</v>
       </c>
       <c r="CA49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB49" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:80">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
         <v>114</v>
@@ -13003,28 +13012,28 @@
         <v>133</v>
       </c>
       <c r="D50" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E50" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13033,34 +13042,34 @@
         <v>1.01</v>
       </c>
       <c r="N50">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O50">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="P50">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="Q50">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="T50">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U50">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V50">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W50">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -13117,52 +13126,52 @@
         <v>1000</v>
       </c>
       <c r="AP50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50">
         <v>1.01</v>
@@ -13174,69 +13183,69 @@
         <v>1000</v>
       </c>
       <c r="BI50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ50">
         <v>1000</v>
       </c>
       <c r="BK50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL50">
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN50">
         <v>1000</v>
       </c>
       <c r="BO50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP50">
         <v>1000</v>
       </c>
       <c r="BQ50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR50">
         <v>1000</v>
       </c>
       <c r="BS50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT50">
         <v>1000</v>
       </c>
       <c r="BU50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV50">
         <v>1000</v>
       </c>
       <c r="BW50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX50">
         <v>1000</v>
       </c>
       <c r="BY50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ50">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB50" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="51" spans="1:80">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="B51" t="s">
         <v>114</v>
@@ -13245,235 +13254,235 @@
         <v>134</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E51" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F51">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J51">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L51">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N51">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="O51">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="P51">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="Q51">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="R51">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S51">
-        <v>6</v>
+        <v>1.84</v>
       </c>
       <c r="T51">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="U51">
-        <v>1.71</v>
+        <v>1.11</v>
       </c>
       <c r="V51">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W51">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X51">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y51">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z51">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA51">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB51">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC51">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD51">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE51">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF51">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG51">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH51">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI51">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ51">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK51">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL51">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM51">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN51">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO51">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP51">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR51">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS51">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT51">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU51">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV51">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW51">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX51">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY51">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA51">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB51">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC51">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD51">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE51">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF51">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG51">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH51">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI51">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ51">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK51">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL51">
         <v>1000</v>
       </c>
       <c r="BM51">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN51">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO51">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP51">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ51">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR51">
         <v>1000</v>
       </c>
       <c r="BS51">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT51">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU51">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV51">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW51">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX51">
         <v>1000</v>
       </c>
       <c r="BY51">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ51">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA51">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="CB51" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="52" spans="1:80">
@@ -13484,417 +13493,417 @@
         <v>114</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F52">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="G52">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="H52">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="I52">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="J52">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K52">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L52">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M52">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N52">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="O52">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="P52">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="Q52">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="R52">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S52">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T52">
         <v>2.26</v>
       </c>
       <c r="U52">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V52">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W52">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="X52">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="Y52">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z52">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AA52">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="AB52">
+        <v>6.8</v>
+      </c>
+      <c r="AC52">
         <v>7.6</v>
       </c>
-      <c r="AC52">
-        <v>9.4</v>
-      </c>
       <c r="AD52">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE52">
+        <v>95</v>
+      </c>
+      <c r="AF52">
+        <v>12.5</v>
+      </c>
+      <c r="AG52">
+        <v>13</v>
+      </c>
+      <c r="AH52">
+        <v>30</v>
+      </c>
+      <c r="AI52">
         <v>130</v>
       </c>
-      <c r="AF52">
-        <v>11.5</v>
-      </c>
-      <c r="AG52">
-        <v>12</v>
-      </c>
-      <c r="AH52">
-        <v>32</v>
-      </c>
-      <c r="AI52">
-        <v>150</v>
-      </c>
       <c r="AJ52">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK52">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AL52">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM52">
         <v>260</v>
       </c>
       <c r="AN52">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AO52">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AP52">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ52">
+        <v>9.4</v>
+      </c>
+      <c r="AR52">
+        <v>6.2</v>
+      </c>
+      <c r="AS52">
+        <v>7.2</v>
+      </c>
+      <c r="AT52">
+        <v>5.9</v>
+      </c>
+      <c r="AU52">
+        <v>6.4</v>
+      </c>
+      <c r="AV52">
+        <v>5.7</v>
+      </c>
+      <c r="AW52">
+        <v>7</v>
+      </c>
+      <c r="AX52">
+        <v>10.5</v>
+      </c>
+      <c r="AY52">
+        <v>10.5</v>
+      </c>
+      <c r="AZ52">
+        <v>6</v>
+      </c>
+      <c r="BA52">
+        <v>7.2</v>
+      </c>
+      <c r="BB52">
+        <v>6.2</v>
+      </c>
+      <c r="BC52">
+        <v>6.4</v>
+      </c>
+      <c r="BD52">
+        <v>7</v>
+      </c>
+      <c r="BE52">
+        <v>7.4</v>
+      </c>
+      <c r="BF52">
+        <v>6.4</v>
+      </c>
+      <c r="BG52">
+        <v>7.2</v>
+      </c>
+      <c r="BH52">
+        <v>2.6</v>
+      </c>
+      <c r="BI52">
+        <v>2.28</v>
+      </c>
+      <c r="BJ52">
         <v>12</v>
       </c>
-      <c r="AR52">
-        <v>36</v>
-      </c>
-      <c r="AS52">
+      <c r="BK52">
+        <v>7.2</v>
+      </c>
+      <c r="BL52">
+        <v>1000</v>
+      </c>
+      <c r="BM52">
+        <v>17.5</v>
+      </c>
+      <c r="BN52">
+        <v>4.7</v>
+      </c>
+      <c r="BO52">
+        <v>3.8</v>
+      </c>
+      <c r="BP52">
+        <v>1000</v>
+      </c>
+      <c r="BQ52">
+        <v>9.6</v>
+      </c>
+      <c r="BR52">
+        <v>1000</v>
+      </c>
+      <c r="BS52">
+        <v>13</v>
+      </c>
+      <c r="BT52">
+        <v>7.4</v>
+      </c>
+      <c r="BU52">
         <v>5.7</v>
       </c>
-      <c r="AT52">
-        <v>5.6</v>
-      </c>
-      <c r="AU52">
-        <v>7</v>
-      </c>
-      <c r="AV52">
-        <v>4.8</v>
-      </c>
-      <c r="AW52">
-        <v>5.6</v>
-      </c>
-      <c r="AX52">
-        <v>8.4</v>
-      </c>
-      <c r="AY52">
-        <v>9.6</v>
-      </c>
-      <c r="AZ52">
-        <v>4.8</v>
-      </c>
-      <c r="BA52">
-        <v>5.6</v>
-      </c>
-      <c r="BB52">
-        <v>4.6</v>
-      </c>
-      <c r="BC52">
-        <v>18</v>
-      </c>
-      <c r="BD52">
-        <v>38</v>
-      </c>
-      <c r="BE52">
-        <v>5.7</v>
-      </c>
-      <c r="BF52">
-        <v>15</v>
-      </c>
-      <c r="BG52">
-        <v>5.7</v>
-      </c>
-      <c r="BH52">
-        <v>1000</v>
-      </c>
-      <c r="BI52">
-        <v>1.04</v>
-      </c>
-      <c r="BJ52">
-        <v>1000</v>
-      </c>
-      <c r="BK52">
-        <v>1.04</v>
-      </c>
-      <c r="BL52">
-        <v>1000</v>
-      </c>
-      <c r="BM52">
-        <v>1.04</v>
-      </c>
-      <c r="BN52">
-        <v>1000</v>
-      </c>
-      <c r="BO52">
-        <v>1.04</v>
-      </c>
-      <c r="BP52">
-        <v>1000</v>
-      </c>
-      <c r="BQ52">
-        <v>1.04</v>
-      </c>
-      <c r="BR52">
-        <v>1000</v>
-      </c>
-      <c r="BS52">
-        <v>1.04</v>
-      </c>
-      <c r="BT52">
-        <v>1000</v>
-      </c>
-      <c r="BU52">
-        <v>1.04</v>
-      </c>
       <c r="BV52">
         <v>1000</v>
       </c>
       <c r="BW52">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX52">
         <v>1000</v>
       </c>
       <c r="BY52">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BZ52">
         <v>1000</v>
       </c>
       <c r="CA52">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="CB52" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:80">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="B53" t="s">
         <v>114</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F53">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="G53">
-        <v>990</v>
+        <v>1.94</v>
       </c>
       <c r="H53">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="I53">
-        <v>990</v>
+        <v>6.2</v>
       </c>
       <c r="J53">
-        <v>1.02</v>
+        <v>3.2</v>
       </c>
       <c r="K53">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L53">
         <v>1.01</v>
       </c>
       <c r="M53">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N53">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O53">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="P53">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q53">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="R53">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>5.4</v>
       </c>
       <c r="T53">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U53">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V53">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W53">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="X53">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z53">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA53">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB53">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC53">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF53">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG53">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH53">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI53">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL53">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM53">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP53">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ53">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR53">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS53">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT53">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU53">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV53">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW53">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX53">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY53">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ53">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA53">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB53">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC53">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD53">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE53">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF53">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG53">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13957,249 +13966,249 @@
         <v>1.04</v>
       </c>
       <c r="CB53" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="1:80">
       <c r="A54" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B54" t="s">
         <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F54">
-        <v>1.82</v>
+        <v>1.15</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>990</v>
       </c>
       <c r="H54">
-        <v>4.1</v>
+        <v>1.13</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>990</v>
       </c>
       <c r="J54">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="K54">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L54">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M54">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N54">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="O54">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="P54">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="Q54">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="R54">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S54">
-        <v>3.2</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="U54">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V54">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="W54">
-        <v>2</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y54">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z54">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA54">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB54">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC54">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD54">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE54">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF54">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG54">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH54">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI54">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ54">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK54">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL54">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM54">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN54">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO54">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP54">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR54">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS54">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT54">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU54">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AV54">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AW54">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX54">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY54">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BA54">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB54">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC54">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD54">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE54">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF54">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG54">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH54">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI54">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ54">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK54">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL54">
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN54">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO54">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP54">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ54">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR54">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS54">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="BT54">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU54">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV54">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW54">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX54">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY54">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BZ54">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="CA54">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB54" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:80">
@@ -14210,184 +14219,184 @@
         <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F55">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="G55">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="I55">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="J55">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K55">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L55">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M55">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N55">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="O55">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="P55">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="Q55">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="R55">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="S55">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T55">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="U55">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W55">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="X55">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Y55">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Z55">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AA55">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AB55">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC55">
+        <v>10</v>
+      </c>
+      <c r="AD55">
+        <v>23</v>
+      </c>
+      <c r="AE55">
+        <v>85</v>
+      </c>
+      <c r="AF55">
         <v>13.5</v>
-      </c>
-      <c r="AC55">
-        <v>10.5</v>
-      </c>
-      <c r="AD55">
-        <v>16.5</v>
-      </c>
-      <c r="AE55">
-        <v>40</v>
-      </c>
-      <c r="AF55">
-        <v>17</v>
       </c>
       <c r="AG55">
         <v>12.5</v>
       </c>
       <c r="AH55">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI55">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="AJ55">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AK55">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL55">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AM55">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AN55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO55">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AP55">
+        <v>3.55</v>
+      </c>
+      <c r="AQ55">
+        <v>3.7</v>
+      </c>
+      <c r="AR55">
+        <v>4.1</v>
+      </c>
+      <c r="AS55">
         <v>4.4</v>
       </c>
-      <c r="AQ55">
+      <c r="AT55">
+        <v>3.1</v>
+      </c>
+      <c r="AU55">
+        <v>3.15</v>
+      </c>
+      <c r="AV55">
+        <v>3.85</v>
+      </c>
+      <c r="AW55">
+        <v>4.3</v>
+      </c>
+      <c r="AX55">
+        <v>3.4</v>
+      </c>
+      <c r="AY55">
+        <v>3.35</v>
+      </c>
+      <c r="AZ55">
+        <v>3.9</v>
+      </c>
+      <c r="BA55">
+        <v>4.3</v>
+      </c>
+      <c r="BB55">
+        <v>3.9</v>
+      </c>
+      <c r="BC55">
+        <v>3.9</v>
+      </c>
+      <c r="BD55">
         <v>4.2</v>
       </c>
-      <c r="AR55">
-        <v>21</v>
-      </c>
-      <c r="AS55">
-        <v>5.2</v>
-      </c>
-      <c r="AT55">
-        <v>3.95</v>
-      </c>
-      <c r="AU55">
-        <v>3.65</v>
-      </c>
-      <c r="AV55">
-        <v>4.2</v>
-      </c>
-      <c r="AW55">
-        <v>4.9</v>
-      </c>
-      <c r="AX55">
-        <v>4.2</v>
-      </c>
-      <c r="AY55">
-        <v>3.85</v>
-      </c>
-      <c r="AZ55">
-        <v>4.3</v>
-      </c>
-      <c r="BA55">
-        <v>5</v>
-      </c>
-      <c r="BB55">
-        <v>4.8</v>
-      </c>
-      <c r="BC55">
-        <v>4.5</v>
-      </c>
-      <c r="BD55">
-        <v>4.8</v>
-      </c>
       <c r="BE55">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF55">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="BG55">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BH55">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BI55">
-        <v>3.15</v>
+        <v>2.64</v>
       </c>
       <c r="BJ55">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BK55">
         <v>5.2</v>
@@ -14396,52 +14405,52 @@
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="BN55">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO55">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="BP55">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ55">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR55">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BS55">
-        <v>8.199999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="BT55">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BU55">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV55">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BW55">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="BX55">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BY55">
-        <v>9</v>
+        <v>2.42</v>
       </c>
       <c r="BZ55">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="CA55">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB55" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:80">
@@ -14452,243 +14461,243 @@
         <v>114</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F56">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="G56">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="H56">
+        <v>3.1</v>
+      </c>
+      <c r="I56">
+        <v>3.45</v>
+      </c>
+      <c r="J56">
+        <v>3.7</v>
+      </c>
+      <c r="K56">
+        <v>4</v>
+      </c>
+      <c r="L56">
+        <v>1.33</v>
+      </c>
+      <c r="M56">
+        <v>1.05</v>
+      </c>
+      <c r="N56">
+        <v>4.4</v>
+      </c>
+      <c r="O56">
+        <v>1.24</v>
+      </c>
+      <c r="P56">
+        <v>2.16</v>
+      </c>
+      <c r="Q56">
+        <v>1.72</v>
+      </c>
+      <c r="R56">
+        <v>1.46</v>
+      </c>
+      <c r="S56">
+        <v>2.8</v>
+      </c>
+      <c r="T56">
+        <v>1.63</v>
+      </c>
+      <c r="U56">
+        <v>2.3</v>
+      </c>
+      <c r="V56">
+        <v>1.4</v>
+      </c>
+      <c r="W56">
+        <v>1.73</v>
+      </c>
+      <c r="X56">
+        <v>22</v>
+      </c>
+      <c r="Y56">
+        <v>17.5</v>
+      </c>
+      <c r="Z56">
+        <v>29</v>
+      </c>
+      <c r="AA56">
+        <v>65</v>
+      </c>
+      <c r="AB56">
+        <v>13.5</v>
+      </c>
+      <c r="AC56">
+        <v>10.5</v>
+      </c>
+      <c r="AD56">
+        <v>16.5</v>
+      </c>
+      <c r="AE56">
+        <v>40</v>
+      </c>
+      <c r="AF56">
+        <v>17</v>
+      </c>
+      <c r="AG56">
+        <v>12.5</v>
+      </c>
+      <c r="AH56">
+        <v>19</v>
+      </c>
+      <c r="AI56">
+        <v>46</v>
+      </c>
+      <c r="AJ56">
+        <v>34</v>
+      </c>
+      <c r="AK56">
+        <v>24</v>
+      </c>
+      <c r="AL56">
+        <v>36</v>
+      </c>
+      <c r="AM56">
+        <v>85</v>
+      </c>
+      <c r="AN56">
+        <v>16</v>
+      </c>
+      <c r="AO56">
+        <v>34</v>
+      </c>
+      <c r="AP56">
+        <v>4.4</v>
+      </c>
+      <c r="AQ56">
+        <v>4.2</v>
+      </c>
+      <c r="AR56">
+        <v>21</v>
+      </c>
+      <c r="AS56">
+        <v>5.2</v>
+      </c>
+      <c r="AT56">
+        <v>9.4</v>
+      </c>
+      <c r="AU56">
+        <v>3.65</v>
+      </c>
+      <c r="AV56">
+        <v>4.2</v>
+      </c>
+      <c r="AW56">
+        <v>4.9</v>
+      </c>
+      <c r="AX56">
+        <v>4.2</v>
+      </c>
+      <c r="AY56">
+        <v>3.85</v>
+      </c>
+      <c r="AZ56">
         <v>4.3</v>
       </c>
-      <c r="I56">
-        <v>5.6</v>
-      </c>
-      <c r="J56">
-        <v>3.45</v>
-      </c>
-      <c r="K56">
-        <v>3.8</v>
-      </c>
-      <c r="L56">
-        <v>1.01</v>
-      </c>
-      <c r="M56">
-        <v>1.01</v>
-      </c>
-      <c r="N56">
-        <v>2.92</v>
-      </c>
-      <c r="O56">
-        <v>1.37</v>
-      </c>
-      <c r="P56">
-        <v>1.68</v>
-      </c>
-      <c r="Q56">
-        <v>2.1</v>
-      </c>
-      <c r="R56">
-        <v>1.08</v>
-      </c>
-      <c r="S56">
-        <v>3.75</v>
-      </c>
-      <c r="T56">
-        <v>1.11</v>
-      </c>
-      <c r="U56">
-        <v>1.11</v>
-      </c>
-      <c r="V56">
-        <v>1.21</v>
-      </c>
-      <c r="W56">
-        <v>1.95</v>
-      </c>
-      <c r="X56">
-        <v>1000</v>
-      </c>
-      <c r="Y56">
-        <v>1000</v>
-      </c>
-      <c r="Z56">
-        <v>1000</v>
-      </c>
-      <c r="AA56">
-        <v>1000</v>
-      </c>
-      <c r="AB56">
-        <v>1000</v>
-      </c>
-      <c r="AC56">
-        <v>1000</v>
-      </c>
-      <c r="AD56">
-        <v>1000</v>
-      </c>
-      <c r="AE56">
-        <v>1000</v>
-      </c>
-      <c r="AF56">
-        <v>1000</v>
-      </c>
-      <c r="AG56">
-        <v>1000</v>
-      </c>
-      <c r="AH56">
-        <v>1000</v>
-      </c>
-      <c r="AI56">
-        <v>1000</v>
-      </c>
-      <c r="AJ56">
-        <v>1000</v>
-      </c>
-      <c r="AK56">
-        <v>1000</v>
-      </c>
-      <c r="AL56">
-        <v>1000</v>
-      </c>
-      <c r="AM56">
-        <v>1000</v>
-      </c>
-      <c r="AN56">
-        <v>1000</v>
-      </c>
-      <c r="AO56">
-        <v>1000</v>
-      </c>
-      <c r="AP56">
-        <v>1.03</v>
-      </c>
-      <c r="AQ56">
-        <v>1.03</v>
-      </c>
-      <c r="AR56">
-        <v>1.03</v>
-      </c>
-      <c r="AS56">
-        <v>1.03</v>
-      </c>
-      <c r="AT56">
-        <v>1.03</v>
-      </c>
-      <c r="AU56">
-        <v>1.03</v>
-      </c>
-      <c r="AV56">
-        <v>1.03</v>
-      </c>
-      <c r="AW56">
-        <v>1.03</v>
-      </c>
-      <c r="AX56">
-        <v>1.03</v>
-      </c>
-      <c r="AY56">
-        <v>1.03</v>
-      </c>
-      <c r="AZ56">
-        <v>1.03</v>
-      </c>
       <c r="BA56">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB56">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC56">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD56">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE56">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF56">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG56">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH56">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BI56">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="BJ56">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK56">
-        <v>1.37</v>
+        <v>5.2</v>
       </c>
       <c r="BL56">
         <v>1000</v>
       </c>
       <c r="BM56">
-        <v>1.37</v>
+        <v>10.5</v>
       </c>
       <c r="BN56">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO56">
-        <v>1.37</v>
+        <v>4.2</v>
       </c>
       <c r="BP56">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ56">
-        <v>1.37</v>
+        <v>6.8</v>
       </c>
       <c r="BR56">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS56">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT56">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU56">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="BV56">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW56">
-        <v>1.37</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX56">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY56">
-        <v>1.37</v>
+        <v>9</v>
       </c>
       <c r="BZ56">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA56">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="CB56" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:80">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
         <v>114</v>
@@ -14697,235 +14706,235 @@
         <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F57">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="G57">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="H57">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="I57">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="J57">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K57">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="L57">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M57">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N57">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="O57">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="P57">
+        <v>1.68</v>
+      </c>
+      <c r="Q57">
+        <v>2.1</v>
+      </c>
+      <c r="R57">
+        <v>1.07</v>
+      </c>
+      <c r="S57">
+        <v>3.75</v>
+      </c>
+      <c r="T57">
+        <v>1.11</v>
+      </c>
+      <c r="U57">
+        <v>1.11</v>
+      </c>
+      <c r="V57">
+        <v>1.21</v>
+      </c>
+      <c r="W57">
         <v>2</v>
       </c>
-      <c r="Q57">
-        <v>1.81</v>
-      </c>
-      <c r="R57">
-        <v>1.39</v>
-      </c>
-      <c r="S57">
-        <v>3.1</v>
-      </c>
-      <c r="T57">
-        <v>1.99</v>
-      </c>
-      <c r="U57">
-        <v>1.86</v>
-      </c>
-      <c r="V57">
-        <v>1.12</v>
-      </c>
-      <c r="W57">
-        <v>2.8</v>
-      </c>
       <c r="X57">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y57">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z57">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA57">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB57">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC57">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD57">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE57">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF57">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG57">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH57">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI57">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ57">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AK57">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL57">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM57">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN57">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO57">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP57">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AR57">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AS57">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AT57">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU57">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV57">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW57">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX57">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY57">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ57">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA57">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB57">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC57">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD57">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE57">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF57">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG57">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH57">
         <v>3.75</v>
       </c>
       <c r="BI57">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="BJ57">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK57">
-        <v>8.800000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="BL57">
         <v>1000</v>
       </c>
       <c r="BM57">
-        <v>12</v>
+        <v>1.37</v>
       </c>
       <c r="BN57">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO57">
-        <v>3.2</v>
+        <v>1.37</v>
       </c>
       <c r="BP57">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ57">
-        <v>5.5</v>
+        <v>1.37</v>
       </c>
       <c r="BR57">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS57">
-        <v>8.6</v>
+        <v>1.37</v>
       </c>
       <c r="BT57">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU57">
-        <v>8.800000000000001</v>
+        <v>1.37</v>
       </c>
       <c r="BV57">
         <v>1000</v>
       </c>
       <c r="BW57">
-        <v>11</v>
+        <v>1.37</v>
       </c>
       <c r="BX57">
         <v>1000</v>
       </c>
       <c r="BY57">
-        <v>11</v>
+        <v>1.37</v>
       </c>
       <c r="BZ57">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA57">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB57" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="58" spans="1:80">
@@ -14939,267 +14948,267 @@
         <v>136</v>
       </c>
       <c r="D58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E58" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F58">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G58">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="H58">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="I58">
-        <v>990</v>
+        <v>9</v>
       </c>
       <c r="J58">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="K58">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L58">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M58">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N58">
-        <v>1.29</v>
+        <v>3.95</v>
       </c>
       <c r="O58">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="P58">
+        <v>2</v>
+      </c>
+      <c r="Q58">
+        <v>1.83</v>
+      </c>
+      <c r="R58">
+        <v>1.39</v>
+      </c>
+      <c r="S58">
+        <v>3.1</v>
+      </c>
+      <c r="T58">
+        <v>1.99</v>
+      </c>
+      <c r="U58">
+        <v>1.86</v>
+      </c>
+      <c r="V58">
         <v>1.12</v>
       </c>
-      <c r="Q58">
-        <v>1.14</v>
-      </c>
-      <c r="R58">
-        <v>1.28</v>
-      </c>
-      <c r="S58">
-        <v>1.14</v>
-      </c>
-      <c r="T58">
-        <v>1.11</v>
-      </c>
-      <c r="U58">
-        <v>1.11</v>
-      </c>
-      <c r="V58">
-        <v>1.01</v>
-      </c>
       <c r="W58">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="X58">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y58">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z58">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA58">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB58">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC58">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD58">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE58">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF58">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG58">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH58">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI58">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ58">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK58">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL58">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM58">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN58">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO58">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP58">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ58">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AR58">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS58">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT58">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU58">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV58">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AW58">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX58">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY58">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ58">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA58">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB58">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC58">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD58">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE58">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF58">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG58">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH58">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI58">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ58">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK58">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN58">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BO58">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP58">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ58">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BR58">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS58">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT58">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU58">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV58">
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX58">
         <v>1000</v>
       </c>
       <c r="BY58">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ58">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="CA58">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="CB58" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:80">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B59" t="s">
         <v>114</v>
       </c>
       <c r="C59" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D59" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E59" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F59">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="G59">
-        <v>990</v>
+        <v>1.94</v>
       </c>
       <c r="H59">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="I59">
         <v>990</v>
       </c>
       <c r="J59">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="K59">
         <v>950</v>
@@ -15211,22 +15220,22 @@
         <v>1.01</v>
       </c>
       <c r="N59">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O59">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="P59">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Q59">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="R59">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S59">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="T59">
         <v>1.11</v>
@@ -15235,10 +15244,10 @@
         <v>1.11</v>
       </c>
       <c r="V59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>2.06</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15352,99 +15361,99 @@
         <v>1000</v>
       </c>
       <c r="BI59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ59">
         <v>1000</v>
       </c>
       <c r="BK59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL59">
         <v>1000</v>
       </c>
       <c r="BM59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN59">
         <v>1000</v>
       </c>
       <c r="BO59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP59">
         <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR59">
         <v>1000</v>
       </c>
       <c r="BS59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT59">
         <v>1000</v>
       </c>
       <c r="BU59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV59">
         <v>1000</v>
       </c>
       <c r="BW59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX59">
         <v>1000</v>
       </c>
       <c r="BY59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ59">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA59">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB59" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:80">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
         <v>114</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D60" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E60" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F60">
-        <v>1.98</v>
+        <v>1.15</v>
       </c>
       <c r="G60">
-        <v>2.28</v>
+        <v>990</v>
       </c>
       <c r="H60">
-        <v>3.75</v>
+        <v>1.15</v>
       </c>
       <c r="I60">
-        <v>6.6</v>
+        <v>990</v>
       </c>
       <c r="J60">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="K60">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15453,22 +15462,22 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O60">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="P60">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="Q60">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="R60">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S60">
-        <v>2.96</v>
+        <v>1.39</v>
       </c>
       <c r="T60">
         <v>1.11</v>
@@ -15477,10 +15486,10 @@
         <v>1.11</v>
       </c>
       <c r="V60">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="W60">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15537,52 +15546,52 @@
         <v>1000</v>
       </c>
       <c r="AP60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF60">
         <v>1.01</v>
@@ -15594,69 +15603,69 @@
         <v>1000</v>
       </c>
       <c r="BI60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ60">
         <v>1000</v>
       </c>
       <c r="BK60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL60">
         <v>1000</v>
       </c>
       <c r="BM60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN60">
         <v>1000</v>
       </c>
       <c r="BO60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP60">
         <v>1000</v>
       </c>
       <c r="BQ60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR60">
         <v>1000</v>
       </c>
       <c r="BS60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT60">
         <v>1000</v>
       </c>
       <c r="BU60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV60">
         <v>1000</v>
       </c>
       <c r="BW60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX60">
         <v>1000</v>
       </c>
       <c r="BY60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ60">
         <v>1000</v>
       </c>
       <c r="CA60">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB60" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:80">
       <c r="A61" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
         <v>114</v>
@@ -15665,240 +15674,240 @@
         <v>137</v>
       </c>
       <c r="D61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E61" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F61">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="G61">
+        <v>2.34</v>
+      </c>
+      <c r="H61">
+        <v>3.75</v>
+      </c>
+      <c r="I61">
+        <v>5</v>
+      </c>
+      <c r="J61">
+        <v>2.92</v>
+      </c>
+      <c r="K61">
+        <v>4.1</v>
+      </c>
+      <c r="L61">
+        <v>1.01</v>
+      </c>
+      <c r="M61">
+        <v>1.01</v>
+      </c>
+      <c r="N61">
+        <v>2.34</v>
+      </c>
+      <c r="O61">
+        <v>1.3</v>
+      </c>
+      <c r="P61">
+        <v>1.45</v>
+      </c>
+      <c r="Q61">
+        <v>2.44</v>
+      </c>
+      <c r="R61">
+        <v>1.08</v>
+      </c>
+      <c r="S61">
+        <v>2.96</v>
+      </c>
+      <c r="T61">
+        <v>1.11</v>
+      </c>
+      <c r="U61">
+        <v>1.11</v>
+      </c>
+      <c r="V61">
+        <v>1.25</v>
+      </c>
+      <c r="W61">
         <v>1.74</v>
       </c>
-      <c r="H61">
-        <v>6.4</v>
-      </c>
-      <c r="I61">
-        <v>7.4</v>
-      </c>
-      <c r="J61">
-        <v>3.6</v>
-      </c>
-      <c r="K61">
-        <v>4</v>
-      </c>
-      <c r="L61">
-        <v>1.49</v>
-      </c>
-      <c r="M61">
-        <v>1.1</v>
-      </c>
-      <c r="N61">
-        <v>2.96</v>
-      </c>
-      <c r="O61">
-        <v>1.43</v>
-      </c>
-      <c r="P61">
-        <v>1.66</v>
-      </c>
-      <c r="Q61">
-        <v>2.28</v>
-      </c>
-      <c r="R61">
-        <v>1.24</v>
-      </c>
-      <c r="S61">
-        <v>4.4</v>
-      </c>
-      <c r="T61">
-        <v>2.18</v>
-      </c>
-      <c r="U61">
-        <v>1.73</v>
-      </c>
-      <c r="V61">
-        <v>1.15</v>
-      </c>
-      <c r="W61">
-        <v>2.34</v>
-      </c>
       <c r="X61">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y61">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z61">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA61">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB61">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC61">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD61">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE61">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF61">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG61">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH61">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI61">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ61">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK61">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL61">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM61">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN61">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO61">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AP61">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ61">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR61">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AS61">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT61">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU61">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV61">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AW61">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX61">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY61">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ61">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA61">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB61">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC61">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BD61">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE61">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BF61">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG61">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH61">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI61">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BJ61">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK61">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL61">
         <v>1000</v>
       </c>
       <c r="BM61">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BN61">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BO61">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP61">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ61">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BR61">
         <v>1000</v>
       </c>
       <c r="BS61">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BT61">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU61">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BV61">
         <v>1000</v>
       </c>
       <c r="BW61">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BX61">
         <v>1000</v>
       </c>
       <c r="BY61">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ61">
         <v>1000</v>
       </c>
       <c r="CA61">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="CB61" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:80">
       <c r="A62" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B62" t="s">
         <v>114</v>
@@ -15907,235 +15916,477 @@
         <v>138</v>
       </c>
       <c r="D62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E62" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F62">
+        <v>1.64</v>
+      </c>
+      <c r="G62">
+        <v>1.72</v>
+      </c>
+      <c r="H62">
+        <v>6.4</v>
+      </c>
+      <c r="I62">
+        <v>7.6</v>
+      </c>
+      <c r="J62">
+        <v>3.6</v>
+      </c>
+      <c r="K62">
+        <v>4</v>
+      </c>
+      <c r="L62">
+        <v>1.48</v>
+      </c>
+      <c r="M62">
+        <v>1.1</v>
+      </c>
+      <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62">
+        <v>1.43</v>
+      </c>
+      <c r="P62">
+        <v>1.68</v>
+      </c>
+      <c r="Q62">
+        <v>2.28</v>
+      </c>
+      <c r="R62">
+        <v>1.25</v>
+      </c>
+      <c r="S62">
+        <v>4.4</v>
+      </c>
+      <c r="T62">
+        <v>2.18</v>
+      </c>
+      <c r="U62">
+        <v>1.73</v>
+      </c>
+      <c r="V62">
+        <v>1.15</v>
+      </c>
+      <c r="W62">
+        <v>2.38</v>
+      </c>
+      <c r="X62">
+        <v>12.5</v>
+      </c>
+      <c r="Y62">
+        <v>18</v>
+      </c>
+      <c r="Z62">
+        <v>75</v>
+      </c>
+      <c r="AA62">
+        <v>270</v>
+      </c>
+      <c r="AB62">
+        <v>6.6</v>
+      </c>
+      <c r="AC62">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD62">
+        <v>38</v>
+      </c>
+      <c r="AE62">
+        <v>150</v>
+      </c>
+      <c r="AF62">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG62">
+        <v>10.5</v>
+      </c>
+      <c r="AH62">
+        <v>38</v>
+      </c>
+      <c r="AI62">
+        <v>150</v>
+      </c>
+      <c r="AJ62">
+        <v>23</v>
+      </c>
+      <c r="AK62">
+        <v>25</v>
+      </c>
+      <c r="AL62">
+        <v>60</v>
+      </c>
+      <c r="AM62">
+        <v>230</v>
+      </c>
+      <c r="AN62">
+        <v>14</v>
+      </c>
+      <c r="AO62">
+        <v>250</v>
+      </c>
+      <c r="AP62">
+        <v>9.6</v>
+      </c>
+      <c r="AQ62">
+        <v>15</v>
+      </c>
+      <c r="AR62">
+        <v>9.6</v>
+      </c>
+      <c r="AS62">
+        <v>11</v>
+      </c>
+      <c r="AT62">
+        <v>5.8</v>
+      </c>
+      <c r="AU62">
+        <v>7.6</v>
+      </c>
+      <c r="AV62">
+        <v>19</v>
+      </c>
+      <c r="AW62">
+        <v>10.5</v>
+      </c>
+      <c r="AX62">
+        <v>7.8</v>
+      </c>
+      <c r="AY62">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ62">
+        <v>20</v>
+      </c>
+      <c r="BA62">
+        <v>10.5</v>
+      </c>
+      <c r="BB62">
+        <v>14.5</v>
+      </c>
+      <c r="BC62">
+        <v>16</v>
+      </c>
+      <c r="BD62">
+        <v>38</v>
+      </c>
+      <c r="BE62">
+        <v>10.5</v>
+      </c>
+      <c r="BF62">
+        <v>12.5</v>
+      </c>
+      <c r="BG62">
+        <v>10.5</v>
+      </c>
+      <c r="BH62">
+        <v>3.05</v>
+      </c>
+      <c r="BI62">
+        <v>2.56</v>
+      </c>
+      <c r="BJ62">
+        <v>12</v>
+      </c>
+      <c r="BK62">
+        <v>9.4</v>
+      </c>
+      <c r="BL62">
+        <v>1000</v>
+      </c>
+      <c r="BM62">
+        <v>14.5</v>
+      </c>
+      <c r="BN62">
+        <v>3.95</v>
+      </c>
+      <c r="BO62">
+        <v>3.55</v>
+      </c>
+      <c r="BP62">
+        <v>12</v>
+      </c>
+      <c r="BQ62">
+        <v>6.8</v>
+      </c>
+      <c r="BR62">
+        <v>1000</v>
+      </c>
+      <c r="BS62">
+        <v>10.5</v>
+      </c>
+      <c r="BT62">
+        <v>10.5</v>
+      </c>
+      <c r="BU62">
+        <v>8</v>
+      </c>
+      <c r="BV62">
+        <v>1000</v>
+      </c>
+      <c r="BW62">
+        <v>13</v>
+      </c>
+      <c r="BX62">
+        <v>1000</v>
+      </c>
+      <c r="BY62">
+        <v>13.5</v>
+      </c>
+      <c r="BZ62">
+        <v>1000</v>
+      </c>
+      <c r="CA62">
+        <v>10</v>
+      </c>
+      <c r="CB62" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="63" spans="1:80">
+      <c r="A63" t="s">
+        <v>95</v>
+      </c>
+      <c r="B63" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" t="s">
+        <v>139</v>
+      </c>
+      <c r="D63" t="s">
+        <v>201</v>
+      </c>
+      <c r="E63" t="s">
+        <v>263</v>
+      </c>
+      <c r="F63">
         <v>1.04</v>
       </c>
-      <c r="G62">
+      <c r="G63">
         <v>990</v>
       </c>
-      <c r="H62">
+      <c r="H63">
         <v>1.04</v>
       </c>
-      <c r="I62">
+      <c r="I63">
         <v>990</v>
       </c>
-      <c r="J62">
+      <c r="J63">
         <v>1.02</v>
       </c>
-      <c r="K62">
+      <c r="K63">
         <v>950</v>
       </c>
-      <c r="L62">
-        <v>1.01</v>
-      </c>
-      <c r="M62">
-        <v>1.01</v>
-      </c>
-      <c r="N62">
-        <v>3.05</v>
-      </c>
-      <c r="O62">
-        <v>1.01</v>
-      </c>
-      <c r="P62">
-        <v>1.05</v>
-      </c>
-      <c r="Q62">
-        <v>1.01</v>
-      </c>
-      <c r="R62">
+      <c r="L63">
+        <v>1.01</v>
+      </c>
+      <c r="M63">
+        <v>1.01</v>
+      </c>
+      <c r="N63">
+        <v>1.1</v>
+      </c>
+      <c r="O63">
+        <v>1.01</v>
+      </c>
+      <c r="P63">
         <v>1.07</v>
       </c>
-      <c r="S62">
-        <v>1.01</v>
-      </c>
-      <c r="T62">
+      <c r="Q63">
+        <v>1.01</v>
+      </c>
+      <c r="R63">
+        <v>1.08</v>
+      </c>
+      <c r="S63">
+        <v>1.58</v>
+      </c>
+      <c r="T63">
         <v>1.11</v>
       </c>
-      <c r="U62">
+      <c r="U63">
         <v>1.11</v>
       </c>
-      <c r="V62">
-        <v>1.01</v>
-      </c>
-      <c r="W62">
-        <v>1.01</v>
-      </c>
-      <c r="X62">
-        <v>1000</v>
-      </c>
-      <c r="Y62">
-        <v>1000</v>
-      </c>
-      <c r="Z62">
-        <v>1000</v>
-      </c>
-      <c r="AA62">
-        <v>1000</v>
-      </c>
-      <c r="AB62">
-        <v>1000</v>
-      </c>
-      <c r="AC62">
-        <v>1000</v>
-      </c>
-      <c r="AD62">
-        <v>1000</v>
-      </c>
-      <c r="AE62">
-        <v>1000</v>
-      </c>
-      <c r="AF62">
-        <v>1000</v>
-      </c>
-      <c r="AG62">
-        <v>1000</v>
-      </c>
-      <c r="AH62">
-        <v>1000</v>
-      </c>
-      <c r="AI62">
-        <v>1000</v>
-      </c>
-      <c r="AJ62">
-        <v>1000</v>
-      </c>
-      <c r="AK62">
-        <v>1000</v>
-      </c>
-      <c r="AL62">
-        <v>1000</v>
-      </c>
-      <c r="AM62">
-        <v>1000</v>
-      </c>
-      <c r="AN62">
-        <v>1000</v>
-      </c>
-      <c r="AO62">
-        <v>1000</v>
-      </c>
-      <c r="AP62">
+      <c r="V63">
+        <v>1.01</v>
+      </c>
+      <c r="W63">
+        <v>1.01</v>
+      </c>
+      <c r="X63">
+        <v>1000</v>
+      </c>
+      <c r="Y63">
+        <v>1000</v>
+      </c>
+      <c r="Z63">
+        <v>1000</v>
+      </c>
+      <c r="AA63">
+        <v>1000</v>
+      </c>
+      <c r="AB63">
+        <v>1000</v>
+      </c>
+      <c r="AC63">
+        <v>1000</v>
+      </c>
+      <c r="AD63">
+        <v>1000</v>
+      </c>
+      <c r="AE63">
+        <v>1000</v>
+      </c>
+      <c r="AF63">
+        <v>1000</v>
+      </c>
+      <c r="AG63">
+        <v>1000</v>
+      </c>
+      <c r="AH63">
+        <v>1000</v>
+      </c>
+      <c r="AI63">
+        <v>1000</v>
+      </c>
+      <c r="AJ63">
+        <v>1000</v>
+      </c>
+      <c r="AK63">
+        <v>1000</v>
+      </c>
+      <c r="AL63">
+        <v>1000</v>
+      </c>
+      <c r="AM63">
+        <v>1000</v>
+      </c>
+      <c r="AN63">
+        <v>1000</v>
+      </c>
+      <c r="AO63">
+        <v>1000</v>
+      </c>
+      <c r="AP63">
         <v>1.03</v>
       </c>
-      <c r="AQ62">
+      <c r="AQ63">
         <v>1.03</v>
       </c>
-      <c r="AR62">
+      <c r="AR63">
         <v>1.03</v>
       </c>
-      <c r="AS62">
+      <c r="AS63">
         <v>1.03</v>
       </c>
-      <c r="AT62">
+      <c r="AT63">
         <v>1.03</v>
       </c>
-      <c r="AU62">
+      <c r="AU63">
         <v>1.03</v>
       </c>
-      <c r="AV62">
+      <c r="AV63">
         <v>1.03</v>
       </c>
-      <c r="AW62">
+      <c r="AW63">
         <v>1.03</v>
       </c>
-      <c r="AX62">
+      <c r="AX63">
         <v>1.03</v>
       </c>
-      <c r="AY62">
+      <c r="AY63">
         <v>1.03</v>
       </c>
-      <c r="AZ62">
+      <c r="AZ63">
         <v>1.03</v>
       </c>
-      <c r="BA62">
+      <c r="BA63">
         <v>1.03</v>
       </c>
-      <c r="BB62">
+      <c r="BB63">
         <v>1.03</v>
       </c>
-      <c r="BC62">
+      <c r="BC63">
         <v>1.03</v>
       </c>
-      <c r="BD62">
+      <c r="BD63">
         <v>1.03</v>
       </c>
-      <c r="BE62">
+      <c r="BE63">
         <v>1.03</v>
       </c>
-      <c r="BF62">
-        <v>1.01</v>
-      </c>
-      <c r="BG62">
-        <v>1.01</v>
-      </c>
-      <c r="BH62">
-        <v>1000</v>
-      </c>
-      <c r="BI62">
-        <v>1.01</v>
-      </c>
-      <c r="BJ62">
-        <v>1000</v>
-      </c>
-      <c r="BK62">
-        <v>1.01</v>
-      </c>
-      <c r="BL62">
-        <v>1000</v>
-      </c>
-      <c r="BM62">
-        <v>1.01</v>
-      </c>
-      <c r="BN62">
-        <v>1000</v>
-      </c>
-      <c r="BO62">
-        <v>1.01</v>
-      </c>
-      <c r="BP62">
-        <v>1000</v>
-      </c>
-      <c r="BQ62">
-        <v>1.01</v>
-      </c>
-      <c r="BR62">
-        <v>1000</v>
-      </c>
-      <c r="BS62">
-        <v>1.01</v>
-      </c>
-      <c r="BT62">
-        <v>1000</v>
-      </c>
-      <c r="BU62">
-        <v>1.01</v>
-      </c>
-      <c r="BV62">
-        <v>1000</v>
-      </c>
-      <c r="BW62">
-        <v>1.01</v>
-      </c>
-      <c r="BX62">
-        <v>1000</v>
-      </c>
-      <c r="BY62">
-        <v>1.01</v>
-      </c>
-      <c r="BZ62">
-        <v>1000</v>
-      </c>
-      <c r="CA62">
-        <v>1.01</v>
-      </c>
-      <c r="CB62" t="s">
-        <v>261</v>
+      <c r="BF63">
+        <v>1.01</v>
+      </c>
+      <c r="BG63">
+        <v>1.01</v>
+      </c>
+      <c r="BH63">
+        <v>1000</v>
+      </c>
+      <c r="BI63">
+        <v>1.01</v>
+      </c>
+      <c r="BJ63">
+        <v>1000</v>
+      </c>
+      <c r="BK63">
+        <v>1.01</v>
+      </c>
+      <c r="BL63">
+        <v>1000</v>
+      </c>
+      <c r="BM63">
+        <v>1.01</v>
+      </c>
+      <c r="BN63">
+        <v>1000</v>
+      </c>
+      <c r="BO63">
+        <v>1.01</v>
+      </c>
+      <c r="BP63">
+        <v>1000</v>
+      </c>
+      <c r="BQ63">
+        <v>1.01</v>
+      </c>
+      <c r="BR63">
+        <v>1000</v>
+      </c>
+      <c r="BS63">
+        <v>1.01</v>
+      </c>
+      <c r="BT63">
+        <v>1000</v>
+      </c>
+      <c r="BU63">
+        <v>1.01</v>
+      </c>
+      <c r="BV63">
+        <v>1000</v>
+      </c>
+      <c r="BW63">
+        <v>1.01</v>
+      </c>
+      <c r="BX63">
+        <v>1000</v>
+      </c>
+      <c r="BY63">
+        <v>1.01</v>
+      </c>
+      <c r="BZ63">
+        <v>1000</v>
+      </c>
+      <c r="CA63">
+        <v>1.01</v>
+      </c>
+      <c r="CB63" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -808,7 +808,7 @@
     <t>Escobar FC</t>
   </si>
   <si>
-    <t>2026-07-23 14:38:54</t>
+    <t>2026-07-23 16:51:23</t>
   </si>
 </sst>
 </file>
@@ -1405,19 +1405,19 @@
         <v>1.84</v>
       </c>
       <c r="G2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H2">
         <v>5.1</v>
       </c>
       <c r="I2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J2">
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1435,7 +1435,7 @@
         <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1444,37 +1444,37 @@
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V2">
         <v>1.23</v>
       </c>
       <c r="W2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2">
         <v>95</v>
@@ -1486,19 +1486,19 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI2">
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK2">
         <v>29</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM2">
         <v>170</v>
@@ -1507,25 +1507,25 @@
         <v>15</v>
       </c>
       <c r="AO2">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR2">
         <v>30</v>
       </c>
       <c r="AS2">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>18.5</v>
@@ -1540,25 +1540,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>55</v>
       </c>
       <c r="BB2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BF2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
         <v>65</v>
@@ -1585,7 +1585,7 @@
         <v>4.3</v>
       </c>
       <c r="BO2">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
         <v>13</v>
@@ -1644,40 +1644,40 @@
         <v>203</v>
       </c>
       <c r="F3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
         <v>2.92</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
         <v>1.18</v>
@@ -1686,19 +1686,19 @@
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
         <v>9.4</v>
@@ -1707,22 +1707,22 @@
         <v>21</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1731,7 +1731,7 @@
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>44</v>
@@ -1740,19 +1740,19 @@
         <v>42</v>
       </c>
       <c r="AL3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="AN3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
         <v>8.4</v>
@@ -1761,16 +1761,16 @@
         <v>18</v>
       </c>
       <c r="AS3">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
         <v>46</v>
@@ -1785,7 +1785,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB3">
         <v>36</v>
@@ -1794,19 +1794,19 @@
         <v>30</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH3">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BI3">
         <v>2.28</v>
@@ -1821,13 +1821,13 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN3">
         <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
         <v>25</v>
@@ -1836,7 +1836,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS3">
         <v>10.5</v>
@@ -1848,13 +1848,13 @@
         <v>5.4</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3">
         <v>11</v>
@@ -1886,7 +1886,7 @@
         <v>204</v>
       </c>
       <c r="F4">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G4">
         <v>1.99</v>
@@ -1910,19 +1910,19 @@
         <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P4">
         <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
         <v>6.2</v>
@@ -1931,7 +1931,7 @@
         <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V4">
         <v>1.23</v>
@@ -1940,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="X4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>12</v>
@@ -1949,7 +1949,7 @@
         <v>38</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>6.2</v>
@@ -1958,37 +1958,37 @@
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF4">
         <v>10</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
+        <v>24</v>
+      </c>
+      <c r="AK4">
+        <v>30</v>
+      </c>
+      <c r="AL4">
+        <v>70</v>
+      </c>
+      <c r="AM4">
+        <v>280</v>
+      </c>
+      <c r="AN4">
         <v>27</v>
-      </c>
-      <c r="AK4">
-        <v>34</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>270</v>
-      </c>
-      <c r="AN4">
-        <v>40</v>
       </c>
       <c r="AO4">
         <v>1000</v>
@@ -1997,25 +1997,25 @@
         <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AT4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW4">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AX4">
         <v>8.800000000000001</v>
@@ -2027,13 +2027,13 @@
         <v>26</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD4">
         <v>60</v>
@@ -2042,10 +2042,10 @@
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BG4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BH4">
         <v>2.74</v>
@@ -2128,19 +2128,19 @@
         <v>205</v>
       </c>
       <c r="F5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>7.8</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
         <v>4.2</v>
@@ -2158,34 +2158,34 @@
         <v>1.42</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
         <v>1.28</v>
       </c>
       <c r="S5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U5">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
         <v>12</v>
       </c>
       <c r="Y5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
         <v>70</v>
@@ -2203,10 +2203,10 @@
         <v>29</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG5">
         <v>10.5</v>
@@ -2215,7 +2215,7 @@
         <v>32</v>
       </c>
       <c r="AI5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
@@ -2227,13 +2227,13 @@
         <v>60</v>
       </c>
       <c r="AM5">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO5">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -2245,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -2254,7 +2254,7 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW5">
         <v>70</v>
@@ -2278,76 +2278,76 @@
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO5">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
         <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="s">
         <v>264</v>
@@ -2376,7 +2376,7 @@
         <v>3.8</v>
       </c>
       <c r="H6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I6">
         <v>2.44</v>
@@ -2418,7 +2418,7 @@
         <v>1.98</v>
       </c>
       <c r="V6">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W6">
         <v>1.36</v>
@@ -2451,7 +2451,7 @@
         <v>29</v>
       </c>
       <c r="AG6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH6">
         <v>23</v>
@@ -2487,7 +2487,7 @@
         <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT6">
         <v>9</v>
@@ -2511,22 +2511,22 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="BB6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC6">
         <v>36</v>
       </c>
       <c r="BD6">
+        <v>5.4</v>
+      </c>
+      <c r="BE6">
+        <v>5.6</v>
+      </c>
+      <c r="BF6">
         <v>5.3</v>
-      </c>
-      <c r="BE6">
-        <v>5.5</v>
-      </c>
-      <c r="BF6">
-        <v>5.2</v>
       </c>
       <c r="BG6">
         <v>16.5</v>
@@ -2612,7 +2612,7 @@
         <v>207</v>
       </c>
       <c r="F7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G7">
         <v>1.66</v>
@@ -2624,7 +2624,7 @@
         <v>6.8</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
         <v>4.9</v>
@@ -2654,7 +2654,7 @@
         <v>2.72</v>
       </c>
       <c r="T7">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U7">
         <v>2.08</v>
@@ -2854,7 +2854,7 @@
         <v>208</v>
       </c>
       <c r="F8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
         <v>2.32</v>
@@ -2863,10 +2863,10 @@
         <v>3.6</v>
       </c>
       <c r="I8">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J8">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K8">
         <v>3.45</v>
@@ -2902,7 +2902,7 @@
         <v>2.02</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
         <v>1.76</v>
@@ -2965,7 +2965,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR8">
         <v>5.2</v>
@@ -2974,7 +2974,7 @@
         <v>5.9</v>
       </c>
       <c r="AT8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU8">
         <v>6.6</v>
@@ -2989,16 +2989,16 @@
         <v>11.5</v>
       </c>
       <c r="AY8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA8">
         <v>5.8</v>
       </c>
       <c r="BB8">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="BC8">
         <v>21</v>
@@ -3126,7 +3126,7 @@
         <v>1.23</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
         <v>1.68</v>
@@ -3141,7 +3141,7 @@
         <v>1.65</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.27</v>
@@ -3156,7 +3156,7 @@
         <v>23</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA9">
         <v>100</v>
@@ -3213,7 +3213,7 @@
         <v>4.1</v>
       </c>
       <c r="AS9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT9">
         <v>8.4</v>
@@ -3255,7 +3255,7 @@
         <v>7.8</v>
       </c>
       <c r="BG9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH9">
         <v>4.1</v>
@@ -3267,7 +3267,7 @@
         <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -3279,7 +3279,7 @@
         <v>5</v>
       </c>
       <c r="BO9">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
@@ -3297,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV9">
         <v>34</v>
@@ -3368,7 +3368,7 @@
         <v>1.32</v>
       </c>
       <c r="P10">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q10">
         <v>2.04</v>
@@ -3395,34 +3395,34 @@
         <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA10">
         <v>55</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC10">
         <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE10">
         <v>40</v>
       </c>
       <c r="AF10">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI10">
         <v>55</v>
@@ -3443,7 +3443,7 @@
         <v>32</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP10">
         <v>10.5</v>
@@ -3455,7 +3455,7 @@
         <v>16.5</v>
       </c>
       <c r="AS10">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="AT10">
         <v>9.6</v>
@@ -3467,7 +3467,7 @@
         <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX10">
         <v>15.5</v>
@@ -3479,25 +3479,25 @@
         <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BB10">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC10">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>5.4</v>
       </c>
       <c r="BE10">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF10">
         <v>21</v>
       </c>
       <c r="BG10">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BH10">
         <v>3.5</v>
@@ -3607,7 +3607,7 @@
         <v>5</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
         <v>2.42</v>
@@ -3619,13 +3619,13 @@
         <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U11">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V11">
         <v>1.82</v>
@@ -3649,7 +3649,7 @@
         <v>18</v>
       </c>
       <c r="AC11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD11">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         <v>14.5</v>
       </c>
       <c r="AH11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI11">
         <v>30</v>
@@ -3822,22 +3822,22 @@
         <v>212</v>
       </c>
       <c r="F12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H12">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>1.26</v>
@@ -3846,7 +3846,7 @@
         <v>1.04</v>
       </c>
       <c r="N12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
         <v>1.22</v>
@@ -3858,7 +3858,7 @@
         <v>1.65</v>
       </c>
       <c r="R12">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S12">
         <v>2.66</v>
@@ -3873,7 +3873,7 @@
         <v>1.25</v>
       </c>
       <c r="W12">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X12">
         <v>26</v>
@@ -3891,7 +3891,7 @@
         <v>13</v>
       </c>
       <c r="AC12">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
         <v>24</v>
@@ -3912,10 +3912,10 @@
         <v>65</v>
       </c>
       <c r="AJ12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL12">
         <v>32</v>
@@ -3924,7 +3924,7 @@
         <v>100</v>
       </c>
       <c r="AN12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO12">
         <v>65</v>
@@ -3936,22 +3936,22 @@
         <v>15.5</v>
       </c>
       <c r="AR12">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS12">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AT12">
         <v>8.199999999999999</v>
       </c>
       <c r="AU12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12">
         <v>15</v>
       </c>
       <c r="AW12">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX12">
         <v>8.800000000000001</v>
@@ -3963,7 +3963,7 @@
         <v>13.5</v>
       </c>
       <c r="BA12">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB12">
         <v>12.5</v>
@@ -3975,19 +3975,19 @@
         <v>21</v>
       </c>
       <c r="BE12">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF12">
         <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH12">
         <v>4.2</v>
       </c>
       <c r="BI12">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12">
         <v>10</v>
@@ -4064,22 +4064,22 @@
         <v>213</v>
       </c>
       <c r="F13">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="H13">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I13">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="J13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4112,10 +4112,10 @@
         <v>2.36</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X13">
         <v>22</v>
@@ -4124,10 +4124,10 @@
         <v>16</v>
       </c>
       <c r="Z13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB13">
         <v>16.5</v>
@@ -4139,7 +4139,7 @@
         <v>15</v>
       </c>
       <c r="AE13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF13">
         <v>25</v>
@@ -4151,7 +4151,7 @@
         <v>19</v>
       </c>
       <c r="AI13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ13">
         <v>50</v>
@@ -4169,19 +4169,19 @@
         <v>25</v>
       </c>
       <c r="AO13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP13">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT13">
         <v>12</v>
@@ -4193,10 +4193,10 @@
         <v>11</v>
       </c>
       <c r="AW13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AY13">
         <v>11</v>
@@ -4205,19 +4205,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
+        <v>4.3</v>
+      </c>
+      <c r="BB13">
+        <v>4.4</v>
+      </c>
+      <c r="BC13">
         <v>4.2</v>
       </c>
-      <c r="BB13">
-        <v>4.2</v>
-      </c>
-      <c r="BC13">
-        <v>4.1</v>
-      </c>
       <c r="BD13">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE13">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF13">
         <v>15</v>
@@ -4560,7 +4560,7 @@
         <v>7.8</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
         <v>5.2</v>
@@ -4569,13 +4569,13 @@
         <v>1.22</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
         <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
         <v>2.02</v>
@@ -4644,7 +4644,7 @@
         <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM15">
         <v>130</v>
@@ -4656,58 +4656,58 @@
         <v>130</v>
       </c>
       <c r="AP15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS15">
+        <v>8.4</v>
+      </c>
+      <c r="AT15">
+        <v>4.6</v>
+      </c>
+      <c r="AU15">
+        <v>4.9</v>
+      </c>
+      <c r="AV15">
+        <v>6.6</v>
+      </c>
+      <c r="AW15">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT15">
-        <v>4.5</v>
-      </c>
-      <c r="AU15">
+      <c r="AX15">
         <v>4.8</v>
       </c>
-      <c r="AV15">
-        <v>6.4</v>
-      </c>
-      <c r="AW15">
-        <v>7.8</v>
-      </c>
-      <c r="AX15">
-        <v>4.7</v>
-      </c>
       <c r="AY15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AZ15">
         <v>6.2</v>
       </c>
       <c r="BA15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB15">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD15">
         <v>7</v>
       </c>
       <c r="BE15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4731,7 +4731,7 @@
         <v>5.8</v>
       </c>
       <c r="BO15">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BP15">
         <v>13.5</v>
@@ -4790,19 +4790,19 @@
         <v>216</v>
       </c>
       <c r="F16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G16">
         <v>990</v>
       </c>
       <c r="H16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I16">
         <v>990</v>
       </c>
       <c r="J16">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K16">
         <v>950</v>
@@ -4811,7 +4811,7 @@
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N16">
         <v>1.1</v>
@@ -5307,7 +5307,7 @@
         <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R18">
         <v>1.37</v>
@@ -5758,16 +5758,16 @@
         <v>220</v>
       </c>
       <c r="F20">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H20">
         <v>4</v>
       </c>
       <c r="I20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J20">
         <v>3.95</v>
@@ -5782,16 +5782,16 @@
         <v>1.05</v>
       </c>
       <c r="N20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O20">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P20">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q20">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R20">
         <v>1.51</v>
@@ -5803,13 +5803,13 @@
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
         <v>1.31</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5827,7 +5827,7 @@
         <v>12</v>
       </c>
       <c r="AC20">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD20">
         <v>17</v>
@@ -5860,7 +5860,7 @@
         <v>75</v>
       </c>
       <c r="AN20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO20">
         <v>38</v>
@@ -5875,7 +5875,7 @@
         <v>27</v>
       </c>
       <c r="AS20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT20">
         <v>10.5</v>
@@ -5884,7 +5884,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW20">
         <v>38</v>
@@ -5911,7 +5911,7 @@
         <v>26</v>
       </c>
       <c r="BE20">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BF20">
         <v>9.4</v>
@@ -6000,19 +6000,19 @@
         <v>221</v>
       </c>
       <c r="F21">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H21">
         <v>6</v>
       </c>
       <c r="I21">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K21">
         <v>4.8</v>
@@ -6024,40 +6024,40 @@
         <v>1.04</v>
       </c>
       <c r="N21">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q21">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R21">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S21">
         <v>2.44</v>
       </c>
       <c r="T21">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V21">
         <v>1.19</v>
       </c>
       <c r="W21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X21">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z21">
         <v>55</v>
@@ -6078,7 +6078,7 @@
         <v>75</v>
       </c>
       <c r="AF21">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -6120,10 +6120,10 @@
         <v>44</v>
       </c>
       <c r="AT21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV21">
         <v>20</v>
@@ -6132,7 +6132,7 @@
         <v>32</v>
       </c>
       <c r="AX21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY21">
         <v>9.199999999999999</v>
@@ -6147,7 +6147,7 @@
         <v>14.5</v>
       </c>
       <c r="BC21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD21">
         <v>23</v>
@@ -6156,7 +6156,7 @@
         <v>34</v>
       </c>
       <c r="BF21">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG21">
         <v>42</v>
@@ -6210,7 +6210,7 @@
         <v>7.8</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY21">
         <v>7.8</v>
@@ -6245,10 +6245,10 @@
         <v>1.5</v>
       </c>
       <c r="G22">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H22">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I22">
         <v>6.8</v>
@@ -6266,7 +6266,7 @@
         <v>1.02</v>
       </c>
       <c r="N22">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O22">
         <v>1.13</v>
@@ -6293,7 +6293,7 @@
         <v>1.17</v>
       </c>
       <c r="W22">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="X22">
         <v>40</v>
@@ -6302,7 +6302,7 @@
         <v>38</v>
       </c>
       <c r="Z22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA22">
         <v>150</v>
@@ -6317,7 +6317,7 @@
         <v>26</v>
       </c>
       <c r="AE22">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF22">
         <v>13.5</v>
@@ -6326,10 +6326,10 @@
         <v>11</v>
       </c>
       <c r="AH22">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ22">
         <v>16.5</v>
@@ -6341,13 +6341,13 @@
         <v>24</v>
       </c>
       <c r="AM22">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN22">
         <v>4.9</v>
       </c>
       <c r="AO22">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP22">
         <v>27</v>
@@ -6359,7 +6359,7 @@
         <v>50</v>
       </c>
       <c r="AS22">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT22">
         <v>13</v>
@@ -6380,7 +6380,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA22">
         <v>44</v>
@@ -6407,10 +6407,10 @@
         <v>5.4</v>
       </c>
       <c r="BI22">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BJ22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK22">
         <v>5.2</v>
@@ -6419,7 +6419,7 @@
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22">
         <v>4.9</v>
@@ -6431,7 +6431,7 @@
         <v>9.6</v>
       </c>
       <c r="BQ22">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BR22">
         <v>18</v>
@@ -6449,7 +6449,7 @@
         <v>38</v>
       </c>
       <c r="BW22">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX22">
         <v>36</v>
@@ -6487,7 +6487,7 @@
         <v>1.93</v>
       </c>
       <c r="G23">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H23">
         <v>3.4</v>
@@ -6529,13 +6529,13 @@
         <v>1.43</v>
       </c>
       <c r="U23">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="V23">
         <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X23">
         <v>48</v>
@@ -6550,13 +6550,13 @@
         <v>100</v>
       </c>
       <c r="AB23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC23">
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE23">
         <v>40</v>
@@ -6583,7 +6583,7 @@
         <v>27</v>
       </c>
       <c r="AM23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN23">
         <v>7.2</v>
@@ -6592,16 +6592,16 @@
         <v>17.5</v>
       </c>
       <c r="AP23">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23">
         <v>21</v>
       </c>
       <c r="AR23">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS23">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT23">
         <v>13.5</v>
@@ -6613,22 +6613,22 @@
         <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX23">
         <v>13</v>
       </c>
       <c r="AY23">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ23">
         <v>11</v>
       </c>
       <c r="BA23">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB23">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BC23">
         <v>12</v>
@@ -6637,7 +6637,7 @@
         <v>16</v>
       </c>
       <c r="BE23">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF23">
         <v>5.1</v>
@@ -6649,7 +6649,7 @@
         <v>5.8</v>
       </c>
       <c r="BI23">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BJ23">
         <v>8.6</v>
@@ -6726,7 +6726,7 @@
         <v>224</v>
       </c>
       <c r="F24">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="G24">
         <v>3.1</v>
@@ -6774,7 +6774,7 @@
         <v>2.58</v>
       </c>
       <c r="V24">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W24">
         <v>1.47</v>
@@ -6980,7 +6980,7 @@
         <v>990</v>
       </c>
       <c r="J25">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K25">
         <v>950</v>
@@ -7016,10 +7016,10 @@
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7210,10 +7210,10 @@
         <v>226</v>
       </c>
       <c r="F26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G26">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H26">
         <v>3.15</v>
@@ -7225,10 +7225,10 @@
         <v>3.6</v>
       </c>
       <c r="K26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M26">
         <v>1.05</v>
@@ -7243,13 +7243,13 @@
         <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
         <v>1.49</v>
       </c>
       <c r="S26">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T26">
         <v>1.62</v>
@@ -7267,7 +7267,7 @@
         <v>22</v>
       </c>
       <c r="Y26">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z26">
         <v>26</v>
@@ -7282,7 +7282,7 @@
         <v>10</v>
       </c>
       <c r="AD26">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE26">
         <v>36</v>
@@ -7294,7 +7294,7 @@
         <v>13</v>
       </c>
       <c r="AH26">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI26">
         <v>38</v>
@@ -7315,7 +7315,7 @@
         <v>15.5</v>
       </c>
       <c r="AO26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP26">
         <v>15</v>
@@ -7327,19 +7327,19 @@
         <v>19</v>
       </c>
       <c r="AS26">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT26">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU26">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
         <v>11</v>
       </c>
       <c r="AW26">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AX26">
         <v>12</v>
@@ -7351,19 +7351,19 @@
         <v>12</v>
       </c>
       <c r="BA26">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB26">
         <v>21</v>
       </c>
       <c r="BC26">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD26">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE26">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
         <v>11.5</v>
@@ -7375,7 +7375,7 @@
         <v>4</v>
       </c>
       <c r="BI26">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ26">
         <v>8.800000000000001</v>
@@ -7464,7 +7464,7 @@
         <v>2.3</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K27">
         <v>4.5</v>
@@ -7482,10 +7482,10 @@
         <v>1.16</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R27">
         <v>1.73</v>
@@ -7703,10 +7703,10 @@
         <v>1.04</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K28">
         <v>950</v>
@@ -7745,7 +7745,7 @@
         <v>1.01</v>
       </c>
       <c r="W28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7936,7 +7936,7 @@
         <v>229</v>
       </c>
       <c r="F29">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G29">
         <v>4.6</v>
@@ -7945,13 +7945,13 @@
         <v>1.8</v>
       </c>
       <c r="I29">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J29">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K29">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L29">
         <v>1.23</v>
@@ -7960,13 +7960,13 @@
         <v>1.02</v>
       </c>
       <c r="N29">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O29">
         <v>1.18</v>
       </c>
       <c r="P29">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q29">
         <v>1.51</v>
@@ -7975,16 +7975,16 @@
         <v>1.64</v>
       </c>
       <c r="S29">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T29">
         <v>1.53</v>
       </c>
       <c r="U29">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V29">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W29">
         <v>1.27</v>
@@ -8098,7 +8098,7 @@
         <v>6.8</v>
       </c>
       <c r="BH29">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI29">
         <v>3.75</v>
@@ -8107,13 +8107,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK29">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN29">
         <v>8.800000000000001</v>
@@ -8122,34 +8122,34 @@
         <v>4.6</v>
       </c>
       <c r="BP29">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ29">
+        <v>7.4</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
         <v>7.6</v>
       </c>
-      <c r="BR29">
-        <v>1000</v>
-      </c>
-      <c r="BS29">
-        <v>7.8</v>
-      </c>
       <c r="BT29">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU29">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV29">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW29">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BX29">
         <v>21</v>
       </c>
       <c r="BY29">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ29">
         <v>0</v>
@@ -8220,7 +8220,7 @@
         <v>3.65</v>
       </c>
       <c r="T30">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U30">
         <v>1.89</v>
@@ -8268,7 +8268,7 @@
         <v>90</v>
       </c>
       <c r="AJ30">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK30">
         <v>20</v>
@@ -8295,7 +8295,7 @@
         <v>7.8</v>
       </c>
       <c r="AS30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT30">
         <v>6.6</v>
@@ -8337,7 +8337,7 @@
         <v>9.6</v>
       </c>
       <c r="BG30">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH30">
         <v>3.4</v>
@@ -8429,7 +8429,7 @@
         <v>3.1</v>
       </c>
       <c r="I31">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J31">
         <v>3.9</v>
@@ -8465,10 +8465,10 @@
         <v>1.53</v>
       </c>
       <c r="U31">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.73</v>
@@ -8486,7 +8486,7 @@
         <v>55</v>
       </c>
       <c r="AB31">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC31">
         <v>10.5</v>
@@ -8498,13 +8498,13 @@
         <v>34</v>
       </c>
       <c r="AF31">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG31">
         <v>13.5</v>
       </c>
       <c r="AH31">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI31">
         <v>38</v>
@@ -8525,7 +8525,7 @@
         <v>13</v>
       </c>
       <c r="AO31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP31">
         <v>19</v>
@@ -8537,19 +8537,19 @@
         <v>19</v>
       </c>
       <c r="AS31">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AT31">
         <v>11.5</v>
       </c>
       <c r="AU31">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV31">
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8561,10 +8561,10 @@
         <v>11.5</v>
       </c>
       <c r="BA31">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB31">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BC31">
         <v>16</v>
@@ -8573,7 +8573,7 @@
         <v>21</v>
       </c>
       <c r="BE31">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF31">
         <v>9.199999999999999</v>
@@ -8662,7 +8662,7 @@
         <v>232</v>
       </c>
       <c r="F32">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G32">
         <v>2.42</v>
@@ -8686,7 +8686,7 @@
         <v>1.12</v>
       </c>
       <c r="N32">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O32">
         <v>1.51</v>
@@ -8704,10 +8704,10 @@
         <v>5.1</v>
       </c>
       <c r="T32">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U32">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V32">
         <v>1.32</v>
@@ -8722,7 +8722,7 @@
         <v>11</v>
       </c>
       <c r="Z32">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AA32">
         <v>110</v>
@@ -8779,7 +8779,7 @@
         <v>6.2</v>
       </c>
       <c r="AS32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT32">
         <v>6.4</v>
@@ -8797,7 +8797,7 @@
         <v>11</v>
       </c>
       <c r="AY32">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ32">
         <v>19.5</v>
@@ -8809,22 +8809,22 @@
         <v>6.6</v>
       </c>
       <c r="BC32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD32">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE32">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG32">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH32">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI32">
         <v>2.26</v>
@@ -8833,13 +8833,13 @@
         <v>12</v>
       </c>
       <c r="BK32">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN32">
         <v>5</v>
@@ -8857,31 +8857,31 @@
         <v>1000</v>
       </c>
       <c r="BS32">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT32">
         <v>7.4</v>
       </c>
       <c r="BU32">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV32">
         <v>1000</v>
       </c>
       <c r="BW32">
+        <v>8.6</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX32">
-        <v>1000</v>
-      </c>
-      <c r="BY32">
-        <v>9.4</v>
-      </c>
-      <c r="BZ32">
-        <v>1000</v>
-      </c>
-      <c r="CA32">
-        <v>9</v>
       </c>
       <c r="CB32" t="s">
         <v>264</v>
@@ -8904,25 +8904,25 @@
         <v>233</v>
       </c>
       <c r="F33">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H33">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I33">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J33">
         <v>3.25</v>
       </c>
       <c r="K33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L33">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M33">
         <v>1.08</v>
@@ -8931,7 +8931,7 @@
         <v>3.3</v>
       </c>
       <c r="O33">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P33">
         <v>1.79</v>
@@ -8940,19 +8940,19 @@
         <v>2.08</v>
       </c>
       <c r="R33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S33">
         <v>3.85</v>
       </c>
       <c r="T33">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U33">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W33">
         <v>1.45</v>
@@ -8961,7 +8961,7 @@
         <v>13</v>
       </c>
       <c r="Y33">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z33">
         <v>18</v>
@@ -8988,7 +8988,7 @@
         <v>14</v>
       </c>
       <c r="AH33">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI33">
         <v>48</v>
@@ -9033,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="AW33">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX33">
         <v>17</v>
@@ -9042,7 +9042,7 @@
         <v>11</v>
       </c>
       <c r="AZ33">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA33">
         <v>36</v>
@@ -9057,10 +9057,10 @@
         <v>40</v>
       </c>
       <c r="BE33">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF33">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG33">
         <v>21</v>
@@ -9069,7 +9069,7 @@
         <v>3.3</v>
       </c>
       <c r="BI33">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ33">
         <v>10.5</v>
@@ -9152,7 +9152,7 @@
         <v>2.88</v>
       </c>
       <c r="H34">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I34">
         <v>2.88</v>
@@ -9161,7 +9161,7 @@
         <v>3.6</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9188,10 +9188,10 @@
         <v>2.74</v>
       </c>
       <c r="T34">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U34">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -9203,13 +9203,13 @@
         <v>23</v>
       </c>
       <c r="Y34">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z34">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA34">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB34">
         <v>16.5</v>
@@ -9251,7 +9251,7 @@
         <v>22</v>
       </c>
       <c r="AO34">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP34">
         <v>14</v>
@@ -9260,10 +9260,10 @@
         <v>10</v>
       </c>
       <c r="AR34">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9281,25 +9281,25 @@
         <v>14.5</v>
       </c>
       <c r="AY34">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34">
         <v>11</v>
       </c>
       <c r="BA34">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC34">
         <v>19.5</v>
       </c>
       <c r="BD34">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE34">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF34">
         <v>13.5</v>
@@ -9388,13 +9388,13 @@
         <v>235</v>
       </c>
       <c r="F35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G35">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H35">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="I35">
         <v>2.36</v>
@@ -9403,49 +9403,49 @@
         <v>3.6</v>
       </c>
       <c r="K35">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M35">
         <v>1.06</v>
       </c>
       <c r="N35">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P35">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q35">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S35">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T35">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V35">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W35">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X35">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y35">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z35">
         <v>16</v>
@@ -9454,13 +9454,13 @@
         <v>30</v>
       </c>
       <c r="AB35">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC35">
         <v>9</v>
       </c>
       <c r="AD35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE35">
         <v>26</v>
@@ -9472,7 +9472,7 @@
         <v>15.5</v>
       </c>
       <c r="AH35">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI35">
         <v>36</v>
@@ -9481,13 +9481,13 @@
         <v>65</v>
       </c>
       <c r="AK35">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL35">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM35">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN35">
         <v>38</v>
@@ -9496,70 +9496,70 @@
         <v>17</v>
       </c>
       <c r="AP35">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ35">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS35">
         <v>21</v>
       </c>
       <c r="AT35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU35">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV35">
         <v>8.6</v>
       </c>
       <c r="AW35">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX35">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY35">
         <v>11</v>
       </c>
       <c r="AZ35">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA35">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB35">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BC35">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD35">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE35">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF35">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH35">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI35">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ35">
         <v>9.6</v>
       </c>
       <c r="BK35">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL35">
         <v>1000</v>
@@ -9568,13 +9568,13 @@
         <v>9.4</v>
       </c>
       <c r="BN35">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO35">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP35">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BQ35">
         <v>7.4</v>
@@ -9583,25 +9583,25 @@
         <v>38</v>
       </c>
       <c r="BS35">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT35">
         <v>5.4</v>
       </c>
       <c r="BU35">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BV35">
         <v>16.5</v>
       </c>
       <c r="BW35">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX35">
         <v>29</v>
       </c>
       <c r="BY35">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>1.73</v>
       </c>
       <c r="G36">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H36">
         <v>4.9</v>
@@ -9642,7 +9642,7 @@
         <v>5.9</v>
       </c>
       <c r="J36">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K36">
         <v>4.2</v>
@@ -9660,10 +9660,10 @@
         <v>1.3</v>
       </c>
       <c r="P36">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R36">
         <v>1.35</v>
@@ -9681,7 +9681,7 @@
         <v>1.2</v>
       </c>
       <c r="W36">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X36">
         <v>18.5</v>
@@ -9699,7 +9699,7 @@
         <v>10.5</v>
       </c>
       <c r="AC36">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD36">
         <v>25</v>
@@ -9744,13 +9744,13 @@
         <v>13</v>
       </c>
       <c r="AR36">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS36">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AT36">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU36">
         <v>6.6</v>
@@ -9759,7 +9759,7 @@
         <v>15</v>
       </c>
       <c r="AW36">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX36">
         <v>8</v>
@@ -9771,7 +9771,7 @@
         <v>14.5</v>
       </c>
       <c r="BA36">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB36">
         <v>13.5</v>
@@ -9780,22 +9780,22 @@
         <v>13.5</v>
       </c>
       <c r="BD36">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE36">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF36">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG36">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH36">
         <v>3.6</v>
       </c>
       <c r="BI36">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ36">
         <v>10.5</v>
@@ -9872,52 +9872,52 @@
         <v>237</v>
       </c>
       <c r="F37">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H37">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I37">
         <v>2.88</v>
       </c>
       <c r="J37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K37">
         <v>3.75</v>
       </c>
       <c r="L37">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M37">
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
         <v>1.34</v>
       </c>
       <c r="P37">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q37">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>1.33</v>
       </c>
       <c r="S37">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T37">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U37">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="V37">
         <v>1.54</v>
@@ -9926,7 +9926,7 @@
         <v>1.47</v>
       </c>
       <c r="X37">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y37">
         <v>13</v>
@@ -9938,7 +9938,7 @@
         <v>48</v>
       </c>
       <c r="AB37">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC37">
         <v>9.4</v>
@@ -9980,31 +9980,31 @@
         <v>30</v>
       </c>
       <c r="AP37">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ37">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR37">
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT37">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU37">
         <v>5.9</v>
       </c>
       <c r="AV37">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AW37">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AX37">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY37">
         <v>9.6</v>
@@ -10013,25 +10013,25 @@
         <v>12.5</v>
       </c>
       <c r="BA37">
+        <v>4.2</v>
+      </c>
+      <c r="BB37">
+        <v>4.3</v>
+      </c>
+      <c r="BC37">
         <v>4.1</v>
       </c>
-      <c r="BB37">
+      <c r="BD37">
         <v>4.2</v>
       </c>
-      <c r="BC37">
-        <v>4</v>
-      </c>
-      <c r="BD37">
+      <c r="BE37">
+        <v>4.4</v>
+      </c>
+      <c r="BF37">
         <v>4.1</v>
       </c>
-      <c r="BE37">
-        <v>4.3</v>
-      </c>
-      <c r="BF37">
-        <v>21</v>
-      </c>
       <c r="BG37">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH37">
         <v>3.45</v>
@@ -10114,10 +10114,10 @@
         <v>238</v>
       </c>
       <c r="F38">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G38">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H38">
         <v>5.7</v>
@@ -10144,13 +10144,13 @@
         <v>1.25</v>
       </c>
       <c r="P38">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q38">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R38">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S38">
         <v>2.88</v>
@@ -10171,22 +10171,22 @@
         <v>21</v>
       </c>
       <c r="Y38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z38">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA38">
         <v>180</v>
       </c>
       <c r="AB38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE38">
         <v>80</v>
@@ -10198,7 +10198,7 @@
         <v>10.5</v>
       </c>
       <c r="AH38">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI38">
         <v>75</v>
@@ -10207,19 +10207,19 @@
         <v>16</v>
       </c>
       <c r="AK38">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL38">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM38">
         <v>110</v>
       </c>
       <c r="AN38">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO38">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP38">
         <v>15</v>
@@ -10228,10 +10228,10 @@
         <v>19.5</v>
       </c>
       <c r="AR38">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="AS38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT38">
         <v>7.8</v>
@@ -10243,10 +10243,10 @@
         <v>20</v>
       </c>
       <c r="AW38">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX38">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY38">
         <v>8.800000000000001</v>
@@ -10255,7 +10255,7 @@
         <v>17.5</v>
       </c>
       <c r="BA38">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BB38">
         <v>13.5</v>
@@ -10267,13 +10267,13 @@
         <v>26</v>
       </c>
       <c r="BE38">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF38">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG38">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10356,25 +10356,25 @@
         <v>239</v>
       </c>
       <c r="F39">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G39">
-        <v>600</v>
+        <v>5.8</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="I39">
-        <v>870</v>
+        <v>2.36</v>
       </c>
       <c r="J39">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="K39">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M39">
         <v>1.01</v>
@@ -10383,31 +10383,31 @@
         <v>1.19</v>
       </c>
       <c r="O39">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P39">
         <v>1.19</v>
       </c>
       <c r="Q39">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="R39">
         <v>1.07</v>
       </c>
       <c r="S39">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V39">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10518,64 +10518,64 @@
         <v>1.01</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI39">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK39">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BQ39">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS39">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW39">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY39">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BZ39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA39">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="CB39" t="s">
         <v>264</v>
@@ -10610,7 +10610,7 @@
         <v>3.95</v>
       </c>
       <c r="J40">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="K40">
         <v>3.25</v>
@@ -10622,7 +10622,7 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="O40">
         <v>1.52</v>
@@ -10631,22 +10631,22 @@
         <v>1.45</v>
       </c>
       <c r="Q40">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R40">
         <v>1.14</v>
       </c>
       <c r="S40">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T40">
         <v>1.11</v>
       </c>
       <c r="U40">
-        <v>1.69</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W40">
         <v>1.57</v>
@@ -10843,13 +10843,13 @@
         <v>3.45</v>
       </c>
       <c r="G41">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H41">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I41">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J41">
         <v>3.2</v>
@@ -10858,7 +10858,7 @@
         <v>3.55</v>
       </c>
       <c r="L41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M41">
         <v>1.07</v>
@@ -10870,7 +10870,7 @@
         <v>1.32</v>
       </c>
       <c r="P41">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q41">
         <v>1.95</v>
@@ -10879,7 +10879,7 @@
         <v>1.37</v>
       </c>
       <c r="S41">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T41">
         <v>1.7</v>
@@ -10888,10 +10888,10 @@
         <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W41">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X41">
         <v>16.5</v>
@@ -10903,7 +10903,7 @@
         <v>16.5</v>
       </c>
       <c r="AA41">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AB41">
         <v>14.5</v>
@@ -10939,10 +10939,10 @@
         <v>60</v>
       </c>
       <c r="AM41">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN41">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO41">
         <v>21</v>
@@ -10954,10 +10954,10 @@
         <v>9.4</v>
       </c>
       <c r="AR41">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS41">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AT41">
         <v>10</v>
@@ -10981,22 +10981,22 @@
         <v>11</v>
       </c>
       <c r="BA41">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB41">
+        <v>7.8</v>
+      </c>
+      <c r="BC41">
         <v>7.4</v>
       </c>
-      <c r="BC41">
-        <v>7</v>
-      </c>
       <c r="BD41">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BE41">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF41">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG41">
         <v>13.5</v>
@@ -11020,34 +11020,34 @@
         <v>9.6</v>
       </c>
       <c r="BN41">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO41">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP41">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ41">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR41">
         <v>38</v>
       </c>
       <c r="BS41">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT41">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU41">
         <v>4</v>
       </c>
       <c r="BV41">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW41">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX41">
         <v>32</v>
@@ -11091,10 +11091,10 @@
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J42">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K42">
         <v>4.7</v>
@@ -11130,10 +11130,10 @@
         <v>2.78</v>
       </c>
       <c r="V42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W42">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X42">
         <v>38</v>
@@ -11148,7 +11148,7 @@
         <v>55</v>
       </c>
       <c r="AB42">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC42">
         <v>11.5</v>
@@ -11160,7 +11160,7 @@
         <v>32</v>
       </c>
       <c r="AF42">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG42">
         <v>12.5</v>
@@ -11190,64 +11190,64 @@
         <v>20</v>
       </c>
       <c r="AP42">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ42">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AR42">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AS42">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AT42">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU42">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV42">
         <v>12.5</v>
       </c>
       <c r="AW42">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX42">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AY42">
         <v>10</v>
       </c>
       <c r="AZ42">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="BA42">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BB42">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC42">
         <v>14</v>
       </c>
       <c r="BD42">
-        <v>20</v>
+        <v>6.8</v>
       </c>
       <c r="BE42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF42">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG42">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH42">
         <v>5.2</v>
       </c>
       <c r="BI42">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BJ42">
         <v>8.6</v>
@@ -11324,22 +11324,22 @@
         <v>243</v>
       </c>
       <c r="F43">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="G43">
-        <v>990</v>
+        <v>4.9</v>
       </c>
       <c r="H43">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="I43">
-        <v>990</v>
+        <v>2.12</v>
       </c>
       <c r="J43">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="K43">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11348,22 +11348,22 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>1.26</v>
+        <v>2.54</v>
       </c>
       <c r="O43">
         <v>1.07</v>
       </c>
       <c r="P43">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q43">
         <v>1.07</v>
       </c>
       <c r="R43">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="T43">
         <v>1.11</v>
@@ -11372,10 +11372,10 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="W43">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11566,19 +11566,19 @@
         <v>244</v>
       </c>
       <c r="F44">
-        <v>1.09</v>
+        <v>2.2</v>
       </c>
       <c r="G44">
-        <v>990</v>
+        <v>3.9</v>
       </c>
       <c r="H44">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="I44">
-        <v>990</v>
+        <v>2.48</v>
       </c>
       <c r="J44">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K44">
         <v>950</v>
@@ -11590,22 +11590,22 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="O44">
         <v>1.04</v>
       </c>
       <c r="P44">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="R44">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="S44">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="T44">
         <v>1.11</v>
@@ -11614,10 +11614,10 @@
         <v>1.11</v>
       </c>
       <c r="V44">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W44">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -11808,7 +11808,7 @@
         <v>245</v>
       </c>
       <c r="F45">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G45">
         <v>1.97</v>
@@ -11820,10 +11820,10 @@
         <v>5.8</v>
       </c>
       <c r="J45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K45">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L45">
         <v>1.53</v>
@@ -11832,7 +11832,7 @@
         <v>1.15</v>
       </c>
       <c r="N45">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O45">
         <v>1.65</v>
@@ -11844,13 +11844,13 @@
         <v>2.94</v>
       </c>
       <c r="R45">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S45">
         <v>6.4</v>
       </c>
       <c r="T45">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U45">
         <v>1.59</v>
@@ -11877,7 +11877,7 @@
         <v>5.8</v>
       </c>
       <c r="AC45">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD45">
         <v>25</v>
@@ -11955,10 +11955,10 @@
         <v>19.5</v>
       </c>
       <c r="BC45">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD45">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE45">
         <v>95</v>
@@ -12292,13 +12292,13 @@
         <v>247</v>
       </c>
       <c r="F47">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G47">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I47">
         <v>5.8</v>
@@ -12331,7 +12331,7 @@
         <v>1.34</v>
       </c>
       <c r="S47">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T47">
         <v>1.85</v>
@@ -12343,7 +12343,7 @@
         <v>1.2</v>
       </c>
       <c r="W47">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X47">
         <v>17</v>
@@ -12373,7 +12373,7 @@
         <v>13</v>
       </c>
       <c r="AG47">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH47">
         <v>25</v>
@@ -12409,7 +12409,7 @@
         <v>32</v>
       </c>
       <c r="AS47">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT47">
         <v>7.2</v>
@@ -12421,7 +12421,7 @@
         <v>17</v>
       </c>
       <c r="AW47">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX47">
         <v>9.199999999999999</v>
@@ -12433,7 +12433,7 @@
         <v>17.5</v>
       </c>
       <c r="BA47">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB47">
         <v>15.5</v>
@@ -12445,13 +12445,13 @@
         <v>30</v>
       </c>
       <c r="BE47">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF47">
         <v>9.4</v>
       </c>
       <c r="BG47">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12561,7 +12561,7 @@
         <v>1.25</v>
       </c>
       <c r="O48">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P48">
         <v>1.25</v>
@@ -12573,7 +12573,7 @@
         <v>1.23</v>
       </c>
       <c r="S48">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="T48">
         <v>1.11</v>
@@ -12785,10 +12785,10 @@
         <v>1.04</v>
       </c>
       <c r="I49">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J49">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K49">
         <v>950</v>
@@ -12824,7 +12824,7 @@
         <v>1.11</v>
       </c>
       <c r="V49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W49">
         <v>1.01</v>
@@ -13018,22 +13018,22 @@
         <v>250</v>
       </c>
       <c r="F50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G50">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="H50">
-        <v>3.15</v>
+        <v>5.4</v>
       </c>
       <c r="I50">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J50">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K50">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13069,7 +13069,7 @@
         <v>1.1</v>
       </c>
       <c r="W50">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -13505,7 +13505,7 @@
         <v>2.18</v>
       </c>
       <c r="G52">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H52">
         <v>4.2</v>
@@ -13517,7 +13517,7 @@
         <v>3.05</v>
       </c>
       <c r="K52">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L52">
         <v>1.54</v>
@@ -13544,7 +13544,7 @@
         <v>6</v>
       </c>
       <c r="T52">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U52">
         <v>1.71</v>
@@ -13553,7 +13553,7 @@
         <v>1.29</v>
       </c>
       <c r="W52">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X52">
         <v>8</v>
@@ -13583,7 +13583,7 @@
         <v>12.5</v>
       </c>
       <c r="AG52">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH52">
         <v>30</v>
@@ -13616,10 +13616,10 @@
         <v>9.4</v>
       </c>
       <c r="AR52">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS52">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT52">
         <v>5.9</v>
@@ -13628,10 +13628,10 @@
         <v>6.4</v>
       </c>
       <c r="AV52">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW52">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX52">
         <v>10.5</v>
@@ -13640,13 +13640,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ52">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA52">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB52">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC52">
         <v>6.4</v>
@@ -13655,13 +13655,13 @@
         <v>7</v>
       </c>
       <c r="BE52">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF52">
         <v>6.4</v>
       </c>
       <c r="BG52">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH52">
         <v>2.6</v>
@@ -13744,10 +13744,10 @@
         <v>253</v>
       </c>
       <c r="F53">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G53">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H53">
         <v>5.5</v>
@@ -13771,7 +13771,7 @@
         <v>2.68</v>
       </c>
       <c r="O53">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P53">
         <v>1.56</v>
@@ -13810,7 +13810,7 @@
         <v>210</v>
       </c>
       <c r="AB53">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC53">
         <v>9.4</v>
@@ -13858,10 +13858,10 @@
         <v>12</v>
       </c>
       <c r="AR53">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS53">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT53">
         <v>5.5</v>
@@ -13870,10 +13870,10 @@
         <v>7</v>
       </c>
       <c r="AV53">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="AW53">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX53">
         <v>8.4</v>
@@ -13882,13 +13882,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ53">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA53">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB53">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BC53">
         <v>18</v>
@@ -13897,13 +13897,13 @@
         <v>38</v>
       </c>
       <c r="BE53">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF53">
-        <v>4.3</v>
+        <v>16</v>
       </c>
       <c r="BG53">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13986,19 +13986,19 @@
         <v>254</v>
       </c>
       <c r="F54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G54">
         <v>990</v>
       </c>
       <c r="H54">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I54">
         <v>990</v>
       </c>
       <c r="J54">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K54">
         <v>950</v>
@@ -14010,22 +14010,22 @@
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="P54">
         <v>1.25</v>
       </c>
       <c r="Q54">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="R54">
         <v>1.18</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T54">
         <v>1.11</v>
@@ -14037,7 +14037,7 @@
         <v>1.02</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -14228,61 +14228,61 @@
         <v>255</v>
       </c>
       <c r="F55">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H55">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I55">
         <v>6</v>
       </c>
       <c r="J55">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K55">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L55">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M55">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N55">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O55">
+        <v>1.32</v>
+      </c>
+      <c r="P55">
+        <v>1.9</v>
+      </c>
+      <c r="Q55">
+        <v>1.87</v>
+      </c>
+      <c r="R55">
         <v>1.34</v>
       </c>
-      <c r="P55">
-        <v>1.81</v>
-      </c>
-      <c r="Q55">
-        <v>1.98</v>
-      </c>
-      <c r="R55">
-        <v>1.31</v>
-      </c>
       <c r="S55">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T55">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="U55">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V55">
         <v>1.2</v>
       </c>
       <c r="W55">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X55">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y55">
         <v>19</v>
@@ -14291,7 +14291,7 @@
         <v>44</v>
       </c>
       <c r="AA55">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB55">
         <v>9.800000000000001</v>
@@ -14303,7 +14303,7 @@
         <v>23</v>
       </c>
       <c r="AE55">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF55">
         <v>13.5</v>
@@ -14312,118 +14312,118 @@
         <v>12.5</v>
       </c>
       <c r="AH55">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI55">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ55">
         <v>25</v>
       </c>
       <c r="AK55">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL55">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM55">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AN55">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO55">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP55">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="AQ55">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AR55">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS55">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT55">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AU55">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AV55">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AW55">
+        <v>4.8</v>
+      </c>
+      <c r="AX55">
+        <v>3.75</v>
+      </c>
+      <c r="AY55">
+        <v>3.65</v>
+      </c>
+      <c r="AZ55">
+        <v>4.2</v>
+      </c>
+      <c r="BA55">
+        <v>4.9</v>
+      </c>
+      <c r="BB55">
         <v>4.3</v>
       </c>
-      <c r="AX55">
-        <v>3.4</v>
-      </c>
-      <c r="AY55">
-        <v>3.35</v>
-      </c>
-      <c r="AZ55">
-        <v>3.9</v>
-      </c>
-      <c r="BA55">
-        <v>4.3</v>
-      </c>
-      <c r="BB55">
-        <v>3.9</v>
-      </c>
       <c r="BC55">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD55">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE55">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BF55">
+        <v>3.8</v>
+      </c>
+      <c r="BG55">
+        <v>4.9</v>
+      </c>
+      <c r="BH55">
         <v>3.6</v>
       </c>
-      <c r="BG55">
-        <v>4.4</v>
-      </c>
-      <c r="BH55">
-        <v>3.4</v>
-      </c>
       <c r="BI55">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="BJ55">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK55">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="BN55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO55">
         <v>3.2</v>
       </c>
       <c r="BP55">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ55">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BR55">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BS55">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="BT55">
         <v>8.4</v>
@@ -14432,22 +14432,22 @@
         <v>4.5</v>
       </c>
       <c r="BV55">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW55">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BX55">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY55">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BZ55">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="CA55">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB55" t="s">
         <v>264</v>
@@ -14485,7 +14485,7 @@
         <v>3.7</v>
       </c>
       <c r="K56">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L56">
         <v>1.33</v>
@@ -14503,7 +14503,7 @@
         <v>2.16</v>
       </c>
       <c r="Q56">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R56">
         <v>1.46</v>
@@ -14954,34 +14954,34 @@
         <v>258</v>
       </c>
       <c r="F58">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G58">
         <v>1.55</v>
       </c>
       <c r="H58">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I58">
         <v>9</v>
       </c>
       <c r="J58">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="K58">
         <v>4.9</v>
       </c>
       <c r="L58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M58">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N58">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O58">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P58">
         <v>2</v>
@@ -14990,190 +14990,190 @@
         <v>1.83</v>
       </c>
       <c r="R58">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S58">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T58">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U58">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V58">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W58">
         <v>2.8</v>
       </c>
       <c r="X58">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y58">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z58">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA58">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB58">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC58">
         <v>11</v>
       </c>
       <c r="AD58">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE58">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF58">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG58">
+        <v>11.5</v>
+      </c>
+      <c r="AH58">
+        <v>28</v>
+      </c>
+      <c r="AI58">
+        <v>1000</v>
+      </c>
+      <c r="AJ58">
+        <v>14.5</v>
+      </c>
+      <c r="AK58">
+        <v>18</v>
+      </c>
+      <c r="AL58">
+        <v>42</v>
+      </c>
+      <c r="AM58">
+        <v>1000</v>
+      </c>
+      <c r="AN58">
+        <v>8.4</v>
+      </c>
+      <c r="AO58">
+        <v>1000</v>
+      </c>
+      <c r="AP58">
+        <v>13.5</v>
+      </c>
+      <c r="AQ58">
+        <v>16.5</v>
+      </c>
+      <c r="AR58">
+        <v>29</v>
+      </c>
+      <c r="AS58">
+        <v>48</v>
+      </c>
+      <c r="AT58">
+        <v>7.2</v>
+      </c>
+      <c r="AU58">
+        <v>8.6</v>
+      </c>
+      <c r="AV58">
+        <v>19</v>
+      </c>
+      <c r="AW58">
+        <v>40</v>
+      </c>
+      <c r="AX58">
+        <v>7.4</v>
+      </c>
+      <c r="AY58">
+        <v>8.6</v>
+      </c>
+      <c r="AZ58">
+        <v>18</v>
+      </c>
+      <c r="BA58">
+        <v>40</v>
+      </c>
+      <c r="BB58">
         <v>10.5</v>
-      </c>
-      <c r="AG58">
-        <v>10.5</v>
-      </c>
-      <c r="AH58">
-        <v>26</v>
-      </c>
-      <c r="AI58">
-        <v>130</v>
-      </c>
-      <c r="AJ58">
-        <v>13.5</v>
-      </c>
-      <c r="AK58">
-        <v>18.5</v>
-      </c>
-      <c r="AL58">
-        <v>40</v>
-      </c>
-      <c r="AM58">
-        <v>170</v>
-      </c>
-      <c r="AN58">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO58">
-        <v>200</v>
-      </c>
-      <c r="AP58">
-        <v>13</v>
-      </c>
-      <c r="AQ58">
-        <v>19</v>
-      </c>
-      <c r="AR58">
-        <v>7.2</v>
-      </c>
-      <c r="AS58">
-        <v>7.8</v>
-      </c>
-      <c r="AT58">
-        <v>6.4</v>
-      </c>
-      <c r="AU58">
-        <v>8</v>
-      </c>
-      <c r="AV58">
-        <v>22</v>
-      </c>
-      <c r="AW58">
-        <v>7.6</v>
-      </c>
-      <c r="AX58">
-        <v>6.8</v>
-      </c>
-      <c r="AY58">
-        <v>7.8</v>
-      </c>
-      <c r="AZ58">
-        <v>18.5</v>
-      </c>
-      <c r="BA58">
-        <v>7.6</v>
-      </c>
-      <c r="BB58">
-        <v>10</v>
       </c>
       <c r="BC58">
         <v>12.5</v>
       </c>
       <c r="BD58">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BE58">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BF58">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG58">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BH58">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BI58">
         <v>3</v>
       </c>
       <c r="BJ58">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK58">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="BN58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BO58">
         <v>3.2</v>
       </c>
       <c r="BP58">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BQ58">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR58">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS58">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT58">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU58">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV58">
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BX58">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY58">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="BZ58">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CA58">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="CB58" t="s">
         <v>264</v>
@@ -15199,7 +15199,7 @@
         <v>1.04</v>
       </c>
       <c r="G59">
-        <v>1.94</v>
+        <v>600</v>
       </c>
       <c r="H59">
         <v>1.04</v>
@@ -15208,7 +15208,7 @@
         <v>990</v>
       </c>
       <c r="J59">
-        <v>2.1</v>
+        <v>1.05</v>
       </c>
       <c r="K59">
         <v>950</v>
@@ -15220,22 +15220,22 @@
         <v>1.01</v>
       </c>
       <c r="N59">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="O59">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="P59">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="Q59">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="R59">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="S59">
-        <v>2.02</v>
+        <v>1.15</v>
       </c>
       <c r="T59">
         <v>1.11</v>
@@ -15247,7 +15247,7 @@
         <v>1.01</v>
       </c>
       <c r="W59">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
         <v>1000</v>
@@ -15438,13 +15438,13 @@
         <v>260</v>
       </c>
       <c r="F60">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G60">
         <v>990</v>
       </c>
       <c r="H60">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I60">
         <v>990</v>
@@ -15462,13 +15462,13 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O60">
         <v>1.02</v>
       </c>
       <c r="P60">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q60">
         <v>1.01</v>
@@ -15477,7 +15477,7 @@
         <v>1.18</v>
       </c>
       <c r="S60">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T60">
         <v>1.11</v>
@@ -15701,7 +15701,7 @@
         <v>1.01</v>
       </c>
       <c r="M61">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N61">
         <v>2.34</v>
@@ -15716,7 +15716,7 @@
         <v>2.44</v>
       </c>
       <c r="R61">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S61">
         <v>2.96</v>
@@ -15842,64 +15842,64 @@
         <v>1.01</v>
       </c>
       <c r="BH61">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="BI61">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BJ61">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK61">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL61">
         <v>1000</v>
       </c>
       <c r="BM61">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN61">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO61">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BP61">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ61">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BR61">
         <v>1000</v>
       </c>
       <c r="BS61">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT61">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU61">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV61">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW61">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BX61">
         <v>1000</v>
       </c>
       <c r="BY61">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BZ61">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="CB61" t="s">
         <v>264</v>
@@ -15940,16 +15940,16 @@
         <v>4</v>
       </c>
       <c r="L62">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M62">
         <v>1.1</v>
       </c>
       <c r="N62">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O62">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P62">
         <v>1.68</v>
@@ -15964,7 +15964,7 @@
         <v>4.4</v>
       </c>
       <c r="T62">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U62">
         <v>1.73</v>
@@ -16015,7 +16015,7 @@
         <v>23</v>
       </c>
       <c r="AK62">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL62">
         <v>60</v>
@@ -16024,7 +16024,7 @@
         <v>230</v>
       </c>
       <c r="AN62">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AO62">
         <v>250</v>
@@ -16036,10 +16036,10 @@
         <v>15</v>
       </c>
       <c r="AR62">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS62">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT62">
         <v>5.8</v>
@@ -16051,7 +16051,7 @@
         <v>19</v>
       </c>
       <c r="AW62">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX62">
         <v>7.8</v>
@@ -16063,7 +16063,7 @@
         <v>20</v>
       </c>
       <c r="BA62">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB62">
         <v>14.5</v>
@@ -16087,7 +16087,7 @@
         <v>3.05</v>
       </c>
       <c r="BI62">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ62">
         <v>12</v>
@@ -16099,7 +16099,7 @@
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN62">
         <v>3.95</v>
@@ -16111,16 +16111,16 @@
         <v>12</v>
       </c>
       <c r="BQ62">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BR62">
         <v>1000</v>
       </c>
       <c r="BS62">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT62">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU62">
         <v>8</v>
@@ -16129,19 +16129,19 @@
         <v>1000</v>
       </c>
       <c r="BW62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX62">
         <v>1000</v>
       </c>
       <c r="BY62">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ62">
         <v>1000</v>
       </c>
       <c r="CA62">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB62" t="s">
         <v>264</v>
@@ -16176,7 +16176,7 @@
         <v>990</v>
       </c>
       <c r="J63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K63">
         <v>950</v>
@@ -16212,10 +16212,10 @@
         <v>1.11</v>
       </c>
       <c r="V63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-24.xlsx
@@ -808,7 +808,7 @@
     <t>Escobar FC</t>
   </si>
   <si>
-    <t>2026-07-23 16:51:23</t>
+    <t>2026-07-23 19:04:18</t>
   </si>
 </sst>
 </file>
@@ -1402,22 +1402,22 @@
         <v>202</v>
       </c>
       <c r="F2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>5.3</v>
       </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.47</v>
@@ -1426,58 +1426,58 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O2">
         <v>1.4</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
         <v>2.22</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
         <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
         <v>1.23</v>
       </c>
       <c r="W2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X2">
         <v>12</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF2">
         <v>10.5</v>
@@ -1486,100 +1486,100 @@
         <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AL2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM2">
         <v>170</v>
       </c>
       <c r="AN2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP2">
         <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS2">
         <v>90</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AX2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC2">
         <v>19.5</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE2">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="BF2">
         <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH2">
         <v>3.15</v>
       </c>
       <c r="BI2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN2">
         <v>4.3</v>
@@ -1597,22 +1597,22 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU2">
         <v>5.7</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
         <v>13.5</v>
@@ -1653,13 +1653,13 @@
         <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L3">
         <v>1.61</v>
@@ -1668,16 +1668,16 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P3">
         <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="R3">
         <v>1.18</v>
@@ -1686,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
         <v>1.8</v>
@@ -1710,13 +1710,13 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3">
         <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>60</v>
@@ -1734,7 +1734,7 @@
         <v>85</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK3">
         <v>42</v>
@@ -1743,7 +1743,7 @@
         <v>75</v>
       </c>
       <c r="AM3">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN3">
         <v>50</v>
@@ -1785,10 +1785,10 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC3">
         <v>30</v>
@@ -1797,19 +1797,19 @@
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG3">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BH3">
         <v>2.68</v>
       </c>
       <c r="BI3">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1821,13 +1821,13 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BN3">
         <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>25</v>
@@ -1845,7 +1845,7 @@
         <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
         <v>36</v>
@@ -1886,16 +1886,16 @@
         <v>204</v>
       </c>
       <c r="F4">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G4">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
         <v>3.25</v>
@@ -1904,7 +1904,7 @@
         <v>3.35</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M4">
         <v>1.14</v>
@@ -1916,7 +1916,7 @@
         <v>1.61</v>
       </c>
       <c r="P4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1928,34 +1928,34 @@
         <v>6.2</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4">
         <v>12</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA4">
         <v>160</v>
       </c>
       <c r="AB4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>24</v>
@@ -1967,16 +1967,16 @@
         <v>10</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK4">
         <v>30</v>
@@ -1985,52 +1985,52 @@
         <v>70</v>
       </c>
       <c r="AM4">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP4">
         <v>7.4</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS4">
         <v>42</v>
       </c>
       <c r="AT4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4">
         <v>85</v>
       </c>
       <c r="AX4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
         <v>26</v>
       </c>
       <c r="BA4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4">
         <v>27</v>
@@ -2063,13 +2063,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP4">
         <v>16.5</v>
@@ -2131,16 +2131,16 @@
         <v>1.61</v>
       </c>
       <c r="G5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.2</v>
@@ -2155,13 +2155,13 @@
         <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R5">
         <v>1.28</v>
@@ -2170,13 +2170,13 @@
         <v>4.3</v>
       </c>
       <c r="T5">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.72</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
         <v>2.52</v>
@@ -2191,19 +2191,19 @@
         <v>70</v>
       </c>
       <c r="AA5">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF5">
         <v>8.800000000000001</v>
@@ -2212,10 +2212,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
@@ -2224,10 +2224,10 @@
         <v>21</v>
       </c>
       <c r="AL5">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN5">
         <v>13</v>
@@ -2239,25 +2239,25 @@
         <v>10</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="AS5">
+        <v>10.5</v>
+      </c>
+      <c r="AT5">
+        <v>5.9</v>
+      </c>
+      <c r="AU5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV5">
+        <v>8</v>
+      </c>
+      <c r="AW5">
         <v>10</v>
-      </c>
-      <c r="AT5">
-        <v>5.8</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>20</v>
-      </c>
-      <c r="AW5">
-        <v>70</v>
       </c>
       <c r="AX5">
         <v>7.6</v>
@@ -2266,34 +2266,34 @@
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BA5">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="BB5">
         <v>12</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BD5">
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
         <v>10.5</v>
       </c>
       <c r="BG5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5">
         <v>12.5</v>
@@ -2308,7 +2308,7 @@
         <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO5">
         <v>3.4</v>
@@ -2323,7 +2323,7 @@
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
         <v>10.5</v>
@@ -2335,10 +2335,10 @@
         <v>95</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY5">
         <v>11.5</v>
@@ -2347,7 +2347,7 @@
         <v>27</v>
       </c>
       <c r="CA5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB5" t="s">
         <v>264</v>
@@ -2385,37 +2385,37 @@
         <v>3.4</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M6">
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
         <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="U6">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V6">
         <v>1.7</v>
@@ -2445,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="AE6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF6">
         <v>29</v>
@@ -2478,7 +2478,7 @@
         <v>28</v>
       </c>
       <c r="AP6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
         <v>6.6</v>
@@ -2523,7 +2523,7 @@
         <v>5.4</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF6">
         <v>5.3</v>
@@ -2532,22 +2532,22 @@
         <v>16.5</v>
       </c>
       <c r="BH6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI6">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN6">
         <v>7</v>
@@ -2559,13 +2559,13 @@
         <v>32</v>
       </c>
       <c r="BQ6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR6">
         <v>46</v>
       </c>
       <c r="BS6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT6">
         <v>5.3</v>
@@ -2574,16 +2574,16 @@
         <v>3.9</v>
       </c>
       <c r="BV6">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6">
         <v>36</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         <v>1.57</v>
       </c>
       <c r="G7">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H7">
         <v>5.8</v>
@@ -2627,49 +2627,49 @@
         <v>4.3</v>
       </c>
       <c r="K7">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
         <v>4.9</v>
       </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.05</v>
-      </c>
-      <c r="N7">
-        <v>4.6</v>
-      </c>
       <c r="O7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="Q7">
         <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S7">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="X7">
         <v>23</v>
       </c>
       <c r="Y7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Z7">
         <v>60</v>
@@ -2678,10 +2678,10 @@
         <v>180</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>27</v>
@@ -2696,10 +2696,10 @@
         <v>12</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
         <v>17.5</v>
@@ -2714,10 +2714,10 @@
         <v>110</v>
       </c>
       <c r="AN7">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO7">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP7">
         <v>15</v>
@@ -2729,7 +2729,7 @@
         <v>38</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT7">
         <v>7.8</v>
@@ -2741,7 +2741,7 @@
         <v>20</v>
       </c>
       <c r="AW7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX7">
         <v>8.199999999999999</v>
@@ -2753,7 +2753,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB7">
         <v>12</v>
@@ -2762,16 +2762,16 @@
         <v>12.5</v>
       </c>
       <c r="BD7">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BE7">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2854,22 +2854,22 @@
         <v>208</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G8">
         <v>2.32</v>
       </c>
       <c r="H8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
         <v>3.95</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8">
         <v>1.43</v>
@@ -2878,7 +2878,7 @@
         <v>1.08</v>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O8">
         <v>1.37</v>
@@ -2908,16 +2908,16 @@
         <v>1.76</v>
       </c>
       <c r="X8">
+        <v>13.5</v>
+      </c>
+      <c r="Y8">
         <v>14</v>
       </c>
-      <c r="Y8">
-        <v>15</v>
-      </c>
       <c r="Z8">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA8">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB8">
         <v>9.199999999999999</v>
@@ -2926,13 +2926,13 @@
         <v>8</v>
       </c>
       <c r="AD8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG8">
         <v>13</v>
@@ -2941,22 +2941,22 @@
         <v>22</v>
       </c>
       <c r="AI8">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AJ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>150</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO8">
         <v>65</v>
@@ -2965,13 +2965,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR8">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="AS8">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT8">
         <v>8</v>
@@ -2983,7 +2983,7 @@
         <v>13</v>
       </c>
       <c r="AW8">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX8">
         <v>11.5</v>
@@ -2995,7 +2995,7 @@
         <v>16</v>
       </c>
       <c r="BA8">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB8">
         <v>24</v>
@@ -3004,16 +3004,16 @@
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE8">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF8">
         <v>15</v>
       </c>
       <c r="BG8">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
@@ -3031,7 +3031,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8">
         <v>5.1</v>
@@ -3040,7 +3040,7 @@
         <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ8">
         <v>6.4</v>
@@ -3067,13 +3067,13 @@
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8">
         <v>32</v>
       </c>
       <c r="CA8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB8" t="s">
         <v>264</v>
@@ -3096,19 +3096,19 @@
         <v>209</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="G9">
         <v>2.02</v>
       </c>
       <c r="H9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I9">
         <v>4.6</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -3144,7 +3144,7 @@
         <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W9">
         <v>1.98</v>
@@ -3153,7 +3153,7 @@
         <v>24</v>
       </c>
       <c r="Y9">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Z9">
         <v>36</v>
@@ -3168,10 +3168,10 @@
         <v>11.5</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9">
         <v>16</v>
@@ -3201,7 +3201,7 @@
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP9">
         <v>14.5</v>
@@ -3210,13 +3210,13 @@
         <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AS9">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
         <v>7</v>
@@ -3225,7 +3225,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>12</v>
       </c>
       <c r="BA9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB9">
         <v>16</v>
@@ -3249,13 +3249,13 @@
         <v>21</v>
       </c>
       <c r="BE9">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF9">
         <v>7.8</v>
       </c>
       <c r="BG9">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH9">
         <v>4.1</v>
@@ -3279,13 +3279,13 @@
         <v>5</v>
       </c>
       <c r="BO9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
         <v>25</v>
@@ -3297,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="BU9">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BV9">
         <v>34</v>
@@ -3338,22 +3338,22 @@
         <v>210</v>
       </c>
       <c r="F10">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="G10">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="H10">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="I10">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.34</v>
@@ -3362,22 +3362,22 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q10">
         <v>2.04</v>
       </c>
       <c r="R10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T10">
         <v>1.72</v>
@@ -3386,148 +3386,148 @@
         <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="X10">
         <v>17.5</v>
       </c>
       <c r="Y10">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA10">
         <v>55</v>
       </c>
       <c r="AB10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC10">
         <v>9.6</v>
       </c>
       <c r="AD10">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
         <v>40</v>
       </c>
       <c r="AF10">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
         <v>55</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK10">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AL10">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AO10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AP10">
         <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS10">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
         <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX10">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA10">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BB10">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC10">
-        <v>5.1</v>
+        <v>18.5</v>
       </c>
       <c r="BD10">
-        <v>5.4</v>
+        <v>27</v>
       </c>
       <c r="BE10">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF10">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BG10">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BH10">
         <v>3.5</v>
       </c>
       <c r="BI10">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BO10">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP10">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3536,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="BT10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BW10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>4.1</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
         <v>1.04</v>
@@ -3613,22 +3613,22 @@
         <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T11">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="U11">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W11">
         <v>1.4</v>
@@ -3640,13 +3640,13 @@
         <v>13.5</v>
       </c>
       <c r="Z11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -3673,7 +3673,7 @@
         <v>65</v>
       </c>
       <c r="AK11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11">
         <v>40</v>
@@ -3688,10 +3688,10 @@
         <v>12</v>
       </c>
       <c r="AP11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR11">
         <v>14</v>
@@ -3742,13 +3742,13 @@
         <v>10.5</v>
       </c>
       <c r="BH11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK11">
         <v>6.8</v>
@@ -3757,7 +3757,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
         <v>7.2</v>
@@ -3775,7 +3775,7 @@
         <v>34</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT11">
         <v>5.5</v>
@@ -3790,10 +3790,10 @@
         <v>6.2</v>
       </c>
       <c r="BX11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3828,10 +3828,10 @@
         <v>1.73</v>
       </c>
       <c r="H12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J12">
         <v>4.5</v>
@@ -3852,16 +3852,16 @@
         <v>1.22</v>
       </c>
       <c r="P12">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q12">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S12">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T12">
         <v>1.71</v>
@@ -3873,7 +3873,7 @@
         <v>1.25</v>
       </c>
       <c r="W12">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X12">
         <v>26</v>
@@ -3978,7 +3978,7 @@
         <v>5.1</v>
       </c>
       <c r="BF12">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BG12">
         <v>4.9</v>
@@ -4064,13 +4064,13 @@
         <v>213</v>
       </c>
       <c r="F13">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G13">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H13">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I13">
         <v>2.72</v>
@@ -4079,7 +4079,7 @@
         <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4163,7 +4163,7 @@
         <v>44</v>
       </c>
       <c r="AM13">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN13">
         <v>25</v>
@@ -4172,16 +4172,16 @@
         <v>23</v>
       </c>
       <c r="AP13">
-        <v>3.95</v>
+        <v>8.4</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AS13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT13">
         <v>12</v>
@@ -4193,10 +4193,10 @@
         <v>11</v>
       </c>
       <c r="AW13">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="AX13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY13">
         <v>11</v>
@@ -4205,19 +4205,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BB13">
         <v>4.4</v>
       </c>
       <c r="BC13">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="BD13">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="BE13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF13">
         <v>15</v>
@@ -4306,19 +4306,19 @@
         <v>214</v>
       </c>
       <c r="F14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G14">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H14">
         <v>5.1</v>
       </c>
       <c r="I14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K14">
         <v>4.6</v>
@@ -4327,7 +4327,7 @@
         <v>1.3</v>
       </c>
       <c r="M14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14">
         <v>1.1</v>
@@ -4345,7 +4345,7 @@
         <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="T14">
         <v>1.81</v>
@@ -4357,7 +4357,7 @@
         <v>1.18</v>
       </c>
       <c r="W14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X14">
         <v>18</v>
@@ -4381,7 +4381,7 @@
         <v>24</v>
       </c>
       <c r="AE14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF14">
         <v>11</v>
@@ -4393,7 +4393,7 @@
         <v>22</v>
       </c>
       <c r="AI14">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ14">
         <v>17.5</v>
@@ -4405,46 +4405,46 @@
         <v>36</v>
       </c>
       <c r="AM14">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN14">
         <v>9.800000000000001</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AP14">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR14">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT14">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU14">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AV14">
+        <v>6.6</v>
+      </c>
+      <c r="AW14">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX14">
+        <v>5.6</v>
+      </c>
+      <c r="AY14">
+        <v>5.8</v>
+      </c>
+      <c r="AZ14">
         <v>6.4</v>
-      </c>
-      <c r="AW14">
-        <v>8</v>
-      </c>
-      <c r="AX14">
-        <v>4.9</v>
-      </c>
-      <c r="AY14">
-        <v>4.8</v>
-      </c>
-      <c r="AZ14">
-        <v>6.2</v>
       </c>
       <c r="BA14">
         <v>8</v>
@@ -4456,13 +4456,13 @@
         <v>6</v>
       </c>
       <c r="BD14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF14">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG14">
         <v>8.199999999999999</v>
@@ -4471,7 +4471,7 @@
         <v>3.8</v>
       </c>
       <c r="BI14">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
@@ -4554,13 +4554,13 @@
         <v>1.61</v>
       </c>
       <c r="H15">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I15">
         <v>7.8</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
         <v>5.2</v>
@@ -4578,16 +4578,16 @@
         <v>1.21</v>
       </c>
       <c r="P15">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Q15">
         <v>1.67</v>
       </c>
       <c r="R15">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T15">
         <v>1.81</v>
@@ -4596,7 +4596,7 @@
         <v>2</v>
       </c>
       <c r="V15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15">
         <v>2.62</v>
@@ -4647,7 +4647,7 @@
         <v>34</v>
       </c>
       <c r="AM15">
-        <v>130</v>
+        <v>380</v>
       </c>
       <c r="AN15">
         <v>7.4</v>
@@ -4668,10 +4668,10 @@
         <v>8.4</v>
       </c>
       <c r="AT15">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU15">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV15">
         <v>6.6</v>
@@ -4680,10 +4680,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX15">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AY15">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AZ15">
         <v>6.2</v>
@@ -4731,7 +4731,7 @@
         <v>5.8</v>
       </c>
       <c r="BO15">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BP15">
         <v>13.5</v>
@@ -4790,22 +4790,22 @@
         <v>216</v>
       </c>
       <c r="F16">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>90</v>
       </c>
       <c r="H16">
-        <v>1.05</v>
+        <v>2.66</v>
       </c>
       <c r="I16">
         <v>990</v>
       </c>
       <c r="J16">
-        <v>1.08</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>80</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4814,19 +4814,19 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="O16">
         <v>1.25</v>
       </c>
       <c r="P16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Q16">
         <v>1.25</v>
       </c>
       <c r="R16">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S16">
         <v>1.25</v>
@@ -4838,64 +4838,64 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA16">
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP16">
         <v>1.03</v>
@@ -4910,10 +4910,10 @@
         <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV16">
         <v>1.03</v>
@@ -4925,7 +4925,7 @@
         <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ16">
         <v>1.03</v>
@@ -4946,10 +4946,10 @@
         <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5131,7 +5131,7 @@
         <v>34</v>
       </c>
       <c r="AM17">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN17">
         <v>16</v>
@@ -5143,7 +5143,7 @@
         <v>4.4</v>
       </c>
       <c r="AQ17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR17">
         <v>4.7</v>
@@ -5170,10 +5170,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB17">
         <v>4.7</v>
@@ -5531,7 +5531,7 @@
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19">
         <v>1.23</v>
@@ -5555,7 +5555,7 @@
         <v>1.51</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T19">
         <v>1.62</v>
@@ -5585,7 +5585,7 @@
         <v>14.5</v>
       </c>
       <c r="AC19">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD19">
         <v>15</v>
@@ -5615,7 +5615,7 @@
         <v>36</v>
       </c>
       <c r="AM19">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN19">
         <v>14</v>
@@ -5633,7 +5633,7 @@
         <v>21</v>
       </c>
       <c r="AS19">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AT19">
         <v>9.800000000000001</v>
@@ -5645,7 +5645,7 @@
         <v>12.5</v>
       </c>
       <c r="AW19">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX19">
         <v>12.5</v>
@@ -5657,7 +5657,7 @@
         <v>12</v>
       </c>
       <c r="BA19">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB19">
         <v>21</v>
@@ -5666,10 +5666,10 @@
         <v>16.5</v>
       </c>
       <c r="BD19">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE19">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF19">
         <v>10</v>
@@ -5681,22 +5681,22 @@
         <v>1000</v>
       </c>
       <c r="BI19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BJ19">
         <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="BN19">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO19">
         <v>3.95</v>
@@ -5705,13 +5705,13 @@
         <v>21</v>
       </c>
       <c r="BQ19">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BR19">
         <v>34</v>
       </c>
       <c r="BS19">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="BT19">
         <v>9.199999999999999</v>
@@ -5723,19 +5723,19 @@
         <v>34</v>
       </c>
       <c r="BW19">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="BX19">
         <v>44</v>
       </c>
       <c r="BY19">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="BZ19">
         <v>26</v>
       </c>
       <c r="CA19">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CB19" t="s">
         <v>264</v>
@@ -5758,22 +5758,22 @@
         <v>220</v>
       </c>
       <c r="F20">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H20">
         <v>4</v>
       </c>
       <c r="I20">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J20">
         <v>3.95</v>
       </c>
       <c r="K20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <v>1.27</v>
@@ -5788,7 +5788,7 @@
         <v>1.23</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q20">
         <v>1.7</v>
@@ -5803,13 +5803,13 @@
         <v>1.66</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V20">
         <v>1.31</v>
       </c>
       <c r="W20">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X20">
         <v>22</v>
@@ -5821,13 +5821,13 @@
         <v>32</v>
       </c>
       <c r="AA20">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB20">
         <v>12</v>
       </c>
       <c r="AC20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD20">
         <v>17</v>
@@ -5881,7 +5881,7 @@
         <v>10.5</v>
       </c>
       <c r="AU20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV20">
         <v>15</v>
@@ -5893,10 +5893,10 @@
         <v>12</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA20">
         <v>40</v>
@@ -6000,28 +6000,28 @@
         <v>221</v>
       </c>
       <c r="F21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G21">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H21">
+        <v>5.8</v>
+      </c>
+      <c r="I21">
         <v>6</v>
-      </c>
-      <c r="I21">
-        <v>6.2</v>
       </c>
       <c r="J21">
         <v>4.7</v>
       </c>
       <c r="K21">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L21">
         <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
         <v>6</v>
@@ -6030,7 +6030,7 @@
         <v>1.19</v>
       </c>
       <c r="P21">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q21">
         <v>1.57</v>
@@ -6039,22 +6039,22 @@
         <v>1.67</v>
       </c>
       <c r="S21">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T21">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U21">
         <v>2.4</v>
       </c>
       <c r="V21">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X21">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y21">
         <v>29</v>
@@ -6063,10 +6063,10 @@
         <v>55</v>
       </c>
       <c r="AA21">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC21">
         <v>11</v>
@@ -6075,13 +6075,13 @@
         <v>23</v>
       </c>
       <c r="AE21">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF21">
         <v>12</v>
       </c>
       <c r="AG21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH21">
         <v>18.5</v>
@@ -6090,31 +6090,31 @@
         <v>65</v>
       </c>
       <c r="AJ21">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AK21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL21">
         <v>27</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN21">
         <v>6.4</v>
       </c>
       <c r="AO21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP21">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ21">
         <v>25</v>
       </c>
       <c r="AR21">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS21">
         <v>44</v>
@@ -6129,7 +6129,7 @@
         <v>20</v>
       </c>
       <c r="AW21">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AX21">
         <v>10.5</v>
@@ -6138,7 +6138,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA21">
         <v>50</v>
@@ -6156,7 +6156,7 @@
         <v>34</v>
       </c>
       <c r="BF21">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG21">
         <v>42</v>
@@ -6242,22 +6242,22 @@
         <v>222</v>
       </c>
       <c r="F22">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G22">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H22">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I22">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L22">
         <v>1.2</v>
@@ -6272,49 +6272,49 @@
         <v>1.13</v>
       </c>
       <c r="P22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R22">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="S22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T22">
         <v>1.56</v>
       </c>
       <c r="U22">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V22">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X22">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z22">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AA22">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE22">
         <v>65</v>
@@ -6332,10 +6332,10 @@
         <v>55</v>
       </c>
       <c r="AJ22">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK22">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL22">
         <v>24</v>
@@ -6344,22 +6344,22 @@
         <v>70</v>
       </c>
       <c r="AN22">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AO22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP22">
         <v>27</v>
       </c>
       <c r="AQ22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AR22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS22">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AT22">
         <v>13</v>
@@ -6380,10 +6380,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ22">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB22">
         <v>14</v>
@@ -6401,46 +6401,46 @@
         <v>4.3</v>
       </c>
       <c r="BG22">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BH22">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BI22">
         <v>4.6</v>
       </c>
       <c r="BJ22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
+        <v>10.5</v>
+      </c>
+      <c r="BN22">
+        <v>5</v>
+      </c>
+      <c r="BO22">
+        <v>3.9</v>
+      </c>
+      <c r="BP22">
         <v>9.800000000000001</v>
       </c>
-      <c r="BN22">
-        <v>4.9</v>
-      </c>
-      <c r="BO22">
-        <v>3.85</v>
-      </c>
-      <c r="BP22">
-        <v>9.6</v>
-      </c>
       <c r="BQ22">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR22">
         <v>18</v>
       </c>
       <c r="BS22">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT22">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU22">
         <v>5.5</v>
@@ -6449,13 +6449,13 @@
         <v>38</v>
       </c>
       <c r="BW22">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX22">
         <v>36</v>
       </c>
       <c r="BY22">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ22">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>1.93</v>
       </c>
       <c r="G23">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H23">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I23">
         <v>3.7</v>
@@ -6499,16 +6499,16 @@
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M23">
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O23">
         <v>1.13</v>
@@ -6517,28 +6517,28 @@
         <v>3.15</v>
       </c>
       <c r="Q23">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R23">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="S23">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="T23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U23">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V23">
         <v>1.37</v>
       </c>
       <c r="W23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X23">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Y23">
         <v>28</v>
@@ -6556,7 +6556,7 @@
         <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE23">
         <v>40</v>
@@ -6565,13 +6565,13 @@
         <v>22</v>
       </c>
       <c r="AG23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH23">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI23">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ23">
         <v>28</v>
@@ -6583,13 +6583,13 @@
         <v>27</v>
       </c>
       <c r="AM23">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AN23">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AO23">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AP23">
         <v>6.4</v>
@@ -6613,7 +6613,7 @@
         <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX23">
         <v>13</v>
@@ -6625,7 +6625,7 @@
         <v>11</v>
       </c>
       <c r="BA23">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BB23">
         <v>21</v>
@@ -6640,16 +6640,16 @@
         <v>6.6</v>
       </c>
       <c r="BF23">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG23">
         <v>14.5</v>
       </c>
       <c r="BH23">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BI23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BJ23">
         <v>8.6</v>
@@ -6658,7 +6658,7 @@
         <v>4.6</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM23">
         <v>8.4</v>
@@ -6667,7 +6667,7 @@
         <v>5.9</v>
       </c>
       <c r="BO23">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP23">
         <v>12.5</v>
@@ -6685,10 +6685,10 @@
         <v>8.4</v>
       </c>
       <c r="BU23">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW23">
         <v>7</v>
@@ -6735,43 +6735,43 @@
         <v>2.3</v>
       </c>
       <c r="I24">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P24">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="R24">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S24">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="T24">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U24">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
         <v>1.69</v>
@@ -6780,22 +6780,22 @@
         <v>1.47</v>
       </c>
       <c r="X24">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y24">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA24">
         <v>34</v>
       </c>
       <c r="AB24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24">
         <v>12.5</v>
@@ -6843,7 +6843,7 @@
         <v>14</v>
       </c>
       <c r="AS24">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT24">
         <v>13</v>
@@ -6867,19 +6867,19 @@
         <v>11.5</v>
       </c>
       <c r="BA24">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB24">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BC24">
         <v>21</v>
       </c>
       <c r="BD24">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF24">
         <v>14</v>
@@ -6888,13 +6888,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH24">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI24">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BJ24">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK24">
         <v>4.7</v>
@@ -6903,7 +6903,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24">
         <v>6.8</v>
@@ -6912,16 +6912,16 @@
         <v>5.1</v>
       </c>
       <c r="BP24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ24">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR24">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT24">
         <v>6</v>
@@ -6930,16 +6930,16 @@
         <v>4.5</v>
       </c>
       <c r="BV24">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BW24">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX24">
         <v>25</v>
       </c>
       <c r="BY24">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ24">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>990</v>
       </c>
       <c r="J25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K25">
         <v>950</v>
@@ -6995,19 +6995,19 @@
         <v>1.25</v>
       </c>
       <c r="O25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P25">
         <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R25">
         <v>1.12</v>
       </c>
       <c r="S25">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T25">
         <v>1.11</v>
@@ -7210,10 +7210,10 @@
         <v>226</v>
       </c>
       <c r="F26">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G26">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H26">
         <v>3.15</v>
@@ -7249,7 +7249,7 @@
         <v>1.49</v>
       </c>
       <c r="S26">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T26">
         <v>1.62</v>
@@ -7276,7 +7276,7 @@
         <v>55</v>
       </c>
       <c r="AB26">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC26">
         <v>10</v>
@@ -7285,7 +7285,7 @@
         <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF26">
         <v>18.5</v>
@@ -7297,7 +7297,7 @@
         <v>16</v>
       </c>
       <c r="AI26">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AJ26">
         <v>34</v>
@@ -7306,7 +7306,7 @@
         <v>26</v>
       </c>
       <c r="AL26">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM26">
         <v>75</v>
@@ -7315,7 +7315,7 @@
         <v>15.5</v>
       </c>
       <c r="AO26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP26">
         <v>15</v>
@@ -7327,7 +7327,7 @@
         <v>19</v>
       </c>
       <c r="AS26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT26">
         <v>11.5</v>
@@ -7339,7 +7339,7 @@
         <v>11</v>
       </c>
       <c r="AW26">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AX26">
         <v>12</v>
@@ -7351,7 +7351,7 @@
         <v>12</v>
       </c>
       <c r="BA26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB26">
         <v>21</v>
@@ -7360,10 +7360,10 @@
         <v>20</v>
       </c>
       <c r="BD26">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BE26">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF26">
         <v>11.5</v>
@@ -7452,16 +7452,16 @@
         <v>227</v>
       </c>
       <c r="F27">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G27">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H27">
         <v>2.1</v>
       </c>
       <c r="I27">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J27">
         <v>4.1</v>
@@ -7473,7 +7473,7 @@
         <v>1.17</v>
       </c>
       <c r="M27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N27">
         <v>6.2</v>
@@ -7500,19 +7500,19 @@
         <v>2.72</v>
       </c>
       <c r="V27">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W27">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X27">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y27">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z27">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA27">
         <v>38</v>
@@ -7542,7 +7542,7 @@
         <v>27</v>
       </c>
       <c r="AJ27">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="AK27">
         <v>44</v>
@@ -7551,16 +7551,16 @@
         <v>44</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AN27">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO27">
         <v>9.6</v>
       </c>
       <c r="AP27">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ27">
         <v>6</v>
@@ -7569,7 +7569,7 @@
         <v>13.5</v>
       </c>
       <c r="AS27">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT27">
         <v>18</v>
@@ -7578,40 +7578,40 @@
         <v>8</v>
       </c>
       <c r="AV27">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW27">
         <v>14</v>
       </c>
       <c r="AX27">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AY27">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AZ27">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA27">
         <v>18</v>
       </c>
       <c r="BB27">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC27">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BD27">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE27">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BF27">
         <v>12.5</v>
       </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7635,7 +7635,7 @@
         <v>10</v>
       </c>
       <c r="BO27">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP27">
         <v>30</v>
@@ -7706,7 +7706,7 @@
         <v>990</v>
       </c>
       <c r="J28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K28">
         <v>950</v>
@@ -7733,7 +7733,7 @@
         <v>1.08</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
         <v>1.11</v>
@@ -7990,10 +7990,10 @@
         <v>1.27</v>
       </c>
       <c r="X29">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="Y29">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z29">
         <v>16.5</v>
@@ -8002,10 +8002,10 @@
         <v>23</v>
       </c>
       <c r="AB29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD29">
         <v>11</v>
@@ -8014,28 +8014,28 @@
         <v>18.5</v>
       </c>
       <c r="AF29">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="AG29">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH29">
         <v>16.5</v>
       </c>
       <c r="AI29">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AJ29">
-        <v>90</v>
+        <v>470</v>
       </c>
       <c r="AK29">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AL29">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="AM29">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AN29">
         <v>34</v>
@@ -8065,7 +8065,7 @@
         <v>8</v>
       </c>
       <c r="AW29">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX29">
         <v>27</v>
@@ -8080,19 +8080,19 @@
         <v>18</v>
       </c>
       <c r="BB29">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC29">
         <v>30</v>
       </c>
       <c r="BD29">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE29">
         <v>40</v>
       </c>
       <c r="BF29">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG29">
         <v>6.8</v>
@@ -8232,7 +8232,7 @@
         <v>2.24</v>
       </c>
       <c r="X30">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y30">
         <v>18.5</v>
@@ -8247,7 +8247,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD30">
         <v>24</v>
@@ -8262,7 +8262,7 @@
         <v>10.5</v>
       </c>
       <c r="AH30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI30">
         <v>90</v>
@@ -8292,10 +8292,10 @@
         <v>15</v>
       </c>
       <c r="AR30">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS30">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT30">
         <v>6.6</v>
@@ -8307,7 +8307,7 @@
         <v>19</v>
       </c>
       <c r="AW30">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX30">
         <v>8.4</v>
@@ -8319,7 +8319,7 @@
         <v>18.5</v>
       </c>
       <c r="BA30">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB30">
         <v>15</v>
@@ -8328,16 +8328,16 @@
         <v>16.5</v>
       </c>
       <c r="BD30">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF30">
         <v>9.6</v>
       </c>
       <c r="BG30">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH30">
         <v>3.4</v>
@@ -8450,13 +8450,13 @@
         <v>1.19</v>
       </c>
       <c r="P31">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q31">
         <v>1.57</v>
       </c>
       <c r="R31">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S31">
         <v>2.42</v>
@@ -8465,7 +8465,7 @@
         <v>1.53</v>
       </c>
       <c r="U31">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -8474,16 +8474,16 @@
         <v>1.73</v>
       </c>
       <c r="X31">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="Y31">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z31">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA31">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB31">
         <v>15.5</v>
@@ -8492,7 +8492,7 @@
         <v>10.5</v>
       </c>
       <c r="AD31">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE31">
         <v>34</v>
@@ -8501,7 +8501,7 @@
         <v>18.5</v>
       </c>
       <c r="AG31">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH31">
         <v>16</v>
@@ -8513,19 +8513,19 @@
         <v>34</v>
       </c>
       <c r="AK31">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL31">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AM31">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AN31">
         <v>13</v>
       </c>
       <c r="AO31">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP31">
         <v>19</v>
@@ -8537,7 +8537,7 @@
         <v>19</v>
       </c>
       <c r="AS31">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT31">
         <v>11.5</v>
@@ -8549,7 +8549,7 @@
         <v>10.5</v>
       </c>
       <c r="AW31">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX31">
         <v>14</v>
@@ -8561,10 +8561,10 @@
         <v>11.5</v>
       </c>
       <c r="BA31">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="BB31">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC31">
         <v>16</v>
@@ -8573,7 +8573,7 @@
         <v>21</v>
       </c>
       <c r="BE31">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BF31">
         <v>9.199999999999999</v>
@@ -8689,19 +8689,19 @@
         <v>2.62</v>
       </c>
       <c r="O32">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P32">
         <v>1.54</v>
       </c>
       <c r="Q32">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T32">
         <v>2.08</v>
@@ -8722,10 +8722,10 @@
         <v>11</v>
       </c>
       <c r="Z32">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AA32">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AB32">
         <v>7.8</v>
@@ -8737,7 +8737,7 @@
         <v>17</v>
       </c>
       <c r="AE32">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AF32">
         <v>14</v>
@@ -8746,19 +8746,19 @@
         <v>13</v>
       </c>
       <c r="AH32">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI32">
-        <v>100</v>
+        <v>460</v>
       </c>
       <c r="AJ32">
         <v>40</v>
       </c>
       <c r="AK32">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AL32">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AM32">
         <v>220</v>
@@ -8767,7 +8767,7 @@
         <v>46</v>
       </c>
       <c r="AO32">
-        <v>110</v>
+        <v>360</v>
       </c>
       <c r="AP32">
         <v>7.8</v>
@@ -8776,10 +8776,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR32">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AS32">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="AT32">
         <v>6.4</v>
@@ -8791,7 +8791,7 @@
         <v>14</v>
       </c>
       <c r="AW32">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AX32">
         <v>11</v>
@@ -8806,16 +8806,16 @@
         <v>7.4</v>
       </c>
       <c r="BB32">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BC32">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BD32">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE32">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF32">
         <v>6.4</v>
@@ -8824,10 +8824,10 @@
         <v>7.4</v>
       </c>
       <c r="BH32">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI32">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ32">
         <v>12</v>
@@ -8848,7 +8848,7 @@
         <v>4.2</v>
       </c>
       <c r="BP32">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ32">
         <v>7</v>
@@ -8904,7 +8904,7 @@
         <v>233</v>
       </c>
       <c r="F33">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G33">
         <v>3.2</v>
@@ -8916,7 +8916,7 @@
         <v>2.76</v>
       </c>
       <c r="J33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K33">
         <v>3.55</v>
@@ -9155,7 +9155,7 @@
         <v>2.58</v>
       </c>
       <c r="I34">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J34">
         <v>3.6</v>
@@ -9194,19 +9194,19 @@
         <v>2.36</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W34">
         <v>1.53</v>
       </c>
       <c r="X34">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y34">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z34">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA34">
         <v>44</v>
@@ -9215,7 +9215,7 @@
         <v>16.5</v>
       </c>
       <c r="AC34">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD34">
         <v>15</v>
@@ -9245,13 +9245,13 @@
         <v>42</v>
       </c>
       <c r="AM34">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN34">
         <v>22</v>
       </c>
       <c r="AO34">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP34">
         <v>14</v>
@@ -9263,7 +9263,7 @@
         <v>14.5</v>
       </c>
       <c r="AS34">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AT34">
         <v>10</v>
@@ -9287,19 +9287,19 @@
         <v>11</v>
       </c>
       <c r="BA34">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="BB34">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BC34">
         <v>19.5</v>
       </c>
       <c r="BD34">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BE34">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF34">
         <v>13.5</v>
@@ -9388,13 +9388,13 @@
         <v>235</v>
       </c>
       <c r="F35">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G35">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H35">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I35">
         <v>2.36</v>
@@ -9415,22 +9415,22 @@
         <v>3.85</v>
       </c>
       <c r="O35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P35">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q35">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R35">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S35">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U35">
         <v>2.18</v>
@@ -9442,13 +9442,13 @@
         <v>1.36</v>
       </c>
       <c r="X35">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA35">
         <v>30</v>
@@ -9457,7 +9457,7 @@
         <v>15</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD35">
         <v>12</v>
@@ -9487,7 +9487,7 @@
         <v>50</v>
       </c>
       <c r="AM35">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN35">
         <v>38</v>
@@ -9529,22 +9529,22 @@
         <v>13</v>
       </c>
       <c r="BA35">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB35">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC35">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD35">
         <v>34</v>
       </c>
       <c r="BE35">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF35">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG35">
         <v>12</v>
@@ -9571,7 +9571,7 @@
         <v>7.2</v>
       </c>
       <c r="BO35">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BP35">
         <v>28</v>
@@ -9589,7 +9589,7 @@
         <v>5.4</v>
       </c>
       <c r="BU35">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV35">
         <v>16.5</v>
@@ -9639,7 +9639,7 @@
         <v>4.9</v>
       </c>
       <c r="I36">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J36">
         <v>3.85</v>
@@ -9648,7 +9648,7 @@
         <v>4.2</v>
       </c>
       <c r="L36">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M36">
         <v>1.06</v>
@@ -9660,13 +9660,13 @@
         <v>1.3</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q36">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S36">
         <v>3.35</v>
@@ -9678,7 +9678,7 @@
         <v>1.98</v>
       </c>
       <c r="V36">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W36">
         <v>2.2</v>
@@ -9872,22 +9872,22 @@
         <v>237</v>
       </c>
       <c r="F37">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G37">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H37">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I37">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K37">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L37">
         <v>1.41</v>
@@ -9896,13 +9896,13 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O37">
         <v>1.34</v>
       </c>
       <c r="P37">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="Q37">
         <v>2</v>
@@ -9917,13 +9917,13 @@
         <v>1.76</v>
       </c>
       <c r="U37">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V37">
         <v>1.54</v>
       </c>
       <c r="W37">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X37">
         <v>16</v>
@@ -9935,19 +9935,19 @@
         <v>22</v>
       </c>
       <c r="AA37">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB37">
         <v>13.5</v>
       </c>
       <c r="AC37">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD37">
         <v>15</v>
       </c>
       <c r="AE37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF37">
         <v>24</v>
@@ -9965,7 +9965,7 @@
         <v>60</v>
       </c>
       <c r="AK37">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL37">
         <v>55</v>
@@ -9974,7 +9974,7 @@
         <v>110</v>
       </c>
       <c r="AN37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO37">
         <v>30</v>
@@ -9989,7 +9989,7 @@
         <v>13</v>
       </c>
       <c r="AS37">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT37">
         <v>8.4</v>
@@ -9998,10 +9998,10 @@
         <v>5.9</v>
       </c>
       <c r="AV37">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW37">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AX37">
         <v>14</v>
@@ -10013,22 +10013,22 @@
         <v>12.5</v>
       </c>
       <c r="BA37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB37">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC37">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BD37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF37">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG37">
         <v>19.5</v>
@@ -10037,7 +10037,7 @@
         <v>3.45</v>
       </c>
       <c r="BI37">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ37">
         <v>10</v>
@@ -10114,25 +10114,25 @@
         <v>238</v>
       </c>
       <c r="F38">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G38">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H38">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I38">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J38">
         <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M38">
         <v>1.05</v>
@@ -10144,10 +10144,10 @@
         <v>1.25</v>
       </c>
       <c r="P38">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q38">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R38">
         <v>1.5</v>
@@ -10159,7 +10159,7 @@
         <v>1.8</v>
       </c>
       <c r="U38">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
         <v>1.19</v>
@@ -10171,25 +10171,25 @@
         <v>21</v>
       </c>
       <c r="Y38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z38">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AA38">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB38">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC38">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE38">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AF38">
         <v>11</v>
@@ -10198,13 +10198,13 @@
         <v>10.5</v>
       </c>
       <c r="AH38">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI38">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ38">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK38">
         <v>17</v>
@@ -10216,10 +10216,10 @@
         <v>110</v>
       </c>
       <c r="AN38">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO38">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="AP38">
         <v>15</v>
@@ -10237,25 +10237,25 @@
         <v>7.8</v>
       </c>
       <c r="AU38">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW38">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="AX38">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY38">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA38">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BB38">
         <v>13.5</v>
@@ -10267,13 +10267,13 @@
         <v>26</v>
       </c>
       <c r="BE38">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF38">
         <v>7.2</v>
       </c>
       <c r="BG38">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10356,19 +10356,19 @@
         <v>239</v>
       </c>
       <c r="F39">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="G39">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="H39">
         <v>1.92</v>
       </c>
       <c r="I39">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="J39">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K39">
         <v>3.7</v>
@@ -10383,19 +10383,19 @@
         <v>1.19</v>
       </c>
       <c r="O39">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P39">
         <v>1.19</v>
       </c>
       <c r="Q39">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="R39">
         <v>1.07</v>
       </c>
       <c r="S39">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="T39">
         <v>1.97</v>
@@ -10404,55 +10404,55 @@
         <v>1.8</v>
       </c>
       <c r="V39">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="W39">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ39">
         <v>1000</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM39">
         <v>1000</v>
@@ -10461,16 +10461,16 @@
         <v>1000</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP39">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ39">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR39">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AS39">
         <v>1.03</v>
@@ -10479,7 +10479,7 @@
         <v>1.03</v>
       </c>
       <c r="AU39">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV39">
         <v>1.03</v>
@@ -10512,10 +10512,10 @@
         <v>1.03</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH39">
         <v>3.05</v>
@@ -10598,22 +10598,22 @@
         <v>240</v>
       </c>
       <c r="F40">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G40">
         <v>2.76</v>
       </c>
       <c r="H40">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I40">
         <v>3.95</v>
       </c>
       <c r="J40">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K40">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>1.54</v>
@@ -10646,7 +10646,7 @@
         <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
         <v>1.57</v>
@@ -10655,46 +10655,46 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z40">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA40">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB40">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AC40">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD40">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE40">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF40">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG40">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AH40">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ40">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM40">
         <v>1000</v>
@@ -10706,58 +10706,58 @@
         <v>1000</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ40">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AR40">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AS40">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AT40">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AU40">
-        <v>1.11</v>
+        <v>4.2</v>
       </c>
       <c r="AV40">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AW40">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="AX40">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AY40">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AZ40">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="BA40">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="BB40">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="BC40">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="BD40">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="BE40">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="BF40">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BG40">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BH40">
         <v>1000</v>
@@ -10846,16 +10846,16 @@
         <v>3.6</v>
       </c>
       <c r="H41">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I41">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J41">
         <v>3.2</v>
       </c>
       <c r="K41">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L41">
         <v>1.4</v>
@@ -10870,7 +10870,7 @@
         <v>1.32</v>
       </c>
       <c r="P41">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q41">
         <v>1.95</v>
@@ -10882,13 +10882,13 @@
         <v>3.35</v>
       </c>
       <c r="T41">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U41">
         <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
         <v>1.38</v>
@@ -10903,7 +10903,7 @@
         <v>16.5</v>
       </c>
       <c r="AA41">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB41">
         <v>14.5</v>
@@ -10918,7 +10918,7 @@
         <v>27</v>
       </c>
       <c r="AF41">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG41">
         <v>15</v>
@@ -10981,22 +10981,22 @@
         <v>11</v>
       </c>
       <c r="BA41">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="BB41">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC41">
         <v>7.4</v>
       </c>
       <c r="BD41">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE41">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF41">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG41">
         <v>13.5</v>
@@ -11005,7 +11005,7 @@
         <v>3.6</v>
       </c>
       <c r="BI41">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ41">
         <v>9.800000000000001</v>
@@ -11082,16 +11082,16 @@
         <v>242</v>
       </c>
       <c r="F42">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G42">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H42">
         <v>3</v>
       </c>
       <c r="I42">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J42">
         <v>4</v>
@@ -11112,13 +11112,13 @@
         <v>1.15</v>
       </c>
       <c r="P42">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q42">
         <v>1.45</v>
       </c>
       <c r="R42">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="S42">
         <v>2.1</v>
@@ -11133,7 +11133,7 @@
         <v>1.41</v>
       </c>
       <c r="W42">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X42">
         <v>38</v>
@@ -11205,7 +11205,7 @@
         <v>6</v>
       </c>
       <c r="AU42">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AV42">
         <v>12.5</v>
@@ -11220,7 +11220,7 @@
         <v>10</v>
       </c>
       <c r="AZ42">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BA42">
         <v>19</v>
@@ -11232,7 +11232,7 @@
         <v>14</v>
       </c>
       <c r="BD42">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BE42">
         <v>28</v>
@@ -11324,22 +11324,22 @@
         <v>243</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G43">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H43">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="I43">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="J43">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="K43">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11357,13 +11357,13 @@
         <v>2.54</v>
       </c>
       <c r="Q43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="S43">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="T43">
         <v>1.11</v>
@@ -11372,10 +11372,10 @@
         <v>1.11</v>
       </c>
       <c r="V43">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="W43">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11393,7 +11393,7 @@
         <v>1000</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD43">
         <v>1000</v>
@@ -11408,7 +11408,7 @@
         <v>1000</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI43">
         <v>1000</v>
@@ -11423,67 +11423,67 @@
         <v>1000</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN43">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO43">
         <v>1000</v>
       </c>
       <c r="AP43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AQ43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AR43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AS43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AT43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AW43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AZ43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BA43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BD43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BE43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG43">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11602,7 +11602,7 @@
         <v>1.04</v>
       </c>
       <c r="R44">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="S44">
         <v>1.5</v>
@@ -11823,7 +11823,7 @@
         <v>3.2</v>
       </c>
       <c r="K45">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L45">
         <v>1.53</v>
@@ -11832,10 +11832,10 @@
         <v>1.15</v>
       </c>
       <c r="N45">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O45">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P45">
         <v>1.46</v>
@@ -11850,13 +11850,13 @@
         <v>6.4</v>
       </c>
       <c r="T45">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U45">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V45">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W45">
         <v>2.02</v>
@@ -11877,10 +11877,10 @@
         <v>5.8</v>
       </c>
       <c r="AC45">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD45">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE45">
         <v>1000</v>
@@ -11904,10 +11904,10 @@
         <v>32</v>
       </c>
       <c r="AL45">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM45">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AN45">
         <v>28</v>
@@ -11922,7 +11922,7 @@
         <v>10.5</v>
       </c>
       <c r="AR45">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AS45">
         <v>44</v>
@@ -11940,22 +11940,22 @@
         <v>40</v>
       </c>
       <c r="AX45">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY45">
         <v>10.5</v>
       </c>
       <c r="AZ45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA45">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB45">
         <v>19.5</v>
       </c>
       <c r="BC45">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD45">
         <v>36</v>
@@ -11964,7 +11964,7 @@
         <v>95</v>
       </c>
       <c r="BF45">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BG45">
         <v>48</v>
@@ -11973,61 +11973,61 @@
         <v>2.6</v>
       </c>
       <c r="BI45">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ45">
         <v>14</v>
       </c>
       <c r="BK45">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL45">
         <v>1000</v>
       </c>
       <c r="BM45">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="BN45">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO45">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="BP45">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ45">
-        <v>7.2</v>
+        <v>1.89</v>
       </c>
       <c r="BR45">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS45">
-        <v>10</v>
+        <v>2.04</v>
       </c>
       <c r="BT45">
         <v>9.199999999999999</v>
       </c>
       <c r="BU45">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BV45">
         <v>75</v>
       </c>
       <c r="BW45">
-        <v>11</v>
+        <v>2.06</v>
       </c>
       <c r="BX45">
         <v>1000</v>
       </c>
       <c r="BY45">
-        <v>11.5</v>
+        <v>2.08</v>
       </c>
       <c r="BZ45">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA45">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="CB45" t="s">
         <v>264</v>
@@ -12050,22 +12050,22 @@
         <v>246</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12074,142 +12074,142 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O46">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="P46">
         <v>4.1</v>
       </c>
       <c r="Q46">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="R46">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.06</v>
+        <v>1.71</v>
       </c>
       <c r="T46">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U46">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="X46">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y46">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z46">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA46">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AB46">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC46">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD46">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE46">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF46">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG46">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH46">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI46">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ46">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AK46">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL46">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM46">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN46">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="AO46">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF46">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG46">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12292,10 +12292,10 @@
         <v>247</v>
       </c>
       <c r="F47">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G47">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H47">
         <v>5.1</v>
@@ -12322,7 +12322,7 @@
         <v>1.33</v>
       </c>
       <c r="P47">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q47">
         <v>1.96</v>
@@ -12334,31 +12334,31 @@
         <v>3.5</v>
       </c>
       <c r="T47">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U47">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V47">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W47">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X47">
         <v>17</v>
       </c>
       <c r="Y47">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z47">
         <v>48</v>
       </c>
       <c r="AA47">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB47">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC47">
         <v>9</v>
@@ -12367,19 +12367,19 @@
         <v>25</v>
       </c>
       <c r="AE47">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AF47">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG47">
         <v>12</v>
       </c>
       <c r="AH47">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI47">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AJ47">
         <v>23</v>
@@ -12391,7 +12391,7 @@
         <v>40</v>
       </c>
       <c r="AM47">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN47">
         <v>14</v>
@@ -12403,16 +12403,16 @@
         <v>12</v>
       </c>
       <c r="AQ47">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AR47">
         <v>32</v>
       </c>
       <c r="AS47">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT47">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU47">
         <v>7.4</v>
@@ -12421,7 +12421,7 @@
         <v>17</v>
       </c>
       <c r="AW47">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX47">
         <v>9.199999999999999</v>
@@ -12433,10 +12433,10 @@
         <v>17.5</v>
       </c>
       <c r="BA47">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB47">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC47">
         <v>16.5</v>
@@ -12445,13 +12445,13 @@
         <v>30</v>
       </c>
       <c r="BE47">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF47">
         <v>9.4</v>
       </c>
       <c r="BG47">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12534,22 +12534,22 @@
         <v>248</v>
       </c>
       <c r="F48">
-        <v>1.08</v>
+        <v>2.28</v>
       </c>
       <c r="G48">
-        <v>990</v>
+        <v>3.45</v>
       </c>
       <c r="H48">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>990</v>
+        <v>2.78</v>
       </c>
       <c r="J48">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="K48">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12558,22 +12558,22 @@
         <v>1.01</v>
       </c>
       <c r="N48">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="O48">
         <v>1.05</v>
       </c>
       <c r="P48">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
         <v>1.05</v>
       </c>
       <c r="R48">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="S48">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
       <c r="T48">
         <v>1.11</v>
@@ -12582,118 +12582,118 @@
         <v>1.11</v>
       </c>
       <c r="V48">
+        <v>1.56</v>
+      </c>
+      <c r="W48">
+        <v>1.41</v>
+      </c>
+      <c r="X48">
+        <v>1000</v>
+      </c>
+      <c r="Y48">
+        <v>1000</v>
+      </c>
+      <c r="Z48">
+        <v>1000</v>
+      </c>
+      <c r="AA48">
+        <v>1000</v>
+      </c>
+      <c r="AB48">
+        <v>1000</v>
+      </c>
+      <c r="AC48">
+        <v>950</v>
+      </c>
+      <c r="AD48">
+        <v>1000</v>
+      </c>
+      <c r="AE48">
+        <v>1000</v>
+      </c>
+      <c r="AF48">
+        <v>1000</v>
+      </c>
+      <c r="AG48">
+        <v>1000</v>
+      </c>
+      <c r="AH48">
+        <v>1000</v>
+      </c>
+      <c r="AI48">
+        <v>1000</v>
+      </c>
+      <c r="AJ48">
+        <v>1000</v>
+      </c>
+      <c r="AK48">
+        <v>1000</v>
+      </c>
+      <c r="AL48">
+        <v>1000</v>
+      </c>
+      <c r="AM48">
+        <v>1000</v>
+      </c>
+      <c r="AN48">
+        <v>1000</v>
+      </c>
+      <c r="AO48">
+        <v>1000</v>
+      </c>
+      <c r="AP48">
         <v>1.02</v>
       </c>
-      <c r="W48">
+      <c r="AQ48">
         <v>1.02</v>
       </c>
-      <c r="X48">
-        <v>1000</v>
-      </c>
-      <c r="Y48">
-        <v>1000</v>
-      </c>
-      <c r="Z48">
-        <v>1000</v>
-      </c>
-      <c r="AA48">
-        <v>1000</v>
-      </c>
-      <c r="AB48">
-        <v>1000</v>
-      </c>
-      <c r="AC48">
-        <v>1000</v>
-      </c>
-      <c r="AD48">
-        <v>1000</v>
-      </c>
-      <c r="AE48">
-        <v>1000</v>
-      </c>
-      <c r="AF48">
-        <v>1000</v>
-      </c>
-      <c r="AG48">
-        <v>1000</v>
-      </c>
-      <c r="AH48">
-        <v>1000</v>
-      </c>
-      <c r="AI48">
-        <v>1000</v>
-      </c>
-      <c r="AJ48">
-        <v>1000</v>
-      </c>
-      <c r="AK48">
-        <v>1000</v>
-      </c>
-      <c r="AL48">
-        <v>1000</v>
-      </c>
-      <c r="AM48">
-        <v>1000</v>
-      </c>
-      <c r="AN48">
-        <v>1000</v>
-      </c>
-      <c r="AO48">
-        <v>1000</v>
-      </c>
-      <c r="AP48">
-        <v>1.01</v>
-      </c>
-      <c r="AQ48">
-        <v>1.01</v>
-      </c>
       <c r="AR48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU48">
         <v>1.01</v>
       </c>
       <c r="AV48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12776,19 +12776,19 @@
         <v>249</v>
       </c>
       <c r="F49">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G49">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H49">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I49">
         <v>990</v>
       </c>
       <c r="J49">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="K49">
         <v>950</v>
@@ -12803,10 +12803,10 @@
         <v>1.24</v>
       </c>
       <c r="O49">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P49">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q49">
         <v>1.41</v>
@@ -12824,67 +12824,67 @@
         <v>1.11</v>
       </c>
       <c r="V49">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W49">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X49">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y49">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z49">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA49">
         <v>1000</v>
       </c>
       <c r="AB49">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC49">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD49">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE49">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AF49">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG49">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH49">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI49">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ49">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK49">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL49">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AM49">
         <v>1000</v>
       </c>
       <c r="AN49">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO49">
         <v>1000</v>
       </c>
       <c r="AP49">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ49">
         <v>1.03</v>
@@ -12896,10 +12896,10 @@
         <v>1.03</v>
       </c>
       <c r="AT49">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU49">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AV49">
         <v>1.03</v>
@@ -12908,7 +12908,7 @@
         <v>1.03</v>
       </c>
       <c r="AX49">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AY49">
         <v>1.03</v>
@@ -12932,10 +12932,10 @@
         <v>1.03</v>
       </c>
       <c r="BF49">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG49">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13018,58 +13018,58 @@
         <v>250</v>
       </c>
       <c r="F50">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="G50">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H50">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I50">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J50">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K50">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L50">
         <v>1.01</v>
       </c>
       <c r="M50">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N50">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O50">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P50">
         <v>1.57</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S50">
         <v>2.84</v>
       </c>
       <c r="T50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W50">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -13174,10 +13174,10 @@
         <v>1.03</v>
       </c>
       <c r="BF50">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BG50">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BH50">
         <v>1000</v>
@@ -13260,22 +13260,22 @@
         <v>251</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13284,7 +13284,7 @@
         <v>1.01</v>
       </c>
       <c r="N51">
-        <v>1.96</v>
+        <v>3.35</v>
       </c>
       <c r="O51">
         <v>1.4</v>
@@ -13293,25 +13293,25 @@
         <v>1.71</v>
       </c>
       <c r="Q51">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S51">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="T51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="V51">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13502,7 +13502,7 @@
         <v>252</v>
       </c>
       <c r="F52">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G52">
         <v>2.24</v>
@@ -13511,13 +13511,13 @@
         <v>4.2</v>
       </c>
       <c r="I52">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J52">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K52">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L52">
         <v>1.54</v>
@@ -13526,28 +13526,28 @@
         <v>1.14</v>
       </c>
       <c r="N52">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
         <v>1.61</v>
       </c>
       <c r="P52">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q52">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R52">
         <v>1.17</v>
       </c>
       <c r="S52">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T52">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U52">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V52">
         <v>1.29</v>
@@ -13559,109 +13559,109 @@
         <v>8</v>
       </c>
       <c r="Y52">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z52">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA52">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB52">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC52">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD52">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE52">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF52">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG52">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH52">
         <v>30</v>
       </c>
       <c r="AI52">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ52">
+        <v>48</v>
+      </c>
+      <c r="AK52">
         <v>38</v>
       </c>
-      <c r="AK52">
-        <v>40</v>
-      </c>
       <c r="AL52">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM52">
         <v>260</v>
       </c>
       <c r="AN52">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO52">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP52">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ52">
         <v>9.4</v>
       </c>
       <c r="AR52">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AS52">
-        <v>7.4</v>
+        <v>36</v>
       </c>
       <c r="AT52">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU52">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV52">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AW52">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AX52">
         <v>10.5</v>
       </c>
       <c r="AY52">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ52">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BA52">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BB52">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="BC52">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD52">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="BE52">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="BF52">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BG52">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="BH52">
         <v>2.6</v>
@@ -13744,10 +13744,10 @@
         <v>253</v>
       </c>
       <c r="F53">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G53">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="H53">
         <v>5.5</v>
@@ -13756,31 +13756,31 @@
         <v>6.2</v>
       </c>
       <c r="J53">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K53">
         <v>3.45</v>
       </c>
       <c r="L53">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M53">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N53">
         <v>2.68</v>
       </c>
       <c r="O53">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P53">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q53">
         <v>2.62</v>
       </c>
       <c r="R53">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S53">
         <v>5.4</v>
@@ -13789,13 +13789,13 @@
         <v>2.28</v>
       </c>
       <c r="U53">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V53">
         <v>1.2</v>
       </c>
       <c r="W53">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X53">
         <v>9.4</v>
@@ -13807,10 +13807,10 @@
         <v>50</v>
       </c>
       <c r="AA53">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AB53">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC53">
         <v>9.4</v>
@@ -13819,7 +13819,7 @@
         <v>28</v>
       </c>
       <c r="AE53">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF53">
         <v>11.5</v>
@@ -13831,7 +13831,7 @@
         <v>32</v>
       </c>
       <c r="AI53">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ53">
         <v>25</v>
@@ -13843,13 +13843,13 @@
         <v>70</v>
       </c>
       <c r="AM53">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN53">
         <v>24</v>
       </c>
       <c r="AO53">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AP53">
         <v>7.6</v>
@@ -13858,10 +13858,10 @@
         <v>12</v>
       </c>
       <c r="AR53">
+        <v>4.9</v>
+      </c>
+      <c r="AS53">
         <v>5.3</v>
-      </c>
-      <c r="AS53">
-        <v>5.8</v>
       </c>
       <c r="AT53">
         <v>5.5</v>
@@ -13870,10 +13870,10 @@
         <v>7</v>
       </c>
       <c r="AV53">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW53">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX53">
         <v>8.4</v>
@@ -13882,13 +13882,13 @@
         <v>9.6</v>
       </c>
       <c r="AZ53">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BA53">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB53">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC53">
         <v>18</v>
@@ -13897,13 +13897,13 @@
         <v>38</v>
       </c>
       <c r="BE53">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF53">
         <v>16</v>
       </c>
       <c r="BG53">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13986,16 +13986,16 @@
         <v>254</v>
       </c>
       <c r="F54">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="G54">
         <v>990</v>
       </c>
       <c r="H54">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="I54">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J54">
         <v>3.05</v>
@@ -14010,7 +14010,7 @@
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="O54">
         <v>1.33</v>
@@ -14034,10 +14034,10 @@
         <v>1.11</v>
       </c>
       <c r="V54">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W54">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -14237,10 +14237,10 @@
         <v>4</v>
       </c>
       <c r="I55">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J55">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K55">
         <v>4.2</v>
@@ -14276,118 +14276,118 @@
         <v>2.04</v>
       </c>
       <c r="V55">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W55">
         <v>2.04</v>
       </c>
       <c r="X55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y55">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Z55">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA55">
         <v>130</v>
       </c>
       <c r="AB55">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD55">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE55">
         <v>75</v>
       </c>
       <c r="AF55">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG55">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH55">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI55">
         <v>80</v>
       </c>
       <c r="AJ55">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK55">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL55">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM55">
         <v>120</v>
       </c>
       <c r="AN55">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO55">
         <v>80</v>
       </c>
       <c r="AP55">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="AQ55">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AR55">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS55">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AT55">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AU55">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV55">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AW55">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX55">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="AY55">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ55">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA55">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BB55">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BC55">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BD55">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE55">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF55">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG55">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH55">
         <v>3.6</v>
@@ -14470,7 +14470,7 @@
         <v>256</v>
       </c>
       <c r="F56">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G56">
         <v>2.36</v>
@@ -14479,64 +14479,64 @@
         <v>3.1</v>
       </c>
       <c r="I56">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J56">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K56">
         <v>4.1</v>
       </c>
       <c r="L56">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M56">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N56">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O56">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="Q56">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="R56">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="S56">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="T56">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W56">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X56">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Y56">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z56">
         <v>29</v>
       </c>
       <c r="AA56">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB56">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC56">
         <v>10.5</v>
@@ -14545,151 +14545,151 @@
         <v>16.5</v>
       </c>
       <c r="AE56">
+        <v>36</v>
+      </c>
+      <c r="AF56">
+        <v>20</v>
+      </c>
+      <c r="AG56">
+        <v>12</v>
+      </c>
+      <c r="AH56">
+        <v>16.5</v>
+      </c>
+      <c r="AI56">
         <v>40</v>
-      </c>
-      <c r="AF56">
-        <v>17</v>
-      </c>
-      <c r="AG56">
-        <v>12.5</v>
-      </c>
-      <c r="AH56">
-        <v>19</v>
-      </c>
-      <c r="AI56">
-        <v>46</v>
       </c>
       <c r="AJ56">
         <v>34</v>
       </c>
       <c r="AK56">
+        <v>22</v>
+      </c>
+      <c r="AL56">
+        <v>30</v>
+      </c>
+      <c r="AM56">
+        <v>320</v>
+      </c>
+      <c r="AN56">
+        <v>13</v>
+      </c>
+      <c r="AO56">
+        <v>25</v>
+      </c>
+      <c r="AP56">
+        <v>5.3</v>
+      </c>
+      <c r="AQ56">
+        <v>5</v>
+      </c>
+      <c r="AR56">
+        <v>19</v>
+      </c>
+      <c r="AS56">
+        <v>6</v>
+      </c>
+      <c r="AT56">
+        <v>10</v>
+      </c>
+      <c r="AU56">
+        <v>7.8</v>
+      </c>
+      <c r="AV56">
+        <v>4.7</v>
+      </c>
+      <c r="AW56">
+        <v>18</v>
+      </c>
+      <c r="AX56">
+        <v>5</v>
+      </c>
+      <c r="AY56">
+        <v>6.2</v>
+      </c>
+      <c r="AZ56">
+        <v>4.7</v>
+      </c>
+      <c r="BA56">
+        <v>20</v>
+      </c>
+      <c r="BB56">
+        <v>5.6</v>
+      </c>
+      <c r="BC56">
+        <v>5.1</v>
+      </c>
+      <c r="BD56">
+        <v>5.5</v>
+      </c>
+      <c r="BE56">
+        <v>6</v>
+      </c>
+      <c r="BF56">
+        <v>4.4</v>
+      </c>
+      <c r="BG56">
+        <v>18.5</v>
+      </c>
+      <c r="BH56">
+        <v>4.5</v>
+      </c>
+      <c r="BI56">
+        <v>3.5</v>
+      </c>
+      <c r="BJ56">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK56">
+        <v>4.9</v>
+      </c>
+      <c r="BL56">
+        <v>1000</v>
+      </c>
+      <c r="BM56">
+        <v>9.6</v>
+      </c>
+      <c r="BN56">
+        <v>5.6</v>
+      </c>
+      <c r="BO56">
+        <v>4.3</v>
+      </c>
+      <c r="BP56">
+        <v>15</v>
+      </c>
+      <c r="BQ56">
+        <v>6.2</v>
+      </c>
+      <c r="BR56">
         <v>24</v>
       </c>
-      <c r="AL56">
-        <v>36</v>
-      </c>
-      <c r="AM56">
-        <v>85</v>
-      </c>
-      <c r="AN56">
-        <v>16</v>
-      </c>
-      <c r="AO56">
-        <v>34</v>
-      </c>
-      <c r="AP56">
-        <v>4.4</v>
-      </c>
-      <c r="AQ56">
-        <v>4.2</v>
-      </c>
-      <c r="AR56">
-        <v>21</v>
-      </c>
-      <c r="AS56">
-        <v>5.2</v>
-      </c>
-      <c r="AT56">
-        <v>9.4</v>
-      </c>
-      <c r="AU56">
-        <v>3.65</v>
-      </c>
-      <c r="AV56">
-        <v>4.2</v>
-      </c>
-      <c r="AW56">
-        <v>4.9</v>
-      </c>
-      <c r="AX56">
-        <v>4.2</v>
-      </c>
-      <c r="AY56">
-        <v>3.85</v>
-      </c>
-      <c r="AZ56">
-        <v>4.3</v>
-      </c>
-      <c r="BA56">
-        <v>5</v>
-      </c>
-      <c r="BB56">
-        <v>4.8</v>
-      </c>
-      <c r="BC56">
-        <v>4.5</v>
-      </c>
-      <c r="BD56">
-        <v>4.8</v>
-      </c>
-      <c r="BE56">
-        <v>5.3</v>
-      </c>
-      <c r="BF56">
-        <v>4.1</v>
-      </c>
-      <c r="BG56">
-        <v>4.8</v>
-      </c>
-      <c r="BH56">
-        <v>3.95</v>
-      </c>
-      <c r="BI56">
-        <v>3.15</v>
-      </c>
-      <c r="BJ56">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK56">
-        <v>5.2</v>
-      </c>
-      <c r="BL56">
-        <v>1000</v>
-      </c>
-      <c r="BM56">
-        <v>10.5</v>
-      </c>
-      <c r="BN56">
-        <v>5.4</v>
-      </c>
-      <c r="BO56">
-        <v>4.2</v>
-      </c>
-      <c r="BP56">
-        <v>15.5</v>
-      </c>
-      <c r="BQ56">
-        <v>6.8</v>
-      </c>
-      <c r="BR56">
-        <v>26</v>
-      </c>
       <c r="BS56">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BT56">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU56">
         <v>5.4</v>
       </c>
       <c r="BV56">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BW56">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BX56">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BY56">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ56">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="CA56">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="CB56" t="s">
         <v>264</v>
@@ -14712,22 +14712,22 @@
         <v>257</v>
       </c>
       <c r="F57">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G57">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H57">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J57">
         <v>3.4</v>
       </c>
       <c r="K57">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14739,7 +14739,7 @@
         <v>2.92</v>
       </c>
       <c r="O57">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P57">
         <v>1.68</v>
@@ -14760,10 +14760,10 @@
         <v>1.11</v>
       </c>
       <c r="V57">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W57">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -14781,7 +14781,7 @@
         <v>1000</v>
       </c>
       <c r="AC57">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD57">
         <v>1000</v>
@@ -14802,7 +14802,7 @@
         <v>1000</v>
       </c>
       <c r="AJ57">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK57">
         <v>1000</v>
@@ -14814,10 +14814,10 @@
         <v>1000</v>
       </c>
       <c r="AN57">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO57">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AP57">
         <v>1.03</v>
@@ -14868,10 +14868,10 @@
         <v>1.03</v>
       </c>
       <c r="BF57">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BG57">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH57">
         <v>3.75</v>
@@ -14960,139 +14960,139 @@
         <v>1.55</v>
       </c>
       <c r="H58">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I58">
         <v>9</v>
       </c>
       <c r="J58">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K58">
         <v>4.9</v>
       </c>
       <c r="L58">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M58">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N58">
         <v>4.1</v>
       </c>
       <c r="O58">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P58">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q58">
         <v>1.83</v>
       </c>
       <c r="R58">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S58">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T58">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U58">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="V58">
         <v>1.13</v>
       </c>
       <c r="W58">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X58">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y58">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z58">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AA58">
         <v>1000</v>
       </c>
       <c r="AB58">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC58">
+        <v>10.5</v>
+      </c>
+      <c r="AD58">
+        <v>32</v>
+      </c>
+      <c r="AE58">
+        <v>1000</v>
+      </c>
+      <c r="AF58">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC58">
-        <v>11</v>
-      </c>
-      <c r="AD58">
-        <v>34</v>
-      </c>
-      <c r="AE58">
-        <v>1000</v>
-      </c>
-      <c r="AF58">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AG58">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH58">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI58">
         <v>1000</v>
       </c>
       <c r="AJ58">
+        <v>13.5</v>
+      </c>
+      <c r="AK58">
+        <v>16.5</v>
+      </c>
+      <c r="AL58">
+        <v>40</v>
+      </c>
+      <c r="AM58">
+        <v>1000</v>
+      </c>
+      <c r="AN58">
+        <v>8</v>
+      </c>
+      <c r="AO58">
+        <v>1000</v>
+      </c>
+      <c r="AP58">
         <v>14.5</v>
       </c>
-      <c r="AK58">
-        <v>18</v>
-      </c>
-      <c r="AL58">
-        <v>42</v>
-      </c>
-      <c r="AM58">
-        <v>1000</v>
-      </c>
-      <c r="AN58">
-        <v>8.4</v>
-      </c>
-      <c r="AO58">
-        <v>1000</v>
-      </c>
-      <c r="AP58">
-        <v>13.5</v>
-      </c>
       <c r="AQ58">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AR58">
         <v>29</v>
       </c>
       <c r="AS58">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AT58">
         <v>7.2</v>
       </c>
       <c r="AU58">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV58">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AW58">
         <v>40</v>
       </c>
       <c r="AX58">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY58">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA58">
         <v>40</v>
@@ -15104,7 +15104,7 @@
         <v>12.5</v>
       </c>
       <c r="BD58">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE58">
         <v>44</v>
@@ -15116,64 +15116,64 @@
         <v>44</v>
       </c>
       <c r="BH58">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BI58">
         <v>3</v>
       </c>
       <c r="BJ58">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK58">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="BN58">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO58">
         <v>3.2</v>
       </c>
       <c r="BP58">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ58">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BR58">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BS58">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT58">
+        <v>11.5</v>
+      </c>
+      <c r="BU58">
         <v>6.2</v>
       </c>
-      <c r="BT58">
-        <v>12</v>
-      </c>
-      <c r="BU58">
-        <v>4.8</v>
-      </c>
       <c r="BV58">
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX58">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY58">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ58">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="CA58">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="CB58" t="s">
         <v>264</v>
@@ -15196,7 +15196,7 @@
         <v>259</v>
       </c>
       <c r="F59">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G59">
         <v>600</v>
@@ -15220,19 +15220,19 @@
         <v>1.01</v>
       </c>
       <c r="N59">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="O59">
         <v>1.09</v>
       </c>
       <c r="P59">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="Q59">
         <v>1.09</v>
       </c>
       <c r="R59">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S59">
         <v>1.15</v>
@@ -15462,13 +15462,13 @@
         <v>1.01</v>
       </c>
       <c r="N60">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O60">
         <v>1.02</v>
       </c>
       <c r="P60">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q60">
         <v>1.01</v>
@@ -15922,43 +15922,43 @@
         <v>262</v>
       </c>
       <c r="F62">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G62">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="H62">
         <v>6.4</v>
       </c>
       <c r="I62">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J62">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K62">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L62">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="M62">
         <v>1.1</v>
       </c>
       <c r="N62">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O62">
         <v>1.44</v>
       </c>
       <c r="P62">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q62">
         <v>2.28</v>
       </c>
       <c r="R62">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S62">
         <v>4.4</v>
@@ -15973,7 +15973,7 @@
         <v>1.15</v>
       </c>
       <c r="W62">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="X62">
         <v>12.5</v>
@@ -16000,7 +16000,7 @@
         <v>150</v>
       </c>
       <c r="AF62">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG62">
         <v>10.5</v>
@@ -16012,10 +16012,10 @@
         <v>150</v>
       </c>
       <c r="AJ62">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AK62">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL62">
         <v>60</v>
@@ -16030,19 +16030,19 @@
         <v>250</v>
       </c>
       <c r="AP62">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ62">
         <v>15</v>
       </c>
       <c r="AR62">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS62">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT62">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU62">
         <v>7.6</v>
@@ -16051,7 +16051,7 @@
         <v>19</v>
       </c>
       <c r="AW62">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX62">
         <v>7.8</v>
@@ -16063,31 +16063,31 @@
         <v>20</v>
       </c>
       <c r="BA62">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB62">
         <v>14.5</v>
       </c>
       <c r="BC62">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BD62">
         <v>38</v>
       </c>
       <c r="BE62">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF62">
         <v>12.5</v>
       </c>
       <c r="BG62">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH62">
         <v>3.05</v>
       </c>
       <c r="BI62">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ62">
         <v>12</v>
@@ -16099,10 +16099,10 @@
         <v>1000</v>
       </c>
       <c r="BM62">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BO62">
         <v>3.55</v>
@@ -16117,31 +16117,31 @@
         <v>1000</v>
       </c>
       <c r="BS62">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT62">
         <v>10</v>
       </c>
       <c r="BU62">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BV62">
         <v>1000</v>
       </c>
       <c r="BW62">
+        <v>13</v>
+      </c>
+      <c r="BX62">
+        <v>1000</v>
+      </c>
+      <c r="BY62">
         <v>13.5</v>
       </c>
-      <c r="BX62">
-        <v>1000</v>
-      </c>
-      <c r="BY62">
-        <v>14</v>
-      </c>
       <c r="BZ62">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA62">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB62" t="s">
         <v>264</v>
@@ -16194,7 +16194,7 @@
         <v>1.01</v>
       </c>
       <c r="P63">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q63">
         <v>1.01</v>
